--- a/Översikt EDA.xlsx
+++ b/Översikt EDA.xlsx
@@ -601,7 +601,7 @@
         <v>45178</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -725,7 +725,7 @@
         <v>45726</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -843,7 +843,7 @@
         <v>44494</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -955,7 +955,7 @@
         <v>45090</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1070,7 +1070,7 @@
         <v>45306</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1188,7 +1188,7 @@
         <v>45154</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1298,7 +1298,7 @@
         <v>44791</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1406,7 +1406,7 @@
         <v>44740</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1518,7 +1518,7 @@
         <v>45407</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1626,7 +1626,7 @@
         <v>45754</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1737,7 +1737,7 @@
         <v>45293</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1852,7 +1852,7 @@
         <v>45358</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1963,7 +1963,7 @@
         <v>44916</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2074,7 +2074,7 @@
         <v>44868</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2180,7 +2180,7 @@
         <v>44865</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2286,7 +2286,7 @@
         <v>44888</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2396,7 +2396,7 @@
         <v>45243</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2502,7 +2502,7 @@
         <v>45091</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2612,7 +2612,7 @@
         <v>45315</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2722,7 +2722,7 @@
         <v>44970</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2828,7 +2828,7 @@
         <v>45310</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2934,7 +2934,7 @@
         <v>45426</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3040,7 +3040,7 @@
         <v>45575</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3146,7 +3146,7 @@
         <v>45856</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3252,7 +3252,7 @@
         <v>45545</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3358,7 +3358,7 @@
         <v>45257</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3463,7 +3463,7 @@
         <v>45721</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3568,7 +3568,7 @@
         <v>45532</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3673,7 +3673,7 @@
         <v>45376</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3782,7 +3782,7 @@
         <v>45243</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3887,7 +3887,7 @@
         <v>45432</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3992,7 +3992,7 @@
         <v>46092</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4097,7 +4097,7 @@
         <v>45244</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4202,7 +4202,7 @@
         <v>46269</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4312,7 +4312,7 @@
         <v>46269</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4421,7 +4421,7 @@
         <v>45777</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4535,7 +4535,7 @@
         <v>44579</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4645,7 +4645,7 @@
         <v>44889</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4718,7 +4718,7 @@
         <v>44461</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4791,7 +4791,7 @@
         <v>44683</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4864,7 +4864,7 @@
         <v>44810</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4937,7 +4937,7 @@
         <v>44529</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5010,7 +5010,7 @@
         <v>44712</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5083,7 +5083,7 @@
         <v>44479</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5156,7 +5156,7 @@
         <v>44479</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5229,7 +5229,7 @@
         <v>44852</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5302,7 +5302,7 @@
         <v>44889</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5375,7 +5375,7 @@
         <v>44608</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5453,7 +5453,7 @@
         <v>44582</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5526,7 +5526,7 @@
         <v>44582</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5599,7 +5599,7 @@
         <v>44851</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5672,7 +5672,7 @@
         <v>44538</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5745,7 +5745,7 @@
         <v>44740</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5818,7 +5818,7 @@
         <v>44816</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5891,7 +5891,7 @@
         <v>44837</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5964,7 +5964,7 @@
         <v>44712</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6037,7 +6037,7 @@
         <v>44529</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6110,7 +6110,7 @@
         <v>44532</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6183,7 +6183,7 @@
         <v>44874</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6256,7 +6256,7 @@
         <v>44586</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6329,7 +6329,7 @@
         <v>44722</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6402,7 +6402,7 @@
         <v>44685</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6475,7 +6475,7 @@
         <v>44809</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6548,7 +6548,7 @@
         <v>44858</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6621,7 +6621,7 @@
         <v>44491</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6694,7 +6694,7 @@
         <v>44670</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6767,7 +6767,7 @@
         <v>44659</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6840,7 +6840,7 @@
         <v>44740</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6913,7 +6913,7 @@
         <v>44510</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6986,7 +6986,7 @@
         <v>44733</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7059,7 +7059,7 @@
         <v>44853</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7132,7 +7132,7 @@
         <v>44557</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7210,7 +7210,7 @@
         <v>44546</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7283,7 +7283,7 @@
         <v>44817</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7356,7 +7356,7 @@
         <v>44614</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7429,7 +7429,7 @@
         <v>44883</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7502,7 +7502,7 @@
         <v>44874</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7575,7 +7575,7 @@
         <v>44874</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7648,7 +7648,7 @@
         <v>44515</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7726,7 +7726,7 @@
         <v>44799</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7799,7 +7799,7 @@
         <v>44881</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7872,7 +7872,7 @@
         <v>44881</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7945,7 +7945,7 @@
         <v>44588</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8018,7 +8018,7 @@
         <v>44581</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8091,7 +8091,7 @@
         <v>44868</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8164,7 +8164,7 @@
         <v>44705</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8237,7 +8237,7 @@
         <v>44573</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8310,7 +8310,7 @@
         <v>44560</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8388,7 +8388,7 @@
         <v>44477</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8461,7 +8461,7 @@
         <v>44614</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8534,7 +8534,7 @@
         <v>44714</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8607,7 +8607,7 @@
         <v>44877</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8680,7 +8680,7 @@
         <v>44491</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8753,7 +8753,7 @@
         <v>44852</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8826,7 +8826,7 @@
         <v>44469</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8899,7 +8899,7 @@
         <v>44662</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8972,7 +8972,7 @@
         <v>44584</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9045,7 +9045,7 @@
         <v>44643</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9118,7 +9118,7 @@
         <v>44614</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9191,7 +9191,7 @@
         <v>44726</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9264,7 +9264,7 @@
         <v>44818</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9337,7 +9337,7 @@
         <v>45736</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9410,7 +9410,7 @@
         <v>44467</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9488,7 +9488,7 @@
         <v>44586</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9561,7 +9561,7 @@
         <v>45040</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9634,7 +9634,7 @@
         <v>44588</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9707,7 +9707,7 @@
         <v>44979</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9780,7 +9780,7 @@
         <v>44881</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9858,7 +9858,7 @@
         <v>45162</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9931,7 +9931,7 @@
         <v>45267</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10004,7 +10004,7 @@
         <v>45054</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10077,7 +10077,7 @@
         <v>45054</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10150,7 +10150,7 @@
         <v>44899</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10223,7 +10223,7 @@
         <v>45189</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10296,7 +10296,7 @@
         <v>44918</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10369,7 +10369,7 @@
         <v>44918</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10442,7 +10442,7 @@
         <v>45184</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10515,7 +10515,7 @@
         <v>45763</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10588,7 +10588,7 @@
         <v>45694</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10661,7 +10661,7 @@
         <v>45733</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10734,7 +10734,7 @@
         <v>45245</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10812,7 +10812,7 @@
         <v>45338</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10885,7 +10885,7 @@
         <v>45510</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10958,7 +10958,7 @@
         <v>45510</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11031,7 +11031,7 @@
         <v>45623</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11104,7 +11104,7 @@
         <v>45265</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11177,7 +11177,7 @@
         <v>44629</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11250,7 +11250,7 @@
         <v>44937</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11323,7 +11323,7 @@
         <v>45091</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11396,7 +11396,7 @@
         <v>45733</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11469,7 +11469,7 @@
         <v>45512</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11542,7 +11542,7 @@
         <v>45609</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11615,7 +11615,7 @@
         <v>44911</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11688,7 +11688,7 @@
         <v>45544</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11761,7 +11761,7 @@
         <v>45110</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11834,7 +11834,7 @@
         <v>45090</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11907,7 +11907,7 @@
         <v>45727</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11980,7 +11980,7 @@
         <v>45727</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12053,7 +12053,7 @@
         <v>45355</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12126,7 +12126,7 @@
         <v>44470</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12199,7 +12199,7 @@
         <v>45161</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12272,7 +12272,7 @@
         <v>45629</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12345,7 +12345,7 @@
         <v>45336</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12418,7 +12418,7 @@
         <v>44474</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12491,7 +12491,7 @@
         <v>45110</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12564,7 +12564,7 @@
         <v>45629</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12637,7 +12637,7 @@
         <v>45173</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12710,7 +12710,7 @@
         <v>45173</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12783,7 +12783,7 @@
         <v>44874</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12856,7 +12856,7 @@
         <v>45435</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12929,7 +12929,7 @@
         <v>44887</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13002,7 +13002,7 @@
         <v>44956</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13075,7 +13075,7 @@
         <v>45749</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13148,7 +13148,7 @@
         <v>45140</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13221,7 +13221,7 @@
         <v>45195</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13294,7 +13294,7 @@
         <v>45434</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13367,7 +13367,7 @@
         <v>45482</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13440,7 +13440,7 @@
         <v>45390</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13513,7 +13513,7 @@
         <v>45271</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13586,7 +13586,7 @@
         <v>45028</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13659,7 +13659,7 @@
         <v>45722</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13732,7 +13732,7 @@
         <v>45245</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13810,7 +13810,7 @@
         <v>45058</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13883,7 +13883,7 @@
         <v>45474</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13956,7 +13956,7 @@
         <v>44904</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14029,7 +14029,7 @@
         <v>45460</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14107,7 +14107,7 @@
         <v>45729</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14180,7 +14180,7 @@
         <v>45293</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14253,7 +14253,7 @@
         <v>45588</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14326,7 +14326,7 @@
         <v>45491</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14399,7 +14399,7 @@
         <v>45623</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14472,7 +14472,7 @@
         <v>44641</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14545,7 +14545,7 @@
         <v>45616</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14618,7 +14618,7 @@
         <v>44991</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14691,7 +14691,7 @@
         <v>44901</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14764,7 +14764,7 @@
         <v>44581</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14837,7 +14837,7 @@
         <v>45694</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14910,7 +14910,7 @@
         <v>45429</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14983,7 +14983,7 @@
         <v>44867</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15056,7 +15056,7 @@
         <v>44998</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15129,7 +15129,7 @@
         <v>44693</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15202,7 +15202,7 @@
         <v>44896</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15275,7 +15275,7 @@
         <v>45456</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15348,7 +15348,7 @@
         <v>45231</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15421,7 +15421,7 @@
         <v>45226</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15494,7 +15494,7 @@
         <v>45261</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15567,7 +15567,7 @@
         <v>44602</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15640,7 +15640,7 @@
         <v>45149</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15718,7 +15718,7 @@
         <v>45558</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15791,7 +15791,7 @@
         <v>44943</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15864,7 +15864,7 @@
         <v>45021</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15937,7 +15937,7 @@
         <v>44790</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16010,7 +16010,7 @@
         <v>45061</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16083,7 +16083,7 @@
         <v>44942</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16156,7 +16156,7 @@
         <v>45016</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16234,7 +16234,7 @@
         <v>45273</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16307,7 +16307,7 @@
         <v>44935</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16380,7 +16380,7 @@
         <v>45142</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16453,7 +16453,7 @@
         <v>45142</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16526,7 +16526,7 @@
         <v>45231</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16599,7 +16599,7 @@
         <v>45680</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16672,7 +16672,7 @@
         <v>45119</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16745,7 +16745,7 @@
         <v>45274</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16818,7 +16818,7 @@
         <v>45176</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16891,7 +16891,7 @@
         <v>45614</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16964,7 +16964,7 @@
         <v>45197</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17037,7 +17037,7 @@
         <v>45729</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17110,7 +17110,7 @@
         <v>44614</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17183,7 +17183,7 @@
         <v>45932</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17256,7 +17256,7 @@
         <v>45041</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17329,7 +17329,7 @@
         <v>45195</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17402,7 +17402,7 @@
         <v>45443</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17475,7 +17475,7 @@
         <v>44966</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17548,7 +17548,7 @@
         <v>45714</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17621,7 +17621,7 @@
         <v>45804</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17694,7 +17694,7 @@
         <v>45525</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17767,7 +17767,7 @@
         <v>45525</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17840,7 +17840,7 @@
         <v>45135</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17913,7 +17913,7 @@
         <v>45156</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17986,7 +17986,7 @@
         <v>45554</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18059,7 +18059,7 @@
         <v>45173</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18132,7 +18132,7 @@
         <v>45915</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18205,7 +18205,7 @@
         <v>45856</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18278,7 +18278,7 @@
         <v>45140</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18351,7 +18351,7 @@
         <v>45583</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18424,7 +18424,7 @@
         <v>45856</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18497,7 +18497,7 @@
         <v>46031</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18570,7 +18570,7 @@
         <v>45891</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18648,7 +18648,7 @@
         <v>44865</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18721,7 +18721,7 @@
         <v>45691</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18794,7 +18794,7 @@
         <v>45418</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18867,7 +18867,7 @@
         <v>44494</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18940,7 +18940,7 @@
         <v>45300</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19013,7 +19013,7 @@
         <v>44865</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19086,7 +19086,7 @@
         <v>45608</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19159,7 +19159,7 @@
         <v>45897</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19237,7 +19237,7 @@
         <v>45671</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19310,7 +19310,7 @@
         <v>45621</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19383,7 +19383,7 @@
         <v>45873</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19456,7 +19456,7 @@
         <v>45897</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19534,7 +19534,7 @@
         <v>45897</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19607,7 +19607,7 @@
         <v>45153</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19680,7 +19680,7 @@
         <v>45903</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19753,7 +19753,7 @@
         <v>45903</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19826,7 +19826,7 @@
         <v>45866</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19899,7 +19899,7 @@
         <v>45903</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19972,7 +19972,7 @@
         <v>45751</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20045,7 +20045,7 @@
         <v>45903</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20118,7 +20118,7 @@
         <v>45642</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20191,7 +20191,7 @@
         <v>45477</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20264,7 +20264,7 @@
         <v>45811</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20337,7 +20337,7 @@
         <v>45267</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20410,7 +20410,7 @@
         <v>46140</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20488,7 +20488,7 @@
         <v>46140</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20561,7 +20561,7 @@
         <v>46140</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20634,7 +20634,7 @@
         <v>45910</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20707,7 +20707,7 @@
         <v>45243</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20780,7 +20780,7 @@
         <v>44872</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20853,7 +20853,7 @@
         <v>46140</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20931,7 +20931,7 @@
         <v>45733</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21004,7 +21004,7 @@
         <v>46031</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21077,7 +21077,7 @@
         <v>46140</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21155,7 +21155,7 @@
         <v>45152</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21228,7 +21228,7 @@
         <v>44596</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21301,7 +21301,7 @@
         <v>45918</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21379,7 +21379,7 @@
         <v>45015</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21452,7 +21452,7 @@
         <v>45910</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21525,7 +21525,7 @@
         <v>45089</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21598,7 +21598,7 @@
         <v>45818</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21671,7 +21671,7 @@
         <v>45920</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21744,7 +21744,7 @@
         <v>44998</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21817,7 +21817,7 @@
         <v>44573</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21890,7 +21890,7 @@
         <v>45252</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -21963,7 +21963,7 @@
         <v>44834</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22041,7 +22041,7 @@
         <v>45924</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22114,7 +22114,7 @@
         <v>45924</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22187,7 +22187,7 @@
         <v>45924</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22260,7 +22260,7 @@
         <v>45929</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22333,7 +22333,7 @@
         <v>45929</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22406,7 +22406,7 @@
         <v>44998</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22479,7 +22479,7 @@
         <v>45929</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22552,7 +22552,7 @@
         <v>45929</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22625,7 +22625,7 @@
         <v>45191</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22698,7 +22698,7 @@
         <v>45532</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22771,7 +22771,7 @@
         <v>44845</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -22844,7 +22844,7 @@
         <v>46146</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -22917,7 +22917,7 @@
         <v>44917</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -22995,7 +22995,7 @@
         <v>44956</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23068,7 +23068,7 @@
         <v>45691</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23141,7 +23141,7 @@
         <v>45440</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23214,7 +23214,7 @@
         <v>45408</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23287,7 +23287,7 @@
         <v>45936</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23365,7 +23365,7 @@
         <v>45638</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23438,7 +23438,7 @@
         <v>45888</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23511,7 +23511,7 @@
         <v>46147</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23584,7 +23584,7 @@
         <v>45936</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23662,7 +23662,7 @@
         <v>44911</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23735,7 +23735,7 @@
         <v>46147</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -23808,7 +23808,7 @@
         <v>44523</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -23881,7 +23881,7 @@
         <v>45477</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -23954,7 +23954,7 @@
         <v>44518</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24027,7 +24027,7 @@
         <v>45397</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24100,7 +24100,7 @@
         <v>45936</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24173,7 +24173,7 @@
         <v>45358</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24246,7 +24246,7 @@
         <v>46147</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24319,7 +24319,7 @@
         <v>45940</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24397,7 +24397,7 @@
         <v>45940</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24475,7 +24475,7 @@
         <v>46148</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24548,7 +24548,7 @@
         <v>46148</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24621,7 +24621,7 @@
         <v>46148</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24694,7 +24694,7 @@
         <v>46148</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -24767,7 +24767,7 @@
         <v>46148</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -24840,7 +24840,7 @@
         <v>46148</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -24913,7 +24913,7 @@
         <v>45623</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -24986,7 +24986,7 @@
         <v>45614</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25059,7 +25059,7 @@
         <v>46149</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25132,7 +25132,7 @@
         <v>45203</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25205,7 +25205,7 @@
         <v>45520</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25278,7 +25278,7 @@
         <v>45737</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25351,7 +25351,7 @@
         <v>45161</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25424,7 +25424,7 @@
         <v>46153</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25502,7 +25502,7 @@
         <v>45950</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25580,7 +25580,7 @@
         <v>44986</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25653,7 +25653,7 @@
         <v>45184</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -25726,7 +25726,7 @@
         <v>45184</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -25799,7 +25799,7 @@
         <v>44543</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -25872,7 +25872,7 @@
         <v>45743</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -25945,7 +25945,7 @@
         <v>45957</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26018,7 +26018,7 @@
         <v>46153</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26096,7 +26096,7 @@
         <v>44865</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26169,7 +26169,7 @@
         <v>44915</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26242,7 +26242,7 @@
         <v>44915</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26315,7 +26315,7 @@
         <v>45692</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26388,7 +26388,7 @@
         <v>45104</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26461,7 +26461,7 @@
         <v>45210</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26534,7 +26534,7 @@
         <v>45733</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26607,7 +26607,7 @@
         <v>44901</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -26680,7 +26680,7 @@
         <v>44851</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -26753,7 +26753,7 @@
         <v>45106</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -26826,7 +26826,7 @@
         <v>44777</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -26899,7 +26899,7 @@
         <v>46154</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -26977,7 +26977,7 @@
         <v>46154</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27050,7 +27050,7 @@
         <v>45090</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27123,7 +27123,7 @@
         <v>45966</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27196,7 +27196,7 @@
         <v>45579</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27269,7 +27269,7 @@
         <v>45968</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27342,7 +27342,7 @@
         <v>45971</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27415,7 +27415,7 @@
         <v>45680</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27488,7 +27488,7 @@
         <v>45971</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27561,7 +27561,7 @@
         <v>45971</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -27639,7 +27639,7 @@
         <v>45971</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -27717,7 +27717,7 @@
         <v>45971</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -27790,7 +27790,7 @@
         <v>45021</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -27868,7 +27868,7 @@
         <v>45834</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -27941,7 +27941,7 @@
         <v>45176</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28014,7 +28014,7 @@
         <v>45975</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28087,7 +28087,7 @@
         <v>45975</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28160,7 +28160,7 @@
         <v>45435</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28233,7 +28233,7 @@
         <v>44483</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28306,7 +28306,7 @@
         <v>45981</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28379,7 +28379,7 @@
         <v>45981</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28452,7 +28452,7 @@
         <v>44881</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28525,7 +28525,7 @@
         <v>45629</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -28598,7 +28598,7 @@
         <v>45603</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -28671,7 +28671,7 @@
         <v>45980</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -28744,7 +28744,7 @@
         <v>45559</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -28817,7 +28817,7 @@
         <v>45981</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -28890,7 +28890,7 @@
         <v>45981</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -28963,7 +28963,7 @@
         <v>45498</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29036,7 +29036,7 @@
         <v>44916</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29109,7 +29109,7 @@
         <v>45756</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29182,7 +29182,7 @@
         <v>45756</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29255,7 +29255,7 @@
         <v>45614</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29328,7 +29328,7 @@
         <v>45281</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29401,7 +29401,7 @@
         <v>45579</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29474,7 +29474,7 @@
         <v>45636</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -29552,7 +29552,7 @@
         <v>45061</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -29625,7 +29625,7 @@
         <v>45111</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -29698,7 +29698,7 @@
         <v>45204</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -29771,7 +29771,7 @@
         <v>44979</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -29844,7 +29844,7 @@
         <v>45980</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -29917,7 +29917,7 @@
         <v>44798</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -29990,7 +29990,7 @@
         <v>45904</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30063,7 +30063,7 @@
         <v>45992</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30136,7 +30136,7 @@
         <v>44977</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30209,7 +30209,7 @@
         <v>45250</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30282,7 +30282,7 @@
         <v>46163</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30355,7 +30355,7 @@
         <v>44482</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30428,7 +30428,7 @@
         <v>44970</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30501,7 +30501,7 @@
         <v>44740</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -30574,7 +30574,7 @@
         <v>45191</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -30647,7 +30647,7 @@
         <v>45992</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -30720,7 +30720,7 @@
         <v>45992</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -30793,7 +30793,7 @@
         <v>45994</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -30866,7 +30866,7 @@
         <v>45995</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -30939,7 +30939,7 @@
         <v>45188</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31012,7 +31012,7 @@
         <v>46163</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31085,7 +31085,7 @@
         <v>45994</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31158,7 +31158,7 @@
         <v>46163</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31231,7 +31231,7 @@
         <v>45995</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31304,7 +31304,7 @@
         <v>46163</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31377,7 +31377,7 @@
         <v>45999</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31450,7 +31450,7 @@
         <v>45704</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -31523,7 +31523,7 @@
         <v>45723</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -31596,7 +31596,7 @@
         <v>45996</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -31669,7 +31669,7 @@
         <v>45520</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -31742,7 +31742,7 @@
         <v>46000</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -31815,7 +31815,7 @@
         <v>45510</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -31888,7 +31888,7 @@
         <v>46002</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -31961,7 +31961,7 @@
         <v>46002</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -32034,7 +32034,7 @@
         <v>46167</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32107,7 +32107,7 @@
         <v>45036</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32180,7 +32180,7 @@
         <v>45071</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32253,7 +32253,7 @@
         <v>44839</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -32326,7 +32326,7 @@
         <v>45301</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -32404,7 +32404,7 @@
         <v>46006</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -32477,7 +32477,7 @@
         <v>46167</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -32550,7 +32550,7 @@
         <v>45412</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -32623,7 +32623,7 @@
         <v>45646</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -32696,7 +32696,7 @@
         <v>46007</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -32769,7 +32769,7 @@
         <v>44799</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -32842,7 +32842,7 @@
         <v>46009</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -32915,7 +32915,7 @@
         <v>46010</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -32988,7 +32988,7 @@
         <v>46013</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -33061,7 +33061,7 @@
         <v>44625</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -33134,7 +33134,7 @@
         <v>46013</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -33207,7 +33207,7 @@
         <v>46013</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -33280,7 +33280,7 @@
         <v>46010</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -33353,7 +33353,7 @@
         <v>45443</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -33426,7 +33426,7 @@
         <v>45475</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -33499,7 +33499,7 @@
         <v>44470</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -33572,7 +33572,7 @@
         <v>46016</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -33645,7 +33645,7 @@
         <v>45307</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -33718,7 +33718,7 @@
         <v>46016</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -33791,7 +33791,7 @@
         <v>46016</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -33864,7 +33864,7 @@
         <v>46016</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -33937,7 +33937,7 @@
         <v>46016</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -34010,7 +34010,7 @@
         <v>46016</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -34083,7 +34083,7 @@
         <v>44476</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -34161,7 +34161,7 @@
         <v>46021</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -34234,7 +34234,7 @@
         <v>46021</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -34312,7 +34312,7 @@
         <v>44858</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -34385,7 +34385,7 @@
         <v>44970</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -34458,7 +34458,7 @@
         <v>45310</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -34531,7 +34531,7 @@
         <v>46029</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -34604,7 +34604,7 @@
         <v>45090</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -34677,7 +34677,7 @@
         <v>46029</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -34750,7 +34750,7 @@
         <v>45090</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -34823,7 +34823,7 @@
         <v>45533</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -34896,7 +34896,7 @@
         <v>46029</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -34969,7 +34969,7 @@
         <v>46029</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -35042,7 +35042,7 @@
         <v>45392</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -35115,7 +35115,7 @@
         <v>46031</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -35188,7 +35188,7 @@
         <v>46031</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -35261,7 +35261,7 @@
         <v>46035</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -35334,7 +35334,7 @@
         <v>44746</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -35407,7 +35407,7 @@
         <v>44951</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -35480,7 +35480,7 @@
         <v>46041</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -35553,7 +35553,7 @@
         <v>44798</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -35626,7 +35626,7 @@
         <v>46041</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -35699,7 +35699,7 @@
         <v>46042</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -35772,7 +35772,7 @@
         <v>45210</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -35845,7 +35845,7 @@
         <v>44896</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -35918,7 +35918,7 @@
         <v>45603</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -35991,7 +35991,7 @@
         <v>46043</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -36064,7 +36064,7 @@
         <v>46048</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -36137,7 +36137,7 @@
         <v>45308</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -36210,7 +36210,7 @@
         <v>45139</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -36283,7 +36283,7 @@
         <v>46050</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -36356,7 +36356,7 @@
         <v>46176</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -36429,7 +36429,7 @@
         <v>46050</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -36502,7 +36502,7 @@
         <v>46050</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -36575,7 +36575,7 @@
         <v>46050</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -36648,7 +36648,7 @@
         <v>45467</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -36721,7 +36721,7 @@
         <v>45105</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -36794,7 +36794,7 @@
         <v>45091</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -36867,7 +36867,7 @@
         <v>45091</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -36940,7 +36940,7 @@
         <v>46177</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -37013,7 +37013,7 @@
         <v>45751</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -37086,7 +37086,7 @@
         <v>46052</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -37164,7 +37164,7 @@
         <v>46055</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -37237,7 +37237,7 @@
         <v>46178</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -37310,7 +37310,7 @@
         <v>45278</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -37383,7 +37383,7 @@
         <v>46055</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -37456,7 +37456,7 @@
         <v>44894</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -37529,7 +37529,7 @@
         <v>45245</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -37607,7 +37607,7 @@
         <v>46059</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -37680,7 +37680,7 @@
         <v>46059</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -37753,7 +37753,7 @@
         <v>46062</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -37826,7 +37826,7 @@
         <v>46062</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -37899,7 +37899,7 @@
         <v>45166</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -37972,7 +37972,7 @@
         <v>46064</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -38045,7 +38045,7 @@
         <v>46064</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -38118,7 +38118,7 @@
         <v>46069</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -38191,7 +38191,7 @@
         <v>45173</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -38264,7 +38264,7 @@
         <v>46069</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -38337,7 +38337,7 @@
         <v>46066</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -38410,7 +38410,7 @@
         <v>44557</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -38483,7 +38483,7 @@
         <v>45085</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -38556,7 +38556,7 @@
         <v>44575</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -38629,7 +38629,7 @@
         <v>44908</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -38702,7 +38702,7 @@
         <v>45600</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -38775,7 +38775,7 @@
         <v>45092</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -38848,7 +38848,7 @@
         <v>45541</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -38921,7 +38921,7 @@
         <v>45296</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -38994,7 +38994,7 @@
         <v>46084</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -39067,7 +39067,7 @@
         <v>45197</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -39140,7 +39140,7 @@
         <v>45224</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -39213,7 +39213,7 @@
         <v>46083</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -39286,7 +39286,7 @@
         <v>46083</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -39359,7 +39359,7 @@
         <v>45532</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -39432,7 +39432,7 @@
         <v>46085</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -39505,7 +39505,7 @@
         <v>46085</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -39578,7 +39578,7 @@
         <v>46085</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -39651,7 +39651,7 @@
         <v>44537</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -39724,7 +39724,7 @@
         <v>45037</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -39797,7 +39797,7 @@
         <v>45719</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -39870,7 +39870,7 @@
         <v>44901</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -39943,7 +39943,7 @@
         <v>46090</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -40021,7 +40021,7 @@
         <v>46092</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -40094,7 +40094,7 @@
         <v>46092</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -40167,7 +40167,7 @@
         <v>46092</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -40240,7 +40240,7 @@
         <v>46092</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -40313,7 +40313,7 @@
         <v>46092</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -40386,7 +40386,7 @@
         <v>45301</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -40459,7 +40459,7 @@
         <v>45617</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -40532,7 +40532,7 @@
         <v>46092</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -40605,7 +40605,7 @@
         <v>44537</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -40678,7 +40678,7 @@
         <v>45054</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -40751,7 +40751,7 @@
         <v>45549</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -40824,7 +40824,7 @@
         <v>46099</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -40897,7 +40897,7 @@
         <v>46196</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -40970,7 +40970,7 @@
         <v>46195</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -41048,7 +41048,7 @@
         <v>45084</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -41121,7 +41121,7 @@
         <v>46099</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -41194,7 +41194,7 @@
         <v>46100</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -41272,7 +41272,7 @@
         <v>46195</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -41350,7 +41350,7 @@
         <v>44546</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -41423,7 +41423,7 @@
         <v>46196</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -41496,7 +41496,7 @@
         <v>44840</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -41569,7 +41569,7 @@
         <v>46101</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -41642,7 +41642,7 @@
         <v>46104</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -41715,7 +41715,7 @@
         <v>45685</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -41788,7 +41788,7 @@
         <v>46197</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -41866,7 +41866,7 @@
         <v>45552</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -41944,7 +41944,7 @@
         <v>44966</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -42017,7 +42017,7 @@
         <v>45090</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -42090,7 +42090,7 @@
         <v>45090</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -42163,7 +42163,7 @@
         <v>45090</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -42236,7 +42236,7 @@
         <v>45553</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -42309,7 +42309,7 @@
         <v>46108</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -42382,7 +42382,7 @@
         <v>45736</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -42455,7 +42455,7 @@
         <v>46107</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -42528,7 +42528,7 @@
         <v>45106</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -42601,7 +42601,7 @@
         <v>44804</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -42674,7 +42674,7 @@
         <v>46108</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -42747,7 +42747,7 @@
         <v>45749</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -42825,7 +42825,7 @@
         <v>45450</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -42898,7 +42898,7 @@
         <v>46199</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -42971,7 +42971,7 @@
         <v>46199</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -43044,7 +43044,7 @@
         <v>46199</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -43117,7 +43117,7 @@
         <v>46199</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -43190,7 +43190,7 @@
         <v>46199</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -43263,7 +43263,7 @@
         <v>45290</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -43336,7 +43336,7 @@
         <v>45290</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -43409,7 +43409,7 @@
         <v>46119</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -43482,7 +43482,7 @@
         <v>46120</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -43555,7 +43555,7 @@
         <v>45146</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -43628,7 +43628,7 @@
         <v>45176</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -43701,7 +43701,7 @@
         <v>45539</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -43774,7 +43774,7 @@
         <v>46119</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -43847,7 +43847,7 @@
         <v>46070</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -43920,7 +43920,7 @@
         <v>45754</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -43993,7 +43993,7 @@
         <v>46119</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -44066,7 +44066,7 @@
         <v>46070</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -44139,7 +44139,7 @@
         <v>46124</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -44212,7 +44212,7 @@
         <v>46124</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -44285,7 +44285,7 @@
         <v>46245</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -44358,7 +44358,7 @@
         <v>45654</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -44431,7 +44431,7 @@
         <v>45152</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -44504,7 +44504,7 @@
         <v>45152</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -44577,7 +44577,7 @@
         <v>46245</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -44650,7 +44650,7 @@
         <v>45758</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -44723,7 +44723,7 @@
         <v>46199</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -44796,7 +44796,7 @@
         <v>46199</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -44869,7 +44869,7 @@
         <v>46127</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -44942,7 +44942,7 @@
         <v>46203</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -45015,7 +45015,7 @@
         <v>45261</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -45088,7 +45088,7 @@
         <v>45775</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -45161,7 +45161,7 @@
         <v>45714</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -45234,7 +45234,7 @@
         <v>45098</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -45307,7 +45307,7 @@
         <v>46135</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -45380,7 +45380,7 @@
         <v>46135</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -45453,7 +45453,7 @@
         <v>46135</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -45526,7 +45526,7 @@
         <v>45272</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -45599,7 +45599,7 @@
         <v>44683</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -45672,7 +45672,7 @@
         <v>45246</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -45745,7 +45745,7 @@
         <v>45084</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -45818,7 +45818,7 @@
         <v>44899</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -45891,7 +45891,7 @@
         <v>45832</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -45964,7 +45964,7 @@
         <v>45204</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -46037,7 +46037,7 @@
         <v>45611</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -46110,7 +46110,7 @@
         <v>46104</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -46183,7 +46183,7 @@
         <v>45114</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -46256,7 +46256,7 @@
         <v>45279</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -46329,7 +46329,7 @@
         <v>45804</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -46402,7 +46402,7 @@
         <v>45525</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -46475,7 +46475,7 @@
         <v>46203</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -46548,7 +46548,7 @@
         <v>45224</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -46626,7 +46626,7 @@
         <v>46247</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -46699,7 +46699,7 @@
         <v>46247</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -46772,7 +46772,7 @@
         <v>46203</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -46845,7 +46845,7 @@
         <v>46247</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -46918,7 +46918,7 @@
         <v>45267</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -46991,7 +46991,7 @@
         <v>45015</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -47064,7 +47064,7 @@
         <v>45370</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -47137,7 +47137,7 @@
         <v>44966</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -47210,7 +47210,7 @@
         <v>45092</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -47283,7 +47283,7 @@
         <v>44883</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -47356,7 +47356,7 @@
         <v>45684</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -47429,7 +47429,7 @@
         <v>45281</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -47502,7 +47502,7 @@
         <v>45603</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -47575,7 +47575,7 @@
         <v>45275</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -47648,7 +47648,7 @@
         <v>45128</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -47721,7 +47721,7 @@
         <v>46252</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -47794,7 +47794,7 @@
         <v>45756</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -47867,7 +47867,7 @@
         <v>45281</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -47940,7 +47940,7 @@
         <v>46253</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -48013,7 +48013,7 @@
         <v>44602</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -48086,7 +48086,7 @@
         <v>45161</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -48159,7 +48159,7 @@
         <v>45245</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -48237,7 +48237,7 @@
         <v>45149</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -48315,7 +48315,7 @@
         <v>45159</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -48388,7 +48388,7 @@
         <v>45089</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -48461,7 +48461,7 @@
         <v>45426</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -48534,7 +48534,7 @@
         <v>45310</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -48607,7 +48607,7 @@
         <v>45310</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -48680,7 +48680,7 @@
         <v>45090</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -48753,7 +48753,7 @@
         <v>44700</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -48831,7 +48831,7 @@
         <v>45432</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -48904,7 +48904,7 @@
         <v>45054</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -48977,7 +48977,7 @@
         <v>45336</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -49050,7 +49050,7 @@
         <v>45546</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -49123,7 +49123,7 @@
         <v>45455</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -49196,7 +49196,7 @@
         <v>45040</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -49269,7 +49269,7 @@
         <v>45294</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -49342,7 +49342,7 @@
         <v>45253</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -49415,7 +49415,7 @@
         <v>45541</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -49488,7 +49488,7 @@
         <v>46261</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -49566,7 +49566,7 @@
         <v>46217</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -49639,7 +49639,7 @@
         <v>46217</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -49712,7 +49712,7 @@
         <v>46261</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -49790,7 +49790,7 @@
         <v>45692</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -49863,7 +49863,7 @@
         <v>46217</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -49936,7 +49936,7 @@
         <v>45674</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -50009,7 +50009,7 @@
         <v>44966</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -50082,7 +50082,7 @@
         <v>46262</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -50160,7 +50160,7 @@
         <v>44998</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -50233,7 +50233,7 @@
         <v>44896</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -50306,7 +50306,7 @@
         <v>45306</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -50379,7 +50379,7 @@
         <v>45676</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -50452,7 +50452,7 @@
         <v>45221</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -50530,7 +50530,7 @@
         <v>45221</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -50608,7 +50608,7 @@
         <v>45229</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -50681,7 +50681,7 @@
         <v>44659</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -50754,7 +50754,7 @@
         <v>45175</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -50827,7 +50827,7 @@
         <v>45616</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -50900,7 +50900,7 @@
         <v>46266</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -50973,7 +50973,7 @@
         <v>46266</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -51046,7 +51046,7 @@
         <v>44776</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -51124,7 +51124,7 @@
         <v>44714</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -51197,7 +51197,7 @@
         <v>46267</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -51270,7 +51270,7 @@
         <v>44636</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -51343,7 +51343,7 @@
         <v>44636</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -51416,7 +51416,7 @@
         <v>44911</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -51489,7 +51489,7 @@
         <v>45015</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -51562,7 +51562,7 @@
         <v>45616</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -51635,7 +51635,7 @@
         <v>44665</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -51708,7 +51708,7 @@
         <v>46269</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -51781,7 +51781,7 @@
         <v>46269</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -51854,7 +51854,7 @@
         <v>45775</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -51927,7 +51927,7 @@
         <v>45777</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -52000,7 +52000,7 @@
         <v>45775</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -52073,7 +52073,7 @@
         <v>45783</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -52146,7 +52146,7 @@
         <v>46275</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -52219,7 +52219,7 @@
         <v>46274</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -52292,7 +52292,7 @@
         <v>46274</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -52365,7 +52365,7 @@
         <v>45567</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -52438,7 +52438,7 @@
         <v>46233</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -52511,7 +52511,7 @@
         <v>46279</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -52584,7 +52584,7 @@
         <v>45730</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -52657,7 +52657,7 @@
         <v>46279</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -52730,7 +52730,7 @@
         <v>46273</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -52803,7 +52803,7 @@
         <v>46238</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -52876,7 +52876,7 @@
         <v>46280</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -52949,7 +52949,7 @@
         <v>46237</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -53022,7 +53022,7 @@
         <v>45629</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -53095,7 +53095,7 @@
         <v>45792</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -53168,7 +53168,7 @@
         <v>45576</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -53241,7 +53241,7 @@
         <v>46240</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -53314,7 +53314,7 @@
         <v>45796</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -53387,7 +53387,7 @@
         <v>46281</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -53460,7 +53460,7 @@
         <v>45803</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -53533,7 +53533,7 @@
         <v>45805</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -53611,7 +53611,7 @@
         <v>45310</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -53684,7 +53684,7 @@
         <v>45600</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -53757,7 +53757,7 @@
         <v>45726</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -53830,7 +53830,7 @@
         <v>45624</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -53903,7 +53903,7 @@
         <v>45378</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -53976,7 +53976,7 @@
         <v>44966</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -54054,7 +54054,7 @@
         <v>45502</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -54127,7 +54127,7 @@
         <v>45580</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -54200,7 +54200,7 @@
         <v>45628</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -54273,7 +54273,7 @@
         <v>45583</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -54346,7 +54346,7 @@
         <v>45742</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -54419,7 +54419,7 @@
         <v>45590</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -54492,7 +54492,7 @@
         <v>45818</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -54565,7 +54565,7 @@
         <v>45818</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -54638,7 +54638,7 @@
         <v>45817</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -54711,7 +54711,7 @@
         <v>45818</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -54784,7 +54784,7 @@
         <v>45758</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -54857,7 +54857,7 @@
         <v>45835</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -54930,7 +54930,7 @@
         <v>45839</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -55003,7 +55003,7 @@
         <v>45838</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -55076,7 +55076,7 @@
         <v>45838</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -55149,7 +55149,7 @@
         <v>45839</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -55222,7 +55222,7 @@
         <v>45841</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -55295,7 +55295,7 @@
         <v>45817</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -55368,7 +55368,7 @@
         <v>45715</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -55441,7 +55441,7 @@
         <v>45253</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -55514,7 +55514,7 @@
         <v>45061</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -55587,7 +55587,7 @@
         <v>45588</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -55660,7 +55660,7 @@
         <v>45736</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -55733,7 +55733,7 @@
         <v>45848</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -55806,7 +55806,7 @@
         <v>45778</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -55879,7 +55879,7 @@
         <v>45856</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -55952,7 +55952,7 @@
         <v>45874</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -56025,7 +56025,7 @@
         <v>45883</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -56098,7 +56098,7 @@
         <v>45882</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -56171,7 +56171,7 @@
         <v>45882</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -56244,7 +56244,7 @@
         <v>45582</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -56317,7 +56317,7 @@
         <v>44579</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -56395,7 +56395,7 @@
         <v>44893</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -56473,7 +56473,7 @@
         <v>44893</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -56551,7 +56551,7 @@
         <v>44893</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -56629,7 +56629,7 @@
         <v>45731</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -56702,7 +56702,7 @@
         <v>45736</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -56775,7 +56775,7 @@
         <v>46035</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -56853,7 +56853,7 @@
         <v>46163</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>

--- a/Översikt EDA.xlsx
+++ b/Översikt EDA.xlsx
@@ -601,7 +601,7 @@
         <v>45178</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -725,7 +725,7 @@
         <v>45726</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -843,7 +843,7 @@
         <v>44494</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -955,7 +955,7 @@
         <v>45090</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1070,7 +1070,7 @@
         <v>45306</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1188,7 +1188,7 @@
         <v>45154</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1298,7 +1298,7 @@
         <v>44791</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1406,7 +1406,7 @@
         <v>44740</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1518,7 +1518,7 @@
         <v>45407</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1626,7 +1626,7 @@
         <v>45358</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1737,7 +1737,7 @@
         <v>45754</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1848,7 +1848,7 @@
         <v>45293</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1963,7 +1963,7 @@
         <v>44916</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2074,7 +2074,7 @@
         <v>44868</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2180,7 +2180,7 @@
         <v>44865</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2286,7 +2286,7 @@
         <v>44888</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2396,7 +2396,7 @@
         <v>45243</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2502,7 +2502,7 @@
         <v>45310</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2608,7 +2608,7 @@
         <v>45575</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2714,7 +2714,7 @@
         <v>44970</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2820,7 +2820,7 @@
         <v>45091</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2930,7 +2930,7 @@
         <v>45856</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3036,7 +3036,7 @@
         <v>45426</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3142,7 +3142,7 @@
         <v>45315</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3252,7 +3252,7 @@
         <v>46290</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3358,7 +3358,7 @@
         <v>45545</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3464,7 +3464,7 @@
         <v>45376</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3573,7 +3573,7 @@
         <v>45257</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3678,7 +3678,7 @@
         <v>45721</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3783,7 +3783,7 @@
         <v>46092</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3888,7 +3888,7 @@
         <v>45244</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3993,7 +3993,7 @@
         <v>46269</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4102,7 +4102,7 @@
         <v>46269</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4212,7 +4212,7 @@
         <v>45243</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4317,7 +4317,7 @@
         <v>45532</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4422,7 +4422,7 @@
         <v>45432</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4527,7 +4527,7 @@
         <v>45777</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4641,7 +4641,7 @@
         <v>44579</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4751,7 +4751,7 @@
         <v>44889</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4824,7 +4824,7 @@
         <v>44683</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4897,7 +4897,7 @@
         <v>44810</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4970,7 +4970,7 @@
         <v>44529</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5043,7 +5043,7 @@
         <v>44712</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5116,7 +5116,7 @@
         <v>44479</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5189,7 +5189,7 @@
         <v>44852</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5262,7 +5262,7 @@
         <v>44479</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5335,7 +5335,7 @@
         <v>44889</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5408,7 +5408,7 @@
         <v>44608</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5486,7 +5486,7 @@
         <v>44582</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5559,7 +5559,7 @@
         <v>44582</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5632,7 +5632,7 @@
         <v>44851</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5705,7 +5705,7 @@
         <v>44538</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5778,7 +5778,7 @@
         <v>44740</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5851,7 +5851,7 @@
         <v>44837</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5924,7 +5924,7 @@
         <v>44816</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5997,7 +5997,7 @@
         <v>44712</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6070,7 +6070,7 @@
         <v>44532</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6143,7 +6143,7 @@
         <v>44874</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6216,7 +6216,7 @@
         <v>44529</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6289,7 +6289,7 @@
         <v>44722</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6362,7 +6362,7 @@
         <v>44586</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6435,7 +6435,7 @@
         <v>44685</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6508,7 +6508,7 @@
         <v>44809</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6581,7 +6581,7 @@
         <v>44858</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6654,7 +6654,7 @@
         <v>44491</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6727,7 +6727,7 @@
         <v>44670</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6800,7 +6800,7 @@
         <v>44659</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6873,7 +6873,7 @@
         <v>44740</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6946,7 +6946,7 @@
         <v>44510</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7019,7 +7019,7 @@
         <v>44733</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7092,7 +7092,7 @@
         <v>44853</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7165,7 +7165,7 @@
         <v>44557</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7243,7 +7243,7 @@
         <v>44546</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7316,7 +7316,7 @@
         <v>44817</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7389,7 +7389,7 @@
         <v>44614</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7462,7 +7462,7 @@
         <v>44883</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7535,7 +7535,7 @@
         <v>44874</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7608,7 +7608,7 @@
         <v>44874</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7681,7 +7681,7 @@
         <v>44515</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7759,7 +7759,7 @@
         <v>44799</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7832,7 +7832,7 @@
         <v>44881</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7905,7 +7905,7 @@
         <v>44881</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7978,7 +7978,7 @@
         <v>44588</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8051,7 +8051,7 @@
         <v>44581</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8124,7 +8124,7 @@
         <v>44868</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8197,7 +8197,7 @@
         <v>44705</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8270,7 +8270,7 @@
         <v>44560</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8348,7 +8348,7 @@
         <v>44573</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8421,7 +8421,7 @@
         <v>44477</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8494,7 +8494,7 @@
         <v>44614</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8567,7 +8567,7 @@
         <v>44714</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8640,7 +8640,7 @@
         <v>44877</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8713,7 +8713,7 @@
         <v>44491</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8786,7 +8786,7 @@
         <v>44852</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8859,7 +8859,7 @@
         <v>44469</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8932,7 +8932,7 @@
         <v>44662</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9005,7 +9005,7 @@
         <v>44584</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9078,7 +9078,7 @@
         <v>44643</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9151,7 +9151,7 @@
         <v>44614</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9224,7 +9224,7 @@
         <v>44726</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9297,7 +9297,7 @@
         <v>44818</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9370,7 +9370,7 @@
         <v>45775</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         <v>45041</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9516,7 +9516,7 @@
         <v>44834</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9594,7 +9594,7 @@
         <v>44865</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9667,7 +9667,7 @@
         <v>45733</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9740,7 +9740,7 @@
         <v>45719</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9813,7 +9813,7 @@
         <v>44908</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9886,7 +9886,7 @@
         <v>45195</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9959,7 +9959,7 @@
         <v>45310</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10032,7 +10032,7 @@
         <v>45763</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10105,7 +10105,7 @@
         <v>45092</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10178,7 +10178,7 @@
         <v>45092</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10251,7 +10251,7 @@
         <v>45229</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10324,7 +10324,7 @@
         <v>45554</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10397,7 +10397,7 @@
         <v>45549</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10470,7 +10470,7 @@
         <v>45456</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10543,7 +10543,7 @@
         <v>44799</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10616,7 +10616,7 @@
         <v>45301</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10694,7 +10694,7 @@
         <v>44956</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10767,7 +10767,7 @@
         <v>44901</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10840,7 +10840,7 @@
         <v>45390</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10913,7 +10913,7 @@
         <v>44894</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10986,7 +10986,7 @@
         <v>45426</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11059,7 +11059,7 @@
         <v>44865</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11132,7 +11132,7 @@
         <v>45477</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11205,7 +11205,7 @@
         <v>44483</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11278,7 +11278,7 @@
         <v>44956</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11351,7 +11351,7 @@
         <v>46013</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11424,7 +11424,7 @@
         <v>46016</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11497,7 +11497,7 @@
         <v>46016</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11570,7 +11570,7 @@
         <v>46016</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11643,7 +11643,7 @@
         <v>46016</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11716,7 +11716,7 @@
         <v>45883</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11789,7 +11789,7 @@
         <v>46016</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11862,7 +11862,7 @@
         <v>46016</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11935,7 +11935,7 @@
         <v>45576</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12008,7 +12008,7 @@
         <v>45582</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12081,7 +12081,7 @@
         <v>45110</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12154,7 +12154,7 @@
         <v>46021</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12227,7 +12227,7 @@
         <v>46021</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12305,7 +12305,7 @@
         <v>46029</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12378,7 +12378,7 @@
         <v>45450</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12451,7 +12451,7 @@
         <v>46029</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12524,7 +12524,7 @@
         <v>46029</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12597,7 +12597,7 @@
         <v>45294</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12670,7 +12670,7 @@
         <v>45796</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12743,7 +12743,7 @@
         <v>45278</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12816,7 +12816,7 @@
         <v>45491</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12889,7 +12889,7 @@
         <v>45532</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12962,7 +12962,7 @@
         <v>44943</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13035,7 +13035,7 @@
         <v>46029</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13108,7 +13108,7 @@
         <v>44602</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13181,7 +13181,7 @@
         <v>46031</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13254,7 +13254,7 @@
         <v>45544</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13327,7 +13327,7 @@
         <v>45176</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13400,7 +13400,7 @@
         <v>45583</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13473,7 +13473,7 @@
         <v>46031</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13546,7 +13546,7 @@
         <v>46035</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13619,7 +13619,7 @@
         <v>44845</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13692,7 +13692,7 @@
         <v>44625</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13765,7 +13765,7 @@
         <v>45891</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13843,7 +13843,7 @@
         <v>46042</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13916,7 +13916,7 @@
         <v>46041</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13989,7 +13989,7 @@
         <v>46041</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14062,7 +14062,7 @@
         <v>45897</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14135,7 +14135,7 @@
         <v>44911</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14208,7 +14208,7 @@
         <v>45897</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14286,7 +14286,7 @@
         <v>45897</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14364,7 +14364,7 @@
         <v>46043</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14437,7 +14437,7 @@
         <v>46048</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14510,7 +14510,7 @@
         <v>45903</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14583,7 +14583,7 @@
         <v>46050</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14656,7 +14656,7 @@
         <v>45903</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14729,7 +14729,7 @@
         <v>45903</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14802,7 +14802,7 @@
         <v>45135</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14875,7 +14875,7 @@
         <v>45903</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14948,7 +14948,7 @@
         <v>46050</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15021,7 +15021,7 @@
         <v>46050</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15094,7 +15094,7 @@
         <v>46050</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15167,7 +15167,7 @@
         <v>46055</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15240,7 +15240,7 @@
         <v>45355</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15313,7 +15313,7 @@
         <v>45910</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15386,7 +15386,7 @@
         <v>45358</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15459,7 +15459,7 @@
         <v>46055</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15532,7 +15532,7 @@
         <v>45559</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15605,7 +15605,7 @@
         <v>45749</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15678,7 +15678,7 @@
         <v>46059</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15751,7 +15751,7 @@
         <v>46059</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15824,7 +15824,7 @@
         <v>45435</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15897,7 +15897,7 @@
         <v>45691</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15970,7 +15970,7 @@
         <v>46062</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16043,7 +16043,7 @@
         <v>45603</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16116,7 +16116,7 @@
         <v>46062</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16189,7 +16189,7 @@
         <v>45918</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16267,7 +16267,7 @@
         <v>45910</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16340,7 +16340,7 @@
         <v>44881</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16418,7 +16418,7 @@
         <v>46064</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16491,7 +16491,7 @@
         <v>45803</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16564,7 +16564,7 @@
         <v>45920</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16637,7 +16637,7 @@
         <v>45028</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16710,7 +16710,7 @@
         <v>46064</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16783,7 +16783,7 @@
         <v>46066</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16856,7 +16856,7 @@
         <v>44896</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16929,7 +16929,7 @@
         <v>46069</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17002,7 +17002,7 @@
         <v>45924</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17075,7 +17075,7 @@
         <v>45924</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17148,7 +17148,7 @@
         <v>45924</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17221,7 +17221,7 @@
         <v>46069</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17294,7 +17294,7 @@
         <v>44942</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17367,7 +17367,7 @@
         <v>45140</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17440,7 +17440,7 @@
         <v>45929</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17513,7 +17513,7 @@
         <v>45929</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17586,7 +17586,7 @@
         <v>45929</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17659,7 +17659,7 @@
         <v>46083</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17732,7 +17732,7 @@
         <v>46083</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17805,7 +17805,7 @@
         <v>45929</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17878,7 +17878,7 @@
         <v>45754</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17951,7 +17951,7 @@
         <v>45805</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18029,7 +18029,7 @@
         <v>45502</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18102,7 +18102,7 @@
         <v>45624</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18175,7 +18175,7 @@
         <v>46084</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18248,7 +18248,7 @@
         <v>44966</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18326,7 +18326,7 @@
         <v>45600</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18399,7 +18399,7 @@
         <v>46085</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18472,7 +18472,7 @@
         <v>46085</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18545,7 +18545,7 @@
         <v>45378</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18618,7 +18618,7 @@
         <v>45310</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18691,7 +18691,7 @@
         <v>46085</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18764,7 +18764,7 @@
         <v>45541</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18837,7 +18837,7 @@
         <v>44641</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18910,7 +18910,7 @@
         <v>45726</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18983,7 +18983,7 @@
         <v>45152</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19056,7 +19056,7 @@
         <v>45152</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19129,7 +19129,7 @@
         <v>45936</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19207,7 +19207,7 @@
         <v>45058</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19280,7 +19280,7 @@
         <v>45888</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19353,7 +19353,7 @@
         <v>45936</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19431,7 +19431,7 @@
         <v>44915</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19504,7 +19504,7 @@
         <v>44915</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19577,7 +19577,7 @@
         <v>45210</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19650,7 +19650,7 @@
         <v>46090</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19728,7 +19728,7 @@
         <v>45722</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19801,7 +19801,7 @@
         <v>45936</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19874,7 +19874,7 @@
         <v>46092</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19947,7 +19947,7 @@
         <v>46092</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20020,7 +20020,7 @@
         <v>46092</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20093,7 +20093,7 @@
         <v>46092</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20166,7 +20166,7 @@
         <v>46092</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20239,7 +20239,7 @@
         <v>44659</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20312,7 +20312,7 @@
         <v>46092</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20385,7 +20385,7 @@
         <v>45623</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20458,7 +20458,7 @@
         <v>44986</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20531,7 +20531,7 @@
         <v>45580</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20604,7 +20604,7 @@
         <v>46099</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20677,7 +20677,7 @@
         <v>46099</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20750,7 +20750,7 @@
         <v>44901</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20823,7 +20823,7 @@
         <v>44614</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20896,7 +20896,7 @@
         <v>46100</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20974,7 +20974,7 @@
         <v>46101</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21047,7 +21047,7 @@
         <v>44746</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21120,7 +21120,7 @@
         <v>45950</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21198,7 +21198,7 @@
         <v>46104</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21271,7 +21271,7 @@
         <v>45628</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21344,7 +21344,7 @@
         <v>46107</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21417,7 +21417,7 @@
         <v>45098</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21490,7 +21490,7 @@
         <v>46108</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21563,7 +21563,7 @@
         <v>45021</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21641,7 +21641,7 @@
         <v>45084</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21714,7 +21714,7 @@
         <v>46108</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21787,7 +21787,7 @@
         <v>44700</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21865,7 +21865,7 @@
         <v>45742</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21938,7 +21938,7 @@
         <v>45957</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22011,7 +22011,7 @@
         <v>46119</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22084,7 +22084,7 @@
         <v>45600</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22157,7 +22157,7 @@
         <v>45579</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22230,7 +22230,7 @@
         <v>46119</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22303,7 +22303,7 @@
         <v>46119</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22376,7 +22376,7 @@
         <v>46120</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22449,7 +22449,7 @@
         <v>46070</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22522,7 +22522,7 @@
         <v>46070</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22595,7 +22595,7 @@
         <v>45434</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22668,7 +22668,7 @@
         <v>46124</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22741,7 +22741,7 @@
         <v>46124</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22814,7 +22814,7 @@
         <v>45037</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -22887,7 +22887,7 @@
         <v>45966</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -22960,7 +22960,7 @@
         <v>45603</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23033,7 +23033,7 @@
         <v>46127</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23106,7 +23106,7 @@
         <v>45609</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23179,7 +23179,7 @@
         <v>45583</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23252,7 +23252,7 @@
         <v>45968</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23325,7 +23325,7 @@
         <v>45971</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23398,7 +23398,7 @@
         <v>45971</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23476,7 +23476,7 @@
         <v>45971</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23549,7 +23549,7 @@
         <v>45971</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23627,7 +23627,7 @@
         <v>45971</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23700,7 +23700,7 @@
         <v>45758</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23773,7 +23773,7 @@
         <v>45275</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -23846,7 +23846,7 @@
         <v>45975</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -23919,7 +23919,7 @@
         <v>44482</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -23992,7 +23992,7 @@
         <v>45638</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24065,7 +24065,7 @@
         <v>45817</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24138,7 +24138,7 @@
         <v>44970</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24211,7 +24211,7 @@
         <v>45166</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24284,7 +24284,7 @@
         <v>44714</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24357,7 +24357,7 @@
         <v>44474</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24430,7 +24430,7 @@
         <v>45617</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24503,7 +24503,7 @@
         <v>45980</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24576,7 +24576,7 @@
         <v>45435</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24649,7 +24649,7 @@
         <v>44998</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24722,7 +24722,7 @@
         <v>44523</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -24795,7 +24795,7 @@
         <v>45614</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -24868,7 +24868,7 @@
         <v>45981</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -24941,7 +24941,7 @@
         <v>45981</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25014,7 +25014,7 @@
         <v>45714</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25087,7 +25087,7 @@
         <v>45981</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25160,7 +25160,7 @@
         <v>45981</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25233,7 +25233,7 @@
         <v>46031</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25306,7 +25306,7 @@
         <v>46135</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25379,7 +25379,7 @@
         <v>45267</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25452,7 +25452,7 @@
         <v>45646</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25525,7 +25525,7 @@
         <v>45443</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25598,7 +25598,7 @@
         <v>45629</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25671,7 +25671,7 @@
         <v>46135</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -25744,7 +25744,7 @@
         <v>45992</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -25817,7 +25817,7 @@
         <v>45980</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -25890,7 +25890,7 @@
         <v>45992</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -25963,7 +25963,7 @@
         <v>45614</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26036,7 +26036,7 @@
         <v>46135</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26109,7 +26109,7 @@
         <v>45994</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26182,7 +26182,7 @@
         <v>44665</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26255,7 +26255,7 @@
         <v>45856</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26328,7 +26328,7 @@
         <v>45856</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26401,7 +26401,7 @@
         <v>45992</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26474,7 +26474,7 @@
         <v>45994</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26547,7 +26547,7 @@
         <v>44979</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26620,7 +26620,7 @@
         <v>45995</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -26693,7 +26693,7 @@
         <v>45995</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -26766,7 +26766,7 @@
         <v>45733</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -26839,7 +26839,7 @@
         <v>46000</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -26912,7 +26912,7 @@
         <v>44865</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -26985,7 +26985,7 @@
         <v>45996</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27058,7 +27058,7 @@
         <v>45184</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27131,7 +27131,7 @@
         <v>45915</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27204,7 +27204,7 @@
         <v>45999</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27277,7 +27277,7 @@
         <v>45188</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27350,7 +27350,7 @@
         <v>46140</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27428,7 +27428,7 @@
         <v>46140</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27506,7 +27506,7 @@
         <v>45040</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27579,7 +27579,7 @@
         <v>45156</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -27652,7 +27652,7 @@
         <v>45671</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -27725,7 +27725,7 @@
         <v>46002</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -27798,7 +27798,7 @@
         <v>45818</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -27871,7 +27871,7 @@
         <v>45804</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -27944,7 +27944,7 @@
         <v>44839</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28017,7 +28017,7 @@
         <v>46002</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28090,7 +28090,7 @@
         <v>45691</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28163,7 +28163,7 @@
         <v>45224</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28241,7 +28241,7 @@
         <v>45590</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28314,7 +28314,7 @@
         <v>45818</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28387,7 +28387,7 @@
         <v>45818</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28460,7 +28460,7 @@
         <v>46140</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28533,7 +28533,7 @@
         <v>46140</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -28606,7 +28606,7 @@
         <v>46006</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -28679,7 +28679,7 @@
         <v>46007</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -28752,7 +28752,7 @@
         <v>46009</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -28825,7 +28825,7 @@
         <v>45224</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -28898,7 +28898,7 @@
         <v>45243</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -28971,7 +28971,7 @@
         <v>46010</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29044,7 +29044,7 @@
         <v>45873</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29117,7 +29117,7 @@
         <v>46010</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29190,7 +29190,7 @@
         <v>45758</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29263,7 +29263,7 @@
         <v>45733</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29336,7 +29336,7 @@
         <v>46104</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29409,7 +29409,7 @@
         <v>46013</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29482,7 +29482,7 @@
         <v>46013</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -29555,7 +29555,7 @@
         <v>45804</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -29628,7 +29628,7 @@
         <v>46140</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -29706,7 +29706,7 @@
         <v>45832</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -29779,7 +29779,7 @@
         <v>45642</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -29852,7 +29852,7 @@
         <v>45737</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -29925,7 +29925,7 @@
         <v>45197</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -29998,7 +29998,7 @@
         <v>45932</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30071,7 +30071,7 @@
         <v>45866</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30144,7 +30144,7 @@
         <v>44899</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30217,7 +30217,7 @@
         <v>44494</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30290,7 +30290,7 @@
         <v>45611</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30363,7 +30363,7 @@
         <v>45751</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30436,7 +30436,7 @@
         <v>45114</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30509,7 +30509,7 @@
         <v>45608</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -30582,7 +30582,7 @@
         <v>45245</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -30660,7 +30660,7 @@
         <v>45173</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -30733,7 +30733,7 @@
         <v>44790</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -30806,7 +30806,7 @@
         <v>45818</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -30879,7 +30879,7 @@
         <v>44858</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -30952,7 +30952,7 @@
         <v>45533</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31025,7 +31025,7 @@
         <v>45588</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31098,7 +31098,7 @@
         <v>46031</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31171,7 +31171,7 @@
         <v>45250</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31244,7 +31244,7 @@
         <v>44467</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31322,7 +31322,7 @@
         <v>44966</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31395,7 +31395,7 @@
         <v>45736</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31468,7 +31468,7 @@
         <v>45054</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -31541,7 +31541,7 @@
         <v>45811</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -31614,7 +31614,7 @@
         <v>45036</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -31687,7 +31687,7 @@
         <v>46146</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -31760,7 +31760,7 @@
         <v>44588</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -31833,7 +31833,7 @@
         <v>46147</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -31906,7 +31906,7 @@
         <v>46148</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -31979,7 +31979,7 @@
         <v>46148</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -32052,7 +32052,7 @@
         <v>46148</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32125,7 +32125,7 @@
         <v>44883</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32198,7 +32198,7 @@
         <v>46148</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32271,7 +32271,7 @@
         <v>45090</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -32344,7 +32344,7 @@
         <v>46148</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -32417,7 +32417,7 @@
         <v>46148</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -32490,7 +32490,7 @@
         <v>46147</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -32563,7 +32563,7 @@
         <v>45245</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -32641,7 +32641,7 @@
         <v>45153</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -32714,7 +32714,7 @@
         <v>44881</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -32787,7 +32787,7 @@
         <v>46149</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -32860,7 +32860,7 @@
         <v>45579</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -32933,7 +32933,7 @@
         <v>46153</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -33011,7 +33011,7 @@
         <v>46153</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -33089,7 +33089,7 @@
         <v>46154</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -33162,7 +33162,7 @@
         <v>46154</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -33240,7 +33240,7 @@
         <v>45090</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -33313,7 +33313,7 @@
         <v>45834</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -33386,7 +33386,7 @@
         <v>45835</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -33459,7 +33459,7 @@
         <v>45838</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -33532,7 +33532,7 @@
         <v>45040</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -33605,7 +33605,7 @@
         <v>45904</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -33678,7 +33678,7 @@
         <v>45089</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -33751,7 +33751,7 @@
         <v>45838</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -33824,7 +33824,7 @@
         <v>45054</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -33897,7 +33897,7 @@
         <v>45054</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -33970,7 +33970,7 @@
         <v>44798</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -34043,7 +34043,7 @@
         <v>45839</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -34116,7 +34116,7 @@
         <v>45839</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -34189,7 +34189,7 @@
         <v>45751</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -34262,7 +34262,7 @@
         <v>45539</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -34335,7 +34335,7 @@
         <v>45558</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -34408,7 +34408,7 @@
         <v>45841</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -34481,7 +34481,7 @@
         <v>44966</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -34554,7 +34554,7 @@
         <v>44966</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -34627,7 +34627,7 @@
         <v>44901</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -34700,7 +34700,7 @@
         <v>46163</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -34773,7 +34773,7 @@
         <v>46163</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -34846,7 +34846,7 @@
         <v>46163</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -34919,7 +34919,7 @@
         <v>45191</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -34992,7 +34992,7 @@
         <v>45336</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -35065,7 +35065,7 @@
         <v>45817</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -35138,7 +35138,7 @@
         <v>45253</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -35211,7 +35211,7 @@
         <v>46163</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -35284,7 +35284,7 @@
         <v>45588</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -35357,7 +35357,7 @@
         <v>45736</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -35430,7 +35430,7 @@
         <v>44951</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -35503,7 +35503,7 @@
         <v>45191</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -35576,7 +35576,7 @@
         <v>45061</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -35649,7 +35649,7 @@
         <v>45715</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -35722,7 +35722,7 @@
         <v>44537</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -35795,7 +35795,7 @@
         <v>45106</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -35868,7 +35868,7 @@
         <v>45848</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -35941,7 +35941,7 @@
         <v>45015</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -36014,7 +36014,7 @@
         <v>45015</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -36087,7 +36087,7 @@
         <v>46167</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -36160,7 +36160,7 @@
         <v>46167</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -36233,7 +36233,7 @@
         <v>44543</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -36306,7 +36306,7 @@
         <v>45142</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -36379,7 +36379,7 @@
         <v>45778</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -36452,7 +36452,7 @@
         <v>45856</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -36525,7 +36525,7 @@
         <v>45119</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -36598,7 +36598,7 @@
         <v>45146</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -36671,7 +36671,7 @@
         <v>45140</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -36744,7 +36744,7 @@
         <v>45467</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -36817,7 +36817,7 @@
         <v>45532</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -36890,7 +36890,7 @@
         <v>45149</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -36968,7 +36968,7 @@
         <v>46176</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -37041,7 +37041,7 @@
         <v>45477</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -37114,7 +37114,7 @@
         <v>45510</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -37187,7 +37187,7 @@
         <v>44991</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -37260,7 +37260,7 @@
         <v>46177</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -37333,7 +37333,7 @@
         <v>44546</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -37406,7 +37406,7 @@
         <v>45306</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -37479,7 +37479,7 @@
         <v>45084</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -37552,7 +37552,7 @@
         <v>45525</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -37625,7 +37625,7 @@
         <v>45475</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -37698,7 +37698,7 @@
         <v>45874</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -37771,7 +37771,7 @@
         <v>46178</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -37844,7 +37844,7 @@
         <v>45429</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -37917,7 +37917,7 @@
         <v>45654</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -37990,7 +37990,7 @@
         <v>45443</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -38063,7 +38063,7 @@
         <v>44970</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -38136,7 +38136,7 @@
         <v>45616</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -38209,7 +38209,7 @@
         <v>44911</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -38282,7 +38282,7 @@
         <v>45173</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -38355,7 +38355,7 @@
         <v>45541</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -38428,7 +38428,7 @@
         <v>44586</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -38501,7 +38501,7 @@
         <v>45106</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -38574,7 +38574,7 @@
         <v>45142</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -38647,7 +38647,7 @@
         <v>46195</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -38725,7 +38725,7 @@
         <v>45336</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -38798,7 +38798,7 @@
         <v>45271</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -38871,7 +38871,7 @@
         <v>46195</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -38949,7 +38949,7 @@
         <v>45204</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -39022,7 +39022,7 @@
         <v>45603</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -39095,7 +39095,7 @@
         <v>45552</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -39173,7 +39173,7 @@
         <v>46197</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -39251,7 +39251,7 @@
         <v>45061</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -39324,7 +39324,7 @@
         <v>46196</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -39397,7 +39397,7 @@
         <v>46196</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -39470,7 +39470,7 @@
         <v>45614</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -39543,7 +39543,7 @@
         <v>46199</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -39616,7 +39616,7 @@
         <v>46199</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -39689,7 +39689,7 @@
         <v>46199</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -39762,7 +39762,7 @@
         <v>45512</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -39835,7 +39835,7 @@
         <v>45204</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -39908,7 +39908,7 @@
         <v>46199</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -39981,7 +39981,7 @@
         <v>45054</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -40054,7 +40054,7 @@
         <v>46199</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -40127,7 +40127,7 @@
         <v>45629</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -40200,7 +40200,7 @@
         <v>46199</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -40273,7 +40273,7 @@
         <v>44581</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -40346,7 +40346,7 @@
         <v>45882</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -40419,7 +40419,7 @@
         <v>45882</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -40492,7 +40492,7 @@
         <v>46203</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -40565,7 +40565,7 @@
         <v>46203</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -40638,7 +40638,7 @@
         <v>45623</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -40711,7 +40711,7 @@
         <v>46203</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -40784,7 +40784,7 @@
         <v>44804</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -40857,7 +40857,7 @@
         <v>45246</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -40930,7 +40930,7 @@
         <v>44636</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -41003,7 +41003,7 @@
         <v>44629</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -41076,7 +41076,7 @@
         <v>46252</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -41149,7 +41149,7 @@
         <v>45091</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -41222,7 +41222,7 @@
         <v>45091</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -41295,7 +41295,7 @@
         <v>45091</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -41368,7 +41368,7 @@
         <v>45110</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -41441,7 +41441,7 @@
         <v>45714</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -41514,7 +41514,7 @@
         <v>44998</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -41587,7 +41587,7 @@
         <v>45104</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -41660,7 +41660,7 @@
         <v>44557</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -41733,7 +41733,7 @@
         <v>45176</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -41806,7 +41806,7 @@
         <v>46253</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -41879,7 +41879,7 @@
         <v>45231</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -41952,7 +41952,7 @@
         <v>45195</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -42025,7 +42025,7 @@
         <v>45111</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -42098,7 +42098,7 @@
         <v>44874</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -42171,7 +42171,7 @@
         <v>45197</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -42244,7 +42244,7 @@
         <v>45616</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -42317,7 +42317,7 @@
         <v>45245</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -42395,7 +42395,7 @@
         <v>45085</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -42468,7 +42468,7 @@
         <v>46217</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -42541,7 +42541,7 @@
         <v>46217</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -42614,7 +42614,7 @@
         <v>45253</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -42687,7 +42687,7 @@
         <v>46217</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -42760,7 +42760,7 @@
         <v>45685</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -42833,7 +42833,7 @@
         <v>46261</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -42911,7 +42911,7 @@
         <v>45173</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -42984,7 +42984,7 @@
         <v>45173</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -43057,7 +43057,7 @@
         <v>46262</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -43135,7 +43135,7 @@
         <v>46261</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -43213,7 +43213,7 @@
         <v>45159</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -43286,7 +43286,7 @@
         <v>44740</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -43359,7 +43359,7 @@
         <v>45175</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -43432,7 +43432,7 @@
         <v>45474</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -43505,7 +43505,7 @@
         <v>45300</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -43578,7 +43578,7 @@
         <v>45267</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -43651,7 +43651,7 @@
         <v>45279</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -43724,7 +43724,7 @@
         <v>46266</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -43797,7 +43797,7 @@
         <v>46266</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -43870,7 +43870,7 @@
         <v>45267</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -43943,7 +43943,7 @@
         <v>46267</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -44016,7 +44016,7 @@
         <v>45440</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -44089,7 +44089,7 @@
         <v>45723</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -44162,7 +44162,7 @@
         <v>45261</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -44235,7 +44235,7 @@
         <v>46269</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -44308,7 +44308,7 @@
         <v>45265</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -44381,7 +44381,7 @@
         <v>46269</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -44454,7 +44454,7 @@
         <v>45015</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -44527,7 +44527,7 @@
         <v>44840</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -44600,7 +44600,7 @@
         <v>44872</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -44673,7 +44673,7 @@
         <v>46274</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -44746,7 +44746,7 @@
         <v>45272</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -44819,7 +44819,7 @@
         <v>45301</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -44892,7 +44892,7 @@
         <v>46274</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -44965,7 +44965,7 @@
         <v>45089</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -45038,7 +45038,7 @@
         <v>45310</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -45111,7 +45111,7 @@
         <v>45274</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -45184,7 +45184,7 @@
         <v>45293</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -45257,7 +45257,7 @@
         <v>46233</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -45330,7 +45330,7 @@
         <v>45743</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -45403,7 +45403,7 @@
         <v>46275</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -45476,7 +45476,7 @@
         <v>45090</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -45549,7 +45549,7 @@
         <v>44798</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -45622,7 +45622,7 @@
         <v>46279</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -45695,7 +45695,7 @@
         <v>46237</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -45768,7 +45768,7 @@
         <v>46273</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -45841,7 +45841,7 @@
         <v>46280</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -45914,7 +45914,7 @@
         <v>46279</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -45987,7 +45987,7 @@
         <v>44693</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -46060,7 +46060,7 @@
         <v>45520</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -46133,7 +46133,7 @@
         <v>44896</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -46206,7 +46206,7 @@
         <v>45290</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -46279,7 +46279,7 @@
         <v>45290</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -46352,7 +46352,7 @@
         <v>45733</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -46425,7 +46425,7 @@
         <v>46238</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -46498,7 +46498,7 @@
         <v>44904</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -46571,7 +46571,7 @@
         <v>45546</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -46644,7 +46644,7 @@
         <v>45296</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -46717,7 +46717,7 @@
         <v>44575</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -46790,7 +46790,7 @@
         <v>44899</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -46863,7 +46863,7 @@
         <v>45680</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -46936,7 +46936,7 @@
         <v>46240</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -47009,7 +47009,7 @@
         <v>44470</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -47082,7 +47082,7 @@
         <v>44573</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -47155,7 +47155,7 @@
         <v>45736</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -47228,7 +47228,7 @@
         <v>45338</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -47301,7 +47301,7 @@
         <v>44998</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -47374,7 +47374,7 @@
         <v>44887</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -47447,7 +47447,7 @@
         <v>44476</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -47525,7 +47525,7 @@
         <v>45525</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -47598,7 +47598,7 @@
         <v>46052</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -47676,7 +47676,7 @@
         <v>44911</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -47749,7 +47749,7 @@
         <v>44911</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -47822,7 +47822,7 @@
         <v>46199</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -47895,7 +47895,7 @@
         <v>46245</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -47968,7 +47968,7 @@
         <v>45261</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -48041,7 +48041,7 @@
         <v>45975</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -48114,7 +48114,7 @@
         <v>46245</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -48187,7 +48187,7 @@
         <v>45553</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -48260,7 +48260,7 @@
         <v>46147</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -48333,7 +48333,7 @@
         <v>45161</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -48406,7 +48406,7 @@
         <v>44896</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -48479,7 +48479,7 @@
         <v>44683</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -48552,7 +48552,7 @@
         <v>44851</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -48625,7 +48625,7 @@
         <v>45412</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -48698,7 +48698,7 @@
         <v>46290</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -48771,7 +48771,7 @@
         <v>46290</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -48844,7 +48844,7 @@
         <v>45090</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -48917,7 +48917,7 @@
         <v>46247</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -48990,7 +48990,7 @@
         <v>46281</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -49063,7 +49063,7 @@
         <v>46289</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -49136,7 +49136,7 @@
         <v>46290</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -49214,7 +49214,7 @@
         <v>45016</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -49292,7 +49292,7 @@
         <v>44777</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -49365,7 +49365,7 @@
         <v>46247</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -49438,7 +49438,7 @@
         <v>46247</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -49511,7 +49511,7 @@
         <v>46290</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -49589,7 +49589,7 @@
         <v>46289</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -49662,7 +49662,7 @@
         <v>45231</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -49735,7 +49735,7 @@
         <v>45281</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -49808,7 +49808,7 @@
         <v>45498</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -49881,7 +49881,7 @@
         <v>45510</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -49954,7 +49954,7 @@
         <v>45510</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -50027,7 +50027,7 @@
         <v>44917</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -50105,7 +50105,7 @@
         <v>44918</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -50178,7 +50178,7 @@
         <v>45128</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -50251,7 +50251,7 @@
         <v>44596</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -50324,7 +50324,7 @@
         <v>45674</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -50397,7 +50397,7 @@
         <v>44602</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -50470,7 +50470,7 @@
         <v>44979</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -50543,7 +50543,7 @@
         <v>45694</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -50616,7 +50616,7 @@
         <v>44518</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -50689,7 +50689,7 @@
         <v>45176</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -50762,7 +50762,7 @@
         <v>45021</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -50835,7 +50835,7 @@
         <v>45071</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -50908,7 +50908,7 @@
         <v>45704</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -50981,7 +50981,7 @@
         <v>44470</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -51054,7 +51054,7 @@
         <v>45370</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -51127,7 +51127,7 @@
         <v>45090</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -51200,7 +51200,7 @@
         <v>45090</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -51273,7 +51273,7 @@
         <v>45090</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -51346,7 +51346,7 @@
         <v>45281</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -51419,7 +51419,7 @@
         <v>45281</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -51492,7 +51492,7 @@
         <v>45418</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -51565,7 +51565,7 @@
         <v>44916</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -51638,7 +51638,7 @@
         <v>44977</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -51711,7 +51711,7 @@
         <v>45621</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -51784,7 +51784,7 @@
         <v>44937</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -51857,7 +51857,7 @@
         <v>45432</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -51930,7 +51930,7 @@
         <v>45061</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -52003,7 +52003,7 @@
         <v>45162</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -52076,7 +52076,7 @@
         <v>45139</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -52149,7 +52149,7 @@
         <v>44966</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -52222,7 +52222,7 @@
         <v>45756</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -52295,7 +52295,7 @@
         <v>45090</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -52368,7 +52368,7 @@
         <v>45161</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -52441,7 +52441,7 @@
         <v>45520</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -52514,7 +52514,7 @@
         <v>44636</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -52587,7 +52587,7 @@
         <v>45203</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -52660,7 +52660,7 @@
         <v>45629</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -52733,7 +52733,7 @@
         <v>45308</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -52806,7 +52806,7 @@
         <v>45105</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -52879,7 +52879,7 @@
         <v>45727</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -52952,7 +52952,7 @@
         <v>45727</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -53025,7 +53025,7 @@
         <v>44776</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -53103,7 +53103,7 @@
         <v>45310</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -53176,7 +53176,7 @@
         <v>44998</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -53249,7 +53249,7 @@
         <v>45692</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -53322,7 +53322,7 @@
         <v>45161</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -53395,7 +53395,7 @@
         <v>45210</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -53468,7 +53468,7 @@
         <v>45307</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -53541,7 +53541,7 @@
         <v>45397</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -53614,7 +53614,7 @@
         <v>45184</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -53687,7 +53687,7 @@
         <v>45184</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -53760,7 +53760,7 @@
         <v>45273</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -53833,7 +53833,7 @@
         <v>45616</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -53906,7 +53906,7 @@
         <v>45392</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -53979,7 +53979,7 @@
         <v>45455</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -54052,7 +54052,7 @@
         <v>44935</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -54125,7 +54125,7 @@
         <v>45636</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -54203,7 +54203,7 @@
         <v>44867</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -54276,7 +54276,7 @@
         <v>45149</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -54354,7 +54354,7 @@
         <v>45680</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -54427,7 +54427,7 @@
         <v>45729</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -54500,7 +54500,7 @@
         <v>45482</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -54573,7 +54573,7 @@
         <v>45756</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -54646,7 +54646,7 @@
         <v>45756</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -54719,7 +54719,7 @@
         <v>45676</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -54792,7 +54792,7 @@
         <v>45152</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -54865,7 +54865,7 @@
         <v>44918</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -54938,7 +54938,7 @@
         <v>45221</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -55016,7 +55016,7 @@
         <v>45221</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -55094,7 +55094,7 @@
         <v>45226</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -55167,7 +55167,7 @@
         <v>45694</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -55240,7 +55240,7 @@
         <v>45245</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -55318,7 +55318,7 @@
         <v>45729</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -55391,7 +55391,7 @@
         <v>45252</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -55464,7 +55464,7 @@
         <v>45684</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -55537,7 +55537,7 @@
         <v>45525</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -55610,7 +55610,7 @@
         <v>45623</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -55683,7 +55683,7 @@
         <v>45692</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -55756,7 +55756,7 @@
         <v>45408</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -55829,7 +55829,7 @@
         <v>45189</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -55902,7 +55902,7 @@
         <v>44537</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -55975,7 +55975,7 @@
         <v>45775</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -56048,7 +56048,7 @@
         <v>45775</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -56121,7 +56121,7 @@
         <v>45777</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -56194,7 +56194,7 @@
         <v>45783</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -56267,7 +56267,7 @@
         <v>45567</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -56340,7 +56340,7 @@
         <v>45730</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -56413,7 +56413,7 @@
         <v>45629</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -56486,7 +56486,7 @@
         <v>45792</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -56559,7 +56559,7 @@
         <v>44579</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -56637,7 +56637,7 @@
         <v>44893</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -56715,7 +56715,7 @@
         <v>44893</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -56793,7 +56793,7 @@
         <v>44893</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -56871,7 +56871,7 @@
         <v>45731</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -56944,7 +56944,7 @@
         <v>45736</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -57017,7 +57017,7 @@
         <v>46035</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -57095,7 +57095,7 @@
         <v>46163</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>

--- a/Översikt EDA.xlsx
+++ b/Översikt EDA.xlsx
@@ -601,7 +601,7 @@
         <v>45178</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -725,7 +725,7 @@
         <v>45726</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -843,7 +843,7 @@
         <v>44494</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -955,7 +955,7 @@
         <v>45090</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1070,7 +1070,7 @@
         <v>45306</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1188,7 +1188,7 @@
         <v>45154</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1298,7 +1298,7 @@
         <v>44791</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1406,7 +1406,7 @@
         <v>44740</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1518,7 +1518,7 @@
         <v>45407</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1626,7 +1626,7 @@
         <v>45358</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1737,7 +1737,7 @@
         <v>45754</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1848,7 +1848,7 @@
         <v>45293</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1963,7 +1963,7 @@
         <v>44916</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2074,7 +2074,7 @@
         <v>44868</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2180,7 +2180,7 @@
         <v>44865</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2286,7 +2286,7 @@
         <v>44888</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2396,7 +2396,7 @@
         <v>45243</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2502,7 +2502,7 @@
         <v>45310</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2608,7 +2608,7 @@
         <v>45575</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2714,7 +2714,7 @@
         <v>44970</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2820,7 +2820,7 @@
         <v>45091</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2930,7 +2930,7 @@
         <v>45856</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3036,7 +3036,7 @@
         <v>45426</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3142,7 +3142,7 @@
         <v>45315</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3252,7 +3252,7 @@
         <v>46290</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3358,7 +3358,7 @@
         <v>45545</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3464,7 +3464,7 @@
         <v>45376</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3573,7 +3573,7 @@
         <v>45257</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3678,7 +3678,7 @@
         <v>45721</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3783,7 +3783,7 @@
         <v>46092</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3888,7 +3888,7 @@
         <v>45244</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3993,7 +3993,7 @@
         <v>46269</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4102,7 +4102,7 @@
         <v>46269</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4212,7 +4212,7 @@
         <v>45243</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4317,7 +4317,7 @@
         <v>45532</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4422,7 +4422,7 @@
         <v>45432</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4527,7 +4527,7 @@
         <v>45777</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4641,7 +4641,7 @@
         <v>44579</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4751,7 +4751,7 @@
         <v>44889</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4824,7 +4824,7 @@
         <v>44683</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4897,7 +4897,7 @@
         <v>44810</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4970,7 +4970,7 @@
         <v>44529</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5043,7 +5043,7 @@
         <v>44712</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5116,7 +5116,7 @@
         <v>44479</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5189,7 +5189,7 @@
         <v>44852</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5262,7 +5262,7 @@
         <v>44479</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5335,7 +5335,7 @@
         <v>44889</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5408,7 +5408,7 @@
         <v>44608</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5486,7 +5486,7 @@
         <v>44582</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5559,7 +5559,7 @@
         <v>44582</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5632,7 +5632,7 @@
         <v>44851</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5705,7 +5705,7 @@
         <v>44538</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5778,7 +5778,7 @@
         <v>44740</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5851,7 +5851,7 @@
         <v>44837</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5924,7 +5924,7 @@
         <v>44816</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5997,7 +5997,7 @@
         <v>44712</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6070,7 +6070,7 @@
         <v>44532</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6143,7 +6143,7 @@
         <v>44874</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6216,7 +6216,7 @@
         <v>44529</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6289,7 +6289,7 @@
         <v>44722</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6362,7 +6362,7 @@
         <v>44586</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6435,7 +6435,7 @@
         <v>44685</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6508,7 +6508,7 @@
         <v>44809</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6581,7 +6581,7 @@
         <v>44858</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6654,7 +6654,7 @@
         <v>44491</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6727,7 +6727,7 @@
         <v>44670</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6800,7 +6800,7 @@
         <v>44659</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6873,7 +6873,7 @@
         <v>44740</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6946,7 +6946,7 @@
         <v>44510</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7019,7 +7019,7 @@
         <v>44733</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7092,7 +7092,7 @@
         <v>44853</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7165,7 +7165,7 @@
         <v>44557</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7243,7 +7243,7 @@
         <v>44546</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7316,7 +7316,7 @@
         <v>44817</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7389,7 +7389,7 @@
         <v>44614</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7462,7 +7462,7 @@
         <v>44883</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7535,7 +7535,7 @@
         <v>44874</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7608,7 +7608,7 @@
         <v>44874</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7681,7 +7681,7 @@
         <v>44515</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7759,7 +7759,7 @@
         <v>44799</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7832,7 +7832,7 @@
         <v>44881</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7905,7 +7905,7 @@
         <v>44881</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7978,7 +7978,7 @@
         <v>44588</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8051,7 +8051,7 @@
         <v>44581</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8124,7 +8124,7 @@
         <v>44868</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8197,7 +8197,7 @@
         <v>44705</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8270,7 +8270,7 @@
         <v>44560</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8348,7 +8348,7 @@
         <v>44573</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8421,7 +8421,7 @@
         <v>44477</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8494,7 +8494,7 @@
         <v>44614</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8567,7 +8567,7 @@
         <v>44714</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8640,7 +8640,7 @@
         <v>44877</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8713,7 +8713,7 @@
         <v>44491</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8786,7 +8786,7 @@
         <v>44852</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8859,7 +8859,7 @@
         <v>44469</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8932,7 +8932,7 @@
         <v>44662</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9005,7 +9005,7 @@
         <v>44584</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9078,7 +9078,7 @@
         <v>44643</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9151,7 +9151,7 @@
         <v>44614</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9224,7 +9224,7 @@
         <v>44726</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9297,7 +9297,7 @@
         <v>44818</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9370,7 +9370,7 @@
         <v>45775</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         <v>45041</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9516,7 +9516,7 @@
         <v>44834</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9594,7 +9594,7 @@
         <v>44865</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9667,7 +9667,7 @@
         <v>45733</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9740,7 +9740,7 @@
         <v>45719</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9813,7 +9813,7 @@
         <v>44908</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9886,7 +9886,7 @@
         <v>45195</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9959,7 +9959,7 @@
         <v>45310</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10032,7 +10032,7 @@
         <v>45763</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10105,7 +10105,7 @@
         <v>45092</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10178,7 +10178,7 @@
         <v>45092</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10251,7 +10251,7 @@
         <v>45229</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10324,7 +10324,7 @@
         <v>45554</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10397,7 +10397,7 @@
         <v>45549</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10470,7 +10470,7 @@
         <v>45456</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10543,7 +10543,7 @@
         <v>44799</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10616,7 +10616,7 @@
         <v>45301</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10694,7 +10694,7 @@
         <v>44956</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10767,7 +10767,7 @@
         <v>44901</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10840,7 +10840,7 @@
         <v>45390</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10913,7 +10913,7 @@
         <v>44894</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10986,7 +10986,7 @@
         <v>45426</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11059,7 +11059,7 @@
         <v>44865</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11132,7 +11132,7 @@
         <v>45477</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11205,7 +11205,7 @@
         <v>44483</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11278,7 +11278,7 @@
         <v>44956</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11351,7 +11351,7 @@
         <v>46013</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11424,7 +11424,7 @@
         <v>46016</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11497,7 +11497,7 @@
         <v>46016</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11570,7 +11570,7 @@
         <v>46016</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11643,7 +11643,7 @@
         <v>46016</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11716,7 +11716,7 @@
         <v>45883</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11789,7 +11789,7 @@
         <v>46016</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11862,7 +11862,7 @@
         <v>46016</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11935,7 +11935,7 @@
         <v>45576</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12008,7 +12008,7 @@
         <v>45582</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12081,7 +12081,7 @@
         <v>45110</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12154,7 +12154,7 @@
         <v>46021</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12227,7 +12227,7 @@
         <v>46021</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12305,7 +12305,7 @@
         <v>46029</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12378,7 +12378,7 @@
         <v>45450</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12451,7 +12451,7 @@
         <v>46029</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12524,7 +12524,7 @@
         <v>46029</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12597,7 +12597,7 @@
         <v>45294</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12670,7 +12670,7 @@
         <v>45796</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12743,7 +12743,7 @@
         <v>45278</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12816,7 +12816,7 @@
         <v>45491</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12889,7 +12889,7 @@
         <v>45532</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12962,7 +12962,7 @@
         <v>44943</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13035,7 +13035,7 @@
         <v>46029</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13108,7 +13108,7 @@
         <v>44602</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13181,7 +13181,7 @@
         <v>46031</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13254,7 +13254,7 @@
         <v>45544</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13327,7 +13327,7 @@
         <v>45176</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13400,7 +13400,7 @@
         <v>45583</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13473,7 +13473,7 @@
         <v>46031</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13546,7 +13546,7 @@
         <v>46035</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13619,7 +13619,7 @@
         <v>44845</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13692,7 +13692,7 @@
         <v>44625</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13765,7 +13765,7 @@
         <v>45891</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13843,7 +13843,7 @@
         <v>46042</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13916,7 +13916,7 @@
         <v>46041</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13989,7 +13989,7 @@
         <v>46041</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14062,7 +14062,7 @@
         <v>45897</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14135,7 +14135,7 @@
         <v>44911</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14208,7 +14208,7 @@
         <v>45897</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14286,7 +14286,7 @@
         <v>45897</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14364,7 +14364,7 @@
         <v>46043</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14437,7 +14437,7 @@
         <v>46048</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14510,7 +14510,7 @@
         <v>45903</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14583,7 +14583,7 @@
         <v>46050</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14656,7 +14656,7 @@
         <v>45903</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14729,7 +14729,7 @@
         <v>45903</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14802,7 +14802,7 @@
         <v>45135</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14875,7 +14875,7 @@
         <v>45903</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14948,7 +14948,7 @@
         <v>46050</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15021,7 +15021,7 @@
         <v>46050</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15094,7 +15094,7 @@
         <v>46050</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15167,7 +15167,7 @@
         <v>46055</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15240,7 +15240,7 @@
         <v>45355</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15313,7 +15313,7 @@
         <v>45910</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15386,7 +15386,7 @@
         <v>45358</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15459,7 +15459,7 @@
         <v>46055</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15532,7 +15532,7 @@
         <v>45559</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15605,7 +15605,7 @@
         <v>45749</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15678,7 +15678,7 @@
         <v>46059</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15751,7 +15751,7 @@
         <v>46059</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15824,7 +15824,7 @@
         <v>45435</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15897,7 +15897,7 @@
         <v>45691</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15970,7 +15970,7 @@
         <v>46062</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16043,7 +16043,7 @@
         <v>45603</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16116,7 +16116,7 @@
         <v>46062</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16189,7 +16189,7 @@
         <v>45918</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16267,7 +16267,7 @@
         <v>45910</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16340,7 +16340,7 @@
         <v>44881</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16418,7 +16418,7 @@
         <v>46064</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16491,7 +16491,7 @@
         <v>45803</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16564,7 +16564,7 @@
         <v>45920</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16637,7 +16637,7 @@
         <v>45028</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16710,7 +16710,7 @@
         <v>46064</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16783,7 +16783,7 @@
         <v>46066</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16856,7 +16856,7 @@
         <v>44896</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16929,7 +16929,7 @@
         <v>46069</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17002,7 +17002,7 @@
         <v>45924</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17075,7 +17075,7 @@
         <v>45924</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17148,7 +17148,7 @@
         <v>45924</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17221,7 +17221,7 @@
         <v>46069</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17294,7 +17294,7 @@
         <v>44942</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17367,7 +17367,7 @@
         <v>45140</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17440,7 +17440,7 @@
         <v>45929</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17513,7 +17513,7 @@
         <v>45929</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17586,7 +17586,7 @@
         <v>45929</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17659,7 +17659,7 @@
         <v>46083</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17732,7 +17732,7 @@
         <v>46083</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17805,7 +17805,7 @@
         <v>45929</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17878,7 +17878,7 @@
         <v>45754</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17951,7 +17951,7 @@
         <v>45805</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18029,7 +18029,7 @@
         <v>45502</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18102,7 +18102,7 @@
         <v>45624</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18175,7 +18175,7 @@
         <v>46084</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18248,7 +18248,7 @@
         <v>44966</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18326,7 +18326,7 @@
         <v>45600</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18399,7 +18399,7 @@
         <v>46085</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18472,7 +18472,7 @@
         <v>46085</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18545,7 +18545,7 @@
         <v>45378</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18618,7 +18618,7 @@
         <v>45310</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18691,7 +18691,7 @@
         <v>46085</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18764,7 +18764,7 @@
         <v>45541</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18837,7 +18837,7 @@
         <v>44641</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18910,7 +18910,7 @@
         <v>45726</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18983,7 +18983,7 @@
         <v>45152</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19056,7 +19056,7 @@
         <v>45152</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19129,7 +19129,7 @@
         <v>45936</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19207,7 +19207,7 @@
         <v>45058</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19280,7 +19280,7 @@
         <v>45888</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19353,7 +19353,7 @@
         <v>45936</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19431,7 +19431,7 @@
         <v>44915</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19504,7 +19504,7 @@
         <v>44915</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19577,7 +19577,7 @@
         <v>45210</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19650,7 +19650,7 @@
         <v>46090</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19728,7 +19728,7 @@
         <v>45722</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19801,7 +19801,7 @@
         <v>45936</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19874,7 +19874,7 @@
         <v>46092</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19947,7 +19947,7 @@
         <v>46092</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20020,7 +20020,7 @@
         <v>46092</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20093,7 +20093,7 @@
         <v>46092</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20166,7 +20166,7 @@
         <v>46092</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20239,7 +20239,7 @@
         <v>44659</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20312,7 +20312,7 @@
         <v>46092</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20385,7 +20385,7 @@
         <v>45623</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20458,7 +20458,7 @@
         <v>44986</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20531,7 +20531,7 @@
         <v>45580</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20604,7 +20604,7 @@
         <v>46099</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20677,7 +20677,7 @@
         <v>46099</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20750,7 +20750,7 @@
         <v>44901</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20823,7 +20823,7 @@
         <v>44614</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20896,7 +20896,7 @@
         <v>46100</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20974,7 +20974,7 @@
         <v>46101</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21047,7 +21047,7 @@
         <v>44746</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21120,7 +21120,7 @@
         <v>45950</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21198,7 +21198,7 @@
         <v>46104</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21271,7 +21271,7 @@
         <v>45628</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21344,7 +21344,7 @@
         <v>46107</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21417,7 +21417,7 @@
         <v>45098</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21490,7 +21490,7 @@
         <v>46108</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21563,7 +21563,7 @@
         <v>45021</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21641,7 +21641,7 @@
         <v>45084</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21714,7 +21714,7 @@
         <v>46108</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21787,7 +21787,7 @@
         <v>44700</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21865,7 +21865,7 @@
         <v>45742</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21938,7 +21938,7 @@
         <v>45957</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22011,7 +22011,7 @@
         <v>46119</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22084,7 +22084,7 @@
         <v>45600</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22157,7 +22157,7 @@
         <v>45579</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22230,7 +22230,7 @@
         <v>46119</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22303,7 +22303,7 @@
         <v>46119</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22376,7 +22376,7 @@
         <v>46120</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22449,7 +22449,7 @@
         <v>46070</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22522,7 +22522,7 @@
         <v>46070</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22595,7 +22595,7 @@
         <v>45434</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22668,7 +22668,7 @@
         <v>46124</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22741,7 +22741,7 @@
         <v>46124</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22814,7 +22814,7 @@
         <v>45037</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -22887,7 +22887,7 @@
         <v>45966</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -22960,7 +22960,7 @@
         <v>45603</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23033,7 +23033,7 @@
         <v>46127</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23106,7 +23106,7 @@
         <v>45609</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23179,7 +23179,7 @@
         <v>45583</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23252,7 +23252,7 @@
         <v>45968</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23325,7 +23325,7 @@
         <v>45971</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23398,7 +23398,7 @@
         <v>45971</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23476,7 +23476,7 @@
         <v>45971</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23549,7 +23549,7 @@
         <v>45971</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23627,7 +23627,7 @@
         <v>45971</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23700,7 +23700,7 @@
         <v>45758</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23773,7 +23773,7 @@
         <v>45275</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -23846,7 +23846,7 @@
         <v>45975</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -23919,7 +23919,7 @@
         <v>44482</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -23992,7 +23992,7 @@
         <v>45638</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24065,7 +24065,7 @@
         <v>45817</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24138,7 +24138,7 @@
         <v>44970</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24211,7 +24211,7 @@
         <v>45166</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24284,7 +24284,7 @@
         <v>44714</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24357,7 +24357,7 @@
         <v>44474</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24430,7 +24430,7 @@
         <v>45617</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24503,7 +24503,7 @@
         <v>45980</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24576,7 +24576,7 @@
         <v>45435</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24649,7 +24649,7 @@
         <v>44998</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24722,7 +24722,7 @@
         <v>44523</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -24795,7 +24795,7 @@
         <v>45614</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -24868,7 +24868,7 @@
         <v>45981</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -24941,7 +24941,7 @@
         <v>45981</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25014,7 +25014,7 @@
         <v>45714</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25087,7 +25087,7 @@
         <v>45981</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25160,7 +25160,7 @@
         <v>45981</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25233,7 +25233,7 @@
         <v>46031</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25306,7 +25306,7 @@
         <v>46135</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25379,7 +25379,7 @@
         <v>45267</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25452,7 +25452,7 @@
         <v>45646</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25525,7 +25525,7 @@
         <v>45443</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25598,7 +25598,7 @@
         <v>45629</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25671,7 +25671,7 @@
         <v>46135</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -25744,7 +25744,7 @@
         <v>45992</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -25817,7 +25817,7 @@
         <v>45980</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -25890,7 +25890,7 @@
         <v>45992</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -25963,7 +25963,7 @@
         <v>45614</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26036,7 +26036,7 @@
         <v>46135</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26109,7 +26109,7 @@
         <v>45994</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26182,7 +26182,7 @@
         <v>44665</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26255,7 +26255,7 @@
         <v>45856</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26328,7 +26328,7 @@
         <v>45856</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26401,7 +26401,7 @@
         <v>45992</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26474,7 +26474,7 @@
         <v>45994</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26547,7 +26547,7 @@
         <v>44979</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26620,7 +26620,7 @@
         <v>45995</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -26693,7 +26693,7 @@
         <v>45995</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -26766,7 +26766,7 @@
         <v>45733</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -26839,7 +26839,7 @@
         <v>46000</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -26912,7 +26912,7 @@
         <v>44865</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -26985,7 +26985,7 @@
         <v>45996</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27058,7 +27058,7 @@
         <v>45184</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27131,7 +27131,7 @@
         <v>45915</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27204,7 +27204,7 @@
         <v>45999</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27277,7 +27277,7 @@
         <v>45188</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27350,7 +27350,7 @@
         <v>46140</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27428,7 +27428,7 @@
         <v>46140</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27506,7 +27506,7 @@
         <v>45040</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27579,7 +27579,7 @@
         <v>45156</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -27652,7 +27652,7 @@
         <v>45671</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -27725,7 +27725,7 @@
         <v>46002</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -27798,7 +27798,7 @@
         <v>45818</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -27871,7 +27871,7 @@
         <v>45804</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -27944,7 +27944,7 @@
         <v>44839</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28017,7 +28017,7 @@
         <v>46002</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28090,7 +28090,7 @@
         <v>45691</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28163,7 +28163,7 @@
         <v>45224</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28241,7 +28241,7 @@
         <v>45590</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28314,7 +28314,7 @@
         <v>45818</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28387,7 +28387,7 @@
         <v>45818</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28460,7 +28460,7 @@
         <v>46140</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28533,7 +28533,7 @@
         <v>46140</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -28606,7 +28606,7 @@
         <v>46006</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -28679,7 +28679,7 @@
         <v>46007</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -28752,7 +28752,7 @@
         <v>46009</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -28825,7 +28825,7 @@
         <v>45224</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -28898,7 +28898,7 @@
         <v>45243</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -28971,7 +28971,7 @@
         <v>46010</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29044,7 +29044,7 @@
         <v>45873</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29117,7 +29117,7 @@
         <v>46010</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29190,7 +29190,7 @@
         <v>45758</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29263,7 +29263,7 @@
         <v>45733</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29336,7 +29336,7 @@
         <v>46104</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29409,7 +29409,7 @@
         <v>46013</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29482,7 +29482,7 @@
         <v>46013</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -29555,7 +29555,7 @@
         <v>45804</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -29628,7 +29628,7 @@
         <v>46140</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -29706,7 +29706,7 @@
         <v>45832</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -29779,7 +29779,7 @@
         <v>45642</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -29852,7 +29852,7 @@
         <v>45737</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -29925,7 +29925,7 @@
         <v>45197</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -29998,7 +29998,7 @@
         <v>45932</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30071,7 +30071,7 @@
         <v>45866</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30144,7 +30144,7 @@
         <v>44899</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30217,7 +30217,7 @@
         <v>44494</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30290,7 +30290,7 @@
         <v>45611</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30363,7 +30363,7 @@
         <v>45751</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30436,7 +30436,7 @@
         <v>45114</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30509,7 +30509,7 @@
         <v>45608</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -30582,7 +30582,7 @@
         <v>45245</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -30660,7 +30660,7 @@
         <v>45173</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -30733,7 +30733,7 @@
         <v>44790</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -30806,7 +30806,7 @@
         <v>45818</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -30879,7 +30879,7 @@
         <v>44858</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -30952,7 +30952,7 @@
         <v>45533</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31025,7 +31025,7 @@
         <v>45588</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31098,7 +31098,7 @@
         <v>46031</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31171,7 +31171,7 @@
         <v>45250</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31244,7 +31244,7 @@
         <v>44467</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31322,7 +31322,7 @@
         <v>44966</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31395,7 +31395,7 @@
         <v>45736</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31468,7 +31468,7 @@
         <v>45054</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -31541,7 +31541,7 @@
         <v>45811</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -31614,7 +31614,7 @@
         <v>45036</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -31687,7 +31687,7 @@
         <v>46146</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -31760,7 +31760,7 @@
         <v>44588</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -31833,7 +31833,7 @@
         <v>46147</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -31906,7 +31906,7 @@
         <v>46148</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -31979,7 +31979,7 @@
         <v>46148</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -32052,7 +32052,7 @@
         <v>46148</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32125,7 +32125,7 @@
         <v>44883</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32198,7 +32198,7 @@
         <v>46148</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32271,7 +32271,7 @@
         <v>45090</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -32344,7 +32344,7 @@
         <v>46148</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -32417,7 +32417,7 @@
         <v>46148</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -32490,7 +32490,7 @@
         <v>46147</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -32563,7 +32563,7 @@
         <v>45245</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -32641,7 +32641,7 @@
         <v>45153</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -32714,7 +32714,7 @@
         <v>44881</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -32787,7 +32787,7 @@
         <v>46149</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -32860,7 +32860,7 @@
         <v>45579</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -32933,7 +32933,7 @@
         <v>46153</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -33011,7 +33011,7 @@
         <v>46153</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -33089,7 +33089,7 @@
         <v>46154</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -33162,7 +33162,7 @@
         <v>46154</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -33240,7 +33240,7 @@
         <v>45090</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -33313,7 +33313,7 @@
         <v>45834</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -33386,7 +33386,7 @@
         <v>45835</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -33459,7 +33459,7 @@
         <v>45838</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -33532,7 +33532,7 @@
         <v>45040</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -33605,7 +33605,7 @@
         <v>45904</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -33678,7 +33678,7 @@
         <v>45089</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -33751,7 +33751,7 @@
         <v>45838</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -33824,7 +33824,7 @@
         <v>45054</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -33897,7 +33897,7 @@
         <v>45054</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -33970,7 +33970,7 @@
         <v>44798</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -34043,7 +34043,7 @@
         <v>45839</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -34116,7 +34116,7 @@
         <v>45839</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -34189,7 +34189,7 @@
         <v>45751</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -34262,7 +34262,7 @@
         <v>45539</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -34335,7 +34335,7 @@
         <v>45558</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -34408,7 +34408,7 @@
         <v>45841</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -34481,7 +34481,7 @@
         <v>44966</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -34554,7 +34554,7 @@
         <v>44966</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -34627,7 +34627,7 @@
         <v>44901</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -34700,7 +34700,7 @@
         <v>46163</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -34773,7 +34773,7 @@
         <v>46163</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -34846,7 +34846,7 @@
         <v>46163</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -34919,7 +34919,7 @@
         <v>45191</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -34992,7 +34992,7 @@
         <v>45336</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -35065,7 +35065,7 @@
         <v>45817</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -35138,7 +35138,7 @@
         <v>45253</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -35211,7 +35211,7 @@
         <v>46163</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -35284,7 +35284,7 @@
         <v>45588</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -35357,7 +35357,7 @@
         <v>45736</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -35430,7 +35430,7 @@
         <v>44951</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -35503,7 +35503,7 @@
         <v>45191</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -35576,7 +35576,7 @@
         <v>45061</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -35649,7 +35649,7 @@
         <v>45715</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -35722,7 +35722,7 @@
         <v>44537</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -35795,7 +35795,7 @@
         <v>45106</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -35868,7 +35868,7 @@
         <v>45848</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -35941,7 +35941,7 @@
         <v>45015</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -36014,7 +36014,7 @@
         <v>45015</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -36087,7 +36087,7 @@
         <v>46167</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -36160,7 +36160,7 @@
         <v>46167</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -36233,7 +36233,7 @@
         <v>44543</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -36306,7 +36306,7 @@
         <v>45142</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -36379,7 +36379,7 @@
         <v>45778</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -36452,7 +36452,7 @@
         <v>45856</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -36525,7 +36525,7 @@
         <v>45119</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -36598,7 +36598,7 @@
         <v>45146</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -36671,7 +36671,7 @@
         <v>45140</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -36744,7 +36744,7 @@
         <v>45467</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -36817,7 +36817,7 @@
         <v>45532</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -36890,7 +36890,7 @@
         <v>45149</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -36968,7 +36968,7 @@
         <v>46176</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -37041,7 +37041,7 @@
         <v>45477</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -37114,7 +37114,7 @@
         <v>45510</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -37187,7 +37187,7 @@
         <v>44991</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -37260,7 +37260,7 @@
         <v>46177</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -37333,7 +37333,7 @@
         <v>44546</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -37406,7 +37406,7 @@
         <v>45306</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -37479,7 +37479,7 @@
         <v>45084</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -37552,7 +37552,7 @@
         <v>45525</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -37625,7 +37625,7 @@
         <v>45475</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -37698,7 +37698,7 @@
         <v>45874</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -37771,7 +37771,7 @@
         <v>46178</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -37844,7 +37844,7 @@
         <v>45429</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -37917,7 +37917,7 @@
         <v>45654</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -37990,7 +37990,7 @@
         <v>45443</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -38063,7 +38063,7 @@
         <v>44970</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -38136,7 +38136,7 @@
         <v>45616</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -38209,7 +38209,7 @@
         <v>44911</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -38282,7 +38282,7 @@
         <v>45173</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -38355,7 +38355,7 @@
         <v>45541</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -38428,7 +38428,7 @@
         <v>44586</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -38501,7 +38501,7 @@
         <v>45106</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -38574,7 +38574,7 @@
         <v>45142</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -38647,7 +38647,7 @@
         <v>46195</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -38725,7 +38725,7 @@
         <v>45336</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -38798,7 +38798,7 @@
         <v>45271</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -38871,7 +38871,7 @@
         <v>46195</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -38949,7 +38949,7 @@
         <v>45204</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -39022,7 +39022,7 @@
         <v>45603</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -39095,7 +39095,7 @@
         <v>45552</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -39173,7 +39173,7 @@
         <v>46197</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -39251,7 +39251,7 @@
         <v>45061</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -39324,7 +39324,7 @@
         <v>46196</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -39397,7 +39397,7 @@
         <v>46196</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -39470,7 +39470,7 @@
         <v>45614</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -39543,7 +39543,7 @@
         <v>46199</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -39616,7 +39616,7 @@
         <v>46199</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -39689,7 +39689,7 @@
         <v>46199</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -39762,7 +39762,7 @@
         <v>45512</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -39835,7 +39835,7 @@
         <v>45204</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -39908,7 +39908,7 @@
         <v>46199</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -39981,7 +39981,7 @@
         <v>45054</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -40054,7 +40054,7 @@
         <v>46199</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -40127,7 +40127,7 @@
         <v>45629</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -40200,7 +40200,7 @@
         <v>46199</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -40273,7 +40273,7 @@
         <v>44581</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -40346,7 +40346,7 @@
         <v>45882</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -40419,7 +40419,7 @@
         <v>45882</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -40492,7 +40492,7 @@
         <v>46203</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -40565,7 +40565,7 @@
         <v>46203</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -40638,7 +40638,7 @@
         <v>45623</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -40711,7 +40711,7 @@
         <v>46203</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -40784,7 +40784,7 @@
         <v>44804</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -40857,7 +40857,7 @@
         <v>45246</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -40930,7 +40930,7 @@
         <v>44636</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -41003,7 +41003,7 @@
         <v>44629</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -41076,7 +41076,7 @@
         <v>46252</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -41149,7 +41149,7 @@
         <v>45091</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -41222,7 +41222,7 @@
         <v>45091</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -41295,7 +41295,7 @@
         <v>45091</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -41368,7 +41368,7 @@
         <v>45110</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -41441,7 +41441,7 @@
         <v>45714</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -41514,7 +41514,7 @@
         <v>44998</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -41587,7 +41587,7 @@
         <v>45104</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -41660,7 +41660,7 @@
         <v>44557</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -41733,7 +41733,7 @@
         <v>45176</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -41806,7 +41806,7 @@
         <v>46253</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -41879,7 +41879,7 @@
         <v>45231</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -41952,7 +41952,7 @@
         <v>45195</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -42025,7 +42025,7 @@
         <v>45111</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -42098,7 +42098,7 @@
         <v>44874</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -42171,7 +42171,7 @@
         <v>45197</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -42244,7 +42244,7 @@
         <v>45616</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -42317,7 +42317,7 @@
         <v>45245</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -42395,7 +42395,7 @@
         <v>45085</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -42468,7 +42468,7 @@
         <v>46217</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -42541,7 +42541,7 @@
         <v>46217</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -42614,7 +42614,7 @@
         <v>45253</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -42687,7 +42687,7 @@
         <v>46217</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -42760,7 +42760,7 @@
         <v>45685</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -42833,7 +42833,7 @@
         <v>46261</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -42911,7 +42911,7 @@
         <v>45173</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -42984,7 +42984,7 @@
         <v>45173</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -43057,7 +43057,7 @@
         <v>46262</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -43135,7 +43135,7 @@
         <v>46261</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -43213,7 +43213,7 @@
         <v>45159</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -43286,7 +43286,7 @@
         <v>44740</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -43359,7 +43359,7 @@
         <v>45175</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -43432,7 +43432,7 @@
         <v>45474</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -43505,7 +43505,7 @@
         <v>45300</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -43578,7 +43578,7 @@
         <v>45267</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -43651,7 +43651,7 @@
         <v>45279</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -43724,7 +43724,7 @@
         <v>46266</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -43797,7 +43797,7 @@
         <v>46266</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -43870,7 +43870,7 @@
         <v>45267</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -43943,7 +43943,7 @@
         <v>46267</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -44016,7 +44016,7 @@
         <v>45440</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -44089,7 +44089,7 @@
         <v>45723</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -44162,7 +44162,7 @@
         <v>45261</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -44235,7 +44235,7 @@
         <v>46269</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -44308,7 +44308,7 @@
         <v>45265</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -44381,7 +44381,7 @@
         <v>46269</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -44454,7 +44454,7 @@
         <v>45015</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -44527,7 +44527,7 @@
         <v>44840</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -44600,7 +44600,7 @@
         <v>44872</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -44673,7 +44673,7 @@
         <v>46274</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -44746,7 +44746,7 @@
         <v>45272</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -44819,7 +44819,7 @@
         <v>45301</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -44892,7 +44892,7 @@
         <v>46274</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -44965,7 +44965,7 @@
         <v>45089</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -45038,7 +45038,7 @@
         <v>45310</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -45111,7 +45111,7 @@
         <v>45274</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -45184,7 +45184,7 @@
         <v>45293</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -45257,7 +45257,7 @@
         <v>46233</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -45330,7 +45330,7 @@
         <v>45743</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -45403,7 +45403,7 @@
         <v>46275</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -45476,7 +45476,7 @@
         <v>45090</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -45549,7 +45549,7 @@
         <v>44798</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -45622,7 +45622,7 @@
         <v>46279</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -45695,7 +45695,7 @@
         <v>46237</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -45768,7 +45768,7 @@
         <v>46273</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -45841,7 +45841,7 @@
         <v>46280</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -45914,7 +45914,7 @@
         <v>46279</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -45987,7 +45987,7 @@
         <v>44693</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -46060,7 +46060,7 @@
         <v>45520</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -46133,7 +46133,7 @@
         <v>44896</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -46206,7 +46206,7 @@
         <v>45290</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -46279,7 +46279,7 @@
         <v>45290</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -46352,7 +46352,7 @@
         <v>45733</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -46425,7 +46425,7 @@
         <v>46238</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -46498,7 +46498,7 @@
         <v>44904</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -46571,7 +46571,7 @@
         <v>45546</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -46644,7 +46644,7 @@
         <v>45296</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -46717,7 +46717,7 @@
         <v>44575</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -46790,7 +46790,7 @@
         <v>44899</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -46863,7 +46863,7 @@
         <v>45680</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -46936,7 +46936,7 @@
         <v>46240</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -47009,7 +47009,7 @@
         <v>44470</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -47082,7 +47082,7 @@
         <v>44573</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -47155,7 +47155,7 @@
         <v>45736</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -47228,7 +47228,7 @@
         <v>45338</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -47301,7 +47301,7 @@
         <v>44998</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -47374,7 +47374,7 @@
         <v>44887</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -47447,7 +47447,7 @@
         <v>44476</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -47525,7 +47525,7 @@
         <v>45525</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -47598,7 +47598,7 @@
         <v>46052</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -47676,7 +47676,7 @@
         <v>44911</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -47749,7 +47749,7 @@
         <v>44911</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -47822,7 +47822,7 @@
         <v>46199</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -47895,7 +47895,7 @@
         <v>46245</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -47968,7 +47968,7 @@
         <v>45261</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -48041,7 +48041,7 @@
         <v>45975</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -48114,7 +48114,7 @@
         <v>46245</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -48187,7 +48187,7 @@
         <v>45553</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -48260,7 +48260,7 @@
         <v>46147</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -48333,7 +48333,7 @@
         <v>45161</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -48406,7 +48406,7 @@
         <v>44896</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -48479,7 +48479,7 @@
         <v>44683</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -48552,7 +48552,7 @@
         <v>44851</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -48625,7 +48625,7 @@
         <v>45412</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -48698,7 +48698,7 @@
         <v>46290</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -48771,7 +48771,7 @@
         <v>46290</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -48844,7 +48844,7 @@
         <v>45090</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -48917,7 +48917,7 @@
         <v>46247</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -48990,7 +48990,7 @@
         <v>46281</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -49063,7 +49063,7 @@
         <v>46289</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -49136,7 +49136,7 @@
         <v>46290</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -49214,7 +49214,7 @@
         <v>45016</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -49292,7 +49292,7 @@
         <v>44777</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -49365,7 +49365,7 @@
         <v>46247</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -49438,7 +49438,7 @@
         <v>46247</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -49511,7 +49511,7 @@
         <v>46290</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -49589,7 +49589,7 @@
         <v>46289</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -49662,7 +49662,7 @@
         <v>45231</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -49735,7 +49735,7 @@
         <v>45281</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -49808,7 +49808,7 @@
         <v>45498</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -49881,7 +49881,7 @@
         <v>45510</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -49954,7 +49954,7 @@
         <v>45510</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -50027,7 +50027,7 @@
         <v>44917</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -50105,7 +50105,7 @@
         <v>44918</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -50178,7 +50178,7 @@
         <v>45128</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -50251,7 +50251,7 @@
         <v>44596</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -50324,7 +50324,7 @@
         <v>45674</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -50397,7 +50397,7 @@
         <v>44602</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -50470,7 +50470,7 @@
         <v>44979</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -50543,7 +50543,7 @@
         <v>45694</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -50616,7 +50616,7 @@
         <v>44518</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -50689,7 +50689,7 @@
         <v>45176</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -50762,7 +50762,7 @@
         <v>45021</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -50835,7 +50835,7 @@
         <v>45071</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -50908,7 +50908,7 @@
         <v>45704</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -50981,7 +50981,7 @@
         <v>44470</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -51054,7 +51054,7 @@
         <v>45370</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -51127,7 +51127,7 @@
         <v>45090</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -51200,7 +51200,7 @@
         <v>45090</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -51273,7 +51273,7 @@
         <v>45090</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -51346,7 +51346,7 @@
         <v>45281</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -51419,7 +51419,7 @@
         <v>45281</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -51492,7 +51492,7 @@
         <v>45418</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -51565,7 +51565,7 @@
         <v>44916</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -51638,7 +51638,7 @@
         <v>44977</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -51711,7 +51711,7 @@
         <v>45621</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -51784,7 +51784,7 @@
         <v>44937</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -51857,7 +51857,7 @@
         <v>45432</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -51930,7 +51930,7 @@
         <v>45061</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -52003,7 +52003,7 @@
         <v>45162</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -52076,7 +52076,7 @@
         <v>45139</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -52149,7 +52149,7 @@
         <v>44966</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -52222,7 +52222,7 @@
         <v>45756</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -52295,7 +52295,7 @@
         <v>45090</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -52368,7 +52368,7 @@
         <v>45161</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -52441,7 +52441,7 @@
         <v>45520</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -52514,7 +52514,7 @@
         <v>44636</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -52587,7 +52587,7 @@
         <v>45203</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -52660,7 +52660,7 @@
         <v>45629</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -52733,7 +52733,7 @@
         <v>45308</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -52806,7 +52806,7 @@
         <v>45105</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -52879,7 +52879,7 @@
         <v>45727</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -52952,7 +52952,7 @@
         <v>45727</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -53025,7 +53025,7 @@
         <v>44776</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -53103,7 +53103,7 @@
         <v>45310</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -53176,7 +53176,7 @@
         <v>44998</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -53249,7 +53249,7 @@
         <v>45692</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -53322,7 +53322,7 @@
         <v>45161</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -53395,7 +53395,7 @@
         <v>45210</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -53468,7 +53468,7 @@
         <v>45307</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -53541,7 +53541,7 @@
         <v>45397</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -53614,7 +53614,7 @@
         <v>45184</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -53687,7 +53687,7 @@
         <v>45184</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -53760,7 +53760,7 @@
         <v>45273</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -53833,7 +53833,7 @@
         <v>45616</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -53906,7 +53906,7 @@
         <v>45392</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -53979,7 +53979,7 @@
         <v>45455</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -54052,7 +54052,7 @@
         <v>44935</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -54125,7 +54125,7 @@
         <v>45636</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -54203,7 +54203,7 @@
         <v>44867</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -54276,7 +54276,7 @@
         <v>45149</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -54354,7 +54354,7 @@
         <v>45680</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -54427,7 +54427,7 @@
         <v>45729</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -54500,7 +54500,7 @@
         <v>45482</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -54573,7 +54573,7 @@
         <v>45756</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -54646,7 +54646,7 @@
         <v>45756</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -54719,7 +54719,7 @@
         <v>45676</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -54792,7 +54792,7 @@
         <v>45152</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -54865,7 +54865,7 @@
         <v>44918</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -54938,7 +54938,7 @@
         <v>45221</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -55016,7 +55016,7 @@
         <v>45221</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -55094,7 +55094,7 @@
         <v>45226</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -55167,7 +55167,7 @@
         <v>45694</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -55240,7 +55240,7 @@
         <v>45245</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -55318,7 +55318,7 @@
         <v>45729</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -55391,7 +55391,7 @@
         <v>45252</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -55464,7 +55464,7 @@
         <v>45684</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -55537,7 +55537,7 @@
         <v>45525</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -55610,7 +55610,7 @@
         <v>45623</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -55683,7 +55683,7 @@
         <v>45692</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -55756,7 +55756,7 @@
         <v>45408</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -55829,7 +55829,7 @@
         <v>45189</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -55902,7 +55902,7 @@
         <v>44537</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -55975,7 +55975,7 @@
         <v>45775</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -56048,7 +56048,7 @@
         <v>45775</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -56121,7 +56121,7 @@
         <v>45777</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -56194,7 +56194,7 @@
         <v>45783</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -56267,7 +56267,7 @@
         <v>45567</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -56340,7 +56340,7 @@
         <v>45730</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -56413,7 +56413,7 @@
         <v>45629</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -56486,7 +56486,7 @@
         <v>45792</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -56559,7 +56559,7 @@
         <v>44579</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -56637,7 +56637,7 @@
         <v>44893</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -56715,7 +56715,7 @@
         <v>44893</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -56793,7 +56793,7 @@
         <v>44893</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -56871,7 +56871,7 @@
         <v>45731</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -56944,7 +56944,7 @@
         <v>45736</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -57017,7 +57017,7 @@
         <v>46035</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -57095,7 +57095,7 @@
         <v>46163</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>

--- a/Översikt EDA.xlsx
+++ b/Översikt EDA.xlsx
@@ -601,7 +601,7 @@
         <v>45178</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -725,7 +725,7 @@
         <v>45726</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -843,7 +843,7 @@
         <v>44494</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -955,7 +955,7 @@
         <v>45090</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1070,7 +1070,7 @@
         <v>45306</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1188,7 +1188,7 @@
         <v>45154</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1298,7 +1298,7 @@
         <v>44791</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1406,7 +1406,7 @@
         <v>44740</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1518,7 +1518,7 @@
         <v>45407</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1626,7 +1626,7 @@
         <v>45754</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1737,7 +1737,7 @@
         <v>45293</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1852,7 +1852,7 @@
         <v>45358</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1963,7 +1963,7 @@
         <v>44916</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2074,7 +2074,7 @@
         <v>44868</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2180,7 +2180,7 @@
         <v>44865</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2286,7 +2286,7 @@
         <v>44888</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2396,7 +2396,7 @@
         <v>45575</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2502,7 +2502,7 @@
         <v>45243</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2608,7 +2608,7 @@
         <v>45091</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2718,7 +2718,7 @@
         <v>45856</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2824,7 +2824,7 @@
         <v>45315</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2934,7 +2934,7 @@
         <v>44970</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3040,7 +3040,7 @@
         <v>45310</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3146,7 +3146,7 @@
         <v>45426</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3252,7 +3252,7 @@
         <v>46290</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3358,7 +3358,7 @@
         <v>45545</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3464,7 +3464,7 @@
         <v>45721</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3569,7 +3569,7 @@
         <v>45257</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3674,7 +3674,7 @@
         <v>45532</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3779,7 +3779,7 @@
         <v>46092</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3884,7 +3884,7 @@
         <v>45376</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3993,7 +3993,7 @@
         <v>45243</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4098,7 +4098,7 @@
         <v>45432</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4203,7 +4203,7 @@
         <v>46269</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4313,7 +4313,7 @@
         <v>46269</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4422,7 +4422,7 @@
         <v>45244</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4527,7 +4527,7 @@
         <v>45777</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4641,7 +4641,7 @@
         <v>44579</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4751,7 +4751,7 @@
         <v>44889</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4824,7 +4824,7 @@
         <v>44683</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4897,7 +4897,7 @@
         <v>44810</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4970,7 +4970,7 @@
         <v>44529</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5043,7 +5043,7 @@
         <v>44712</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5116,7 +5116,7 @@
         <v>44479</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5189,7 +5189,7 @@
         <v>44852</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5262,7 +5262,7 @@
         <v>44479</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5335,7 +5335,7 @@
         <v>44889</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5408,7 +5408,7 @@
         <v>44608</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5486,7 +5486,7 @@
         <v>44582</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5559,7 +5559,7 @@
         <v>44582</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5632,7 +5632,7 @@
         <v>44851</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5705,7 +5705,7 @@
         <v>44538</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5778,7 +5778,7 @@
         <v>44740</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5851,7 +5851,7 @@
         <v>44837</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5924,7 +5924,7 @@
         <v>44816</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5997,7 +5997,7 @@
         <v>44712</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6070,7 +6070,7 @@
         <v>44874</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6143,7 +6143,7 @@
         <v>44529</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6216,7 +6216,7 @@
         <v>44532</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6289,7 +6289,7 @@
         <v>44586</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6362,7 +6362,7 @@
         <v>44722</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6435,7 +6435,7 @@
         <v>44685</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6508,7 +6508,7 @@
         <v>44809</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6581,7 +6581,7 @@
         <v>44858</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6654,7 +6654,7 @@
         <v>44491</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6727,7 +6727,7 @@
         <v>44670</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6800,7 +6800,7 @@
         <v>44659</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6873,7 +6873,7 @@
         <v>44740</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6946,7 +6946,7 @@
         <v>44510</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7019,7 +7019,7 @@
         <v>44733</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7092,7 +7092,7 @@
         <v>44853</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7165,7 +7165,7 @@
         <v>44557</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7243,7 +7243,7 @@
         <v>44546</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7316,7 +7316,7 @@
         <v>44817</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7389,7 +7389,7 @@
         <v>44614</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7462,7 +7462,7 @@
         <v>44883</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7535,7 +7535,7 @@
         <v>44874</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7608,7 +7608,7 @@
         <v>44874</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7681,7 +7681,7 @@
         <v>44515</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7759,7 +7759,7 @@
         <v>44799</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7832,7 +7832,7 @@
         <v>44881</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7905,7 +7905,7 @@
         <v>44881</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7978,7 +7978,7 @@
         <v>44588</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8051,7 +8051,7 @@
         <v>44581</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8124,7 +8124,7 @@
         <v>44868</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8197,7 +8197,7 @@
         <v>44705</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8270,7 +8270,7 @@
         <v>44573</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8343,7 +8343,7 @@
         <v>44560</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8421,7 +8421,7 @@
         <v>44477</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8494,7 +8494,7 @@
         <v>44614</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8567,7 +8567,7 @@
         <v>44714</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8640,7 +8640,7 @@
         <v>44877</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8713,7 +8713,7 @@
         <v>44491</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8786,7 +8786,7 @@
         <v>44852</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8859,7 +8859,7 @@
         <v>44584</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8932,7 +8932,7 @@
         <v>44662</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9005,7 +9005,7 @@
         <v>44643</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9078,7 +9078,7 @@
         <v>44614</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9151,7 +9151,7 @@
         <v>44726</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9224,7 +9224,7 @@
         <v>44818</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9297,7 +9297,7 @@
         <v>45736</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9370,7 +9370,7 @@
         <v>45040</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         <v>44588</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9516,7 +9516,7 @@
         <v>44881</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9594,7 +9594,7 @@
         <v>44586</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9667,7 +9667,7 @@
         <v>45267</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9740,7 +9740,7 @@
         <v>44899</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9813,7 +9813,7 @@
         <v>44979</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9886,7 +9886,7 @@
         <v>45162</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9959,7 +9959,7 @@
         <v>45054</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10032,7 +10032,7 @@
         <v>45054</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10105,7 +10105,7 @@
         <v>44918</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10178,7 +10178,7 @@
         <v>44918</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10251,7 +10251,7 @@
         <v>45694</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10324,7 +10324,7 @@
         <v>45733</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10397,7 +10397,7 @@
         <v>45184</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10470,7 +10470,7 @@
         <v>45510</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10543,7 +10543,7 @@
         <v>45265</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10616,7 +10616,7 @@
         <v>45189</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10689,7 +10689,7 @@
         <v>44937</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10762,7 +10762,7 @@
         <v>45763</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10835,7 +10835,7 @@
         <v>45338</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10908,7 +10908,7 @@
         <v>44629</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10981,7 +10981,7 @@
         <v>45245</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11059,7 +11059,7 @@
         <v>45510</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11132,7 +11132,7 @@
         <v>45623</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11205,7 +11205,7 @@
         <v>45110</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11278,7 +11278,7 @@
         <v>46002</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11351,7 +11351,7 @@
         <v>45090</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11424,7 +11424,7 @@
         <v>45091</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11497,7 +11497,7 @@
         <v>45733</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11570,7 +11570,7 @@
         <v>46002</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11643,7 +11643,7 @@
         <v>46006</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11716,7 +11716,7 @@
         <v>45512</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11789,7 +11789,7 @@
         <v>45609</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11862,7 +11862,7 @@
         <v>46007</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11935,7 +11935,7 @@
         <v>45195</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12008,7 +12008,7 @@
         <v>45482</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12081,7 +12081,7 @@
         <v>45390</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12154,7 +12154,7 @@
         <v>45544</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12227,7 +12227,7 @@
         <v>46009</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12300,7 +12300,7 @@
         <v>46010</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12373,7 +12373,7 @@
         <v>46013</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12446,7 +12446,7 @@
         <v>45727</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12519,7 +12519,7 @@
         <v>45727</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12592,7 +12592,7 @@
         <v>46013</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12665,7 +12665,7 @@
         <v>46013</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12738,7 +12738,7 @@
         <v>46010</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12811,7 +12811,7 @@
         <v>45583</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12884,7 +12884,7 @@
         <v>46016</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12957,7 +12957,7 @@
         <v>46016</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13030,7 +13030,7 @@
         <v>46016</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13103,7 +13103,7 @@
         <v>46016</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13176,7 +13176,7 @@
         <v>46016</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13249,7 +13249,7 @@
         <v>46016</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13322,7 +13322,7 @@
         <v>46021</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13395,7 +13395,7 @@
         <v>46021</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13473,7 +13473,7 @@
         <v>45355</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13546,7 +13546,7 @@
         <v>45891</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13624,7 +13624,7 @@
         <v>45161</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13697,7 +13697,7 @@
         <v>44474</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13770,7 +13770,7 @@
         <v>46029</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13843,7 +13843,7 @@
         <v>45336</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13916,7 +13916,7 @@
         <v>45110</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13989,7 +13989,7 @@
         <v>46029</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14062,7 +14062,7 @@
         <v>45629</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14135,7 +14135,7 @@
         <v>46029</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14208,7 +14208,7 @@
         <v>45897</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14286,7 +14286,7 @@
         <v>46029</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14359,7 +14359,7 @@
         <v>46031</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14432,7 +14432,7 @@
         <v>45629</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14505,7 +14505,7 @@
         <v>45173</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14578,7 +14578,7 @@
         <v>45173</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14651,7 +14651,7 @@
         <v>45897</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14729,7 +14729,7 @@
         <v>45897</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14802,7 +14802,7 @@
         <v>46031</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14875,7 +14875,7 @@
         <v>45629</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14948,7 +14948,7 @@
         <v>46035</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15021,7 +15021,7 @@
         <v>44887</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15094,7 +15094,7 @@
         <v>45903</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15167,7 +15167,7 @@
         <v>44874</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15240,7 +15240,7 @@
         <v>45903</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15313,7 +15313,7 @@
         <v>45435</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15386,7 +15386,7 @@
         <v>44956</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15459,7 +15459,7 @@
         <v>45903</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15532,7 +15532,7 @@
         <v>45434</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15605,7 +15605,7 @@
         <v>45749</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15678,7 +15678,7 @@
         <v>45903</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15751,7 +15751,7 @@
         <v>46041</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15824,7 +15824,7 @@
         <v>45140</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15897,7 +15897,7 @@
         <v>46041</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15970,7 +15970,7 @@
         <v>46042</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16043,7 +16043,7 @@
         <v>45792</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16116,7 +16116,7 @@
         <v>45910</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16189,7 +16189,7 @@
         <v>45576</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16262,7 +16262,7 @@
         <v>46043</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16335,7 +16335,7 @@
         <v>45796</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16408,7 +16408,7 @@
         <v>46048</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16481,7 +16481,7 @@
         <v>45028</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16554,7 +16554,7 @@
         <v>45722</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16627,7 +16627,7 @@
         <v>45245</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16705,7 +16705,7 @@
         <v>45474</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16778,7 +16778,7 @@
         <v>45918</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16856,7 +16856,7 @@
         <v>45623</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16929,7 +16929,7 @@
         <v>45803</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17002,7 +17002,7 @@
         <v>46050</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17075,7 +17075,7 @@
         <v>45271</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17148,7 +17148,7 @@
         <v>45910</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17221,7 +17221,7 @@
         <v>46050</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17294,7 +17294,7 @@
         <v>46050</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17367,7 +17367,7 @@
         <v>46050</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17440,7 +17440,7 @@
         <v>45805</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17518,7 +17518,7 @@
         <v>45058</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17591,7 +17591,7 @@
         <v>45310</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17664,7 +17664,7 @@
         <v>44904</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17737,7 +17737,7 @@
         <v>45600</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17810,7 +17810,7 @@
         <v>45920</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17883,7 +17883,7 @@
         <v>46055</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17956,7 +17956,7 @@
         <v>46055</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18029,7 +18029,7 @@
         <v>45293</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18102,7 +18102,7 @@
         <v>45924</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18175,7 +18175,7 @@
         <v>45924</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18248,7 +18248,7 @@
         <v>45924</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18321,7 +18321,7 @@
         <v>45929</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18394,7 +18394,7 @@
         <v>45929</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18467,7 +18467,7 @@
         <v>45729</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18540,7 +18540,7 @@
         <v>45588</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18613,7 +18613,7 @@
         <v>45491</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18686,7 +18686,7 @@
         <v>45726</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18759,7 +18759,7 @@
         <v>45929</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18832,7 +18832,7 @@
         <v>46059</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18905,7 +18905,7 @@
         <v>45624</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18978,7 +18978,7 @@
         <v>45929</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19051,7 +19051,7 @@
         <v>46059</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19124,7 +19124,7 @@
         <v>46062</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19197,7 +19197,7 @@
         <v>44641</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19270,7 +19270,7 @@
         <v>46062</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19343,7 +19343,7 @@
         <v>46064</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19416,7 +19416,7 @@
         <v>46064</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19489,7 +19489,7 @@
         <v>46069</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19562,7 +19562,7 @@
         <v>45936</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19640,7 +19640,7 @@
         <v>46069</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19713,7 +19713,7 @@
         <v>45616</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19786,7 +19786,7 @@
         <v>45888</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19859,7 +19859,7 @@
         <v>44991</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19932,7 +19932,7 @@
         <v>44901</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20005,7 +20005,7 @@
         <v>45936</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20083,7 +20083,7 @@
         <v>46066</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20156,7 +20156,7 @@
         <v>44581</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20229,7 +20229,7 @@
         <v>45936</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20302,7 +20302,7 @@
         <v>44998</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20375,7 +20375,7 @@
         <v>45694</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20448,7 +20448,7 @@
         <v>45429</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20521,7 +20521,7 @@
         <v>44867</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20594,7 +20594,7 @@
         <v>44693</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20667,7 +20667,7 @@
         <v>45378</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20740,7 +20740,7 @@
         <v>44896</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20813,7 +20813,7 @@
         <v>45231</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20886,7 +20886,7 @@
         <v>44966</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20964,7 +20964,7 @@
         <v>45456</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21037,7 +21037,7 @@
         <v>45502</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21110,7 +21110,7 @@
         <v>45580</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21183,7 +21183,7 @@
         <v>45226</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21256,7 +21256,7 @@
         <v>44602</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21329,7 +21329,7 @@
         <v>45261</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21402,7 +21402,7 @@
         <v>45950</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21480,7 +21480,7 @@
         <v>45628</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21553,7 +21553,7 @@
         <v>46084</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21626,7 +21626,7 @@
         <v>46083</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21699,7 +21699,7 @@
         <v>46083</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21772,7 +21772,7 @@
         <v>45149</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21850,7 +21850,7 @@
         <v>46085</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21923,7 +21923,7 @@
         <v>45558</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -21996,7 +21996,7 @@
         <v>46085</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22069,7 +22069,7 @@
         <v>45957</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22142,7 +22142,7 @@
         <v>46085</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22215,7 +22215,7 @@
         <v>45583</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22288,7 +22288,7 @@
         <v>45742</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22361,7 +22361,7 @@
         <v>46090</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22439,7 +22439,7 @@
         <v>45021</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22512,7 +22512,7 @@
         <v>44790</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22585,7 +22585,7 @@
         <v>46092</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22658,7 +22658,7 @@
         <v>46092</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22731,7 +22731,7 @@
         <v>46092</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22804,7 +22804,7 @@
         <v>46092</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -22877,7 +22877,7 @@
         <v>46092</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -22950,7 +22950,7 @@
         <v>44943</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23023,7 +23023,7 @@
         <v>46092</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23096,7 +23096,7 @@
         <v>45590</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23169,7 +23169,7 @@
         <v>45966</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23242,7 +23242,7 @@
         <v>45061</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23315,7 +23315,7 @@
         <v>44942</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23388,7 +23388,7 @@
         <v>45968</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23461,7 +23461,7 @@
         <v>45016</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23539,7 +23539,7 @@
         <v>44935</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23612,7 +23612,7 @@
         <v>45971</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23685,7 +23685,7 @@
         <v>45971</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23758,7 +23758,7 @@
         <v>45971</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -23836,7 +23836,7 @@
         <v>45971</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -23914,7 +23914,7 @@
         <v>45971</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -23987,7 +23987,7 @@
         <v>46099</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24060,7 +24060,7 @@
         <v>46099</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24133,7 +24133,7 @@
         <v>46100</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24211,7 +24211,7 @@
         <v>45273</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24284,7 +24284,7 @@
         <v>45680</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24357,7 +24357,7 @@
         <v>45975</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24430,7 +24430,7 @@
         <v>46101</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24503,7 +24503,7 @@
         <v>46104</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24576,7 +24576,7 @@
         <v>45142</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24649,7 +24649,7 @@
         <v>45142</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24722,7 +24722,7 @@
         <v>45231</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -24795,7 +24795,7 @@
         <v>45818</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -24868,7 +24868,7 @@
         <v>45818</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -24941,7 +24941,7 @@
         <v>45817</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25014,7 +25014,7 @@
         <v>45981</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25087,7 +25087,7 @@
         <v>45981</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25160,7 +25160,7 @@
         <v>45980</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25233,7 +25233,7 @@
         <v>45274</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25306,7 +25306,7 @@
         <v>45119</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25379,7 +25379,7 @@
         <v>45818</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25452,7 +25452,7 @@
         <v>45981</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25525,7 +25525,7 @@
         <v>45981</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25598,7 +25598,7 @@
         <v>46108</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25671,7 +25671,7 @@
         <v>46107</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -25744,7 +25744,7 @@
         <v>46108</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -25817,7 +25817,7 @@
         <v>45729</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -25890,7 +25890,7 @@
         <v>45758</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -25963,7 +25963,7 @@
         <v>45176</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26036,7 +26036,7 @@
         <v>45614</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26109,7 +26109,7 @@
         <v>45197</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26182,7 +26182,7 @@
         <v>44614</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26255,7 +26255,7 @@
         <v>46119</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26328,7 +26328,7 @@
         <v>45980</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26401,7 +26401,7 @@
         <v>46120</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26474,7 +26474,7 @@
         <v>45041</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26547,7 +26547,7 @@
         <v>45195</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26620,7 +26620,7 @@
         <v>46119</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -26693,7 +26693,7 @@
         <v>46070</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -26766,7 +26766,7 @@
         <v>46119</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -26839,7 +26839,7 @@
         <v>46070</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -26912,7 +26912,7 @@
         <v>45992</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -26985,7 +26985,7 @@
         <v>46124</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27058,7 +27058,7 @@
         <v>44966</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27131,7 +27131,7 @@
         <v>46124</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27204,7 +27204,7 @@
         <v>45992</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27277,7 +27277,7 @@
         <v>45992</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27350,7 +27350,7 @@
         <v>45714</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27423,7 +27423,7 @@
         <v>45994</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27496,7 +27496,7 @@
         <v>45995</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27569,7 +27569,7 @@
         <v>45994</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -27642,7 +27642,7 @@
         <v>45995</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -27715,7 +27715,7 @@
         <v>45525</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -27788,7 +27788,7 @@
         <v>45525</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -27861,7 +27861,7 @@
         <v>45758</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -27934,7 +27934,7 @@
         <v>45999</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28007,7 +28007,7 @@
         <v>45996</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28080,7 +28080,7 @@
         <v>45135</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28153,7 +28153,7 @@
         <v>46000</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28226,7 +28226,7 @@
         <v>46127</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28299,7 +28299,7 @@
         <v>45554</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28372,7 +28372,7 @@
         <v>45173</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28445,7 +28445,7 @@
         <v>45140</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28518,7 +28518,7 @@
         <v>45714</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -28591,7 +28591,7 @@
         <v>46135</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -28664,7 +28664,7 @@
         <v>46135</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -28737,7 +28737,7 @@
         <v>46135</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -28810,7 +28810,7 @@
         <v>45835</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -28883,7 +28883,7 @@
         <v>45418</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -28956,7 +28956,7 @@
         <v>45300</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29029,7 +29029,7 @@
         <v>44899</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29102,7 +29102,7 @@
         <v>45839</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29175,7 +29175,7 @@
         <v>44865</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29248,7 +29248,7 @@
         <v>45832</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29321,7 +29321,7 @@
         <v>45838</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29394,7 +29394,7 @@
         <v>45838</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29467,7 +29467,7 @@
         <v>45839</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -29540,7 +29540,7 @@
         <v>45621</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -29613,7 +29613,7 @@
         <v>45611</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -29686,7 +29686,7 @@
         <v>45841</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -29759,7 +29759,7 @@
         <v>46104</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -29832,7 +29832,7 @@
         <v>45114</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -29905,7 +29905,7 @@
         <v>45153</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -29978,7 +29978,7 @@
         <v>45804</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30051,7 +30051,7 @@
         <v>45932</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30124,7 +30124,7 @@
         <v>45443</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30197,7 +30197,7 @@
         <v>45477</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30270,7 +30270,7 @@
         <v>45817</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30343,7 +30343,7 @@
         <v>45715</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30416,7 +30416,7 @@
         <v>45804</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30489,7 +30489,7 @@
         <v>45253</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -30562,7 +30562,7 @@
         <v>45061</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -30635,7 +30635,7 @@
         <v>45588</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -30708,7 +30708,7 @@
         <v>45736</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -30781,7 +30781,7 @@
         <v>45267</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -30854,7 +30854,7 @@
         <v>45848</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -30927,7 +30927,7 @@
         <v>45156</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31000,7 +31000,7 @@
         <v>44872</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31073,7 +31073,7 @@
         <v>45915</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31146,7 +31146,7 @@
         <v>45856</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31219,7 +31219,7 @@
         <v>45856</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31292,7 +31292,7 @@
         <v>45152</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31365,7 +31365,7 @@
         <v>46031</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31438,7 +31438,7 @@
         <v>44596</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -31511,7 +31511,7 @@
         <v>45015</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -31584,7 +31584,7 @@
         <v>44865</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -31657,7 +31657,7 @@
         <v>45089</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -31730,7 +31730,7 @@
         <v>45691</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -31803,7 +31803,7 @@
         <v>45778</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -31876,7 +31876,7 @@
         <v>44494</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -31949,7 +31949,7 @@
         <v>44998</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -32022,7 +32022,7 @@
         <v>44573</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32095,7 +32095,7 @@
         <v>45608</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32168,7 +32168,7 @@
         <v>45252</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32241,7 +32241,7 @@
         <v>44834</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -32319,7 +32319,7 @@
         <v>45671</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -32392,7 +32392,7 @@
         <v>45873</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -32465,7 +32465,7 @@
         <v>45856</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -32538,7 +32538,7 @@
         <v>45866</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -32611,7 +32611,7 @@
         <v>44998</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -32684,7 +32684,7 @@
         <v>45751</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -32757,7 +32757,7 @@
         <v>45191</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -32830,7 +32830,7 @@
         <v>45642</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -32903,7 +32903,7 @@
         <v>45532</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -32976,7 +32976,7 @@
         <v>44845</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -33049,7 +33049,7 @@
         <v>45811</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -33122,7 +33122,7 @@
         <v>44917</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -33200,7 +33200,7 @@
         <v>44956</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -33273,7 +33273,7 @@
         <v>45691</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -33346,7 +33346,7 @@
         <v>45440</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -33419,7 +33419,7 @@
         <v>45408</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -33492,7 +33492,7 @@
         <v>46140</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -33570,7 +33570,7 @@
         <v>46140</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -33643,7 +33643,7 @@
         <v>46140</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -33716,7 +33716,7 @@
         <v>45638</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -33789,7 +33789,7 @@
         <v>45243</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -33862,7 +33862,7 @@
         <v>46140</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -33940,7 +33940,7 @@
         <v>45733</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -34013,7 +34013,7 @@
         <v>46031</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -34086,7 +34086,7 @@
         <v>44911</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -34159,7 +34159,7 @@
         <v>44523</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -34232,7 +34232,7 @@
         <v>45477</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -34305,7 +34305,7 @@
         <v>44518</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -34378,7 +34378,7 @@
         <v>45397</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -34451,7 +34451,7 @@
         <v>45358</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -34524,7 +34524,7 @@
         <v>46140</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -34602,7 +34602,7 @@
         <v>45623</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -34675,7 +34675,7 @@
         <v>45614</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -34748,7 +34748,7 @@
         <v>45818</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -34821,7 +34821,7 @@
         <v>45203</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -34894,7 +34894,7 @@
         <v>45520</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -34967,7 +34967,7 @@
         <v>45737</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -35040,7 +35040,7 @@
         <v>45161</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -35113,7 +35113,7 @@
         <v>46146</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -35186,7 +35186,7 @@
         <v>46147</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -35259,7 +35259,7 @@
         <v>44986</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -35332,7 +35332,7 @@
         <v>45184</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -35405,7 +35405,7 @@
         <v>45184</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -35478,7 +35478,7 @@
         <v>46147</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -35551,7 +35551,7 @@
         <v>44543</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -35624,7 +35624,7 @@
         <v>46148</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -35697,7 +35697,7 @@
         <v>46148</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -35770,7 +35770,7 @@
         <v>46148</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -35843,7 +35843,7 @@
         <v>46148</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -35916,7 +35916,7 @@
         <v>46148</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -35989,7 +35989,7 @@
         <v>46148</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -36062,7 +36062,7 @@
         <v>45743</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -36135,7 +36135,7 @@
         <v>46149</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -36208,7 +36208,7 @@
         <v>44865</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -36281,7 +36281,7 @@
         <v>46153</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -36359,7 +36359,7 @@
         <v>44915</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -36432,7 +36432,7 @@
         <v>44915</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -36505,7 +36505,7 @@
         <v>45692</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -36578,7 +36578,7 @@
         <v>46153</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -36656,7 +36656,7 @@
         <v>45104</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -36729,7 +36729,7 @@
         <v>45210</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -36802,7 +36802,7 @@
         <v>45733</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -36875,7 +36875,7 @@
         <v>44901</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -36948,7 +36948,7 @@
         <v>46154</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -37026,7 +37026,7 @@
         <v>46154</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -37099,7 +37099,7 @@
         <v>45579</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -37172,7 +37172,7 @@
         <v>44851</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -37245,7 +37245,7 @@
         <v>45106</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -37318,7 +37318,7 @@
         <v>44777</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -37391,7 +37391,7 @@
         <v>45834</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -37464,7 +37464,7 @@
         <v>45090</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -37537,7 +37537,7 @@
         <v>45680</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -37610,7 +37610,7 @@
         <v>44798</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -37683,7 +37683,7 @@
         <v>45904</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -37756,7 +37756,7 @@
         <v>45021</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -37834,7 +37834,7 @@
         <v>45874</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -37907,7 +37907,7 @@
         <v>45176</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -37980,7 +37980,7 @@
         <v>46163</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -38053,7 +38053,7 @@
         <v>45191</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -38126,7 +38126,7 @@
         <v>46163</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -38199,7 +38199,7 @@
         <v>46163</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -38272,7 +38272,7 @@
         <v>46163</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -38345,7 +38345,7 @@
         <v>45435</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -38418,7 +38418,7 @@
         <v>44483</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -38491,7 +38491,7 @@
         <v>44881</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -38564,7 +38564,7 @@
         <v>45629</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -38637,7 +38637,7 @@
         <v>46167</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -38710,7 +38710,7 @@
         <v>45603</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -38783,7 +38783,7 @@
         <v>45559</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -38856,7 +38856,7 @@
         <v>46167</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -38929,7 +38929,7 @@
         <v>45498</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -39002,7 +39002,7 @@
         <v>44916</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -39075,7 +39075,7 @@
         <v>45756</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -39148,7 +39148,7 @@
         <v>45756</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -39221,7 +39221,7 @@
         <v>45614</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -39294,7 +39294,7 @@
         <v>45281</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -39367,7 +39367,7 @@
         <v>45579</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -39440,7 +39440,7 @@
         <v>45636</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -39518,7 +39518,7 @@
         <v>45061</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -39591,7 +39591,7 @@
         <v>45111</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -39664,7 +39664,7 @@
         <v>45204</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -39737,7 +39737,7 @@
         <v>44979</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -39810,7 +39810,7 @@
         <v>45883</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -39883,7 +39883,7 @@
         <v>45882</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -39956,7 +39956,7 @@
         <v>45882</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -40029,7 +40029,7 @@
         <v>45582</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -40102,7 +40102,7 @@
         <v>46176</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -40175,7 +40175,7 @@
         <v>46177</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -40248,7 +40248,7 @@
         <v>46178</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -40321,7 +40321,7 @@
         <v>44977</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -40394,7 +40394,7 @@
         <v>45250</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -40467,7 +40467,7 @@
         <v>44482</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -40540,7 +40540,7 @@
         <v>44970</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -40613,7 +40613,7 @@
         <v>44740</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -40686,7 +40686,7 @@
         <v>45188</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -40759,7 +40759,7 @@
         <v>45704</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -40832,7 +40832,7 @@
         <v>45723</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -40905,7 +40905,7 @@
         <v>45520</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -40978,7 +40978,7 @@
         <v>45510</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -41051,7 +41051,7 @@
         <v>45036</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -41124,7 +41124,7 @@
         <v>45071</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -41197,7 +41197,7 @@
         <v>44839</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -41270,7 +41270,7 @@
         <v>45301</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -41348,7 +41348,7 @@
         <v>45412</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -41421,7 +41421,7 @@
         <v>45646</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -41494,7 +41494,7 @@
         <v>44799</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -41567,7 +41567,7 @@
         <v>46196</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -41640,7 +41640,7 @@
         <v>46195</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -41718,7 +41718,7 @@
         <v>46195</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -41796,7 +41796,7 @@
         <v>46196</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -41869,7 +41869,7 @@
         <v>44625</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -41942,7 +41942,7 @@
         <v>46197</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -42020,7 +42020,7 @@
         <v>45552</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -42098,7 +42098,7 @@
         <v>45443</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -42171,7 +42171,7 @@
         <v>45475</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -42244,7 +42244,7 @@
         <v>45307</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -42317,7 +42317,7 @@
         <v>44476</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -42395,7 +42395,7 @@
         <v>46199</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -42468,7 +42468,7 @@
         <v>46199</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -42541,7 +42541,7 @@
         <v>46199</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -42614,7 +42614,7 @@
         <v>46199</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -42687,7 +42687,7 @@
         <v>46199</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -42760,7 +42760,7 @@
         <v>44858</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -42833,7 +42833,7 @@
         <v>44970</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -42906,7 +42906,7 @@
         <v>45310</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -42979,7 +42979,7 @@
         <v>46199</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -43052,7 +43052,7 @@
         <v>45090</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -43125,7 +43125,7 @@
         <v>45090</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -43198,7 +43198,7 @@
         <v>45533</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -43271,7 +43271,7 @@
         <v>46203</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -43344,7 +43344,7 @@
         <v>45392</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -43417,7 +43417,7 @@
         <v>45246</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -43490,7 +43490,7 @@
         <v>46203</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -43563,7 +43563,7 @@
         <v>46203</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -43636,7 +43636,7 @@
         <v>44746</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -43709,7 +43709,7 @@
         <v>44951</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -43782,7 +43782,7 @@
         <v>44798</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -43855,7 +43855,7 @@
         <v>45210</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -43928,7 +43928,7 @@
         <v>44896</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -44001,7 +44001,7 @@
         <v>45603</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -44074,7 +44074,7 @@
         <v>45308</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -44147,7 +44147,7 @@
         <v>45139</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -44220,7 +44220,7 @@
         <v>46261</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -44298,7 +44298,7 @@
         <v>45467</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -44371,7 +44371,7 @@
         <v>45105</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -44444,7 +44444,7 @@
         <v>45091</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -44517,7 +44517,7 @@
         <v>45091</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -44590,7 +44590,7 @@
         <v>45751</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -44663,7 +44663,7 @@
         <v>46217</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -44736,7 +44736,7 @@
         <v>46217</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -44809,7 +44809,7 @@
         <v>45278</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -44882,7 +44882,7 @@
         <v>46261</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -44960,7 +44960,7 @@
         <v>44894</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -45033,7 +45033,7 @@
         <v>46217</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -45106,7 +45106,7 @@
         <v>45245</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -45184,7 +45184,7 @@
         <v>46262</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -45262,7 +45262,7 @@
         <v>45166</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -45335,7 +45335,7 @@
         <v>46266</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -45408,7 +45408,7 @@
         <v>46266</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -45481,7 +45481,7 @@
         <v>46267</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -45554,7 +45554,7 @@
         <v>45173</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -45627,7 +45627,7 @@
         <v>44557</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -45700,7 +45700,7 @@
         <v>45085</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -45773,7 +45773,7 @@
         <v>46269</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -45846,7 +45846,7 @@
         <v>46269</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -45919,7 +45919,7 @@
         <v>44575</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -45992,7 +45992,7 @@
         <v>44908</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -46065,7 +46065,7 @@
         <v>45600</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -46138,7 +46138,7 @@
         <v>45092</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -46211,7 +46211,7 @@
         <v>45541</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -46284,7 +46284,7 @@
         <v>45296</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -46357,7 +46357,7 @@
         <v>45197</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -46430,7 +46430,7 @@
         <v>46275</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -46503,7 +46503,7 @@
         <v>45224</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -46576,7 +46576,7 @@
         <v>46274</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -46649,7 +46649,7 @@
         <v>46274</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -46722,7 +46722,7 @@
         <v>45532</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -46795,7 +46795,7 @@
         <v>46233</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -46868,7 +46868,7 @@
         <v>46279</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -46941,7 +46941,7 @@
         <v>46279</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -47014,7 +47014,7 @@
         <v>46273</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -47087,7 +47087,7 @@
         <v>46238</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -47160,7 +47160,7 @@
         <v>44537</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -47233,7 +47233,7 @@
         <v>45037</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -47306,7 +47306,7 @@
         <v>45719</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -47379,7 +47379,7 @@
         <v>44901</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -47452,7 +47452,7 @@
         <v>46280</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -47525,7 +47525,7 @@
         <v>46237</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -47598,7 +47598,7 @@
         <v>45301</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -47671,7 +47671,7 @@
         <v>45617</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -47744,7 +47744,7 @@
         <v>44537</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -47817,7 +47817,7 @@
         <v>46240</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -47890,7 +47890,7 @@
         <v>45054</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -47963,7 +47963,7 @@
         <v>45549</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -48036,7 +48036,7 @@
         <v>45084</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -48109,7 +48109,7 @@
         <v>44546</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -48182,7 +48182,7 @@
         <v>46052</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -48260,7 +48260,7 @@
         <v>44840</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -48333,7 +48333,7 @@
         <v>45685</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -48406,7 +48406,7 @@
         <v>45975</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -48479,7 +48479,7 @@
         <v>44966</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -48552,7 +48552,7 @@
         <v>44911</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -48625,7 +48625,7 @@
         <v>46199</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -48698,7 +48698,7 @@
         <v>45090</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -48771,7 +48771,7 @@
         <v>45090</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -48844,7 +48844,7 @@
         <v>45090</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -48917,7 +48917,7 @@
         <v>45553</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -48990,7 +48990,7 @@
         <v>44911</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -49063,7 +49063,7 @@
         <v>46147</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -49136,7 +49136,7 @@
         <v>45736</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -49209,7 +49209,7 @@
         <v>45106</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -49282,7 +49282,7 @@
         <v>44804</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -49355,7 +49355,7 @@
         <v>45450</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -49428,7 +49428,7 @@
         <v>46289</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -49501,7 +49501,7 @@
         <v>46281</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -49574,7 +49574,7 @@
         <v>46245</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -49647,7 +49647,7 @@
         <v>45290</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -49720,7 +49720,7 @@
         <v>45290</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -49793,7 +49793,7 @@
         <v>46245</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -49866,7 +49866,7 @@
         <v>45146</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -49939,7 +49939,7 @@
         <v>45176</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -50012,7 +50012,7 @@
         <v>46289</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -50085,7 +50085,7 @@
         <v>45539</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -50158,7 +50158,7 @@
         <v>45754</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -50231,7 +50231,7 @@
         <v>45654</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -50304,7 +50304,7 @@
         <v>45152</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -50377,7 +50377,7 @@
         <v>45152</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -50450,7 +50450,7 @@
         <v>46290</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -50523,7 +50523,7 @@
         <v>46290</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -50596,7 +50596,7 @@
         <v>46247</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -50669,7 +50669,7 @@
         <v>46247</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -50742,7 +50742,7 @@
         <v>45261</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -50815,7 +50815,7 @@
         <v>45775</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -50888,7 +50888,7 @@
         <v>46290</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -50966,7 +50966,7 @@
         <v>45098</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -51039,7 +51039,7 @@
         <v>46290</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -51117,7 +51117,7 @@
         <v>45272</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -51190,7 +51190,7 @@
         <v>44683</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -51263,7 +51263,7 @@
         <v>46294</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -51336,7 +51336,7 @@
         <v>45084</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -51409,7 +51409,7 @@
         <v>46252</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -51482,7 +51482,7 @@
         <v>45204</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -51555,7 +51555,7 @@
         <v>45279</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -51628,7 +51628,7 @@
         <v>45525</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -51701,7 +51701,7 @@
         <v>45224</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -51779,7 +51779,7 @@
         <v>46297</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -51852,7 +51852,7 @@
         <v>45267</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -51925,7 +51925,7 @@
         <v>45015</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -51998,7 +51998,7 @@
         <v>46297</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -52076,7 +52076,7 @@
         <v>45370</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -52149,7 +52149,7 @@
         <v>44966</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -52222,7 +52222,7 @@
         <v>45092</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -52295,7 +52295,7 @@
         <v>44883</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -52368,7 +52368,7 @@
         <v>45684</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -52441,7 +52441,7 @@
         <v>46297</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -52514,7 +52514,7 @@
         <v>46247</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -52587,7 +52587,7 @@
         <v>46253</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -52660,7 +52660,7 @@
         <v>45281</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -52733,7 +52733,7 @@
         <v>45603</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -52806,7 +52806,7 @@
         <v>45275</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -52879,7 +52879,7 @@
         <v>45128</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -52952,7 +52952,7 @@
         <v>45756</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -53025,7 +53025,7 @@
         <v>45281</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -53098,7 +53098,7 @@
         <v>44602</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -53171,7 +53171,7 @@
         <v>45161</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -53244,7 +53244,7 @@
         <v>45245</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -53322,7 +53322,7 @@
         <v>45149</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -53400,7 +53400,7 @@
         <v>45159</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -53473,7 +53473,7 @@
         <v>45089</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -53546,7 +53546,7 @@
         <v>45426</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -53619,7 +53619,7 @@
         <v>45310</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -53692,7 +53692,7 @@
         <v>45310</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -53765,7 +53765,7 @@
         <v>45090</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -53838,7 +53838,7 @@
         <v>44700</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -53916,7 +53916,7 @@
         <v>45432</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -53989,7 +53989,7 @@
         <v>45054</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -54062,7 +54062,7 @@
         <v>45336</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -54135,7 +54135,7 @@
         <v>45546</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -54208,7 +54208,7 @@
         <v>45455</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -54281,7 +54281,7 @@
         <v>45040</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -54354,7 +54354,7 @@
         <v>45294</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -54427,7 +54427,7 @@
         <v>45253</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -54500,7 +54500,7 @@
         <v>45541</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -54573,7 +54573,7 @@
         <v>45692</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -54646,7 +54646,7 @@
         <v>45674</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -54719,7 +54719,7 @@
         <v>44966</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -54792,7 +54792,7 @@
         <v>44998</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -54865,7 +54865,7 @@
         <v>44896</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -54938,7 +54938,7 @@
         <v>45306</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -55011,7 +55011,7 @@
         <v>45676</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -55084,7 +55084,7 @@
         <v>45221</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -55162,7 +55162,7 @@
         <v>45221</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -55240,7 +55240,7 @@
         <v>45229</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -55313,7 +55313,7 @@
         <v>44659</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -55386,7 +55386,7 @@
         <v>45175</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -55459,7 +55459,7 @@
         <v>45616</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -55532,7 +55532,7 @@
         <v>44776</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -55610,7 +55610,7 @@
         <v>44714</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -55683,7 +55683,7 @@
         <v>44636</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -55756,7 +55756,7 @@
         <v>44636</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -55829,7 +55829,7 @@
         <v>44911</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -55902,7 +55902,7 @@
         <v>45015</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -55975,7 +55975,7 @@
         <v>45616</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -56048,7 +56048,7 @@
         <v>44665</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -56121,7 +56121,7 @@
         <v>45775</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -56194,7 +56194,7 @@
         <v>45777</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -56267,7 +56267,7 @@
         <v>45775</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -56340,7 +56340,7 @@
         <v>45783</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -56413,7 +56413,7 @@
         <v>45567</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -56486,7 +56486,7 @@
         <v>45730</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -56559,7 +56559,7 @@
         <v>44579</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -56637,7 +56637,7 @@
         <v>44893</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -56715,7 +56715,7 @@
         <v>44893</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -56793,7 +56793,7 @@
         <v>44893</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -56871,7 +56871,7 @@
         <v>45731</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -56944,7 +56944,7 @@
         <v>45736</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -57017,7 +57017,7 @@
         <v>46035</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -57095,7 +57095,7 @@
         <v>46163</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>

--- a/Översikt EDA.xlsx
+++ b/Översikt EDA.xlsx
@@ -601,7 +601,7 @@
         <v>45178</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -725,7 +725,7 @@
         <v>45726</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -843,7 +843,7 @@
         <v>44494</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -955,7 +955,7 @@
         <v>45090</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1070,7 +1070,7 @@
         <v>45306</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1188,7 +1188,7 @@
         <v>45154</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1298,7 +1298,7 @@
         <v>44791</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1406,7 +1406,7 @@
         <v>44740</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1518,7 +1518,7 @@
         <v>45407</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1626,7 +1626,7 @@
         <v>45754</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1737,7 +1737,7 @@
         <v>45293</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1852,7 +1852,7 @@
         <v>45358</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1963,7 +1963,7 @@
         <v>44916</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2074,7 +2074,7 @@
         <v>44868</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2180,7 +2180,7 @@
         <v>44865</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2286,7 +2286,7 @@
         <v>44888</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2396,7 +2396,7 @@
         <v>45575</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2502,7 +2502,7 @@
         <v>45243</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2608,7 +2608,7 @@
         <v>45091</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2718,7 +2718,7 @@
         <v>45856</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2824,7 +2824,7 @@
         <v>45315</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2934,7 +2934,7 @@
         <v>44970</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3040,7 +3040,7 @@
         <v>45310</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3146,7 +3146,7 @@
         <v>45426</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3252,7 +3252,7 @@
         <v>46290</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3358,7 +3358,7 @@
         <v>45545</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3464,7 +3464,7 @@
         <v>45721</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3569,7 +3569,7 @@
         <v>45257</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3674,7 +3674,7 @@
         <v>45532</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3779,7 +3779,7 @@
         <v>46092</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3884,7 +3884,7 @@
         <v>45376</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3993,7 +3993,7 @@
         <v>45243</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4098,7 +4098,7 @@
         <v>45432</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4203,7 +4203,7 @@
         <v>46269</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4313,7 +4313,7 @@
         <v>46269</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4422,7 +4422,7 @@
         <v>45244</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4527,7 +4527,7 @@
         <v>45777</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4641,7 +4641,7 @@
         <v>44579</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4751,7 +4751,7 @@
         <v>44889</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4824,7 +4824,7 @@
         <v>44683</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4897,7 +4897,7 @@
         <v>44810</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4970,7 +4970,7 @@
         <v>44529</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5043,7 +5043,7 @@
         <v>44712</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5116,7 +5116,7 @@
         <v>44479</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5189,7 +5189,7 @@
         <v>44852</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5262,7 +5262,7 @@
         <v>44479</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5335,7 +5335,7 @@
         <v>44889</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5408,7 +5408,7 @@
         <v>44608</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5486,7 +5486,7 @@
         <v>44582</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5559,7 +5559,7 @@
         <v>44582</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5632,7 +5632,7 @@
         <v>44851</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5705,7 +5705,7 @@
         <v>44538</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5778,7 +5778,7 @@
         <v>44740</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5851,7 +5851,7 @@
         <v>44837</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5924,7 +5924,7 @@
         <v>44816</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5997,7 +5997,7 @@
         <v>44712</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6070,7 +6070,7 @@
         <v>44874</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6143,7 +6143,7 @@
         <v>44529</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6216,7 +6216,7 @@
         <v>44532</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6289,7 +6289,7 @@
         <v>44586</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6362,7 +6362,7 @@
         <v>44722</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6435,7 +6435,7 @@
         <v>44685</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6508,7 +6508,7 @@
         <v>44809</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6581,7 +6581,7 @@
         <v>44858</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6654,7 +6654,7 @@
         <v>44491</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6727,7 +6727,7 @@
         <v>44670</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6800,7 +6800,7 @@
         <v>44659</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6873,7 +6873,7 @@
         <v>44740</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6946,7 +6946,7 @@
         <v>44510</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7019,7 +7019,7 @@
         <v>44733</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7092,7 +7092,7 @@
         <v>44853</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7165,7 +7165,7 @@
         <v>44557</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7243,7 +7243,7 @@
         <v>44546</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7316,7 +7316,7 @@
         <v>44817</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7389,7 +7389,7 @@
         <v>44614</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7462,7 +7462,7 @@
         <v>44883</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7535,7 +7535,7 @@
         <v>44874</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7608,7 +7608,7 @@
         <v>44874</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7681,7 +7681,7 @@
         <v>44515</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7759,7 +7759,7 @@
         <v>44799</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7832,7 +7832,7 @@
         <v>44881</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7905,7 +7905,7 @@
         <v>44881</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7978,7 +7978,7 @@
         <v>44588</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8051,7 +8051,7 @@
         <v>44581</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8124,7 +8124,7 @@
         <v>44868</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8197,7 +8197,7 @@
         <v>44705</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8270,7 +8270,7 @@
         <v>44573</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8343,7 +8343,7 @@
         <v>44560</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8421,7 +8421,7 @@
         <v>44477</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8494,7 +8494,7 @@
         <v>44614</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8567,7 +8567,7 @@
         <v>44714</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8640,7 +8640,7 @@
         <v>44877</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8713,7 +8713,7 @@
         <v>44491</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8786,7 +8786,7 @@
         <v>44852</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8859,7 +8859,7 @@
         <v>44584</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8932,7 +8932,7 @@
         <v>44662</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9005,7 +9005,7 @@
         <v>44643</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9078,7 +9078,7 @@
         <v>44614</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9151,7 +9151,7 @@
         <v>44726</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9224,7 +9224,7 @@
         <v>44818</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9297,7 +9297,7 @@
         <v>45736</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9370,7 +9370,7 @@
         <v>45040</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         <v>44588</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9516,7 +9516,7 @@
         <v>44881</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9594,7 +9594,7 @@
         <v>44586</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9667,7 +9667,7 @@
         <v>45267</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9740,7 +9740,7 @@
         <v>44899</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9813,7 +9813,7 @@
         <v>44979</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9886,7 +9886,7 @@
         <v>45162</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9959,7 +9959,7 @@
         <v>45054</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10032,7 +10032,7 @@
         <v>45054</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10105,7 +10105,7 @@
         <v>44918</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10178,7 +10178,7 @@
         <v>44918</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10251,7 +10251,7 @@
         <v>45694</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10324,7 +10324,7 @@
         <v>45733</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10397,7 +10397,7 @@
         <v>45184</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10470,7 +10470,7 @@
         <v>45510</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10543,7 +10543,7 @@
         <v>45265</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10616,7 +10616,7 @@
         <v>45189</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10689,7 +10689,7 @@
         <v>44937</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10762,7 +10762,7 @@
         <v>45763</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10835,7 +10835,7 @@
         <v>45338</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10908,7 +10908,7 @@
         <v>44629</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10981,7 +10981,7 @@
         <v>45245</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11059,7 +11059,7 @@
         <v>45510</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11132,7 +11132,7 @@
         <v>45623</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11205,7 +11205,7 @@
         <v>45110</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11278,7 +11278,7 @@
         <v>46002</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11351,7 +11351,7 @@
         <v>45090</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11424,7 +11424,7 @@
         <v>45091</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11497,7 +11497,7 @@
         <v>45733</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11570,7 +11570,7 @@
         <v>46002</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11643,7 +11643,7 @@
         <v>46006</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11716,7 +11716,7 @@
         <v>45512</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11789,7 +11789,7 @@
         <v>45609</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11862,7 +11862,7 @@
         <v>46007</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11935,7 +11935,7 @@
         <v>45195</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12008,7 +12008,7 @@
         <v>45482</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12081,7 +12081,7 @@
         <v>45390</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12154,7 +12154,7 @@
         <v>45544</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12227,7 +12227,7 @@
         <v>46009</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12300,7 +12300,7 @@
         <v>46010</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12373,7 +12373,7 @@
         <v>46013</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12446,7 +12446,7 @@
         <v>45727</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12519,7 +12519,7 @@
         <v>45727</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12592,7 +12592,7 @@
         <v>46013</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12665,7 +12665,7 @@
         <v>46013</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12738,7 +12738,7 @@
         <v>46010</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12811,7 +12811,7 @@
         <v>45583</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12884,7 +12884,7 @@
         <v>46016</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12957,7 +12957,7 @@
         <v>46016</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13030,7 +13030,7 @@
         <v>46016</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13103,7 +13103,7 @@
         <v>46016</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13176,7 +13176,7 @@
         <v>46016</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13249,7 +13249,7 @@
         <v>46016</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13322,7 +13322,7 @@
         <v>46021</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13395,7 +13395,7 @@
         <v>46021</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13473,7 +13473,7 @@
         <v>45355</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13546,7 +13546,7 @@
         <v>45891</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13624,7 +13624,7 @@
         <v>45161</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13697,7 +13697,7 @@
         <v>44474</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13770,7 +13770,7 @@
         <v>46029</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13843,7 +13843,7 @@
         <v>45336</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13916,7 +13916,7 @@
         <v>45110</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13989,7 +13989,7 @@
         <v>46029</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14062,7 +14062,7 @@
         <v>45629</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14135,7 +14135,7 @@
         <v>46029</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14208,7 +14208,7 @@
         <v>45897</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14286,7 +14286,7 @@
         <v>46029</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14359,7 +14359,7 @@
         <v>46031</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14432,7 +14432,7 @@
         <v>45629</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14505,7 +14505,7 @@
         <v>45173</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14578,7 +14578,7 @@
         <v>45173</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14651,7 +14651,7 @@
         <v>45897</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14729,7 +14729,7 @@
         <v>45897</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14802,7 +14802,7 @@
         <v>46031</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14875,7 +14875,7 @@
         <v>45629</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14948,7 +14948,7 @@
         <v>46035</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15021,7 +15021,7 @@
         <v>44887</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15094,7 +15094,7 @@
         <v>45903</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15167,7 +15167,7 @@
         <v>44874</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15240,7 +15240,7 @@
         <v>45903</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15313,7 +15313,7 @@
         <v>45435</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15386,7 +15386,7 @@
         <v>44956</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15459,7 +15459,7 @@
         <v>45903</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15532,7 +15532,7 @@
         <v>45434</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15605,7 +15605,7 @@
         <v>45749</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15678,7 +15678,7 @@
         <v>45903</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15751,7 +15751,7 @@
         <v>46041</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15824,7 +15824,7 @@
         <v>45140</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15897,7 +15897,7 @@
         <v>46041</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15970,7 +15970,7 @@
         <v>46042</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16043,7 +16043,7 @@
         <v>45792</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16116,7 +16116,7 @@
         <v>45910</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16189,7 +16189,7 @@
         <v>45576</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16262,7 +16262,7 @@
         <v>46043</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16335,7 +16335,7 @@
         <v>45796</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16408,7 +16408,7 @@
         <v>46048</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16481,7 +16481,7 @@
         <v>45028</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16554,7 +16554,7 @@
         <v>45722</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16627,7 +16627,7 @@
         <v>45245</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16705,7 +16705,7 @@
         <v>45474</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16778,7 +16778,7 @@
         <v>45918</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16856,7 +16856,7 @@
         <v>45623</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16929,7 +16929,7 @@
         <v>45803</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17002,7 +17002,7 @@
         <v>46050</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17075,7 +17075,7 @@
         <v>45271</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17148,7 +17148,7 @@
         <v>45910</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17221,7 +17221,7 @@
         <v>46050</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17294,7 +17294,7 @@
         <v>46050</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17367,7 +17367,7 @@
         <v>46050</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17440,7 +17440,7 @@
         <v>45805</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17518,7 +17518,7 @@
         <v>45058</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17591,7 +17591,7 @@
         <v>45310</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17664,7 +17664,7 @@
         <v>44904</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17737,7 +17737,7 @@
         <v>45600</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17810,7 +17810,7 @@
         <v>45920</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17883,7 +17883,7 @@
         <v>46055</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17956,7 +17956,7 @@
         <v>46055</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18029,7 +18029,7 @@
         <v>45293</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18102,7 +18102,7 @@
         <v>45924</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18175,7 +18175,7 @@
         <v>45924</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18248,7 +18248,7 @@
         <v>45924</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18321,7 +18321,7 @@
         <v>45929</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18394,7 +18394,7 @@
         <v>45929</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18467,7 +18467,7 @@
         <v>45729</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18540,7 +18540,7 @@
         <v>45588</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18613,7 +18613,7 @@
         <v>45491</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18686,7 +18686,7 @@
         <v>45726</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18759,7 +18759,7 @@
         <v>45929</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18832,7 +18832,7 @@
         <v>46059</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18905,7 +18905,7 @@
         <v>45624</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18978,7 +18978,7 @@
         <v>45929</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19051,7 +19051,7 @@
         <v>46059</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19124,7 +19124,7 @@
         <v>46062</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19197,7 +19197,7 @@
         <v>44641</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19270,7 +19270,7 @@
         <v>46062</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19343,7 +19343,7 @@
         <v>46064</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19416,7 +19416,7 @@
         <v>46064</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19489,7 +19489,7 @@
         <v>46069</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19562,7 +19562,7 @@
         <v>45936</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19640,7 +19640,7 @@
         <v>46069</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19713,7 +19713,7 @@
         <v>45616</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19786,7 +19786,7 @@
         <v>45888</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19859,7 +19859,7 @@
         <v>44991</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19932,7 +19932,7 @@
         <v>44901</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20005,7 +20005,7 @@
         <v>45936</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20083,7 +20083,7 @@
         <v>46066</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20156,7 +20156,7 @@
         <v>44581</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20229,7 +20229,7 @@
         <v>45936</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20302,7 +20302,7 @@
         <v>44998</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20375,7 +20375,7 @@
         <v>45694</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20448,7 +20448,7 @@
         <v>45429</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20521,7 +20521,7 @@
         <v>44867</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20594,7 +20594,7 @@
         <v>44693</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20667,7 +20667,7 @@
         <v>45378</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20740,7 +20740,7 @@
         <v>44896</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20813,7 +20813,7 @@
         <v>45231</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20886,7 +20886,7 @@
         <v>44966</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20964,7 +20964,7 @@
         <v>45456</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21037,7 +21037,7 @@
         <v>45502</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21110,7 +21110,7 @@
         <v>45580</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21183,7 +21183,7 @@
         <v>45226</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21256,7 +21256,7 @@
         <v>44602</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21329,7 +21329,7 @@
         <v>45261</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21402,7 +21402,7 @@
         <v>45950</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21480,7 +21480,7 @@
         <v>45628</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21553,7 +21553,7 @@
         <v>46084</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21626,7 +21626,7 @@
         <v>46083</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21699,7 +21699,7 @@
         <v>46083</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21772,7 +21772,7 @@
         <v>45149</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21850,7 +21850,7 @@
         <v>46085</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21923,7 +21923,7 @@
         <v>45558</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -21996,7 +21996,7 @@
         <v>46085</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22069,7 +22069,7 @@
         <v>45957</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22142,7 +22142,7 @@
         <v>46085</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22215,7 +22215,7 @@
         <v>45583</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22288,7 +22288,7 @@
         <v>45742</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22361,7 +22361,7 @@
         <v>46090</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22439,7 +22439,7 @@
         <v>45021</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22512,7 +22512,7 @@
         <v>44790</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22585,7 +22585,7 @@
         <v>46092</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22658,7 +22658,7 @@
         <v>46092</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22731,7 +22731,7 @@
         <v>46092</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22804,7 +22804,7 @@
         <v>46092</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -22877,7 +22877,7 @@
         <v>46092</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -22950,7 +22950,7 @@
         <v>44943</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23023,7 +23023,7 @@
         <v>46092</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23096,7 +23096,7 @@
         <v>45590</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23169,7 +23169,7 @@
         <v>45966</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23242,7 +23242,7 @@
         <v>45061</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23315,7 +23315,7 @@
         <v>44942</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23388,7 +23388,7 @@
         <v>45968</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23461,7 +23461,7 @@
         <v>45016</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23539,7 +23539,7 @@
         <v>44935</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23612,7 +23612,7 @@
         <v>45971</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23685,7 +23685,7 @@
         <v>45971</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23758,7 +23758,7 @@
         <v>45971</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -23836,7 +23836,7 @@
         <v>45971</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -23914,7 +23914,7 @@
         <v>45971</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -23987,7 +23987,7 @@
         <v>46099</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24060,7 +24060,7 @@
         <v>46099</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24133,7 +24133,7 @@
         <v>46100</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24211,7 +24211,7 @@
         <v>45273</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24284,7 +24284,7 @@
         <v>45680</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24357,7 +24357,7 @@
         <v>45975</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24430,7 +24430,7 @@
         <v>46101</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24503,7 +24503,7 @@
         <v>46104</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24576,7 +24576,7 @@
         <v>45142</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24649,7 +24649,7 @@
         <v>45142</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24722,7 +24722,7 @@
         <v>45231</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -24795,7 +24795,7 @@
         <v>45818</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -24868,7 +24868,7 @@
         <v>45818</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -24941,7 +24941,7 @@
         <v>45817</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25014,7 +25014,7 @@
         <v>45981</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25087,7 +25087,7 @@
         <v>45981</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25160,7 +25160,7 @@
         <v>45980</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25233,7 +25233,7 @@
         <v>45274</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25306,7 +25306,7 @@
         <v>45119</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25379,7 +25379,7 @@
         <v>45818</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25452,7 +25452,7 @@
         <v>45981</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25525,7 +25525,7 @@
         <v>45981</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25598,7 +25598,7 @@
         <v>46108</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25671,7 +25671,7 @@
         <v>46107</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -25744,7 +25744,7 @@
         <v>46108</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -25817,7 +25817,7 @@
         <v>45729</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -25890,7 +25890,7 @@
         <v>45758</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -25963,7 +25963,7 @@
         <v>45176</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26036,7 +26036,7 @@
         <v>45614</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26109,7 +26109,7 @@
         <v>45197</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26182,7 +26182,7 @@
         <v>44614</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26255,7 +26255,7 @@
         <v>46119</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26328,7 +26328,7 @@
         <v>45980</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26401,7 +26401,7 @@
         <v>46120</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26474,7 +26474,7 @@
         <v>45041</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26547,7 +26547,7 @@
         <v>45195</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26620,7 +26620,7 @@
         <v>46119</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -26693,7 +26693,7 @@
         <v>46070</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -26766,7 +26766,7 @@
         <v>46119</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -26839,7 +26839,7 @@
         <v>46070</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -26912,7 +26912,7 @@
         <v>45992</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -26985,7 +26985,7 @@
         <v>46124</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27058,7 +27058,7 @@
         <v>44966</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27131,7 +27131,7 @@
         <v>46124</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27204,7 +27204,7 @@
         <v>45992</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27277,7 +27277,7 @@
         <v>45992</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27350,7 +27350,7 @@
         <v>45714</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27423,7 +27423,7 @@
         <v>45994</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27496,7 +27496,7 @@
         <v>45995</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27569,7 +27569,7 @@
         <v>45994</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -27642,7 +27642,7 @@
         <v>45995</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -27715,7 +27715,7 @@
         <v>45525</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -27788,7 +27788,7 @@
         <v>45525</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -27861,7 +27861,7 @@
         <v>45758</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -27934,7 +27934,7 @@
         <v>45999</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28007,7 +28007,7 @@
         <v>45996</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28080,7 +28080,7 @@
         <v>45135</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28153,7 +28153,7 @@
         <v>46000</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28226,7 +28226,7 @@
         <v>46127</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28299,7 +28299,7 @@
         <v>45554</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28372,7 +28372,7 @@
         <v>45173</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28445,7 +28445,7 @@
         <v>45140</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28518,7 +28518,7 @@
         <v>45714</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -28591,7 +28591,7 @@
         <v>46135</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -28664,7 +28664,7 @@
         <v>46135</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -28737,7 +28737,7 @@
         <v>46135</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -28810,7 +28810,7 @@
         <v>45835</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -28883,7 +28883,7 @@
         <v>45418</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -28956,7 +28956,7 @@
         <v>45300</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29029,7 +29029,7 @@
         <v>44899</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29102,7 +29102,7 @@
         <v>45839</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29175,7 +29175,7 @@
         <v>44865</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29248,7 +29248,7 @@
         <v>45832</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29321,7 +29321,7 @@
         <v>45838</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29394,7 +29394,7 @@
         <v>45838</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29467,7 +29467,7 @@
         <v>45839</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -29540,7 +29540,7 @@
         <v>45621</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -29613,7 +29613,7 @@
         <v>45611</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -29686,7 +29686,7 @@
         <v>45841</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -29759,7 +29759,7 @@
         <v>46104</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -29832,7 +29832,7 @@
         <v>45114</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -29905,7 +29905,7 @@
         <v>45153</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -29978,7 +29978,7 @@
         <v>45804</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30051,7 +30051,7 @@
         <v>45932</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30124,7 +30124,7 @@
         <v>45443</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30197,7 +30197,7 @@
         <v>45477</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30270,7 +30270,7 @@
         <v>45817</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30343,7 +30343,7 @@
         <v>45715</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30416,7 +30416,7 @@
         <v>45804</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30489,7 +30489,7 @@
         <v>45253</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -30562,7 +30562,7 @@
         <v>45061</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -30635,7 +30635,7 @@
         <v>45588</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -30708,7 +30708,7 @@
         <v>45736</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -30781,7 +30781,7 @@
         <v>45267</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -30854,7 +30854,7 @@
         <v>45848</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -30927,7 +30927,7 @@
         <v>45156</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31000,7 +31000,7 @@
         <v>44872</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31073,7 +31073,7 @@
         <v>45915</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31146,7 +31146,7 @@
         <v>45856</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31219,7 +31219,7 @@
         <v>45856</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31292,7 +31292,7 @@
         <v>45152</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31365,7 +31365,7 @@
         <v>46031</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31438,7 +31438,7 @@
         <v>44596</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -31511,7 +31511,7 @@
         <v>45015</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -31584,7 +31584,7 @@
         <v>44865</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -31657,7 +31657,7 @@
         <v>45089</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -31730,7 +31730,7 @@
         <v>45691</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -31803,7 +31803,7 @@
         <v>45778</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -31876,7 +31876,7 @@
         <v>44494</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -31949,7 +31949,7 @@
         <v>44998</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -32022,7 +32022,7 @@
         <v>44573</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32095,7 +32095,7 @@
         <v>45608</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32168,7 +32168,7 @@
         <v>45252</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32241,7 +32241,7 @@
         <v>44834</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -32319,7 +32319,7 @@
         <v>45671</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -32392,7 +32392,7 @@
         <v>45873</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -32465,7 +32465,7 @@
         <v>45856</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -32538,7 +32538,7 @@
         <v>45866</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -32611,7 +32611,7 @@
         <v>44998</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -32684,7 +32684,7 @@
         <v>45751</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -32757,7 +32757,7 @@
         <v>45191</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -32830,7 +32830,7 @@
         <v>45642</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -32903,7 +32903,7 @@
         <v>45532</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -32976,7 +32976,7 @@
         <v>44845</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -33049,7 +33049,7 @@
         <v>45811</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -33122,7 +33122,7 @@
         <v>44917</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -33200,7 +33200,7 @@
         <v>44956</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -33273,7 +33273,7 @@
         <v>45691</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -33346,7 +33346,7 @@
         <v>45440</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -33419,7 +33419,7 @@
         <v>45408</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -33492,7 +33492,7 @@
         <v>46140</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -33570,7 +33570,7 @@
         <v>46140</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -33643,7 +33643,7 @@
         <v>46140</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -33716,7 +33716,7 @@
         <v>45638</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -33789,7 +33789,7 @@
         <v>45243</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -33862,7 +33862,7 @@
         <v>46140</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -33940,7 +33940,7 @@
         <v>45733</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -34013,7 +34013,7 @@
         <v>46031</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -34086,7 +34086,7 @@
         <v>44911</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -34159,7 +34159,7 @@
         <v>44523</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -34232,7 +34232,7 @@
         <v>45477</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -34305,7 +34305,7 @@
         <v>44518</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -34378,7 +34378,7 @@
         <v>45397</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -34451,7 +34451,7 @@
         <v>45358</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -34524,7 +34524,7 @@
         <v>46140</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -34602,7 +34602,7 @@
         <v>45623</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -34675,7 +34675,7 @@
         <v>45614</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -34748,7 +34748,7 @@
         <v>45818</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -34821,7 +34821,7 @@
         <v>45203</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -34894,7 +34894,7 @@
         <v>45520</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -34967,7 +34967,7 @@
         <v>45737</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -35040,7 +35040,7 @@
         <v>45161</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -35113,7 +35113,7 @@
         <v>46146</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -35186,7 +35186,7 @@
         <v>46147</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -35259,7 +35259,7 @@
         <v>44986</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -35332,7 +35332,7 @@
         <v>45184</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -35405,7 +35405,7 @@
         <v>45184</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -35478,7 +35478,7 @@
         <v>46147</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -35551,7 +35551,7 @@
         <v>44543</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -35624,7 +35624,7 @@
         <v>46148</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -35697,7 +35697,7 @@
         <v>46148</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -35770,7 +35770,7 @@
         <v>46148</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -35843,7 +35843,7 @@
         <v>46148</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -35916,7 +35916,7 @@
         <v>46148</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -35989,7 +35989,7 @@
         <v>46148</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -36062,7 +36062,7 @@
         <v>45743</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -36135,7 +36135,7 @@
         <v>46149</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -36208,7 +36208,7 @@
         <v>44865</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -36281,7 +36281,7 @@
         <v>46153</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -36359,7 +36359,7 @@
         <v>44915</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -36432,7 +36432,7 @@
         <v>44915</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -36505,7 +36505,7 @@
         <v>45692</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -36578,7 +36578,7 @@
         <v>46153</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -36656,7 +36656,7 @@
         <v>45104</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -36729,7 +36729,7 @@
         <v>45210</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -36802,7 +36802,7 @@
         <v>45733</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -36875,7 +36875,7 @@
         <v>44901</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -36948,7 +36948,7 @@
         <v>46154</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -37026,7 +37026,7 @@
         <v>46154</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -37099,7 +37099,7 @@
         <v>45579</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -37172,7 +37172,7 @@
         <v>44851</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -37245,7 +37245,7 @@
         <v>45106</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -37318,7 +37318,7 @@
         <v>44777</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -37391,7 +37391,7 @@
         <v>45834</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -37464,7 +37464,7 @@
         <v>45090</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -37537,7 +37537,7 @@
         <v>45680</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -37610,7 +37610,7 @@
         <v>44798</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -37683,7 +37683,7 @@
         <v>45904</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -37756,7 +37756,7 @@
         <v>45021</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -37834,7 +37834,7 @@
         <v>45874</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -37907,7 +37907,7 @@
         <v>45176</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -37980,7 +37980,7 @@
         <v>46163</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -38053,7 +38053,7 @@
         <v>45191</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -38126,7 +38126,7 @@
         <v>46163</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -38199,7 +38199,7 @@
         <v>46163</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -38272,7 +38272,7 @@
         <v>46163</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -38345,7 +38345,7 @@
         <v>45435</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -38418,7 +38418,7 @@
         <v>44483</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -38491,7 +38491,7 @@
         <v>44881</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -38564,7 +38564,7 @@
         <v>45629</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -38637,7 +38637,7 @@
         <v>46167</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -38710,7 +38710,7 @@
         <v>45603</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -38783,7 +38783,7 @@
         <v>45559</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -38856,7 +38856,7 @@
         <v>46167</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -38929,7 +38929,7 @@
         <v>45498</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -39002,7 +39002,7 @@
         <v>44916</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -39075,7 +39075,7 @@
         <v>45756</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -39148,7 +39148,7 @@
         <v>45756</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -39221,7 +39221,7 @@
         <v>45614</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -39294,7 +39294,7 @@
         <v>45281</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -39367,7 +39367,7 @@
         <v>45579</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -39440,7 +39440,7 @@
         <v>45636</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -39518,7 +39518,7 @@
         <v>45061</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -39591,7 +39591,7 @@
         <v>45111</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -39664,7 +39664,7 @@
         <v>45204</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -39737,7 +39737,7 @@
         <v>44979</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -39810,7 +39810,7 @@
         <v>45883</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -39883,7 +39883,7 @@
         <v>45882</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -39956,7 +39956,7 @@
         <v>45882</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -40029,7 +40029,7 @@
         <v>45582</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -40102,7 +40102,7 @@
         <v>46176</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -40175,7 +40175,7 @@
         <v>46177</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -40248,7 +40248,7 @@
         <v>46178</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -40321,7 +40321,7 @@
         <v>44977</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -40394,7 +40394,7 @@
         <v>45250</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -40467,7 +40467,7 @@
         <v>44482</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -40540,7 +40540,7 @@
         <v>44970</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -40613,7 +40613,7 @@
         <v>44740</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -40686,7 +40686,7 @@
         <v>45188</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -40759,7 +40759,7 @@
         <v>45704</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -40832,7 +40832,7 @@
         <v>45723</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -40905,7 +40905,7 @@
         <v>45520</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -40978,7 +40978,7 @@
         <v>45510</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -41051,7 +41051,7 @@
         <v>45036</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -41124,7 +41124,7 @@
         <v>45071</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -41197,7 +41197,7 @@
         <v>44839</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -41270,7 +41270,7 @@
         <v>45301</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -41348,7 +41348,7 @@
         <v>45412</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -41421,7 +41421,7 @@
         <v>45646</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -41494,7 +41494,7 @@
         <v>44799</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -41567,7 +41567,7 @@
         <v>46196</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -41640,7 +41640,7 @@
         <v>46195</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -41718,7 +41718,7 @@
         <v>46195</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -41796,7 +41796,7 @@
         <v>46196</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -41869,7 +41869,7 @@
         <v>44625</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -41942,7 +41942,7 @@
         <v>46197</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -42020,7 +42020,7 @@
         <v>45552</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -42098,7 +42098,7 @@
         <v>45443</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -42171,7 +42171,7 @@
         <v>45475</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -42244,7 +42244,7 @@
         <v>45307</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -42317,7 +42317,7 @@
         <v>44476</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -42395,7 +42395,7 @@
         <v>46199</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -42468,7 +42468,7 @@
         <v>46199</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -42541,7 +42541,7 @@
         <v>46199</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -42614,7 +42614,7 @@
         <v>46199</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -42687,7 +42687,7 @@
         <v>46199</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -42760,7 +42760,7 @@
         <v>44858</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -42833,7 +42833,7 @@
         <v>44970</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -42906,7 +42906,7 @@
         <v>45310</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -42979,7 +42979,7 @@
         <v>46199</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -43052,7 +43052,7 @@
         <v>45090</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -43125,7 +43125,7 @@
         <v>45090</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -43198,7 +43198,7 @@
         <v>45533</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -43271,7 +43271,7 @@
         <v>46203</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -43344,7 +43344,7 @@
         <v>45392</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -43417,7 +43417,7 @@
         <v>45246</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -43490,7 +43490,7 @@
         <v>46203</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -43563,7 +43563,7 @@
         <v>46203</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -43636,7 +43636,7 @@
         <v>44746</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -43709,7 +43709,7 @@
         <v>44951</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -43782,7 +43782,7 @@
         <v>44798</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -43855,7 +43855,7 @@
         <v>45210</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -43928,7 +43928,7 @@
         <v>44896</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -44001,7 +44001,7 @@
         <v>45603</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -44074,7 +44074,7 @@
         <v>45308</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -44147,7 +44147,7 @@
         <v>45139</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -44220,7 +44220,7 @@
         <v>46261</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -44298,7 +44298,7 @@
         <v>45467</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -44371,7 +44371,7 @@
         <v>45105</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -44444,7 +44444,7 @@
         <v>45091</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -44517,7 +44517,7 @@
         <v>45091</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -44590,7 +44590,7 @@
         <v>45751</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -44663,7 +44663,7 @@
         <v>46217</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -44736,7 +44736,7 @@
         <v>46217</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -44809,7 +44809,7 @@
         <v>45278</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -44882,7 +44882,7 @@
         <v>46261</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -44960,7 +44960,7 @@
         <v>44894</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -45033,7 +45033,7 @@
         <v>46217</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -45106,7 +45106,7 @@
         <v>45245</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -45184,7 +45184,7 @@
         <v>46262</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -45262,7 +45262,7 @@
         <v>45166</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -45335,7 +45335,7 @@
         <v>46266</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -45408,7 +45408,7 @@
         <v>46266</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -45481,7 +45481,7 @@
         <v>46267</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -45554,7 +45554,7 @@
         <v>45173</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -45627,7 +45627,7 @@
         <v>44557</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -45700,7 +45700,7 @@
         <v>45085</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -45773,7 +45773,7 @@
         <v>46269</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -45846,7 +45846,7 @@
         <v>46269</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -45919,7 +45919,7 @@
         <v>44575</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -45992,7 +45992,7 @@
         <v>44908</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -46065,7 +46065,7 @@
         <v>45600</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -46138,7 +46138,7 @@
         <v>45092</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -46211,7 +46211,7 @@
         <v>45541</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -46284,7 +46284,7 @@
         <v>45296</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -46357,7 +46357,7 @@
         <v>45197</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -46430,7 +46430,7 @@
         <v>46275</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -46503,7 +46503,7 @@
         <v>45224</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -46576,7 +46576,7 @@
         <v>46274</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -46649,7 +46649,7 @@
         <v>46274</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -46722,7 +46722,7 @@
         <v>45532</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -46795,7 +46795,7 @@
         <v>46233</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -46868,7 +46868,7 @@
         <v>46279</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -46941,7 +46941,7 @@
         <v>46279</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -47014,7 +47014,7 @@
         <v>46273</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -47087,7 +47087,7 @@
         <v>46238</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -47160,7 +47160,7 @@
         <v>44537</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -47233,7 +47233,7 @@
         <v>45037</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -47306,7 +47306,7 @@
         <v>45719</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -47379,7 +47379,7 @@
         <v>44901</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -47452,7 +47452,7 @@
         <v>46280</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -47525,7 +47525,7 @@
         <v>46237</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -47598,7 +47598,7 @@
         <v>45301</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -47671,7 +47671,7 @@
         <v>45617</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -47744,7 +47744,7 @@
         <v>44537</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -47817,7 +47817,7 @@
         <v>46240</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -47890,7 +47890,7 @@
         <v>45054</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -47963,7 +47963,7 @@
         <v>45549</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -48036,7 +48036,7 @@
         <v>45084</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -48109,7 +48109,7 @@
         <v>44546</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -48182,7 +48182,7 @@
         <v>46052</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -48260,7 +48260,7 @@
         <v>44840</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -48333,7 +48333,7 @@
         <v>45685</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -48406,7 +48406,7 @@
         <v>45975</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -48479,7 +48479,7 @@
         <v>44966</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -48552,7 +48552,7 @@
         <v>44911</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -48625,7 +48625,7 @@
         <v>46199</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -48698,7 +48698,7 @@
         <v>45090</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -48771,7 +48771,7 @@
         <v>45090</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -48844,7 +48844,7 @@
         <v>45090</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -48917,7 +48917,7 @@
         <v>45553</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -48990,7 +48990,7 @@
         <v>44911</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -49063,7 +49063,7 @@
         <v>46147</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -49136,7 +49136,7 @@
         <v>45736</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -49209,7 +49209,7 @@
         <v>45106</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -49282,7 +49282,7 @@
         <v>44804</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -49355,7 +49355,7 @@
         <v>45450</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -49428,7 +49428,7 @@
         <v>46289</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -49501,7 +49501,7 @@
         <v>46281</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -49574,7 +49574,7 @@
         <v>46245</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -49647,7 +49647,7 @@
         <v>45290</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -49720,7 +49720,7 @@
         <v>45290</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -49793,7 +49793,7 @@
         <v>46245</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -49866,7 +49866,7 @@
         <v>45146</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -49939,7 +49939,7 @@
         <v>45176</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -50012,7 +50012,7 @@
         <v>46289</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -50085,7 +50085,7 @@
         <v>45539</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -50158,7 +50158,7 @@
         <v>45754</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -50231,7 +50231,7 @@
         <v>45654</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -50304,7 +50304,7 @@
         <v>45152</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -50377,7 +50377,7 @@
         <v>45152</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -50450,7 +50450,7 @@
         <v>46290</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -50523,7 +50523,7 @@
         <v>46290</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -50596,7 +50596,7 @@
         <v>46247</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -50669,7 +50669,7 @@
         <v>46247</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -50742,7 +50742,7 @@
         <v>45261</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -50815,7 +50815,7 @@
         <v>45775</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -50888,7 +50888,7 @@
         <v>46290</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -50966,7 +50966,7 @@
         <v>45098</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -51039,7 +51039,7 @@
         <v>46290</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -51117,7 +51117,7 @@
         <v>45272</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -51190,7 +51190,7 @@
         <v>44683</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -51263,7 +51263,7 @@
         <v>46294</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -51336,7 +51336,7 @@
         <v>45084</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -51409,7 +51409,7 @@
         <v>46252</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -51482,7 +51482,7 @@
         <v>45204</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -51555,7 +51555,7 @@
         <v>45279</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -51628,7 +51628,7 @@
         <v>45525</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -51701,7 +51701,7 @@
         <v>45224</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -51779,7 +51779,7 @@
         <v>46297</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -51852,7 +51852,7 @@
         <v>45267</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -51925,7 +51925,7 @@
         <v>45015</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -51998,7 +51998,7 @@
         <v>46297</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -52076,7 +52076,7 @@
         <v>45370</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -52149,7 +52149,7 @@
         <v>44966</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -52222,7 +52222,7 @@
         <v>45092</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -52295,7 +52295,7 @@
         <v>44883</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -52368,7 +52368,7 @@
         <v>45684</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -52441,7 +52441,7 @@
         <v>46297</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -52514,7 +52514,7 @@
         <v>46247</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -52587,7 +52587,7 @@
         <v>46253</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -52660,7 +52660,7 @@
         <v>45281</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -52733,7 +52733,7 @@
         <v>45603</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -52806,7 +52806,7 @@
         <v>45275</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -52879,7 +52879,7 @@
         <v>45128</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -52952,7 +52952,7 @@
         <v>45756</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -53025,7 +53025,7 @@
         <v>45281</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -53098,7 +53098,7 @@
         <v>44602</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -53171,7 +53171,7 @@
         <v>45161</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -53244,7 +53244,7 @@
         <v>45245</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -53322,7 +53322,7 @@
         <v>45149</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -53400,7 +53400,7 @@
         <v>45159</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -53473,7 +53473,7 @@
         <v>45089</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -53546,7 +53546,7 @@
         <v>45426</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -53619,7 +53619,7 @@
         <v>45310</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -53692,7 +53692,7 @@
         <v>45310</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -53765,7 +53765,7 @@
         <v>45090</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -53838,7 +53838,7 @@
         <v>44700</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -53916,7 +53916,7 @@
         <v>45432</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -53989,7 +53989,7 @@
         <v>45054</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -54062,7 +54062,7 @@
         <v>45336</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -54135,7 +54135,7 @@
         <v>45546</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -54208,7 +54208,7 @@
         <v>45455</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -54281,7 +54281,7 @@
         <v>45040</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -54354,7 +54354,7 @@
         <v>45294</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -54427,7 +54427,7 @@
         <v>45253</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -54500,7 +54500,7 @@
         <v>45541</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -54573,7 +54573,7 @@
         <v>45692</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -54646,7 +54646,7 @@
         <v>45674</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -54719,7 +54719,7 @@
         <v>44966</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -54792,7 +54792,7 @@
         <v>44998</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -54865,7 +54865,7 @@
         <v>44896</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -54938,7 +54938,7 @@
         <v>45306</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -55011,7 +55011,7 @@
         <v>45676</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -55084,7 +55084,7 @@
         <v>45221</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -55162,7 +55162,7 @@
         <v>45221</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -55240,7 +55240,7 @@
         <v>45229</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -55313,7 +55313,7 @@
         <v>44659</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -55386,7 +55386,7 @@
         <v>45175</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -55459,7 +55459,7 @@
         <v>45616</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -55532,7 +55532,7 @@
         <v>44776</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -55610,7 +55610,7 @@
         <v>44714</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -55683,7 +55683,7 @@
         <v>44636</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -55756,7 +55756,7 @@
         <v>44636</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -55829,7 +55829,7 @@
         <v>44911</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -55902,7 +55902,7 @@
         <v>45015</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -55975,7 +55975,7 @@
         <v>45616</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -56048,7 +56048,7 @@
         <v>44665</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -56121,7 +56121,7 @@
         <v>45775</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -56194,7 +56194,7 @@
         <v>45777</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -56267,7 +56267,7 @@
         <v>45775</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -56340,7 +56340,7 @@
         <v>45783</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -56413,7 +56413,7 @@
         <v>45567</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -56486,7 +56486,7 @@
         <v>45730</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -56559,7 +56559,7 @@
         <v>44579</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -56637,7 +56637,7 @@
         <v>44893</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -56715,7 +56715,7 @@
         <v>44893</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -56793,7 +56793,7 @@
         <v>44893</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -56871,7 +56871,7 @@
         <v>45731</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -56944,7 +56944,7 @@
         <v>45736</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -57017,7 +57017,7 @@
         <v>46035</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -57095,7 +57095,7 @@
         <v>46163</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>

--- a/Översikt EDA.xlsx
+++ b/Översikt EDA.xlsx
@@ -601,7 +601,7 @@
         <v>45178</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -725,7 +725,7 @@
         <v>45726</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -843,7 +843,7 @@
         <v>44494</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -955,7 +955,7 @@
         <v>45090</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1070,7 +1070,7 @@
         <v>45154</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1180,7 +1180,7 @@
         <v>45306</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1298,7 +1298,7 @@
         <v>44791</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1406,7 +1406,7 @@
         <v>45407</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1514,7 +1514,7 @@
         <v>44740</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1626,7 +1626,7 @@
         <v>45358</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1737,7 +1737,7 @@
         <v>45754</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1848,7 +1848,7 @@
         <v>45293</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1963,7 +1963,7 @@
         <v>44916</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2074,7 +2074,7 @@
         <v>44868</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2180,7 +2180,7 @@
         <v>44888</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2290,7 +2290,7 @@
         <v>44865</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2396,7 +2396,7 @@
         <v>45243</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2502,7 +2502,7 @@
         <v>45310</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2608,7 +2608,7 @@
         <v>45426</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2714,7 +2714,7 @@
         <v>45575</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2820,7 +2820,7 @@
         <v>44970</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2926,7 +2926,7 @@
         <v>45315</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3036,7 +3036,7 @@
         <v>45856</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3142,7 +3142,7 @@
         <v>45091</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3252,7 +3252,7 @@
         <v>46290</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3358,7 +3358,7 @@
         <v>45545</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3464,7 +3464,7 @@
         <v>45532</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3569,7 +3569,7 @@
         <v>45376</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3678,7 +3678,7 @@
         <v>45257</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3783,7 +3783,7 @@
         <v>45432</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3888,7 +3888,7 @@
         <v>45777</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4002,7 +4002,7 @@
         <v>45721</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4107,7 +4107,7 @@
         <v>45244</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4212,7 +4212,7 @@
         <v>45243</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4317,7 +4317,7 @@
         <v>46092</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4422,7 +4422,7 @@
         <v>46269</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4531,7 +4531,7 @@
         <v>46269</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4641,7 +4641,7 @@
         <v>44579</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4751,7 +4751,7 @@
         <v>44889</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4824,7 +4824,7 @@
         <v>44683</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4897,7 +4897,7 @@
         <v>44810</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4970,7 +4970,7 @@
         <v>44529</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5043,7 +5043,7 @@
         <v>44712</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5116,7 +5116,7 @@
         <v>44479</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5189,7 +5189,7 @@
         <v>44479</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5262,7 +5262,7 @@
         <v>44852</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5335,7 +5335,7 @@
         <v>44889</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5408,7 +5408,7 @@
         <v>44608</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5486,7 +5486,7 @@
         <v>44582</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5559,7 +5559,7 @@
         <v>44582</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5632,7 +5632,7 @@
         <v>44851</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5705,7 +5705,7 @@
         <v>44538</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5778,7 +5778,7 @@
         <v>44816</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5851,7 +5851,7 @@
         <v>44740</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5924,7 +5924,7 @@
         <v>44837</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5997,7 +5997,7 @@
         <v>44712</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6070,7 +6070,7 @@
         <v>44532</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6143,7 +6143,7 @@
         <v>44529</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6216,7 +6216,7 @@
         <v>44874</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6289,7 +6289,7 @@
         <v>44722</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6362,7 +6362,7 @@
         <v>44586</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6435,7 +6435,7 @@
         <v>44685</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6508,7 +6508,7 @@
         <v>44809</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6581,7 +6581,7 @@
         <v>44858</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6654,7 +6654,7 @@
         <v>44491</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6727,7 +6727,7 @@
         <v>44670</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6800,7 +6800,7 @@
         <v>44877</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6873,7 +6873,7 @@
         <v>44883</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6946,7 +6946,7 @@
         <v>44874</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7019,7 +7019,7 @@
         <v>44874</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7092,7 +7092,7 @@
         <v>44491</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7165,7 +7165,7 @@
         <v>44560</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7243,7 +7243,7 @@
         <v>44573</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7316,7 +7316,7 @@
         <v>44515</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7394,7 +7394,7 @@
         <v>44659</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7467,7 +7467,7 @@
         <v>44740</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7540,7 +7540,7 @@
         <v>44614</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7613,7 +7613,7 @@
         <v>44852</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7686,7 +7686,7 @@
         <v>44799</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7759,7 +7759,7 @@
         <v>44510</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7832,7 +7832,7 @@
         <v>44881</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7905,7 +7905,7 @@
         <v>44881</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7978,7 +7978,7 @@
         <v>44588</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8051,7 +8051,7 @@
         <v>44581</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8124,7 +8124,7 @@
         <v>44868</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8197,7 +8197,7 @@
         <v>44705</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8270,7 +8270,7 @@
         <v>44733</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8343,7 +8343,7 @@
         <v>44853</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8416,7 +8416,7 @@
         <v>44662</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8489,7 +8489,7 @@
         <v>44557</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8567,7 +8567,7 @@
         <v>44546</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8640,7 +8640,7 @@
         <v>44714</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8713,7 +8713,7 @@
         <v>44817</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8786,7 +8786,7 @@
         <v>44614</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8859,7 +8859,7 @@
         <v>44584</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8932,7 +8932,7 @@
         <v>44643</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9005,7 +9005,7 @@
         <v>45719</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9078,7 +9078,7 @@
         <v>44883</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9151,7 +9151,7 @@
         <v>44908</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9224,7 +9224,7 @@
         <v>44726</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9297,7 +9297,7 @@
         <v>44614</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9370,7 +9370,7 @@
         <v>45061</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         <v>45090</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9516,7 +9516,7 @@
         <v>45162</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9589,7 +9589,7 @@
         <v>44818</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9662,7 +9662,7 @@
         <v>45310</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9735,7 +9735,7 @@
         <v>45139</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9808,7 +9808,7 @@
         <v>45245</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9886,7 +9886,7 @@
         <v>45153</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9959,7 +9959,7 @@
         <v>44881</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10032,7 +10032,7 @@
         <v>45092</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10105,7 +10105,7 @@
         <v>45092</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10178,7 +10178,7 @@
         <v>45763</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10251,7 +10251,7 @@
         <v>44966</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10324,7 +10324,7 @@
         <v>45756</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10397,7 +10397,7 @@
         <v>45229</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10470,7 +10470,7 @@
         <v>45090</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10543,7 +10543,7 @@
         <v>45090</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10616,7 +10616,7 @@
         <v>45775</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10689,7 +10689,7 @@
         <v>45161</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10762,7 +10762,7 @@
         <v>45520</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10835,7 +10835,7 @@
         <v>45040</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10908,7 +10908,7 @@
         <v>44636</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10981,7 +10981,7 @@
         <v>45089</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11054,7 +11054,7 @@
         <v>45203</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11127,7 +11127,7 @@
         <v>45054</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11200,7 +11200,7 @@
         <v>45054</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11273,7 +11273,7 @@
         <v>45041</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11346,7 +11346,7 @@
         <v>45456</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11419,7 +11419,7 @@
         <v>45629</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11492,7 +11492,7 @@
         <v>45308</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11565,7 +11565,7 @@
         <v>45554</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11638,7 +11638,7 @@
         <v>45105</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11711,7 +11711,7 @@
         <v>45751</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11784,7 +11784,7 @@
         <v>45727</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11857,7 +11857,7 @@
         <v>45727</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11930,7 +11930,7 @@
         <v>44901</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12003,7 +12003,7 @@
         <v>45549</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12076,7 +12076,7 @@
         <v>44799</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12149,7 +12149,7 @@
         <v>44956</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12222,7 +12222,7 @@
         <v>44776</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12300,7 +12300,7 @@
         <v>45310</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12373,7 +12373,7 @@
         <v>45301</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12451,7 +12451,7 @@
         <v>45539</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12524,7 +12524,7 @@
         <v>45558</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12597,7 +12597,7 @@
         <v>44998</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12670,7 +12670,7 @@
         <v>44894</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12743,7 +12743,7 @@
         <v>45692</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12816,7 +12816,7 @@
         <v>44865</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12889,7 +12889,7 @@
         <v>45390</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12962,7 +12962,7 @@
         <v>45161</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13035,7 +13035,7 @@
         <v>44966</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13108,7 +13108,7 @@
         <v>44966</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13181,7 +13181,7 @@
         <v>44834</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13259,7 +13259,7 @@
         <v>44901</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13332,7 +13332,7 @@
         <v>45426</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13405,7 +13405,7 @@
         <v>45733</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13478,7 +13478,7 @@
         <v>45336</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13551,7 +13551,7 @@
         <v>45210</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13624,7 +13624,7 @@
         <v>44865</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13697,7 +13697,7 @@
         <v>45307</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13770,7 +13770,7 @@
         <v>45195</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13843,7 +13843,7 @@
         <v>44951</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13916,7 +13916,7 @@
         <v>45191</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13989,7 +13989,7 @@
         <v>44537</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14062,7 +14062,7 @@
         <v>45106</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14135,7 +14135,7 @@
         <v>45397</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14208,7 +14208,7 @@
         <v>45015</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14281,7 +14281,7 @@
         <v>45015</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14354,7 +14354,7 @@
         <v>44543</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14427,7 +14427,7 @@
         <v>45184</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14500,7 +14500,7 @@
         <v>45184</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14573,7 +14573,7 @@
         <v>45142</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14646,7 +14646,7 @@
         <v>45273</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14719,7 +14719,7 @@
         <v>45477</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14792,7 +14792,7 @@
         <v>45616</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14865,7 +14865,7 @@
         <v>45392</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14938,7 +14938,7 @@
         <v>45455</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15011,7 +15011,7 @@
         <v>44935</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15084,7 +15084,7 @@
         <v>45636</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15162,7 +15162,7 @@
         <v>44483</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15235,7 +15235,7 @@
         <v>45883</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15308,7 +15308,7 @@
         <v>44867</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15381,7 +15381,7 @@
         <v>45582</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15454,7 +15454,7 @@
         <v>44956</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15527,7 +15527,7 @@
         <v>45149</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15605,7 +15605,7 @@
         <v>45110</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15678,7 +15678,7 @@
         <v>45119</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15751,7 +15751,7 @@
         <v>45680</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15824,7 +15824,7 @@
         <v>45146</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15897,7 +15897,7 @@
         <v>45140</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15970,7 +15970,7 @@
         <v>45450</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16043,7 +16043,7 @@
         <v>45729</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16116,7 +16116,7 @@
         <v>45482</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16189,7 +16189,7 @@
         <v>45583</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16262,7 +16262,7 @@
         <v>45294</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16335,7 +16335,7 @@
         <v>45467</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16408,7 +16408,7 @@
         <v>45532</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16481,7 +16481,7 @@
         <v>45756</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16554,7 +16554,7 @@
         <v>45756</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16627,7 +16627,7 @@
         <v>45676</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16700,7 +16700,7 @@
         <v>45149</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16778,7 +16778,7 @@
         <v>45278</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16851,7 +16851,7 @@
         <v>45152</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16924,7 +16924,7 @@
         <v>45491</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16997,7 +16997,7 @@
         <v>44918</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17070,7 +17070,7 @@
         <v>45532</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17143,7 +17143,7 @@
         <v>44943</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17216,7 +17216,7 @@
         <v>44602</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17289,7 +17289,7 @@
         <v>45891</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17367,7 +17367,7 @@
         <v>45544</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17440,7 +17440,7 @@
         <v>45897</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17513,7 +17513,7 @@
         <v>45897</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17591,7 +17591,7 @@
         <v>45897</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17669,7 +17669,7 @@
         <v>45221</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17747,7 +17747,7 @@
         <v>45221</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17825,7 +17825,7 @@
         <v>45176</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17898,7 +17898,7 @@
         <v>45226</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17971,7 +17971,7 @@
         <v>44845</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18044,7 +18044,7 @@
         <v>45694</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18117,7 +18117,7 @@
         <v>45245</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18195,7 +18195,7 @@
         <v>45729</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18268,7 +18268,7 @@
         <v>45252</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18341,7 +18341,7 @@
         <v>45684</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18414,7 +18414,7 @@
         <v>44625</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18487,7 +18487,7 @@
         <v>45525</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18560,7 +18560,7 @@
         <v>45903</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18633,7 +18633,7 @@
         <v>45903</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18706,7 +18706,7 @@
         <v>45903</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18779,7 +18779,7 @@
         <v>45477</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18852,7 +18852,7 @@
         <v>45903</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18925,7 +18925,7 @@
         <v>45623</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18998,7 +18998,7 @@
         <v>45510</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19071,7 +19071,7 @@
         <v>45692</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19144,7 +19144,7 @@
         <v>44991</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19217,7 +19217,7 @@
         <v>45408</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19290,7 +19290,7 @@
         <v>44911</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19363,7 +19363,7 @@
         <v>44546</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19436,7 +19436,7 @@
         <v>45189</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19509,7 +19509,7 @@
         <v>44537</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19582,7 +19582,7 @@
         <v>45775</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19655,7 +19655,7 @@
         <v>45910</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19728,7 +19728,7 @@
         <v>45306</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19801,7 +19801,7 @@
         <v>45084</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19874,7 +19874,7 @@
         <v>45775</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19947,7 +19947,7 @@
         <v>45525</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20020,7 +20020,7 @@
         <v>45475</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20093,7 +20093,7 @@
         <v>45777</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20166,7 +20166,7 @@
         <v>45135</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20239,7 +20239,7 @@
         <v>45429</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20312,7 +20312,7 @@
         <v>45654</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20385,7 +20385,7 @@
         <v>45783</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20458,7 +20458,7 @@
         <v>45567</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20531,7 +20531,7 @@
         <v>45443</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20604,7 +20604,7 @@
         <v>45355</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20677,7 +20677,7 @@
         <v>45730</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20750,7 +20750,7 @@
         <v>45358</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20823,7 +20823,7 @@
         <v>45559</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20896,7 +20896,7 @@
         <v>44970</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20969,7 +20969,7 @@
         <v>45749</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21042,7 +21042,7 @@
         <v>45918</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21120,7 +21120,7 @@
         <v>45910</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21193,7 +21193,7 @@
         <v>45435</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21266,7 +21266,7 @@
         <v>45616</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21339,7 +21339,7 @@
         <v>45691</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21412,7 +21412,7 @@
         <v>44911</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21485,7 +21485,7 @@
         <v>45173</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21558,7 +21558,7 @@
         <v>45603</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21631,7 +21631,7 @@
         <v>45541</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21704,7 +21704,7 @@
         <v>45920</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21777,7 +21777,7 @@
         <v>44881</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21855,7 +21855,7 @@
         <v>44586</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21928,7 +21928,7 @@
         <v>45106</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22001,7 +22001,7 @@
         <v>45028</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22074,7 +22074,7 @@
         <v>45924</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22147,7 +22147,7 @@
         <v>45142</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22220,7 +22220,7 @@
         <v>44896</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22293,7 +22293,7 @@
         <v>45924</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22366,7 +22366,7 @@
         <v>45924</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22439,7 +22439,7 @@
         <v>45629</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22512,7 +22512,7 @@
         <v>45336</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22585,7 +22585,7 @@
         <v>45271</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22658,7 +22658,7 @@
         <v>45204</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22731,7 +22731,7 @@
         <v>45603</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22804,7 +22804,7 @@
         <v>44942</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -22877,7 +22877,7 @@
         <v>45061</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -22950,7 +22950,7 @@
         <v>45140</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23023,7 +23023,7 @@
         <v>45792</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23096,7 +23096,7 @@
         <v>45929</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23169,7 +23169,7 @@
         <v>45929</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23242,7 +23242,7 @@
         <v>45929</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23315,7 +23315,7 @@
         <v>45929</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23388,7 +23388,7 @@
         <v>45576</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23461,7 +23461,7 @@
         <v>45614</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23534,7 +23534,7 @@
         <v>45754</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23607,7 +23607,7 @@
         <v>45512</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23680,7 +23680,7 @@
         <v>45204</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23753,7 +23753,7 @@
         <v>45054</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -23826,7 +23826,7 @@
         <v>45796</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -23899,7 +23899,7 @@
         <v>45629</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -23972,7 +23972,7 @@
         <v>45541</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24045,7 +24045,7 @@
         <v>44641</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24118,7 +24118,7 @@
         <v>44581</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24191,7 +24191,7 @@
         <v>45152</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24264,7 +24264,7 @@
         <v>45152</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24337,7 +24337,7 @@
         <v>45058</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24410,7 +24410,7 @@
         <v>44915</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24483,7 +24483,7 @@
         <v>44915</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24556,7 +24556,7 @@
         <v>45210</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24629,7 +24629,7 @@
         <v>45722</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24702,7 +24702,7 @@
         <v>45623</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -24775,7 +24775,7 @@
         <v>45936</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -24853,7 +24853,7 @@
         <v>44659</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -24926,7 +24926,7 @@
         <v>45888</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -24999,7 +24999,7 @@
         <v>45936</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25077,7 +25077,7 @@
         <v>45623</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25150,7 +25150,7 @@
         <v>44804</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25223,7 +25223,7 @@
         <v>44636</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25296,7 +25296,7 @@
         <v>44986</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25369,7 +25369,7 @@
         <v>45803</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25442,7 +25442,7 @@
         <v>44629</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25515,7 +25515,7 @@
         <v>45091</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25588,7 +25588,7 @@
         <v>45091</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25661,7 +25661,7 @@
         <v>45091</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -25734,7 +25734,7 @@
         <v>45936</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -25807,7 +25807,7 @@
         <v>44901</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -25880,7 +25880,7 @@
         <v>44614</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -25953,7 +25953,7 @@
         <v>45110</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26026,7 +26026,7 @@
         <v>45805</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26104,7 +26104,7 @@
         <v>45502</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26177,7 +26177,7 @@
         <v>45714</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26250,7 +26250,7 @@
         <v>45624</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26323,7 +26323,7 @@
         <v>44998</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26396,7 +26396,7 @@
         <v>44966</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26474,7 +26474,7 @@
         <v>45600</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26547,7 +26547,7 @@
         <v>45378</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26620,7 +26620,7 @@
         <v>45104</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -26693,7 +26693,7 @@
         <v>45310</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -26766,7 +26766,7 @@
         <v>44746</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -26839,7 +26839,7 @@
         <v>45726</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -26912,7 +26912,7 @@
         <v>45580</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -26985,7 +26985,7 @@
         <v>45628</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27058,7 +27058,7 @@
         <v>44557</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27131,7 +27131,7 @@
         <v>45176</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27204,7 +27204,7 @@
         <v>45742</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27277,7 +27277,7 @@
         <v>45231</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27350,7 +27350,7 @@
         <v>45583</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27423,7 +27423,7 @@
         <v>45098</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27496,7 +27496,7 @@
         <v>45021</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27574,7 +27574,7 @@
         <v>45084</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -27647,7 +27647,7 @@
         <v>45195</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -27720,7 +27720,7 @@
         <v>44700</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -27798,7 +27798,7 @@
         <v>45111</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -27871,7 +27871,7 @@
         <v>45817</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -27944,7 +27944,7 @@
         <v>45818</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28017,7 +28017,7 @@
         <v>45590</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28090,7 +28090,7 @@
         <v>45818</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28163,7 +28163,7 @@
         <v>45818</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28236,7 +28236,7 @@
         <v>44874</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28309,7 +28309,7 @@
         <v>45600</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28382,7 +28382,7 @@
         <v>45579</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28455,7 +28455,7 @@
         <v>45758</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28528,7 +28528,7 @@
         <v>45197</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -28601,7 +28601,7 @@
         <v>45616</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -28674,7 +28674,7 @@
         <v>45434</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -28747,7 +28747,7 @@
         <v>45037</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -28820,7 +28820,7 @@
         <v>45950</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -28898,7 +28898,7 @@
         <v>45603</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -28971,7 +28971,7 @@
         <v>45245</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29049,7 +29049,7 @@
         <v>45085</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29122,7 +29122,7 @@
         <v>45609</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29195,7 +29195,7 @@
         <v>45957</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29268,7 +29268,7 @@
         <v>45253</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29341,7 +29341,7 @@
         <v>45275</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29414,7 +29414,7 @@
         <v>45685</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29487,7 +29487,7 @@
         <v>44482</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -29560,7 +29560,7 @@
         <v>45638</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -29633,7 +29633,7 @@
         <v>44970</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -29706,7 +29706,7 @@
         <v>45835</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -29779,7 +29779,7 @@
         <v>45838</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -29852,7 +29852,7 @@
         <v>45166</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -29925,7 +29925,7 @@
         <v>45173</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -29998,7 +29998,7 @@
         <v>45173</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30071,7 +30071,7 @@
         <v>44714</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30144,7 +30144,7 @@
         <v>45838</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30217,7 +30217,7 @@
         <v>45617</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30290,7 +30290,7 @@
         <v>45966</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30363,7 +30363,7 @@
         <v>45159</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30436,7 +30436,7 @@
         <v>45435</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30509,7 +30509,7 @@
         <v>44998</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -30582,7 +30582,7 @@
         <v>45839</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -30655,7 +30655,7 @@
         <v>45839</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -30728,7 +30728,7 @@
         <v>44523</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -30801,7 +30801,7 @@
         <v>45614</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -30874,7 +30874,7 @@
         <v>44740</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -30947,7 +30947,7 @@
         <v>45175</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31020,7 +31020,7 @@
         <v>45267</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31093,7 +31093,7 @@
         <v>45646</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31166,7 +31166,7 @@
         <v>45474</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31239,7 +31239,7 @@
         <v>45968</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31312,7 +31312,7 @@
         <v>45841</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31385,7 +31385,7 @@
         <v>45971</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31458,7 +31458,7 @@
         <v>45971</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -31536,7 +31536,7 @@
         <v>45971</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -31609,7 +31609,7 @@
         <v>45971</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -31687,7 +31687,7 @@
         <v>45629</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -31760,7 +31760,7 @@
         <v>45971</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -31833,7 +31833,7 @@
         <v>45300</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -31906,7 +31906,7 @@
         <v>45817</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -31979,7 +31979,7 @@
         <v>45267</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -32052,7 +32052,7 @@
         <v>45253</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32125,7 +32125,7 @@
         <v>45588</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32198,7 +32198,7 @@
         <v>45614</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32271,7 +32271,7 @@
         <v>45736</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -32344,7 +32344,7 @@
         <v>45061</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -32417,7 +32417,7 @@
         <v>45715</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -32490,7 +32490,7 @@
         <v>45848</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -32563,7 +32563,7 @@
         <v>45975</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -32636,7 +32636,7 @@
         <v>44665</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -32709,7 +32709,7 @@
         <v>45279</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -32782,7 +32782,7 @@
         <v>44979</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -32855,7 +32855,7 @@
         <v>45778</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -32928,7 +32928,7 @@
         <v>45856</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -33001,7 +33001,7 @@
         <v>45733</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -33074,7 +33074,7 @@
         <v>45184</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -33147,7 +33147,7 @@
         <v>45267</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -33220,7 +33220,7 @@
         <v>45188</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -33293,7 +33293,7 @@
         <v>45440</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -33366,7 +33366,7 @@
         <v>45723</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -33439,7 +33439,7 @@
         <v>45040</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -33512,7 +33512,7 @@
         <v>45261</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -33585,7 +33585,7 @@
         <v>44839</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -33658,7 +33658,7 @@
         <v>45265</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -33731,7 +33731,7 @@
         <v>45224</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -33809,7 +33809,7 @@
         <v>45874</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -33882,7 +33882,7 @@
         <v>45980</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -33955,7 +33955,7 @@
         <v>45015</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -34028,7 +34028,7 @@
         <v>45224</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -34101,7 +34101,7 @@
         <v>44840</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -34174,7 +34174,7 @@
         <v>44872</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -34247,7 +34247,7 @@
         <v>45272</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -34320,7 +34320,7 @@
         <v>45301</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -34393,7 +34393,7 @@
         <v>45089</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -34466,7 +34466,7 @@
         <v>45310</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -34539,7 +34539,7 @@
         <v>45981</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -34612,7 +34612,7 @@
         <v>45981</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -34685,7 +34685,7 @@
         <v>45274</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -34758,7 +34758,7 @@
         <v>45737</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -34831,7 +34831,7 @@
         <v>45293</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -34904,7 +34904,7 @@
         <v>45743</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -34977,7 +34977,7 @@
         <v>45197</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -35050,7 +35050,7 @@
         <v>45882</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -35123,7 +35123,7 @@
         <v>45882</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -35196,7 +35196,7 @@
         <v>45981</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -35269,7 +35269,7 @@
         <v>45981</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -35342,7 +35342,7 @@
         <v>46099</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -35415,7 +35415,7 @@
         <v>46099</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -35488,7 +35488,7 @@
         <v>45090</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -35561,7 +35561,7 @@
         <v>45245</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -35639,7 +35639,7 @@
         <v>44798</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -35712,7 +35712,7 @@
         <v>45173</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -35785,7 +35785,7 @@
         <v>44693</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -35858,7 +35858,7 @@
         <v>46100</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -35936,7 +35936,7 @@
         <v>46101</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -36009,7 +36009,7 @@
         <v>44790</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -36082,7 +36082,7 @@
         <v>45520</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -36155,7 +36155,7 @@
         <v>44896</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -36228,7 +36228,7 @@
         <v>44858</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -36301,7 +36301,7 @@
         <v>45290</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -36374,7 +36374,7 @@
         <v>45290</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -36447,7 +36447,7 @@
         <v>45733</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -36520,7 +36520,7 @@
         <v>45533</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -36593,7 +36593,7 @@
         <v>45588</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -36666,7 +36666,7 @@
         <v>45250</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -36739,7 +36739,7 @@
         <v>46104</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -36812,7 +36812,7 @@
         <v>46107</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -36885,7 +36885,7 @@
         <v>44904</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -36958,7 +36958,7 @@
         <v>44966</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -37031,7 +37031,7 @@
         <v>45736</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -37104,7 +37104,7 @@
         <v>45054</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -37177,7 +37177,7 @@
         <v>46108</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -37250,7 +37250,7 @@
         <v>45546</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -37323,7 +37323,7 @@
         <v>45992</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -37396,7 +37396,7 @@
         <v>45980</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -37469,7 +37469,7 @@
         <v>45992</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -37542,7 +37542,7 @@
         <v>46108</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -37615,7 +37615,7 @@
         <v>45036</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -37688,7 +37688,7 @@
         <v>45296</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -37761,7 +37761,7 @@
         <v>44588</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -37834,7 +37834,7 @@
         <v>44575</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -37907,7 +37907,7 @@
         <v>44899</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -37980,7 +37980,7 @@
         <v>45680</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -38053,7 +38053,7 @@
         <v>46119</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -38126,7 +38126,7 @@
         <v>45994</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -38199,7 +38199,7 @@
         <v>46119</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -38272,7 +38272,7 @@
         <v>46119</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -38345,7 +38345,7 @@
         <v>46120</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -38418,7 +38418,7 @@
         <v>46070</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -38491,7 +38491,7 @@
         <v>46070</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -38564,7 +38564,7 @@
         <v>46124</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -38637,7 +38637,7 @@
         <v>46124</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -38710,7 +38710,7 @@
         <v>45992</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -38783,7 +38783,7 @@
         <v>45994</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -38856,7 +38856,7 @@
         <v>44573</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -38929,7 +38929,7 @@
         <v>45736</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -39002,7 +39002,7 @@
         <v>45995</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -39075,7 +39075,7 @@
         <v>45338</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -39148,7 +39148,7 @@
         <v>44998</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -39221,7 +39221,7 @@
         <v>45995</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -39294,7 +39294,7 @@
         <v>46127</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -39367,7 +39367,7 @@
         <v>46000</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -39440,7 +39440,7 @@
         <v>45996</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -39513,7 +39513,7 @@
         <v>45999</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -39586,7 +39586,7 @@
         <v>44887</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -39659,7 +39659,7 @@
         <v>45758</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -39732,7 +39732,7 @@
         <v>46002</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -39805,7 +39805,7 @@
         <v>45525</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -39878,7 +39878,7 @@
         <v>46002</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -39951,7 +39951,7 @@
         <v>45261</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -40024,7 +40024,7 @@
         <v>45714</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -40097,7 +40097,7 @@
         <v>46031</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -40170,7 +40170,7 @@
         <v>45553</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -40243,7 +40243,7 @@
         <v>46135</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -40316,7 +40316,7 @@
         <v>45161</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -40389,7 +40389,7 @@
         <v>44896</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -40462,7 +40462,7 @@
         <v>44683</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -40535,7 +40535,7 @@
         <v>44851</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -40608,7 +40608,7 @@
         <v>45412</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -40681,7 +40681,7 @@
         <v>45443</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -40754,7 +40754,7 @@
         <v>45090</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -40827,7 +40827,7 @@
         <v>46006</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -40900,7 +40900,7 @@
         <v>46007</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -40973,7 +40973,7 @@
         <v>46135</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -41046,7 +41046,7 @@
         <v>46009</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -41119,7 +41119,7 @@
         <v>46010</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -41192,7 +41192,7 @@
         <v>45016</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -41270,7 +41270,7 @@
         <v>46135</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -41343,7 +41343,7 @@
         <v>44777</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -41416,7 +41416,7 @@
         <v>46010</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -41489,7 +41489,7 @@
         <v>45856</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -41562,7 +41562,7 @@
         <v>45856</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -41635,7 +41635,7 @@
         <v>46013</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -41708,7 +41708,7 @@
         <v>46013</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -41781,7 +41781,7 @@
         <v>46013</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -41854,7 +41854,7 @@
         <v>46016</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -41927,7 +41927,7 @@
         <v>46016</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -42000,7 +42000,7 @@
         <v>46016</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -42073,7 +42073,7 @@
         <v>46016</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -42146,7 +42146,7 @@
         <v>46016</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -42219,7 +42219,7 @@
         <v>46016</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -42292,7 +42292,7 @@
         <v>45231</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -42365,7 +42365,7 @@
         <v>46021</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -42438,7 +42438,7 @@
         <v>46021</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -42516,7 +42516,7 @@
         <v>45281</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -42589,7 +42589,7 @@
         <v>44865</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -42662,7 +42662,7 @@
         <v>45498</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -42735,7 +42735,7 @@
         <v>45915</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -42808,7 +42808,7 @@
         <v>46029</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -42881,7 +42881,7 @@
         <v>46140</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -42959,7 +42959,7 @@
         <v>46029</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -43032,7 +43032,7 @@
         <v>46029</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -43105,7 +43105,7 @@
         <v>45510</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -43178,7 +43178,7 @@
         <v>45510</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -43251,7 +43251,7 @@
         <v>44917</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -43329,7 +43329,7 @@
         <v>46140</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -43407,7 +43407,7 @@
         <v>45156</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -43480,7 +43480,7 @@
         <v>45671</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -43553,7 +43553,7 @@
         <v>44918</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -43626,7 +43626,7 @@
         <v>46029</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -43699,7 +43699,7 @@
         <v>45804</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -43772,7 +43772,7 @@
         <v>45691</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -43845,7 +43845,7 @@
         <v>46031</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -43918,7 +43918,7 @@
         <v>46140</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -43991,7 +43991,7 @@
         <v>46140</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -44064,7 +44064,7 @@
         <v>45128</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -44137,7 +44137,7 @@
         <v>44596</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -44210,7 +44210,7 @@
         <v>45674</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -44283,7 +44283,7 @@
         <v>46031</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -44356,7 +44356,7 @@
         <v>44602</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -44429,7 +44429,7 @@
         <v>44979</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -44502,7 +44502,7 @@
         <v>45243</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -44575,7 +44575,7 @@
         <v>45694</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -44648,7 +44648,7 @@
         <v>46035</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -44721,7 +44721,7 @@
         <v>44518</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -44794,7 +44794,7 @@
         <v>45873</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -44867,7 +44867,7 @@
         <v>45176</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -44940,7 +44940,7 @@
         <v>46042</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -45013,7 +45013,7 @@
         <v>46041</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -45086,7 +45086,7 @@
         <v>46041</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -45159,7 +45159,7 @@
         <v>45021</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -45232,7 +45232,7 @@
         <v>45071</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -45305,7 +45305,7 @@
         <v>45704</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -45378,7 +45378,7 @@
         <v>45733</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -45451,7 +45451,7 @@
         <v>46104</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -45524,7 +45524,7 @@
         <v>45804</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -45597,7 +45597,7 @@
         <v>46140</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -45675,7 +45675,7 @@
         <v>45832</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -45748,7 +45748,7 @@
         <v>45642</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -45821,7 +45821,7 @@
         <v>46043</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -45894,7 +45894,7 @@
         <v>45932</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -45967,7 +45967,7 @@
         <v>45866</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -46040,7 +46040,7 @@
         <v>44899</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -46113,7 +46113,7 @@
         <v>45370</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -46186,7 +46186,7 @@
         <v>44494</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -46259,7 +46259,7 @@
         <v>45611</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -46332,7 +46332,7 @@
         <v>45090</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -46405,7 +46405,7 @@
         <v>45090</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -46478,7 +46478,7 @@
         <v>45090</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -46551,7 +46551,7 @@
         <v>45751</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -46624,7 +46624,7 @@
         <v>46048</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -46697,7 +46697,7 @@
         <v>45281</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -46770,7 +46770,7 @@
         <v>45281</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -46843,7 +46843,7 @@
         <v>45114</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -46916,7 +46916,7 @@
         <v>45608</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -46989,7 +46989,7 @@
         <v>45418</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -47062,7 +47062,7 @@
         <v>44916</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -47135,7 +47135,7 @@
         <v>44977</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -47208,7 +47208,7 @@
         <v>45818</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -47281,7 +47281,7 @@
         <v>45621</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -47354,7 +47354,7 @@
         <v>44937</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -47427,7 +47427,7 @@
         <v>46050</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -47500,7 +47500,7 @@
         <v>46031</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -47573,7 +47573,7 @@
         <v>45432</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -47646,7 +47646,7 @@
         <v>46050</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -47719,7 +47719,7 @@
         <v>46050</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -47792,7 +47792,7 @@
         <v>46050</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -47865,7 +47865,7 @@
         <v>46055</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -47938,7 +47938,7 @@
         <v>46055</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -48011,7 +48011,7 @@
         <v>46059</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -48084,7 +48084,7 @@
         <v>46059</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -48157,7 +48157,7 @@
         <v>45811</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -48230,7 +48230,7 @@
         <v>46062</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -48303,7 +48303,7 @@
         <v>46062</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -48376,7 +48376,7 @@
         <v>46146</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -48449,7 +48449,7 @@
         <v>46064</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -48522,7 +48522,7 @@
         <v>46147</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -48595,7 +48595,7 @@
         <v>46148</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -48668,7 +48668,7 @@
         <v>46148</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -48741,7 +48741,7 @@
         <v>46148</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -48814,7 +48814,7 @@
         <v>46064</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -48887,7 +48887,7 @@
         <v>46066</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -48960,7 +48960,7 @@
         <v>46148</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -49033,7 +49033,7 @@
         <v>46148</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -49106,7 +49106,7 @@
         <v>46148</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -49179,7 +49179,7 @@
         <v>46147</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -49252,7 +49252,7 @@
         <v>46069</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -49325,7 +49325,7 @@
         <v>46069</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -49398,7 +49398,7 @@
         <v>46149</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -49471,7 +49471,7 @@
         <v>45579</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -49544,7 +49544,7 @@
         <v>46153</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -49622,7 +49622,7 @@
         <v>46153</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -49700,7 +49700,7 @@
         <v>46154</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -49773,7 +49773,7 @@
         <v>46083</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -49846,7 +49846,7 @@
         <v>46083</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -49919,7 +49919,7 @@
         <v>46154</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -49997,7 +49997,7 @@
         <v>45834</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -50070,7 +50070,7 @@
         <v>46084</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -50143,7 +50143,7 @@
         <v>46085</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -50216,7 +50216,7 @@
         <v>46085</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -50289,7 +50289,7 @@
         <v>46085</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -50362,7 +50362,7 @@
         <v>45904</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -50435,7 +50435,7 @@
         <v>46090</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -50513,7 +50513,7 @@
         <v>44798</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -50586,7 +50586,7 @@
         <v>46092</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -50659,7 +50659,7 @@
         <v>46092</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -50732,7 +50732,7 @@
         <v>46092</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -50805,7 +50805,7 @@
         <v>46092</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -50878,7 +50878,7 @@
         <v>46092</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -50951,7 +50951,7 @@
         <v>46092</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -51024,7 +51024,7 @@
         <v>46163</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -51097,7 +51097,7 @@
         <v>46163</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -51170,7 +51170,7 @@
         <v>46163</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -51243,7 +51243,7 @@
         <v>45191</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -51316,7 +51316,7 @@
         <v>46163</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -51389,7 +51389,7 @@
         <v>46167</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -51462,7 +51462,7 @@
         <v>46167</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -51535,7 +51535,7 @@
         <v>46176</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -51608,7 +51608,7 @@
         <v>46177</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -51681,7 +51681,7 @@
         <v>46178</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -51754,7 +51754,7 @@
         <v>46195</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -51832,7 +51832,7 @@
         <v>46195</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -51910,7 +51910,7 @@
         <v>45552</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -51988,7 +51988,7 @@
         <v>46197</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -52066,7 +52066,7 @@
         <v>46196</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -52139,7 +52139,7 @@
         <v>46196</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -52212,7 +52212,7 @@
         <v>46199</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -52285,7 +52285,7 @@
         <v>46199</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -52358,7 +52358,7 @@
         <v>46199</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -52431,7 +52431,7 @@
         <v>46199</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -52504,7 +52504,7 @@
         <v>46199</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -52577,7 +52577,7 @@
         <v>46199</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -52650,7 +52650,7 @@
         <v>46203</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -52723,7 +52723,7 @@
         <v>46203</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -52796,7 +52796,7 @@
         <v>46203</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -52869,7 +52869,7 @@
         <v>45246</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -52942,7 +52942,7 @@
         <v>46217</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -53015,7 +53015,7 @@
         <v>46217</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -53088,7 +53088,7 @@
         <v>46217</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -53161,7 +53161,7 @@
         <v>46266</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -53234,7 +53234,7 @@
         <v>46266</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -53307,7 +53307,7 @@
         <v>46267</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -53380,7 +53380,7 @@
         <v>46269</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -53453,7 +53453,7 @@
         <v>46269</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -53526,7 +53526,7 @@
         <v>46274</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -53599,7 +53599,7 @@
         <v>46274</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -53672,7 +53672,7 @@
         <v>46233</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -53745,7 +53745,7 @@
         <v>46275</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -53818,7 +53818,7 @@
         <v>46279</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -53891,7 +53891,7 @@
         <v>46237</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -53964,7 +53964,7 @@
         <v>46273</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -54037,7 +54037,7 @@
         <v>46280</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -54110,7 +54110,7 @@
         <v>46279</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -54183,7 +54183,7 @@
         <v>46238</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -54256,7 +54256,7 @@
         <v>46240</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -54329,7 +54329,7 @@
         <v>46052</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -54407,7 +54407,7 @@
         <v>44911</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -54480,7 +54480,7 @@
         <v>44911</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -54553,7 +54553,7 @@
         <v>46199</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -54626,7 +54626,7 @@
         <v>46245</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -54699,7 +54699,7 @@
         <v>45975</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -54772,7 +54772,7 @@
         <v>46245</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -54845,7 +54845,7 @@
         <v>46147</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -54918,7 +54918,7 @@
         <v>46290</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -54991,7 +54991,7 @@
         <v>46290</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -55064,7 +55064,7 @@
         <v>46247</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -55137,7 +55137,7 @@
         <v>46281</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -55210,7 +55210,7 @@
         <v>46289</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -55283,7 +55283,7 @@
         <v>46290</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -55361,7 +55361,7 @@
         <v>46247</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -55434,7 +55434,7 @@
         <v>46290</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -55512,7 +55512,7 @@
         <v>46289</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -55585,7 +55585,7 @@
         <v>46294</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -55658,7 +55658,7 @@
         <v>46252</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -55731,7 +55731,7 @@
         <v>46253</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -55804,7 +55804,7 @@
         <v>46297</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -55877,7 +55877,7 @@
         <v>46297</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -55950,7 +55950,7 @@
         <v>46297</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -56028,7 +56028,7 @@
         <v>46247</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -56101,7 +56101,7 @@
         <v>46300</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -56174,7 +56174,7 @@
         <v>46261</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -56252,7 +56252,7 @@
         <v>46261</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -56330,7 +56330,7 @@
         <v>46262</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -56408,7 +56408,7 @@
         <v>44579</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -56486,7 +56486,7 @@
         <v>44893</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -56564,7 +56564,7 @@
         <v>44893</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -56642,7 +56642,7 @@
         <v>44893</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -56720,7 +56720,7 @@
         <v>45731</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -56793,7 +56793,7 @@
         <v>45736</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -56866,7 +56866,7 @@
         <v>46035</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -56944,7 +56944,7 @@
         <v>46163</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>

--- a/Översikt EDA.xlsx
+++ b/Översikt EDA.xlsx
@@ -601,7 +601,7 @@
         <v>45178</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -725,7 +725,7 @@
         <v>45726</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -843,7 +843,7 @@
         <v>44494</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -955,7 +955,7 @@
         <v>45090</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1070,7 +1070,7 @@
         <v>45154</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1180,7 +1180,7 @@
         <v>45306</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1298,7 +1298,7 @@
         <v>44791</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1406,7 +1406,7 @@
         <v>45407</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1514,7 +1514,7 @@
         <v>44740</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1626,7 +1626,7 @@
         <v>45358</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1737,7 +1737,7 @@
         <v>45754</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1848,7 +1848,7 @@
         <v>45293</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1963,7 +1963,7 @@
         <v>44916</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2074,7 +2074,7 @@
         <v>44868</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2180,7 +2180,7 @@
         <v>44888</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2290,7 +2290,7 @@
         <v>44865</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2396,7 +2396,7 @@
         <v>45243</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2502,7 +2502,7 @@
         <v>45310</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2608,7 +2608,7 @@
         <v>45426</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2714,7 +2714,7 @@
         <v>45575</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2820,7 +2820,7 @@
         <v>44970</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2926,7 +2926,7 @@
         <v>45315</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3036,7 +3036,7 @@
         <v>45856</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3142,7 +3142,7 @@
         <v>45091</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3252,7 +3252,7 @@
         <v>46290</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3358,7 +3358,7 @@
         <v>45545</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3464,7 +3464,7 @@
         <v>45532</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3569,7 +3569,7 @@
         <v>45376</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3678,7 +3678,7 @@
         <v>45257</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3783,7 +3783,7 @@
         <v>45432</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3888,7 +3888,7 @@
         <v>45777</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4002,7 +4002,7 @@
         <v>45721</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4107,7 +4107,7 @@
         <v>45244</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4212,7 +4212,7 @@
         <v>45243</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4317,7 +4317,7 @@
         <v>46092</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4422,7 +4422,7 @@
         <v>46269</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4531,7 +4531,7 @@
         <v>46269</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4641,7 +4641,7 @@
         <v>44579</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4751,7 +4751,7 @@
         <v>44889</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4824,7 +4824,7 @@
         <v>44683</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4897,7 +4897,7 @@
         <v>44810</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4970,7 +4970,7 @@
         <v>44529</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5043,7 +5043,7 @@
         <v>44712</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5116,7 +5116,7 @@
         <v>44479</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5189,7 +5189,7 @@
         <v>44479</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5262,7 +5262,7 @@
         <v>44852</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5335,7 +5335,7 @@
         <v>44889</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5408,7 +5408,7 @@
         <v>44608</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5486,7 +5486,7 @@
         <v>44582</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5559,7 +5559,7 @@
         <v>44582</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5632,7 +5632,7 @@
         <v>44851</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5705,7 +5705,7 @@
         <v>44538</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5778,7 +5778,7 @@
         <v>44816</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5851,7 +5851,7 @@
         <v>44740</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5924,7 +5924,7 @@
         <v>44837</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5997,7 +5997,7 @@
         <v>44712</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6070,7 +6070,7 @@
         <v>44532</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6143,7 +6143,7 @@
         <v>44529</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6216,7 +6216,7 @@
         <v>44874</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6289,7 +6289,7 @@
         <v>44722</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6362,7 +6362,7 @@
         <v>44586</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6435,7 +6435,7 @@
         <v>44685</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6508,7 +6508,7 @@
         <v>44809</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6581,7 +6581,7 @@
         <v>44858</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6654,7 +6654,7 @@
         <v>44491</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6727,7 +6727,7 @@
         <v>44670</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6800,7 +6800,7 @@
         <v>44877</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6873,7 +6873,7 @@
         <v>44883</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6946,7 +6946,7 @@
         <v>44874</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7019,7 +7019,7 @@
         <v>44874</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7092,7 +7092,7 @@
         <v>44491</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7165,7 +7165,7 @@
         <v>44560</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7243,7 +7243,7 @@
         <v>44573</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7316,7 +7316,7 @@
         <v>44515</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7394,7 +7394,7 @@
         <v>44659</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7467,7 +7467,7 @@
         <v>44740</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7540,7 +7540,7 @@
         <v>44614</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7613,7 +7613,7 @@
         <v>44852</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7686,7 +7686,7 @@
         <v>44799</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7759,7 +7759,7 @@
         <v>44510</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7832,7 +7832,7 @@
         <v>44881</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7905,7 +7905,7 @@
         <v>44881</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7978,7 +7978,7 @@
         <v>44588</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8051,7 +8051,7 @@
         <v>44581</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8124,7 +8124,7 @@
         <v>44868</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8197,7 +8197,7 @@
         <v>44705</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8270,7 +8270,7 @@
         <v>44733</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8343,7 +8343,7 @@
         <v>44853</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8416,7 +8416,7 @@
         <v>44662</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8489,7 +8489,7 @@
         <v>44557</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8567,7 +8567,7 @@
         <v>44546</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8640,7 +8640,7 @@
         <v>44714</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8713,7 +8713,7 @@
         <v>44817</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8786,7 +8786,7 @@
         <v>44614</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8859,7 +8859,7 @@
         <v>44584</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8932,7 +8932,7 @@
         <v>44643</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9005,7 +9005,7 @@
         <v>45719</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9078,7 +9078,7 @@
         <v>44883</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9151,7 +9151,7 @@
         <v>44908</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9224,7 +9224,7 @@
         <v>44726</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9297,7 +9297,7 @@
         <v>44614</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9370,7 +9370,7 @@
         <v>45061</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         <v>45090</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9516,7 +9516,7 @@
         <v>45162</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9589,7 +9589,7 @@
         <v>44818</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9662,7 +9662,7 @@
         <v>45310</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9735,7 +9735,7 @@
         <v>45139</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9808,7 +9808,7 @@
         <v>45245</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9886,7 +9886,7 @@
         <v>45153</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9959,7 +9959,7 @@
         <v>44881</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10032,7 +10032,7 @@
         <v>45092</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10105,7 +10105,7 @@
         <v>45092</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10178,7 +10178,7 @@
         <v>45763</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10251,7 +10251,7 @@
         <v>44966</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10324,7 +10324,7 @@
         <v>45756</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10397,7 +10397,7 @@
         <v>45229</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10470,7 +10470,7 @@
         <v>45090</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10543,7 +10543,7 @@
         <v>45090</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10616,7 +10616,7 @@
         <v>45775</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10689,7 +10689,7 @@
         <v>45161</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10762,7 +10762,7 @@
         <v>45520</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10835,7 +10835,7 @@
         <v>45040</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10908,7 +10908,7 @@
         <v>44636</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10981,7 +10981,7 @@
         <v>45089</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11054,7 +11054,7 @@
         <v>45203</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11127,7 +11127,7 @@
         <v>45054</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11200,7 +11200,7 @@
         <v>45054</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11273,7 +11273,7 @@
         <v>45041</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11346,7 +11346,7 @@
         <v>45456</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11419,7 +11419,7 @@
         <v>45629</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11492,7 +11492,7 @@
         <v>45308</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11565,7 +11565,7 @@
         <v>45554</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11638,7 +11638,7 @@
         <v>45105</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11711,7 +11711,7 @@
         <v>45751</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11784,7 +11784,7 @@
         <v>45727</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11857,7 +11857,7 @@
         <v>45727</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11930,7 +11930,7 @@
         <v>44901</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12003,7 +12003,7 @@
         <v>45549</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12076,7 +12076,7 @@
         <v>44799</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12149,7 +12149,7 @@
         <v>44956</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12222,7 +12222,7 @@
         <v>44776</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12300,7 +12300,7 @@
         <v>45310</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12373,7 +12373,7 @@
         <v>45301</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12451,7 +12451,7 @@
         <v>45539</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12524,7 +12524,7 @@
         <v>45558</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12597,7 +12597,7 @@
         <v>44998</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12670,7 +12670,7 @@
         <v>44894</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12743,7 +12743,7 @@
         <v>45692</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12816,7 +12816,7 @@
         <v>44865</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12889,7 +12889,7 @@
         <v>45390</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12962,7 +12962,7 @@
         <v>45161</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13035,7 +13035,7 @@
         <v>44966</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13108,7 +13108,7 @@
         <v>44966</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13181,7 +13181,7 @@
         <v>44834</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13259,7 +13259,7 @@
         <v>44901</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13332,7 +13332,7 @@
         <v>45426</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13405,7 +13405,7 @@
         <v>45733</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13478,7 +13478,7 @@
         <v>45336</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13551,7 +13551,7 @@
         <v>45210</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13624,7 +13624,7 @@
         <v>44865</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13697,7 +13697,7 @@
         <v>45307</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13770,7 +13770,7 @@
         <v>45195</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13843,7 +13843,7 @@
         <v>44951</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13916,7 +13916,7 @@
         <v>45191</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13989,7 +13989,7 @@
         <v>44537</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14062,7 +14062,7 @@
         <v>45106</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14135,7 +14135,7 @@
         <v>45397</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14208,7 +14208,7 @@
         <v>45015</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14281,7 +14281,7 @@
         <v>45015</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14354,7 +14354,7 @@
         <v>44543</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14427,7 +14427,7 @@
         <v>45184</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14500,7 +14500,7 @@
         <v>45184</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14573,7 +14573,7 @@
         <v>45142</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14646,7 +14646,7 @@
         <v>45273</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14719,7 +14719,7 @@
         <v>45477</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14792,7 +14792,7 @@
         <v>45616</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14865,7 +14865,7 @@
         <v>45392</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14938,7 +14938,7 @@
         <v>45455</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15011,7 +15011,7 @@
         <v>44935</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15084,7 +15084,7 @@
         <v>45636</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15162,7 +15162,7 @@
         <v>44483</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15235,7 +15235,7 @@
         <v>45883</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15308,7 +15308,7 @@
         <v>44867</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15381,7 +15381,7 @@
         <v>45582</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15454,7 +15454,7 @@
         <v>44956</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15527,7 +15527,7 @@
         <v>45149</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15605,7 +15605,7 @@
         <v>45110</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15678,7 +15678,7 @@
         <v>45119</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15751,7 +15751,7 @@
         <v>45680</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15824,7 +15824,7 @@
         <v>45146</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15897,7 +15897,7 @@
         <v>45140</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15970,7 +15970,7 @@
         <v>45450</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16043,7 +16043,7 @@
         <v>45729</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16116,7 +16116,7 @@
         <v>45482</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16189,7 +16189,7 @@
         <v>45583</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16262,7 +16262,7 @@
         <v>45294</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16335,7 +16335,7 @@
         <v>45467</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16408,7 +16408,7 @@
         <v>45532</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16481,7 +16481,7 @@
         <v>45756</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16554,7 +16554,7 @@
         <v>45756</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16627,7 +16627,7 @@
         <v>45676</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16700,7 +16700,7 @@
         <v>45149</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16778,7 +16778,7 @@
         <v>45278</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16851,7 +16851,7 @@
         <v>45152</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16924,7 +16924,7 @@
         <v>45491</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16997,7 +16997,7 @@
         <v>44918</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17070,7 +17070,7 @@
         <v>45532</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17143,7 +17143,7 @@
         <v>44943</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17216,7 +17216,7 @@
         <v>44602</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17289,7 +17289,7 @@
         <v>45891</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17367,7 +17367,7 @@
         <v>45544</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17440,7 +17440,7 @@
         <v>45897</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17513,7 +17513,7 @@
         <v>45897</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17591,7 +17591,7 @@
         <v>45897</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17669,7 +17669,7 @@
         <v>45221</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17747,7 +17747,7 @@
         <v>45221</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17825,7 +17825,7 @@
         <v>45176</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17898,7 +17898,7 @@
         <v>45226</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17971,7 +17971,7 @@
         <v>44845</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18044,7 +18044,7 @@
         <v>45694</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18117,7 +18117,7 @@
         <v>45245</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18195,7 +18195,7 @@
         <v>45729</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18268,7 +18268,7 @@
         <v>45252</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18341,7 +18341,7 @@
         <v>45684</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18414,7 +18414,7 @@
         <v>44625</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18487,7 +18487,7 @@
         <v>45525</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18560,7 +18560,7 @@
         <v>45903</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18633,7 +18633,7 @@
         <v>45903</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18706,7 +18706,7 @@
         <v>45903</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18779,7 +18779,7 @@
         <v>45477</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18852,7 +18852,7 @@
         <v>45903</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18925,7 +18925,7 @@
         <v>45623</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18998,7 +18998,7 @@
         <v>45510</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19071,7 +19071,7 @@
         <v>45692</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19144,7 +19144,7 @@
         <v>44991</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19217,7 +19217,7 @@
         <v>45408</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19290,7 +19290,7 @@
         <v>44911</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19363,7 +19363,7 @@
         <v>44546</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19436,7 +19436,7 @@
         <v>45189</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19509,7 +19509,7 @@
         <v>44537</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19582,7 +19582,7 @@
         <v>45775</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19655,7 +19655,7 @@
         <v>45910</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19728,7 +19728,7 @@
         <v>45306</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19801,7 +19801,7 @@
         <v>45084</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19874,7 +19874,7 @@
         <v>45775</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19947,7 +19947,7 @@
         <v>45525</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20020,7 +20020,7 @@
         <v>45475</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20093,7 +20093,7 @@
         <v>45777</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20166,7 +20166,7 @@
         <v>45135</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20239,7 +20239,7 @@
         <v>45429</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20312,7 +20312,7 @@
         <v>45654</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20385,7 +20385,7 @@
         <v>45783</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20458,7 +20458,7 @@
         <v>45567</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20531,7 +20531,7 @@
         <v>45443</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20604,7 +20604,7 @@
         <v>45355</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20677,7 +20677,7 @@
         <v>45730</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20750,7 +20750,7 @@
         <v>45358</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20823,7 +20823,7 @@
         <v>45559</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20896,7 +20896,7 @@
         <v>44970</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20969,7 +20969,7 @@
         <v>45749</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21042,7 +21042,7 @@
         <v>45918</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21120,7 +21120,7 @@
         <v>45910</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21193,7 +21193,7 @@
         <v>45435</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21266,7 +21266,7 @@
         <v>45616</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21339,7 +21339,7 @@
         <v>45691</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21412,7 +21412,7 @@
         <v>44911</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21485,7 +21485,7 @@
         <v>45173</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21558,7 +21558,7 @@
         <v>45603</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21631,7 +21631,7 @@
         <v>45541</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21704,7 +21704,7 @@
         <v>45920</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21777,7 +21777,7 @@
         <v>44881</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21855,7 +21855,7 @@
         <v>44586</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21928,7 +21928,7 @@
         <v>45106</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22001,7 +22001,7 @@
         <v>45028</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22074,7 +22074,7 @@
         <v>45924</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22147,7 +22147,7 @@
         <v>45142</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22220,7 +22220,7 @@
         <v>44896</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22293,7 +22293,7 @@
         <v>45924</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22366,7 +22366,7 @@
         <v>45924</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22439,7 +22439,7 @@
         <v>45629</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22512,7 +22512,7 @@
         <v>45336</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22585,7 +22585,7 @@
         <v>45271</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22658,7 +22658,7 @@
         <v>45204</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22731,7 +22731,7 @@
         <v>45603</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22804,7 +22804,7 @@
         <v>44942</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -22877,7 +22877,7 @@
         <v>45061</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -22950,7 +22950,7 @@
         <v>45140</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23023,7 +23023,7 @@
         <v>45792</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23096,7 +23096,7 @@
         <v>45929</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23169,7 +23169,7 @@
         <v>45929</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23242,7 +23242,7 @@
         <v>45929</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23315,7 +23315,7 @@
         <v>45929</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23388,7 +23388,7 @@
         <v>45576</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23461,7 +23461,7 @@
         <v>45614</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23534,7 +23534,7 @@
         <v>45754</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23607,7 +23607,7 @@
         <v>45512</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23680,7 +23680,7 @@
         <v>45204</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23753,7 +23753,7 @@
         <v>45054</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -23826,7 +23826,7 @@
         <v>45796</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -23899,7 +23899,7 @@
         <v>45629</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -23972,7 +23972,7 @@
         <v>45541</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24045,7 +24045,7 @@
         <v>44641</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24118,7 +24118,7 @@
         <v>44581</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24191,7 +24191,7 @@
         <v>45152</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24264,7 +24264,7 @@
         <v>45152</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24337,7 +24337,7 @@
         <v>45058</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24410,7 +24410,7 @@
         <v>44915</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24483,7 +24483,7 @@
         <v>44915</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24556,7 +24556,7 @@
         <v>45210</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24629,7 +24629,7 @@
         <v>45722</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24702,7 +24702,7 @@
         <v>45623</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -24775,7 +24775,7 @@
         <v>45936</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -24853,7 +24853,7 @@
         <v>44659</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -24926,7 +24926,7 @@
         <v>45888</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -24999,7 +24999,7 @@
         <v>45936</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25077,7 +25077,7 @@
         <v>45623</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25150,7 +25150,7 @@
         <v>44804</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25223,7 +25223,7 @@
         <v>44636</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25296,7 +25296,7 @@
         <v>44986</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25369,7 +25369,7 @@
         <v>45803</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25442,7 +25442,7 @@
         <v>44629</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25515,7 +25515,7 @@
         <v>45091</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25588,7 +25588,7 @@
         <v>45091</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25661,7 +25661,7 @@
         <v>45091</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -25734,7 +25734,7 @@
         <v>45936</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -25807,7 +25807,7 @@
         <v>44901</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -25880,7 +25880,7 @@
         <v>44614</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -25953,7 +25953,7 @@
         <v>45110</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26026,7 +26026,7 @@
         <v>45805</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26104,7 +26104,7 @@
         <v>45502</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26177,7 +26177,7 @@
         <v>45714</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26250,7 +26250,7 @@
         <v>45624</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26323,7 +26323,7 @@
         <v>44998</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26396,7 +26396,7 @@
         <v>44966</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26474,7 +26474,7 @@
         <v>45600</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26547,7 +26547,7 @@
         <v>45378</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26620,7 +26620,7 @@
         <v>45104</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -26693,7 +26693,7 @@
         <v>45310</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -26766,7 +26766,7 @@
         <v>44746</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -26839,7 +26839,7 @@
         <v>45726</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -26912,7 +26912,7 @@
         <v>45580</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -26985,7 +26985,7 @@
         <v>45628</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27058,7 +27058,7 @@
         <v>44557</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27131,7 +27131,7 @@
         <v>45176</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27204,7 +27204,7 @@
         <v>45742</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27277,7 +27277,7 @@
         <v>45231</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27350,7 +27350,7 @@
         <v>45583</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27423,7 +27423,7 @@
         <v>45098</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27496,7 +27496,7 @@
         <v>45021</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27574,7 +27574,7 @@
         <v>45084</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -27647,7 +27647,7 @@
         <v>45195</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -27720,7 +27720,7 @@
         <v>44700</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -27798,7 +27798,7 @@
         <v>45111</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -27871,7 +27871,7 @@
         <v>45817</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -27944,7 +27944,7 @@
         <v>45818</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28017,7 +28017,7 @@
         <v>45590</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28090,7 +28090,7 @@
         <v>45818</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28163,7 +28163,7 @@
         <v>45818</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28236,7 +28236,7 @@
         <v>44874</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28309,7 +28309,7 @@
         <v>45600</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28382,7 +28382,7 @@
         <v>45579</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28455,7 +28455,7 @@
         <v>45758</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28528,7 +28528,7 @@
         <v>45197</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -28601,7 +28601,7 @@
         <v>45616</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -28674,7 +28674,7 @@
         <v>45434</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -28747,7 +28747,7 @@
         <v>45037</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -28820,7 +28820,7 @@
         <v>45950</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -28898,7 +28898,7 @@
         <v>45603</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -28971,7 +28971,7 @@
         <v>45245</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29049,7 +29049,7 @@
         <v>45085</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29122,7 +29122,7 @@
         <v>45609</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29195,7 +29195,7 @@
         <v>45957</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29268,7 +29268,7 @@
         <v>45253</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29341,7 +29341,7 @@
         <v>45275</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29414,7 +29414,7 @@
         <v>45685</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29487,7 +29487,7 @@
         <v>44482</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -29560,7 +29560,7 @@
         <v>45638</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -29633,7 +29633,7 @@
         <v>44970</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -29706,7 +29706,7 @@
         <v>45835</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -29779,7 +29779,7 @@
         <v>45838</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -29852,7 +29852,7 @@
         <v>45166</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -29925,7 +29925,7 @@
         <v>45173</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -29998,7 +29998,7 @@
         <v>45173</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30071,7 +30071,7 @@
         <v>44714</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30144,7 +30144,7 @@
         <v>45838</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30217,7 +30217,7 @@
         <v>45617</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30290,7 +30290,7 @@
         <v>45966</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30363,7 +30363,7 @@
         <v>45159</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30436,7 +30436,7 @@
         <v>45435</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30509,7 +30509,7 @@
         <v>44998</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -30582,7 +30582,7 @@
         <v>45839</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -30655,7 +30655,7 @@
         <v>45839</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -30728,7 +30728,7 @@
         <v>44523</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -30801,7 +30801,7 @@
         <v>45614</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -30874,7 +30874,7 @@
         <v>44740</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -30947,7 +30947,7 @@
         <v>45175</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31020,7 +31020,7 @@
         <v>45267</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31093,7 +31093,7 @@
         <v>45646</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31166,7 +31166,7 @@
         <v>45474</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31239,7 +31239,7 @@
         <v>45968</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31312,7 +31312,7 @@
         <v>45841</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31385,7 +31385,7 @@
         <v>45971</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31458,7 +31458,7 @@
         <v>45971</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -31536,7 +31536,7 @@
         <v>45971</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -31609,7 +31609,7 @@
         <v>45971</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -31687,7 +31687,7 @@
         <v>45629</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -31760,7 +31760,7 @@
         <v>45971</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -31833,7 +31833,7 @@
         <v>45300</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -31906,7 +31906,7 @@
         <v>45817</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -31979,7 +31979,7 @@
         <v>45267</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -32052,7 +32052,7 @@
         <v>45253</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32125,7 +32125,7 @@
         <v>45588</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32198,7 +32198,7 @@
         <v>45614</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32271,7 +32271,7 @@
         <v>45736</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -32344,7 +32344,7 @@
         <v>45061</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -32417,7 +32417,7 @@
         <v>45715</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -32490,7 +32490,7 @@
         <v>45848</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -32563,7 +32563,7 @@
         <v>45975</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -32636,7 +32636,7 @@
         <v>44665</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -32709,7 +32709,7 @@
         <v>45279</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -32782,7 +32782,7 @@
         <v>44979</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -32855,7 +32855,7 @@
         <v>45778</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -32928,7 +32928,7 @@
         <v>45856</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -33001,7 +33001,7 @@
         <v>45733</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -33074,7 +33074,7 @@
         <v>45184</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -33147,7 +33147,7 @@
         <v>45267</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -33220,7 +33220,7 @@
         <v>45188</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -33293,7 +33293,7 @@
         <v>45440</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -33366,7 +33366,7 @@
         <v>45723</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -33439,7 +33439,7 @@
         <v>45040</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -33512,7 +33512,7 @@
         <v>45261</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -33585,7 +33585,7 @@
         <v>44839</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -33658,7 +33658,7 @@
         <v>45265</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -33731,7 +33731,7 @@
         <v>45224</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -33809,7 +33809,7 @@
         <v>45874</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -33882,7 +33882,7 @@
         <v>45980</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -33955,7 +33955,7 @@
         <v>45015</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -34028,7 +34028,7 @@
         <v>45224</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -34101,7 +34101,7 @@
         <v>44840</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -34174,7 +34174,7 @@
         <v>44872</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -34247,7 +34247,7 @@
         <v>45272</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -34320,7 +34320,7 @@
         <v>45301</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -34393,7 +34393,7 @@
         <v>45089</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -34466,7 +34466,7 @@
         <v>45310</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -34539,7 +34539,7 @@
         <v>45981</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -34612,7 +34612,7 @@
         <v>45981</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -34685,7 +34685,7 @@
         <v>45274</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -34758,7 +34758,7 @@
         <v>45737</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -34831,7 +34831,7 @@
         <v>45293</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -34904,7 +34904,7 @@
         <v>45743</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -34977,7 +34977,7 @@
         <v>45197</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -35050,7 +35050,7 @@
         <v>45882</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -35123,7 +35123,7 @@
         <v>45882</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -35196,7 +35196,7 @@
         <v>45981</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -35269,7 +35269,7 @@
         <v>45981</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -35342,7 +35342,7 @@
         <v>46099</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -35415,7 +35415,7 @@
         <v>46099</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -35488,7 +35488,7 @@
         <v>45090</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -35561,7 +35561,7 @@
         <v>45245</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -35639,7 +35639,7 @@
         <v>44798</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -35712,7 +35712,7 @@
         <v>45173</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -35785,7 +35785,7 @@
         <v>44693</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -35858,7 +35858,7 @@
         <v>46100</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -35936,7 +35936,7 @@
         <v>46101</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -36009,7 +36009,7 @@
         <v>44790</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -36082,7 +36082,7 @@
         <v>45520</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -36155,7 +36155,7 @@
         <v>44896</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -36228,7 +36228,7 @@
         <v>44858</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -36301,7 +36301,7 @@
         <v>45290</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -36374,7 +36374,7 @@
         <v>45290</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -36447,7 +36447,7 @@
         <v>45733</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -36520,7 +36520,7 @@
         <v>45533</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -36593,7 +36593,7 @@
         <v>45588</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -36666,7 +36666,7 @@
         <v>45250</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -36739,7 +36739,7 @@
         <v>46104</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -36812,7 +36812,7 @@
         <v>46107</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -36885,7 +36885,7 @@
         <v>44904</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -36958,7 +36958,7 @@
         <v>44966</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -37031,7 +37031,7 @@
         <v>45736</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -37104,7 +37104,7 @@
         <v>45054</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -37177,7 +37177,7 @@
         <v>46108</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -37250,7 +37250,7 @@
         <v>45546</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -37323,7 +37323,7 @@
         <v>45992</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -37396,7 +37396,7 @@
         <v>45980</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -37469,7 +37469,7 @@
         <v>45992</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -37542,7 +37542,7 @@
         <v>46108</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -37615,7 +37615,7 @@
         <v>45036</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -37688,7 +37688,7 @@
         <v>45296</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -37761,7 +37761,7 @@
         <v>44588</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -37834,7 +37834,7 @@
         <v>44575</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -37907,7 +37907,7 @@
         <v>44899</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -37980,7 +37980,7 @@
         <v>45680</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -38053,7 +38053,7 @@
         <v>46119</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -38126,7 +38126,7 @@
         <v>45994</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -38199,7 +38199,7 @@
         <v>46119</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -38272,7 +38272,7 @@
         <v>46119</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -38345,7 +38345,7 @@
         <v>46120</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -38418,7 +38418,7 @@
         <v>46070</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -38491,7 +38491,7 @@
         <v>46070</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -38564,7 +38564,7 @@
         <v>46124</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -38637,7 +38637,7 @@
         <v>46124</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -38710,7 +38710,7 @@
         <v>45992</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -38783,7 +38783,7 @@
         <v>45994</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -38856,7 +38856,7 @@
         <v>44573</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -38929,7 +38929,7 @@
         <v>45736</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -39002,7 +39002,7 @@
         <v>45995</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -39075,7 +39075,7 @@
         <v>45338</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -39148,7 +39148,7 @@
         <v>44998</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -39221,7 +39221,7 @@
         <v>45995</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -39294,7 +39294,7 @@
         <v>46127</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -39367,7 +39367,7 @@
         <v>46000</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -39440,7 +39440,7 @@
         <v>45996</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -39513,7 +39513,7 @@
         <v>45999</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -39586,7 +39586,7 @@
         <v>44887</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -39659,7 +39659,7 @@
         <v>45758</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -39732,7 +39732,7 @@
         <v>46002</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -39805,7 +39805,7 @@
         <v>45525</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -39878,7 +39878,7 @@
         <v>46002</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -39951,7 +39951,7 @@
         <v>45261</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -40024,7 +40024,7 @@
         <v>45714</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -40097,7 +40097,7 @@
         <v>46031</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -40170,7 +40170,7 @@
         <v>45553</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -40243,7 +40243,7 @@
         <v>46135</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -40316,7 +40316,7 @@
         <v>45161</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -40389,7 +40389,7 @@
         <v>44896</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -40462,7 +40462,7 @@
         <v>44683</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -40535,7 +40535,7 @@
         <v>44851</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -40608,7 +40608,7 @@
         <v>45412</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -40681,7 +40681,7 @@
         <v>45443</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -40754,7 +40754,7 @@
         <v>45090</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -40827,7 +40827,7 @@
         <v>46006</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -40900,7 +40900,7 @@
         <v>46007</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -40973,7 +40973,7 @@
         <v>46135</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -41046,7 +41046,7 @@
         <v>46009</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -41119,7 +41119,7 @@
         <v>46010</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -41192,7 +41192,7 @@
         <v>45016</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -41270,7 +41270,7 @@
         <v>46135</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -41343,7 +41343,7 @@
         <v>44777</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -41416,7 +41416,7 @@
         <v>46010</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -41489,7 +41489,7 @@
         <v>45856</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -41562,7 +41562,7 @@
         <v>45856</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -41635,7 +41635,7 @@
         <v>46013</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -41708,7 +41708,7 @@
         <v>46013</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -41781,7 +41781,7 @@
         <v>46013</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -41854,7 +41854,7 @@
         <v>46016</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -41927,7 +41927,7 @@
         <v>46016</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -42000,7 +42000,7 @@
         <v>46016</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -42073,7 +42073,7 @@
         <v>46016</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -42146,7 +42146,7 @@
         <v>46016</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -42219,7 +42219,7 @@
         <v>46016</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -42292,7 +42292,7 @@
         <v>45231</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -42365,7 +42365,7 @@
         <v>46021</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -42438,7 +42438,7 @@
         <v>46021</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -42516,7 +42516,7 @@
         <v>45281</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -42589,7 +42589,7 @@
         <v>44865</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -42662,7 +42662,7 @@
         <v>45498</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -42735,7 +42735,7 @@
         <v>45915</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -42808,7 +42808,7 @@
         <v>46029</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -42881,7 +42881,7 @@
         <v>46140</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -42959,7 +42959,7 @@
         <v>46029</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -43032,7 +43032,7 @@
         <v>46029</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -43105,7 +43105,7 @@
         <v>45510</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -43178,7 +43178,7 @@
         <v>45510</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -43251,7 +43251,7 @@
         <v>44917</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -43329,7 +43329,7 @@
         <v>46140</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -43407,7 +43407,7 @@
         <v>45156</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -43480,7 +43480,7 @@
         <v>45671</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -43553,7 +43553,7 @@
         <v>44918</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -43626,7 +43626,7 @@
         <v>46029</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -43699,7 +43699,7 @@
         <v>45804</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -43772,7 +43772,7 @@
         <v>45691</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -43845,7 +43845,7 @@
         <v>46031</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -43918,7 +43918,7 @@
         <v>46140</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -43991,7 +43991,7 @@
         <v>46140</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -44064,7 +44064,7 @@
         <v>45128</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -44137,7 +44137,7 @@
         <v>44596</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -44210,7 +44210,7 @@
         <v>45674</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -44283,7 +44283,7 @@
         <v>46031</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -44356,7 +44356,7 @@
         <v>44602</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -44429,7 +44429,7 @@
         <v>44979</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -44502,7 +44502,7 @@
         <v>45243</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -44575,7 +44575,7 @@
         <v>45694</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -44648,7 +44648,7 @@
         <v>46035</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -44721,7 +44721,7 @@
         <v>44518</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -44794,7 +44794,7 @@
         <v>45873</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -44867,7 +44867,7 @@
         <v>45176</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -44940,7 +44940,7 @@
         <v>46042</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -45013,7 +45013,7 @@
         <v>46041</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -45086,7 +45086,7 @@
         <v>46041</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -45159,7 +45159,7 @@
         <v>45021</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -45232,7 +45232,7 @@
         <v>45071</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -45305,7 +45305,7 @@
         <v>45704</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -45378,7 +45378,7 @@
         <v>45733</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -45451,7 +45451,7 @@
         <v>46104</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -45524,7 +45524,7 @@
         <v>45804</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -45597,7 +45597,7 @@
         <v>46140</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -45675,7 +45675,7 @@
         <v>45832</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -45748,7 +45748,7 @@
         <v>45642</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -45821,7 +45821,7 @@
         <v>46043</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -45894,7 +45894,7 @@
         <v>45932</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -45967,7 +45967,7 @@
         <v>45866</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -46040,7 +46040,7 @@
         <v>44899</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -46113,7 +46113,7 @@
         <v>45370</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -46186,7 +46186,7 @@
         <v>44494</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -46259,7 +46259,7 @@
         <v>45611</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -46332,7 +46332,7 @@
         <v>45090</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -46405,7 +46405,7 @@
         <v>45090</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -46478,7 +46478,7 @@
         <v>45090</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -46551,7 +46551,7 @@
         <v>45751</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -46624,7 +46624,7 @@
         <v>46048</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -46697,7 +46697,7 @@
         <v>45281</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -46770,7 +46770,7 @@
         <v>45281</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -46843,7 +46843,7 @@
         <v>45114</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -46916,7 +46916,7 @@
         <v>45608</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -46989,7 +46989,7 @@
         <v>45418</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -47062,7 +47062,7 @@
         <v>44916</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -47135,7 +47135,7 @@
         <v>44977</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -47208,7 +47208,7 @@
         <v>45818</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -47281,7 +47281,7 @@
         <v>45621</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -47354,7 +47354,7 @@
         <v>44937</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -47427,7 +47427,7 @@
         <v>46050</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -47500,7 +47500,7 @@
         <v>46031</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -47573,7 +47573,7 @@
         <v>45432</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -47646,7 +47646,7 @@
         <v>46050</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -47719,7 +47719,7 @@
         <v>46050</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -47792,7 +47792,7 @@
         <v>46050</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -47865,7 +47865,7 @@
         <v>46055</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -47938,7 +47938,7 @@
         <v>46055</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -48011,7 +48011,7 @@
         <v>46059</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -48084,7 +48084,7 @@
         <v>46059</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -48157,7 +48157,7 @@
         <v>45811</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -48230,7 +48230,7 @@
         <v>46062</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -48303,7 +48303,7 @@
         <v>46062</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -48376,7 +48376,7 @@
         <v>46146</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -48449,7 +48449,7 @@
         <v>46064</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -48522,7 +48522,7 @@
         <v>46147</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -48595,7 +48595,7 @@
         <v>46148</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -48668,7 +48668,7 @@
         <v>46148</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -48741,7 +48741,7 @@
         <v>46148</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -48814,7 +48814,7 @@
         <v>46064</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -48887,7 +48887,7 @@
         <v>46066</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -48960,7 +48960,7 @@
         <v>46148</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -49033,7 +49033,7 @@
         <v>46148</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -49106,7 +49106,7 @@
         <v>46148</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -49179,7 +49179,7 @@
         <v>46147</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -49252,7 +49252,7 @@
         <v>46069</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -49325,7 +49325,7 @@
         <v>46069</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -49398,7 +49398,7 @@
         <v>46149</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -49471,7 +49471,7 @@
         <v>45579</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -49544,7 +49544,7 @@
         <v>46153</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -49622,7 +49622,7 @@
         <v>46153</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -49700,7 +49700,7 @@
         <v>46154</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -49773,7 +49773,7 @@
         <v>46083</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -49846,7 +49846,7 @@
         <v>46083</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -49919,7 +49919,7 @@
         <v>46154</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -49997,7 +49997,7 @@
         <v>45834</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -50070,7 +50070,7 @@
         <v>46084</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -50143,7 +50143,7 @@
         <v>46085</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -50216,7 +50216,7 @@
         <v>46085</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -50289,7 +50289,7 @@
         <v>46085</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -50362,7 +50362,7 @@
         <v>45904</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -50435,7 +50435,7 @@
         <v>46090</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -50513,7 +50513,7 @@
         <v>44798</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -50586,7 +50586,7 @@
         <v>46092</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -50659,7 +50659,7 @@
         <v>46092</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -50732,7 +50732,7 @@
         <v>46092</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -50805,7 +50805,7 @@
         <v>46092</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -50878,7 +50878,7 @@
         <v>46092</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -50951,7 +50951,7 @@
         <v>46092</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -51024,7 +51024,7 @@
         <v>46163</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -51097,7 +51097,7 @@
         <v>46163</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -51170,7 +51170,7 @@
         <v>46163</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -51243,7 +51243,7 @@
         <v>45191</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -51316,7 +51316,7 @@
         <v>46163</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -51389,7 +51389,7 @@
         <v>46167</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -51462,7 +51462,7 @@
         <v>46167</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -51535,7 +51535,7 @@
         <v>46176</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -51608,7 +51608,7 @@
         <v>46177</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -51681,7 +51681,7 @@
         <v>46178</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -51754,7 +51754,7 @@
         <v>46195</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -51832,7 +51832,7 @@
         <v>46195</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -51910,7 +51910,7 @@
         <v>45552</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -51988,7 +51988,7 @@
         <v>46197</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -52066,7 +52066,7 @@
         <v>46196</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -52139,7 +52139,7 @@
         <v>46196</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -52212,7 +52212,7 @@
         <v>46199</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -52285,7 +52285,7 @@
         <v>46199</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -52358,7 +52358,7 @@
         <v>46199</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -52431,7 +52431,7 @@
         <v>46199</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -52504,7 +52504,7 @@
         <v>46199</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -52577,7 +52577,7 @@
         <v>46199</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -52650,7 +52650,7 @@
         <v>46203</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -52723,7 +52723,7 @@
         <v>46203</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -52796,7 +52796,7 @@
         <v>46203</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -52869,7 +52869,7 @@
         <v>45246</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -52942,7 +52942,7 @@
         <v>46217</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -53015,7 +53015,7 @@
         <v>46217</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -53088,7 +53088,7 @@
         <v>46217</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -53161,7 +53161,7 @@
         <v>46266</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -53234,7 +53234,7 @@
         <v>46266</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -53307,7 +53307,7 @@
         <v>46267</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -53380,7 +53380,7 @@
         <v>46269</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -53453,7 +53453,7 @@
         <v>46269</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -53526,7 +53526,7 @@
         <v>46274</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -53599,7 +53599,7 @@
         <v>46274</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -53672,7 +53672,7 @@
         <v>46233</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -53745,7 +53745,7 @@
         <v>46275</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -53818,7 +53818,7 @@
         <v>46279</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -53891,7 +53891,7 @@
         <v>46237</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -53964,7 +53964,7 @@
         <v>46273</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -54037,7 +54037,7 @@
         <v>46280</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -54110,7 +54110,7 @@
         <v>46279</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -54183,7 +54183,7 @@
         <v>46238</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -54256,7 +54256,7 @@
         <v>46240</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -54329,7 +54329,7 @@
         <v>46052</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -54407,7 +54407,7 @@
         <v>44911</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -54480,7 +54480,7 @@
         <v>44911</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -54553,7 +54553,7 @@
         <v>46199</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -54626,7 +54626,7 @@
         <v>46245</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -54699,7 +54699,7 @@
         <v>45975</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -54772,7 +54772,7 @@
         <v>46245</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -54845,7 +54845,7 @@
         <v>46147</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -54918,7 +54918,7 @@
         <v>46290</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -54991,7 +54991,7 @@
         <v>46290</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -55064,7 +55064,7 @@
         <v>46247</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -55137,7 +55137,7 @@
         <v>46281</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -55210,7 +55210,7 @@
         <v>46289</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -55283,7 +55283,7 @@
         <v>46290</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -55361,7 +55361,7 @@
         <v>46247</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -55434,7 +55434,7 @@
         <v>46290</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -55512,7 +55512,7 @@
         <v>46289</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -55585,7 +55585,7 @@
         <v>46294</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -55658,7 +55658,7 @@
         <v>46252</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -55731,7 +55731,7 @@
         <v>46253</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -55804,7 +55804,7 @@
         <v>46297</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -55877,7 +55877,7 @@
         <v>46297</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -55950,7 +55950,7 @@
         <v>46297</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -56028,7 +56028,7 @@
         <v>46247</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -56101,7 +56101,7 @@
         <v>46300</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -56174,7 +56174,7 @@
         <v>46261</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -56252,7 +56252,7 @@
         <v>46261</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -56330,7 +56330,7 @@
         <v>46262</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -56408,7 +56408,7 @@
         <v>44579</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -56486,7 +56486,7 @@
         <v>44893</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -56564,7 +56564,7 @@
         <v>44893</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -56642,7 +56642,7 @@
         <v>44893</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -56720,7 +56720,7 @@
         <v>45731</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -56793,7 +56793,7 @@
         <v>45736</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -56866,7 +56866,7 @@
         <v>46035</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -56944,7 +56944,7 @@
         <v>46163</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>

--- a/Översikt EDA.xlsx
+++ b/Översikt EDA.xlsx
@@ -601,7 +601,7 @@
         <v>45178</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -725,7 +725,7 @@
         <v>45726</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -843,7 +843,7 @@
         <v>44494</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -955,7 +955,7 @@
         <v>45090</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1070,7 +1070,7 @@
         <v>45306</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1188,7 +1188,7 @@
         <v>45154</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1298,7 +1298,7 @@
         <v>44791</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1406,7 +1406,7 @@
         <v>44740</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1518,7 +1518,7 @@
         <v>45407</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1626,7 +1626,7 @@
         <v>45754</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1737,7 +1737,7 @@
         <v>45293</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1852,7 +1852,7 @@
         <v>45358</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1963,7 +1963,7 @@
         <v>44916</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2074,7 +2074,7 @@
         <v>44868</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2180,7 +2180,7 @@
         <v>44865</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2286,7 +2286,7 @@
         <v>44888</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2396,7 +2396,7 @@
         <v>45243</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2502,7 +2502,7 @@
         <v>45091</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2612,7 +2612,7 @@
         <v>45315</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2722,7 +2722,7 @@
         <v>44970</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2828,7 +2828,7 @@
         <v>45310</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2934,7 +2934,7 @@
         <v>45426</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3040,7 +3040,7 @@
         <v>46290</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3146,7 +3146,7 @@
         <v>45575</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3252,7 +3252,7 @@
         <v>45856</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3358,7 +3358,7 @@
         <v>45545</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3464,7 +3464,7 @@
         <v>45257</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3569,7 +3569,7 @@
         <v>45721</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3674,7 +3674,7 @@
         <v>45532</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3779,7 +3779,7 @@
         <v>45376</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3888,7 +3888,7 @@
         <v>45243</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3993,7 +3993,7 @@
         <v>45432</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4098,7 +4098,7 @@
         <v>46092</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4203,7 +4203,7 @@
         <v>45244</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4308,7 +4308,7 @@
         <v>45777</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4422,7 +4422,7 @@
         <v>46269</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4532,7 +4532,7 @@
         <v>46269</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4641,7 +4641,7 @@
         <v>44579</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4751,7 +4751,7 @@
         <v>44889</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4824,7 +4824,7 @@
         <v>44683</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4897,7 +4897,7 @@
         <v>44810</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4970,7 +4970,7 @@
         <v>44529</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5043,7 +5043,7 @@
         <v>44712</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5116,7 +5116,7 @@
         <v>44852</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5189,7 +5189,7 @@
         <v>44889</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5262,7 +5262,7 @@
         <v>44608</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5340,7 +5340,7 @@
         <v>44582</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5413,7 +5413,7 @@
         <v>44582</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5486,7 +5486,7 @@
         <v>44851</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5559,7 +5559,7 @@
         <v>44538</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5632,7 +5632,7 @@
         <v>44740</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5705,7 +5705,7 @@
         <v>44837</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5778,7 +5778,7 @@
         <v>44816</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5851,7 +5851,7 @@
         <v>44712</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5924,7 +5924,7 @@
         <v>44532</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5997,7 +5997,7 @@
         <v>44874</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6070,7 +6070,7 @@
         <v>44529</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6143,7 +6143,7 @@
         <v>44722</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6216,7 +6216,7 @@
         <v>44586</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6289,7 +6289,7 @@
         <v>44685</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6362,7 +6362,7 @@
         <v>44809</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6435,7 +6435,7 @@
         <v>44858</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6508,7 +6508,7 @@
         <v>44491</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6581,7 +6581,7 @@
         <v>44670</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6654,7 +6654,7 @@
         <v>44659</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6727,7 +6727,7 @@
         <v>44740</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6800,7 +6800,7 @@
         <v>44510</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6873,7 +6873,7 @@
         <v>44733</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6946,7 +6946,7 @@
         <v>44853</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7019,7 +7019,7 @@
         <v>44557</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7097,7 +7097,7 @@
         <v>44546</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7170,7 +7170,7 @@
         <v>44817</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7243,7 +7243,7 @@
         <v>44614</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7316,7 +7316,7 @@
         <v>44883</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7389,7 +7389,7 @@
         <v>44874</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7462,7 +7462,7 @@
         <v>44874</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7535,7 +7535,7 @@
         <v>44515</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7613,7 +7613,7 @@
         <v>44799</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7686,7 +7686,7 @@
         <v>44881</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7759,7 +7759,7 @@
         <v>44881</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7832,7 +7832,7 @@
         <v>44588</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7905,7 +7905,7 @@
         <v>44868</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7978,7 +7978,7 @@
         <v>44705</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8051,7 +8051,7 @@
         <v>44581</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8124,7 +8124,7 @@
         <v>44560</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8202,7 +8202,7 @@
         <v>44573</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8275,7 +8275,7 @@
         <v>44614</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8348,7 +8348,7 @@
         <v>44714</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8421,7 +8421,7 @@
         <v>44877</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8494,7 +8494,7 @@
         <v>44491</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8567,7 +8567,7 @@
         <v>44852</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8640,7 +8640,7 @@
         <v>44662</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8713,7 +8713,7 @@
         <v>44584</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8786,7 +8786,7 @@
         <v>44643</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8859,7 +8859,7 @@
         <v>44614</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8932,7 +8932,7 @@
         <v>44726</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9005,7 +9005,7 @@
         <v>44818</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9078,7 +9078,7 @@
         <v>45736</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9151,7 +9151,7 @@
         <v>44586</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9224,7 +9224,7 @@
         <v>45040</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9297,7 +9297,7 @@
         <v>44588</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9370,7 +9370,7 @@
         <v>44979</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         <v>45267</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9516,7 +9516,7 @@
         <v>44881</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9594,7 +9594,7 @@
         <v>45162</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9667,7 +9667,7 @@
         <v>45054</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9740,7 +9740,7 @@
         <v>45054</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9813,7 +9813,7 @@
         <v>44918</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9886,7 +9886,7 @@
         <v>45189</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9959,7 +9959,7 @@
         <v>44918</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10032,7 +10032,7 @@
         <v>45184</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10105,7 +10105,7 @@
         <v>44899</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10178,7 +10178,7 @@
         <v>45694</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10251,7 +10251,7 @@
         <v>45733</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10324,7 +10324,7 @@
         <v>45763</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10397,7 +10397,7 @@
         <v>45245</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10475,7 +10475,7 @@
         <v>45510</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10548,7 +10548,7 @@
         <v>45265</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10621,7 +10621,7 @@
         <v>44937</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10694,7 +10694,7 @@
         <v>45338</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10767,7 +10767,7 @@
         <v>44629</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10840,7 +10840,7 @@
         <v>45510</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10913,7 +10913,7 @@
         <v>45623</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10986,7 +10986,7 @@
         <v>45091</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11059,7 +11059,7 @@
         <v>45733</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11132,7 +11132,7 @@
         <v>45110</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11205,7 +11205,7 @@
         <v>45090</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11278,7 +11278,7 @@
         <v>45544</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11351,7 +11351,7 @@
         <v>45512</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11424,7 +11424,7 @@
         <v>45609</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11497,7 +11497,7 @@
         <v>45195</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11570,7 +11570,7 @@
         <v>45482</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11643,7 +11643,7 @@
         <v>45390</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11716,7 +11716,7 @@
         <v>45727</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11789,7 +11789,7 @@
         <v>45727</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11862,7 +11862,7 @@
         <v>45355</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11935,7 +11935,7 @@
         <v>45629</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12008,7 +12008,7 @@
         <v>45161</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12081,7 +12081,7 @@
         <v>45336</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12154,7 +12154,7 @@
         <v>45629</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12227,7 +12227,7 @@
         <v>45110</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12300,7 +12300,7 @@
         <v>45173</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12373,7 +12373,7 @@
         <v>45173</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12446,7 +12446,7 @@
         <v>44874</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12519,7 +12519,7 @@
         <v>45749</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12592,7 +12592,7 @@
         <v>45435</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12665,7 +12665,7 @@
         <v>44956</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12738,7 +12738,7 @@
         <v>44887</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12811,7 +12811,7 @@
         <v>45434</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12884,7 +12884,7 @@
         <v>45140</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12957,7 +12957,7 @@
         <v>45028</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13030,7 +13030,7 @@
         <v>45271</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13103,7 +13103,7 @@
         <v>45722</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13176,7 +13176,7 @@
         <v>45245</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13254,7 +13254,7 @@
         <v>45623</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13327,7 +13327,7 @@
         <v>45474</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13400,7 +13400,7 @@
         <v>45058</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13473,7 +13473,7 @@
         <v>44904</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13546,7 +13546,7 @@
         <v>45729</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13619,7 +13619,7 @@
         <v>45293</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13692,7 +13692,7 @@
         <v>45588</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13765,7 +13765,7 @@
         <v>45491</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13838,7 +13838,7 @@
         <v>45616</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13911,7 +13911,7 @@
         <v>44581</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13984,7 +13984,7 @@
         <v>44991</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14057,7 +14057,7 @@
         <v>44901</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14130,7 +14130,7 @@
         <v>44641</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14203,7 +14203,7 @@
         <v>44998</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14276,7 +14276,7 @@
         <v>45694</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14349,7 +14349,7 @@
         <v>44693</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14422,7 +14422,7 @@
         <v>45429</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14495,7 +14495,7 @@
         <v>44867</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14568,7 +14568,7 @@
         <v>44896</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14641,7 +14641,7 @@
         <v>45231</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14714,7 +14714,7 @@
         <v>45456</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14787,7 +14787,7 @@
         <v>45261</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14860,7 +14860,7 @@
         <v>45226</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14933,7 +14933,7 @@
         <v>44602</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15006,7 +15006,7 @@
         <v>45149</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15084,7 +15084,7 @@
         <v>45558</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15157,7 +15157,7 @@
         <v>45021</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15230,7 +15230,7 @@
         <v>44790</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15303,7 +15303,7 @@
         <v>44943</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15376,7 +15376,7 @@
         <v>45061</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15449,7 +15449,7 @@
         <v>44942</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15522,7 +15522,7 @@
         <v>45016</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15600,7 +15600,7 @@
         <v>44935</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15673,7 +15673,7 @@
         <v>45273</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15746,7 +15746,7 @@
         <v>45142</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15819,7 +15819,7 @@
         <v>45142</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15892,7 +15892,7 @@
         <v>45231</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15965,7 +15965,7 @@
         <v>45680</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16038,7 +16038,7 @@
         <v>45119</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16111,7 +16111,7 @@
         <v>45729</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16184,7 +16184,7 @@
         <v>45582</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16257,7 +16257,7 @@
         <v>45274</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16330,7 +16330,7 @@
         <v>45932</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16403,7 +16403,7 @@
         <v>45443</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16476,7 +16476,7 @@
         <v>45176</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16549,7 +16549,7 @@
         <v>45614</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16622,7 +16622,7 @@
         <v>45804</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16695,7 +16695,7 @@
         <v>45197</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16768,7 +16768,7 @@
         <v>44614</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16841,7 +16841,7 @@
         <v>45156</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16914,7 +16914,7 @@
         <v>45915</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16987,7 +16987,7 @@
         <v>45856</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17060,7 +17060,7 @@
         <v>45041</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17133,7 +17133,7 @@
         <v>45856</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17206,7 +17206,7 @@
         <v>45195</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17279,7 +17279,7 @@
         <v>46031</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17352,7 +17352,7 @@
         <v>44966</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17425,7 +17425,7 @@
         <v>45714</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17498,7 +17498,7 @@
         <v>45583</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17571,7 +17571,7 @@
         <v>44865</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17644,7 +17644,7 @@
         <v>45691</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17717,7 +17717,7 @@
         <v>44494</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17790,7 +17790,7 @@
         <v>45525</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17863,7 +17863,7 @@
         <v>45525</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17936,7 +17936,7 @@
         <v>45608</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18009,7 +18009,7 @@
         <v>45891</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18087,7 +18087,7 @@
         <v>45671</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18160,7 +18160,7 @@
         <v>45873</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18233,7 +18233,7 @@
         <v>45135</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18306,7 +18306,7 @@
         <v>45554</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18379,7 +18379,7 @@
         <v>45173</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18452,7 +18452,7 @@
         <v>45140</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18525,7 +18525,7 @@
         <v>45897</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18603,7 +18603,7 @@
         <v>45897</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18681,7 +18681,7 @@
         <v>45897</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18754,7 +18754,7 @@
         <v>45866</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18827,7 +18827,7 @@
         <v>45751</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18900,7 +18900,7 @@
         <v>45642</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18973,7 +18973,7 @@
         <v>45811</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19046,7 +19046,7 @@
         <v>46140</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19124,7 +19124,7 @@
         <v>46140</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19197,7 +19197,7 @@
         <v>46140</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19270,7 +19270,7 @@
         <v>45243</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19343,7 +19343,7 @@
         <v>46140</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19421,7 +19421,7 @@
         <v>45733</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19494,7 +19494,7 @@
         <v>46031</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19567,7 +19567,7 @@
         <v>45903</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19640,7 +19640,7 @@
         <v>46140</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19718,7 +19718,7 @@
         <v>45903</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19791,7 +19791,7 @@
         <v>45903</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19864,7 +19864,7 @@
         <v>45418</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19937,7 +19937,7 @@
         <v>45903</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20010,7 +20010,7 @@
         <v>45300</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20083,7 +20083,7 @@
         <v>45818</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20156,7 +20156,7 @@
         <v>44865</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20229,7 +20229,7 @@
         <v>45621</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20302,7 +20302,7 @@
         <v>45910</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20375,7 +20375,7 @@
         <v>45153</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20448,7 +20448,7 @@
         <v>46146</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20521,7 +20521,7 @@
         <v>45918</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20599,7 +20599,7 @@
         <v>45910</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20672,7 +20672,7 @@
         <v>45477</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20745,7 +20745,7 @@
         <v>45920</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20818,7 +20818,7 @@
         <v>45267</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20891,7 +20891,7 @@
         <v>46147</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20964,7 +20964,7 @@
         <v>45924</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21037,7 +21037,7 @@
         <v>45924</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21110,7 +21110,7 @@
         <v>44872</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21183,7 +21183,7 @@
         <v>46148</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21256,7 +21256,7 @@
         <v>46148</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21329,7 +21329,7 @@
         <v>45924</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21402,7 +21402,7 @@
         <v>46148</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21475,7 +21475,7 @@
         <v>45929</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21548,7 +21548,7 @@
         <v>46148</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21621,7 +21621,7 @@
         <v>46148</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21694,7 +21694,7 @@
         <v>46148</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21767,7 +21767,7 @@
         <v>45929</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21840,7 +21840,7 @@
         <v>46149</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21913,7 +21913,7 @@
         <v>45152</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -21986,7 +21986,7 @@
         <v>45929</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22059,7 +22059,7 @@
         <v>45929</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22132,7 +22132,7 @@
         <v>44596</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22205,7 +22205,7 @@
         <v>45015</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22278,7 +22278,7 @@
         <v>46153</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22356,7 +22356,7 @@
         <v>46153</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22434,7 +22434,7 @@
         <v>45936</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22512,7 +22512,7 @@
         <v>45888</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22585,7 +22585,7 @@
         <v>45936</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22663,7 +22663,7 @@
         <v>45089</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22736,7 +22736,7 @@
         <v>44998</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22809,7 +22809,7 @@
         <v>45936</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -22882,7 +22882,7 @@
         <v>44573</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -22955,7 +22955,7 @@
         <v>45252</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23028,7 +23028,7 @@
         <v>44834</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23106,7 +23106,7 @@
         <v>44998</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23179,7 +23179,7 @@
         <v>45191</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23252,7 +23252,7 @@
         <v>46154</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23330,7 +23330,7 @@
         <v>46154</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23403,7 +23403,7 @@
         <v>45532</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23476,7 +23476,7 @@
         <v>44845</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23549,7 +23549,7 @@
         <v>45579</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23622,7 +23622,7 @@
         <v>44917</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23700,7 +23700,7 @@
         <v>44956</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23773,7 +23773,7 @@
         <v>45950</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -23851,7 +23851,7 @@
         <v>45691</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -23924,7 +23924,7 @@
         <v>45440</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -23997,7 +23997,7 @@
         <v>45834</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24070,7 +24070,7 @@
         <v>45408</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24143,7 +24143,7 @@
         <v>45638</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24216,7 +24216,7 @@
         <v>44911</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24289,7 +24289,7 @@
         <v>44523</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24362,7 +24362,7 @@
         <v>45477</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24435,7 +24435,7 @@
         <v>45957</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24508,7 +24508,7 @@
         <v>44518</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24581,7 +24581,7 @@
         <v>45397</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24654,7 +24654,7 @@
         <v>45358</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24727,7 +24727,7 @@
         <v>45623</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -24800,7 +24800,7 @@
         <v>45614</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -24873,7 +24873,7 @@
         <v>44798</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -24946,7 +24946,7 @@
         <v>45904</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25019,7 +25019,7 @@
         <v>45966</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25092,7 +25092,7 @@
         <v>45968</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25165,7 +25165,7 @@
         <v>45203</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25238,7 +25238,7 @@
         <v>45520</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25311,7 +25311,7 @@
         <v>45971</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25384,7 +25384,7 @@
         <v>45737</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25457,7 +25457,7 @@
         <v>45971</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25530,7 +25530,7 @@
         <v>45971</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25608,7 +25608,7 @@
         <v>45161</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25681,7 +25681,7 @@
         <v>45971</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -25759,7 +25759,7 @@
         <v>45971</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -25832,7 +25832,7 @@
         <v>46163</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -25905,7 +25905,7 @@
         <v>44986</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -25978,7 +25978,7 @@
         <v>45184</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26051,7 +26051,7 @@
         <v>45184</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26124,7 +26124,7 @@
         <v>45975</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26197,7 +26197,7 @@
         <v>45191</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26270,7 +26270,7 @@
         <v>44543</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26343,7 +26343,7 @@
         <v>45743</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26416,7 +26416,7 @@
         <v>44865</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26489,7 +26489,7 @@
         <v>46163</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26562,7 +26562,7 @@
         <v>46163</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26635,7 +26635,7 @@
         <v>45981</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -26708,7 +26708,7 @@
         <v>45981</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -26781,7 +26781,7 @@
         <v>46163</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -26854,7 +26854,7 @@
         <v>44915</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -26927,7 +26927,7 @@
         <v>44915</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27000,7 +27000,7 @@
         <v>45692</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27073,7 +27073,7 @@
         <v>45980</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27146,7 +27146,7 @@
         <v>45104</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27219,7 +27219,7 @@
         <v>45981</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27292,7 +27292,7 @@
         <v>45981</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27365,7 +27365,7 @@
         <v>45210</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27438,7 +27438,7 @@
         <v>45733</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27511,7 +27511,7 @@
         <v>44901</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27584,7 +27584,7 @@
         <v>46167</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -27657,7 +27657,7 @@
         <v>44851</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -27730,7 +27730,7 @@
         <v>45106</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -27803,7 +27803,7 @@
         <v>44777</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -27876,7 +27876,7 @@
         <v>45090</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -27949,7 +27949,7 @@
         <v>46167</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28022,7 +28022,7 @@
         <v>45980</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28095,7 +28095,7 @@
         <v>45680</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28168,7 +28168,7 @@
         <v>45021</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28246,7 +28246,7 @@
         <v>45992</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28319,7 +28319,7 @@
         <v>45176</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28392,7 +28392,7 @@
         <v>45992</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28465,7 +28465,7 @@
         <v>45992</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28538,7 +28538,7 @@
         <v>45994</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -28611,7 +28611,7 @@
         <v>45995</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -28684,7 +28684,7 @@
         <v>45994</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -28757,7 +28757,7 @@
         <v>45995</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -28830,7 +28830,7 @@
         <v>45999</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -28903,7 +28903,7 @@
         <v>45435</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -28976,7 +28976,7 @@
         <v>45996</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29049,7 +29049,7 @@
         <v>44881</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29122,7 +29122,7 @@
         <v>46000</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29195,7 +29195,7 @@
         <v>45629</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29268,7 +29268,7 @@
         <v>45603</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29341,7 +29341,7 @@
         <v>45559</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29414,7 +29414,7 @@
         <v>45498</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29487,7 +29487,7 @@
         <v>46002</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -29560,7 +29560,7 @@
         <v>44916</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -29633,7 +29633,7 @@
         <v>46002</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -29706,7 +29706,7 @@
         <v>45756</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -29779,7 +29779,7 @@
         <v>45756</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -29852,7 +29852,7 @@
         <v>45614</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -29925,7 +29925,7 @@
         <v>45281</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -29998,7 +29998,7 @@
         <v>45579</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30071,7 +30071,7 @@
         <v>45636</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30149,7 +30149,7 @@
         <v>46006</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30222,7 +30222,7 @@
         <v>46007</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30295,7 +30295,7 @@
         <v>45061</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30368,7 +30368,7 @@
         <v>45111</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30441,7 +30441,7 @@
         <v>46009</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30514,7 +30514,7 @@
         <v>45204</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -30587,7 +30587,7 @@
         <v>44979</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -30660,7 +30660,7 @@
         <v>46010</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -30733,7 +30733,7 @@
         <v>46013</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -30806,7 +30806,7 @@
         <v>46013</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -30879,7 +30879,7 @@
         <v>46013</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -30952,7 +30952,7 @@
         <v>46010</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31025,7 +31025,7 @@
         <v>46016</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31098,7 +31098,7 @@
         <v>46016</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31171,7 +31171,7 @@
         <v>46016</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31244,7 +31244,7 @@
         <v>44977</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31317,7 +31317,7 @@
         <v>46016</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31390,7 +31390,7 @@
         <v>46016</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31463,7 +31463,7 @@
         <v>45250</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -31536,7 +31536,7 @@
         <v>46016</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -31609,7 +31609,7 @@
         <v>46021</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -31682,7 +31682,7 @@
         <v>46021</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -31760,7 +31760,7 @@
         <v>44970</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -31833,7 +31833,7 @@
         <v>44740</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -31906,7 +31906,7 @@
         <v>46029</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -31979,7 +31979,7 @@
         <v>46029</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -32052,7 +32052,7 @@
         <v>46029</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32125,7 +32125,7 @@
         <v>46029</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32198,7 +32198,7 @@
         <v>46031</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32271,7 +32271,7 @@
         <v>45188</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -32344,7 +32344,7 @@
         <v>46031</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -32417,7 +32417,7 @@
         <v>45704</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -32490,7 +32490,7 @@
         <v>45723</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -32563,7 +32563,7 @@
         <v>46035</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -32636,7 +32636,7 @@
         <v>45520</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -32709,7 +32709,7 @@
         <v>46176</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -32782,7 +32782,7 @@
         <v>46177</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -32855,7 +32855,7 @@
         <v>46178</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -32928,7 +32928,7 @@
         <v>46041</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -33001,7 +33001,7 @@
         <v>46041</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -33074,7 +33074,7 @@
         <v>45510</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -33147,7 +33147,7 @@
         <v>46042</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -33220,7 +33220,7 @@
         <v>45036</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -33293,7 +33293,7 @@
         <v>46043</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -33366,7 +33366,7 @@
         <v>45071</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -33439,7 +33439,7 @@
         <v>44839</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -33512,7 +33512,7 @@
         <v>45301</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -33590,7 +33590,7 @@
         <v>45412</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -33663,7 +33663,7 @@
         <v>46048</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -33736,7 +33736,7 @@
         <v>45646</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -33809,7 +33809,7 @@
         <v>44799</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -33882,7 +33882,7 @@
         <v>46050</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -33955,7 +33955,7 @@
         <v>46050</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -34028,7 +34028,7 @@
         <v>46050</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -34101,7 +34101,7 @@
         <v>46050</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -34174,7 +34174,7 @@
         <v>46055</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -34247,7 +34247,7 @@
         <v>44625</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -34320,7 +34320,7 @@
         <v>45443</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -34393,7 +34393,7 @@
         <v>46059</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -34466,7 +34466,7 @@
         <v>45475</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -34539,7 +34539,7 @@
         <v>45307</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -34612,7 +34612,7 @@
         <v>46059</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -34685,7 +34685,7 @@
         <v>46062</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -34758,7 +34758,7 @@
         <v>46062</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -34831,7 +34831,7 @@
         <v>46064</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -34904,7 +34904,7 @@
         <v>46064</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -34977,7 +34977,7 @@
         <v>46069</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -35050,7 +35050,7 @@
         <v>46069</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -35123,7 +35123,7 @@
         <v>46066</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -35196,7 +35196,7 @@
         <v>44858</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -35269,7 +35269,7 @@
         <v>44970</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -35342,7 +35342,7 @@
         <v>45310</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -35415,7 +35415,7 @@
         <v>45090</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -35488,7 +35488,7 @@
         <v>45090</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -35561,7 +35561,7 @@
         <v>45533</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -35634,7 +35634,7 @@
         <v>45392</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -35707,7 +35707,7 @@
         <v>44746</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -35780,7 +35780,7 @@
         <v>46084</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -35853,7 +35853,7 @@
         <v>46083</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -35926,7 +35926,7 @@
         <v>46083</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -35999,7 +35999,7 @@
         <v>44951</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -36072,7 +36072,7 @@
         <v>46085</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -36145,7 +36145,7 @@
         <v>46085</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -36218,7 +36218,7 @@
         <v>46085</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -36291,7 +36291,7 @@
         <v>46090</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -36369,7 +36369,7 @@
         <v>44798</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -36442,7 +36442,7 @@
         <v>46092</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -36515,7 +36515,7 @@
         <v>46092</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -36588,7 +36588,7 @@
         <v>46092</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -36661,7 +36661,7 @@
         <v>46092</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -36734,7 +36734,7 @@
         <v>46092</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -36807,7 +36807,7 @@
         <v>46092</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -36880,7 +36880,7 @@
         <v>45210</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -36953,7 +36953,7 @@
         <v>44896</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -37026,7 +37026,7 @@
         <v>45603</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -37099,7 +37099,7 @@
         <v>46099</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -37172,7 +37172,7 @@
         <v>46196</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -37245,7 +37245,7 @@
         <v>45308</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -37318,7 +37318,7 @@
         <v>46099</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -37391,7 +37391,7 @@
         <v>46100</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -37469,7 +37469,7 @@
         <v>46195</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -37547,7 +37547,7 @@
         <v>45139</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -37620,7 +37620,7 @@
         <v>46195</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -37698,7 +37698,7 @@
         <v>46101</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -37771,7 +37771,7 @@
         <v>45467</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -37844,7 +37844,7 @@
         <v>46104</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -37917,7 +37917,7 @@
         <v>45105</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -37990,7 +37990,7 @@
         <v>45091</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -38063,7 +38063,7 @@
         <v>45091</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -38136,7 +38136,7 @@
         <v>45751</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -38209,7 +38209,7 @@
         <v>45278</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -38282,7 +38282,7 @@
         <v>44894</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -38355,7 +38355,7 @@
         <v>46196</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -38428,7 +38428,7 @@
         <v>45245</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -38506,7 +38506,7 @@
         <v>46197</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -38584,7 +38584,7 @@
         <v>45552</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -38662,7 +38662,7 @@
         <v>46108</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -38735,7 +38735,7 @@
         <v>46107</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -38808,7 +38808,7 @@
         <v>46108</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -38881,7 +38881,7 @@
         <v>45166</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -38954,7 +38954,7 @@
         <v>46199</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -39027,7 +39027,7 @@
         <v>46119</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -39100,7 +39100,7 @@
         <v>46199</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -39173,7 +39173,7 @@
         <v>46120</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -39246,7 +39246,7 @@
         <v>45173</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -39319,7 +39319,7 @@
         <v>46199</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -39392,7 +39392,7 @@
         <v>46199</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -39465,7 +39465,7 @@
         <v>46119</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -39538,7 +39538,7 @@
         <v>46199</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -39611,7 +39611,7 @@
         <v>44557</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -39684,7 +39684,7 @@
         <v>46070</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -39757,7 +39757,7 @@
         <v>46119</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -39830,7 +39830,7 @@
         <v>46070</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -39903,7 +39903,7 @@
         <v>46124</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -39976,7 +39976,7 @@
         <v>46124</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -40049,7 +40049,7 @@
         <v>45085</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -40122,7 +40122,7 @@
         <v>44575</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -40195,7 +40195,7 @@
         <v>45758</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -40268,7 +40268,7 @@
         <v>44908</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -40341,7 +40341,7 @@
         <v>45600</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -40414,7 +40414,7 @@
         <v>46199</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -40487,7 +40487,7 @@
         <v>46127</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -40560,7 +40560,7 @@
         <v>45092</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -40633,7 +40633,7 @@
         <v>45541</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -40706,7 +40706,7 @@
         <v>45296</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -40779,7 +40779,7 @@
         <v>45714</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -40852,7 +40852,7 @@
         <v>46203</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -40925,7 +40925,7 @@
         <v>46135</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -40998,7 +40998,7 @@
         <v>45246</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -41071,7 +41071,7 @@
         <v>46135</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -41144,7 +41144,7 @@
         <v>45197</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -41217,7 +41217,7 @@
         <v>45224</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -41290,7 +41290,7 @@
         <v>46135</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -41363,7 +41363,7 @@
         <v>45532</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -41436,7 +41436,7 @@
         <v>46203</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -41509,7 +41509,7 @@
         <v>44899</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -41582,7 +41582,7 @@
         <v>46203</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -41655,7 +41655,7 @@
         <v>44537</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -41728,7 +41728,7 @@
         <v>45832</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -41801,7 +41801,7 @@
         <v>45037</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -41874,7 +41874,7 @@
         <v>45719</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -41947,7 +41947,7 @@
         <v>44901</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -42020,7 +42020,7 @@
         <v>45611</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -42093,7 +42093,7 @@
         <v>46104</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -42166,7 +42166,7 @@
         <v>45114</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -42239,7 +42239,7 @@
         <v>45804</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -42312,7 +42312,7 @@
         <v>45301</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -42385,7 +42385,7 @@
         <v>45617</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -42458,7 +42458,7 @@
         <v>44537</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -42531,7 +42531,7 @@
         <v>45054</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -42604,7 +42604,7 @@
         <v>45549</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -42677,7 +42677,7 @@
         <v>45084</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -42750,7 +42750,7 @@
         <v>44546</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -42823,7 +42823,7 @@
         <v>44840</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -42896,7 +42896,7 @@
         <v>45685</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -42969,7 +42969,7 @@
         <v>44966</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -43042,7 +43042,7 @@
         <v>45090</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -43115,7 +43115,7 @@
         <v>45090</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -43188,7 +43188,7 @@
         <v>45090</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -43261,7 +43261,7 @@
         <v>45553</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -43334,7 +43334,7 @@
         <v>45736</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -43407,7 +43407,7 @@
         <v>45106</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -43480,7 +43480,7 @@
         <v>46217</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -43553,7 +43553,7 @@
         <v>44804</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -43626,7 +43626,7 @@
         <v>46217</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -43699,7 +43699,7 @@
         <v>46217</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -43772,7 +43772,7 @@
         <v>45450</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -43845,7 +43845,7 @@
         <v>45290</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -43918,7 +43918,7 @@
         <v>45290</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -43991,7 +43991,7 @@
         <v>45146</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -44064,7 +44064,7 @@
         <v>45176</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -44137,7 +44137,7 @@
         <v>45539</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -44210,7 +44210,7 @@
         <v>45754</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -44283,7 +44283,7 @@
         <v>45654</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -44356,7 +44356,7 @@
         <v>45152</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -44429,7 +44429,7 @@
         <v>45152</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -44502,7 +44502,7 @@
         <v>46275</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -44575,7 +44575,7 @@
         <v>46274</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -44648,7 +44648,7 @@
         <v>46274</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -44721,7 +44721,7 @@
         <v>46233</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -44794,7 +44794,7 @@
         <v>45261</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -44867,7 +44867,7 @@
         <v>45775</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -44940,7 +44940,7 @@
         <v>45098</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -45013,7 +45013,7 @@
         <v>46279</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -45086,7 +45086,7 @@
         <v>46279</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -45159,7 +45159,7 @@
         <v>46273</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -45232,7 +45232,7 @@
         <v>45272</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -45305,7 +45305,7 @@
         <v>44683</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -45378,7 +45378,7 @@
         <v>45084</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -45451,7 +45451,7 @@
         <v>46238</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -45524,7 +45524,7 @@
         <v>45204</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -45597,7 +45597,7 @@
         <v>45279</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -45670,7 +45670,7 @@
         <v>46280</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -45743,7 +45743,7 @@
         <v>45525</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -45816,7 +45816,7 @@
         <v>46237</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -45889,7 +45889,7 @@
         <v>45224</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -45967,7 +45967,7 @@
         <v>46240</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -46040,7 +46040,7 @@
         <v>45267</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -46113,7 +46113,7 @@
         <v>45015</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -46186,7 +46186,7 @@
         <v>45370</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -46259,7 +46259,7 @@
         <v>44966</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -46332,7 +46332,7 @@
         <v>45092</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -46405,7 +46405,7 @@
         <v>44883</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -46478,7 +46478,7 @@
         <v>45684</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -46551,7 +46551,7 @@
         <v>46052</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -46629,7 +46629,7 @@
         <v>45281</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -46702,7 +46702,7 @@
         <v>45975</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -46775,7 +46775,7 @@
         <v>44911</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -46848,7 +46848,7 @@
         <v>45603</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -46921,7 +46921,7 @@
         <v>46199</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -46994,7 +46994,7 @@
         <v>45275</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -47067,7 +47067,7 @@
         <v>44911</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -47140,7 +47140,7 @@
         <v>46147</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -47213,7 +47213,7 @@
         <v>45128</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -47286,7 +47286,7 @@
         <v>45756</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -47359,7 +47359,7 @@
         <v>45281</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -47432,7 +47432,7 @@
         <v>44602</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -47505,7 +47505,7 @@
         <v>45161</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -47578,7 +47578,7 @@
         <v>46289</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -47651,7 +47651,7 @@
         <v>46281</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -47724,7 +47724,7 @@
         <v>45245</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -47802,7 +47802,7 @@
         <v>46245</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -47875,7 +47875,7 @@
         <v>45149</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -47953,7 +47953,7 @@
         <v>45159</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -48026,7 +48026,7 @@
         <v>46245</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -48099,7 +48099,7 @@
         <v>46289</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -48172,7 +48172,7 @@
         <v>45089</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -48245,7 +48245,7 @@
         <v>45426</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -48318,7 +48318,7 @@
         <v>45310</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -48391,7 +48391,7 @@
         <v>45310</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -48464,7 +48464,7 @@
         <v>45090</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -48537,7 +48537,7 @@
         <v>44700</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -48615,7 +48615,7 @@
         <v>45432</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -48688,7 +48688,7 @@
         <v>45054</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -48761,7 +48761,7 @@
         <v>45336</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -48834,7 +48834,7 @@
         <v>45546</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -48907,7 +48907,7 @@
         <v>45455</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -48980,7 +48980,7 @@
         <v>45040</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -49053,7 +49053,7 @@
         <v>46290</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -49126,7 +49126,7 @@
         <v>46290</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -49199,7 +49199,7 @@
         <v>46247</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -49272,7 +49272,7 @@
         <v>46247</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -49345,7 +49345,7 @@
         <v>45294</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -49418,7 +49418,7 @@
         <v>45253</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -49491,7 +49491,7 @@
         <v>45541</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -49564,7 +49564,7 @@
         <v>46290</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -49642,7 +49642,7 @@
         <v>46290</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -49720,7 +49720,7 @@
         <v>46294</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -49793,7 +49793,7 @@
         <v>45692</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -49866,7 +49866,7 @@
         <v>46252</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -49939,7 +49939,7 @@
         <v>45674</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -50012,7 +50012,7 @@
         <v>44966</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -50085,7 +50085,7 @@
         <v>44998</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -50158,7 +50158,7 @@
         <v>44896</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -50231,7 +50231,7 @@
         <v>45306</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -50304,7 +50304,7 @@
         <v>45676</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -50377,7 +50377,7 @@
         <v>45221</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -50455,7 +50455,7 @@
         <v>45221</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -50533,7 +50533,7 @@
         <v>45229</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -50606,7 +50606,7 @@
         <v>44659</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -50679,7 +50679,7 @@
         <v>45175</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -50752,7 +50752,7 @@
         <v>45616</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -50825,7 +50825,7 @@
         <v>44776</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -50903,7 +50903,7 @@
         <v>44714</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -50976,7 +50976,7 @@
         <v>46297</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -51049,7 +51049,7 @@
         <v>44636</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -51122,7 +51122,7 @@
         <v>44636</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -51195,7 +51195,7 @@
         <v>46297</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -51273,7 +51273,7 @@
         <v>46297</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -51346,7 +51346,7 @@
         <v>46247</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -51419,7 +51419,7 @@
         <v>46253</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -51492,7 +51492,7 @@
         <v>44911</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -51565,7 +51565,7 @@
         <v>45015</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -51638,7 +51638,7 @@
         <v>45616</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -51711,7 +51711,7 @@
         <v>44665</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -51784,7 +51784,7 @@
         <v>45775</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -51857,7 +51857,7 @@
         <v>45777</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -51930,7 +51930,7 @@
         <v>45775</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -52003,7 +52003,7 @@
         <v>45783</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -52076,7 +52076,7 @@
         <v>45567</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -52149,7 +52149,7 @@
         <v>45730</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -52222,7 +52222,7 @@
         <v>45629</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -52295,7 +52295,7 @@
         <v>45792</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -52368,7 +52368,7 @@
         <v>46261</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -52446,7 +52446,7 @@
         <v>45576</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -52519,7 +52519,7 @@
         <v>46300</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -52592,7 +52592,7 @@
         <v>45796</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -52665,7 +52665,7 @@
         <v>46261</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -52743,7 +52743,7 @@
         <v>46262</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -52821,7 +52821,7 @@
         <v>45803</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -52894,7 +52894,7 @@
         <v>46266</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -52967,7 +52967,7 @@
         <v>46266</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -53040,7 +53040,7 @@
         <v>45805</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -53118,7 +53118,7 @@
         <v>46308</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -53191,7 +53191,7 @@
         <v>45310</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -53264,7 +53264,7 @@
         <v>45600</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -53337,7 +53337,7 @@
         <v>45726</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -53410,7 +53410,7 @@
         <v>45624</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -53483,7 +53483,7 @@
         <v>46309</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -53556,7 +53556,7 @@
         <v>46147</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -53629,7 +53629,7 @@
         <v>45378</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -53702,7 +53702,7 @@
         <v>44966</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -53780,7 +53780,7 @@
         <v>45502</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -53853,7 +53853,7 @@
         <v>45580</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -53926,7 +53926,7 @@
         <v>45628</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -53999,7 +53999,7 @@
         <v>46269</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -54072,7 +54072,7 @@
         <v>45583</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -54145,7 +54145,7 @@
         <v>45742</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -54218,7 +54218,7 @@
         <v>45590</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -54291,7 +54291,7 @@
         <v>46267</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -54364,7 +54364,7 @@
         <v>45818</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -54437,7 +54437,7 @@
         <v>45818</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -54510,7 +54510,7 @@
         <v>45817</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -54583,7 +54583,7 @@
         <v>45818</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -54656,7 +54656,7 @@
         <v>46310</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -54734,7 +54734,7 @@
         <v>45758</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -54807,7 +54807,7 @@
         <v>46311</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -54880,7 +54880,7 @@
         <v>46269</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -54953,7 +54953,7 @@
         <v>45835</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -55026,7 +55026,7 @@
         <v>45839</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -55099,7 +55099,7 @@
         <v>45838</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -55172,7 +55172,7 @@
         <v>45838</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -55245,7 +55245,7 @@
         <v>45839</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -55318,7 +55318,7 @@
         <v>45841</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -55391,7 +55391,7 @@
         <v>45817</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -55464,7 +55464,7 @@
         <v>45715</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -55537,7 +55537,7 @@
         <v>45253</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -55610,7 +55610,7 @@
         <v>45061</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -55683,7 +55683,7 @@
         <v>45588</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -55756,7 +55756,7 @@
         <v>45736</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -55829,7 +55829,7 @@
         <v>45848</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -55902,7 +55902,7 @@
         <v>45778</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -55975,7 +55975,7 @@
         <v>45856</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -56048,7 +56048,7 @@
         <v>45874</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -56121,7 +56121,7 @@
         <v>45883</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -56194,7 +56194,7 @@
         <v>45882</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -56267,7 +56267,7 @@
         <v>45882</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -56340,7 +56340,7 @@
         <v>44579</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -56418,7 +56418,7 @@
         <v>44893</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -56496,7 +56496,7 @@
         <v>44893</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -56574,7 +56574,7 @@
         <v>44893</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -56652,7 +56652,7 @@
         <v>45731</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -56725,7 +56725,7 @@
         <v>45736</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -56798,7 +56798,7 @@
         <v>46035</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -56876,7 +56876,7 @@
         <v>46163</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>

--- a/Översikt EDA.xlsx
+++ b/Översikt EDA.xlsx
@@ -601,7 +601,7 @@
         <v>45178</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -725,7 +725,7 @@
         <v>45726</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -843,7 +843,7 @@
         <v>44494</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -955,7 +955,7 @@
         <v>45090</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1070,7 +1070,7 @@
         <v>45306</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1188,7 +1188,7 @@
         <v>45154</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1298,7 +1298,7 @@
         <v>44791</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1406,7 +1406,7 @@
         <v>44740</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1518,7 +1518,7 @@
         <v>45407</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1626,7 +1626,7 @@
         <v>45754</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1737,7 +1737,7 @@
         <v>45293</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1852,7 +1852,7 @@
         <v>45358</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1963,7 +1963,7 @@
         <v>44916</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2074,7 +2074,7 @@
         <v>44868</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2180,7 +2180,7 @@
         <v>44865</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2286,7 +2286,7 @@
         <v>44888</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2396,7 +2396,7 @@
         <v>45243</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2502,7 +2502,7 @@
         <v>45091</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2612,7 +2612,7 @@
         <v>45315</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2722,7 +2722,7 @@
         <v>44970</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2828,7 +2828,7 @@
         <v>45310</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2934,7 +2934,7 @@
         <v>45426</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3040,7 +3040,7 @@
         <v>46290</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3146,7 +3146,7 @@
         <v>45575</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3252,7 +3252,7 @@
         <v>45856</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3358,7 +3358,7 @@
         <v>45545</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3464,7 +3464,7 @@
         <v>45257</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3569,7 +3569,7 @@
         <v>45721</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3674,7 +3674,7 @@
         <v>45532</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3779,7 +3779,7 @@
         <v>45376</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3888,7 +3888,7 @@
         <v>45243</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3993,7 +3993,7 @@
         <v>45432</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4098,7 +4098,7 @@
         <v>46092</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4203,7 +4203,7 @@
         <v>45244</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4308,7 +4308,7 @@
         <v>45777</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4422,7 +4422,7 @@
         <v>46269</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4532,7 +4532,7 @@
         <v>46269</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4641,7 +4641,7 @@
         <v>44579</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4751,7 +4751,7 @@
         <v>44889</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4824,7 +4824,7 @@
         <v>44683</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4897,7 +4897,7 @@
         <v>44810</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4970,7 +4970,7 @@
         <v>44529</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5043,7 +5043,7 @@
         <v>44712</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5116,7 +5116,7 @@
         <v>44852</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5189,7 +5189,7 @@
         <v>44889</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5262,7 +5262,7 @@
         <v>44608</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5340,7 +5340,7 @@
         <v>44582</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5413,7 +5413,7 @@
         <v>44582</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5486,7 +5486,7 @@
         <v>44851</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5559,7 +5559,7 @@
         <v>44538</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5632,7 +5632,7 @@
         <v>44740</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5705,7 +5705,7 @@
         <v>44837</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5778,7 +5778,7 @@
         <v>44816</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5851,7 +5851,7 @@
         <v>44712</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5924,7 +5924,7 @@
         <v>44532</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5997,7 +5997,7 @@
         <v>44874</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6070,7 +6070,7 @@
         <v>44529</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6143,7 +6143,7 @@
         <v>44722</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6216,7 +6216,7 @@
         <v>44586</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6289,7 +6289,7 @@
         <v>44685</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6362,7 +6362,7 @@
         <v>44809</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6435,7 +6435,7 @@
         <v>44858</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6508,7 +6508,7 @@
         <v>44491</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6581,7 +6581,7 @@
         <v>44670</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6654,7 +6654,7 @@
         <v>44659</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6727,7 +6727,7 @@
         <v>44740</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6800,7 +6800,7 @@
         <v>44510</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6873,7 +6873,7 @@
         <v>44733</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6946,7 +6946,7 @@
         <v>44853</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7019,7 +7019,7 @@
         <v>44557</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7097,7 +7097,7 @@
         <v>44546</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7170,7 +7170,7 @@
         <v>44817</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7243,7 +7243,7 @@
         <v>44614</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7316,7 +7316,7 @@
         <v>44883</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7389,7 +7389,7 @@
         <v>44874</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7462,7 +7462,7 @@
         <v>44874</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7535,7 +7535,7 @@
         <v>44515</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7613,7 +7613,7 @@
         <v>44799</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7686,7 +7686,7 @@
         <v>44881</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7759,7 +7759,7 @@
         <v>44881</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7832,7 +7832,7 @@
         <v>44588</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7905,7 +7905,7 @@
         <v>44868</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7978,7 +7978,7 @@
         <v>44705</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8051,7 +8051,7 @@
         <v>44581</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8124,7 +8124,7 @@
         <v>44560</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8202,7 +8202,7 @@
         <v>44573</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8275,7 +8275,7 @@
         <v>44614</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8348,7 +8348,7 @@
         <v>44714</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8421,7 +8421,7 @@
         <v>44877</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8494,7 +8494,7 @@
         <v>44491</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8567,7 +8567,7 @@
         <v>44852</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8640,7 +8640,7 @@
         <v>44662</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8713,7 +8713,7 @@
         <v>44584</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8786,7 +8786,7 @@
         <v>44643</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8859,7 +8859,7 @@
         <v>44614</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8932,7 +8932,7 @@
         <v>44726</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9005,7 +9005,7 @@
         <v>44818</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9078,7 +9078,7 @@
         <v>45736</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9151,7 +9151,7 @@
         <v>44586</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9224,7 +9224,7 @@
         <v>45040</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9297,7 +9297,7 @@
         <v>44588</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9370,7 +9370,7 @@
         <v>44979</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         <v>45267</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9516,7 +9516,7 @@
         <v>44881</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9594,7 +9594,7 @@
         <v>45162</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9667,7 +9667,7 @@
         <v>45054</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9740,7 +9740,7 @@
         <v>45054</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9813,7 +9813,7 @@
         <v>44918</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9886,7 +9886,7 @@
         <v>45189</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9959,7 +9959,7 @@
         <v>44918</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10032,7 +10032,7 @@
         <v>45184</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10105,7 +10105,7 @@
         <v>44899</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10178,7 +10178,7 @@
         <v>45694</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10251,7 +10251,7 @@
         <v>45733</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10324,7 +10324,7 @@
         <v>45763</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10397,7 +10397,7 @@
         <v>45245</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10475,7 +10475,7 @@
         <v>45510</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10548,7 +10548,7 @@
         <v>45265</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10621,7 +10621,7 @@
         <v>44937</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10694,7 +10694,7 @@
         <v>45338</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10767,7 +10767,7 @@
         <v>44629</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10840,7 +10840,7 @@
         <v>45510</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10913,7 +10913,7 @@
         <v>45623</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10986,7 +10986,7 @@
         <v>45091</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11059,7 +11059,7 @@
         <v>45733</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11132,7 +11132,7 @@
         <v>45110</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11205,7 +11205,7 @@
         <v>45090</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11278,7 +11278,7 @@
         <v>45544</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11351,7 +11351,7 @@
         <v>45512</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11424,7 +11424,7 @@
         <v>45609</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11497,7 +11497,7 @@
         <v>45195</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11570,7 +11570,7 @@
         <v>45482</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11643,7 +11643,7 @@
         <v>45390</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11716,7 +11716,7 @@
         <v>45727</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11789,7 +11789,7 @@
         <v>45727</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11862,7 +11862,7 @@
         <v>45355</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11935,7 +11935,7 @@
         <v>45629</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12008,7 +12008,7 @@
         <v>45161</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12081,7 +12081,7 @@
         <v>45336</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12154,7 +12154,7 @@
         <v>45629</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12227,7 +12227,7 @@
         <v>45110</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12300,7 +12300,7 @@
         <v>45173</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12373,7 +12373,7 @@
         <v>45173</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12446,7 +12446,7 @@
         <v>44874</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12519,7 +12519,7 @@
         <v>45749</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12592,7 +12592,7 @@
         <v>45435</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12665,7 +12665,7 @@
         <v>44956</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12738,7 +12738,7 @@
         <v>44887</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12811,7 +12811,7 @@
         <v>45434</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12884,7 +12884,7 @@
         <v>45140</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12957,7 +12957,7 @@
         <v>45028</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13030,7 +13030,7 @@
         <v>45271</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13103,7 +13103,7 @@
         <v>45722</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13176,7 +13176,7 @@
         <v>45245</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13254,7 +13254,7 @@
         <v>45623</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13327,7 +13327,7 @@
         <v>45474</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13400,7 +13400,7 @@
         <v>45058</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13473,7 +13473,7 @@
         <v>44904</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13546,7 +13546,7 @@
         <v>45729</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13619,7 +13619,7 @@
         <v>45293</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13692,7 +13692,7 @@
         <v>45588</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13765,7 +13765,7 @@
         <v>45491</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13838,7 +13838,7 @@
         <v>45616</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13911,7 +13911,7 @@
         <v>44581</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13984,7 +13984,7 @@
         <v>44991</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14057,7 +14057,7 @@
         <v>44901</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14130,7 +14130,7 @@
         <v>44641</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14203,7 +14203,7 @@
         <v>44998</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14276,7 +14276,7 @@
         <v>45694</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14349,7 +14349,7 @@
         <v>44693</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14422,7 +14422,7 @@
         <v>45429</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14495,7 +14495,7 @@
         <v>44867</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14568,7 +14568,7 @@
         <v>44896</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14641,7 +14641,7 @@
         <v>45231</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14714,7 +14714,7 @@
         <v>45456</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14787,7 +14787,7 @@
         <v>45261</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14860,7 +14860,7 @@
         <v>45226</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14933,7 +14933,7 @@
         <v>44602</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15006,7 +15006,7 @@
         <v>45149</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15084,7 +15084,7 @@
         <v>45558</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15157,7 +15157,7 @@
         <v>45021</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15230,7 +15230,7 @@
         <v>44790</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15303,7 +15303,7 @@
         <v>44943</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15376,7 +15376,7 @@
         <v>45061</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15449,7 +15449,7 @@
         <v>44942</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15522,7 +15522,7 @@
         <v>45016</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15600,7 +15600,7 @@
         <v>44935</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15673,7 +15673,7 @@
         <v>45273</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15746,7 +15746,7 @@
         <v>45142</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15819,7 +15819,7 @@
         <v>45142</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15892,7 +15892,7 @@
         <v>45231</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15965,7 +15965,7 @@
         <v>45680</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16038,7 +16038,7 @@
         <v>45119</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16111,7 +16111,7 @@
         <v>45729</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16184,7 +16184,7 @@
         <v>45582</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16257,7 +16257,7 @@
         <v>45274</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16330,7 +16330,7 @@
         <v>45932</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16403,7 +16403,7 @@
         <v>45443</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16476,7 +16476,7 @@
         <v>45176</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16549,7 +16549,7 @@
         <v>45614</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16622,7 +16622,7 @@
         <v>45804</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16695,7 +16695,7 @@
         <v>45197</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16768,7 +16768,7 @@
         <v>44614</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16841,7 +16841,7 @@
         <v>45156</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16914,7 +16914,7 @@
         <v>45915</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16987,7 +16987,7 @@
         <v>45856</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17060,7 +17060,7 @@
         <v>45041</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17133,7 +17133,7 @@
         <v>45856</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17206,7 +17206,7 @@
         <v>45195</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17279,7 +17279,7 @@
         <v>46031</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17352,7 +17352,7 @@
         <v>44966</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17425,7 +17425,7 @@
         <v>45714</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17498,7 +17498,7 @@
         <v>45583</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17571,7 +17571,7 @@
         <v>44865</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17644,7 +17644,7 @@
         <v>45691</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17717,7 +17717,7 @@
         <v>44494</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17790,7 +17790,7 @@
         <v>45525</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17863,7 +17863,7 @@
         <v>45525</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17936,7 +17936,7 @@
         <v>45608</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18009,7 +18009,7 @@
         <v>45891</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18087,7 +18087,7 @@
         <v>45671</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18160,7 +18160,7 @@
         <v>45873</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18233,7 +18233,7 @@
         <v>45135</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18306,7 +18306,7 @@
         <v>45554</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18379,7 +18379,7 @@
         <v>45173</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18452,7 +18452,7 @@
         <v>45140</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18525,7 +18525,7 @@
         <v>45897</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18603,7 +18603,7 @@
         <v>45897</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18681,7 +18681,7 @@
         <v>45897</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18754,7 +18754,7 @@
         <v>45866</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18827,7 +18827,7 @@
         <v>45751</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18900,7 +18900,7 @@
         <v>45642</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18973,7 +18973,7 @@
         <v>45811</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19046,7 +19046,7 @@
         <v>46140</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19124,7 +19124,7 @@
         <v>46140</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19197,7 +19197,7 @@
         <v>46140</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19270,7 +19270,7 @@
         <v>45243</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19343,7 +19343,7 @@
         <v>46140</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19421,7 +19421,7 @@
         <v>45733</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19494,7 +19494,7 @@
         <v>46031</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19567,7 +19567,7 @@
         <v>45903</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19640,7 +19640,7 @@
         <v>46140</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19718,7 +19718,7 @@
         <v>45903</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19791,7 +19791,7 @@
         <v>45903</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19864,7 +19864,7 @@
         <v>45418</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19937,7 +19937,7 @@
         <v>45903</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20010,7 +20010,7 @@
         <v>45300</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20083,7 +20083,7 @@
         <v>45818</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20156,7 +20156,7 @@
         <v>44865</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20229,7 +20229,7 @@
         <v>45621</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20302,7 +20302,7 @@
         <v>45910</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20375,7 +20375,7 @@
         <v>45153</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20448,7 +20448,7 @@
         <v>46146</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20521,7 +20521,7 @@
         <v>45918</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20599,7 +20599,7 @@
         <v>45910</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20672,7 +20672,7 @@
         <v>45477</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20745,7 +20745,7 @@
         <v>45920</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20818,7 +20818,7 @@
         <v>45267</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20891,7 +20891,7 @@
         <v>46147</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20964,7 +20964,7 @@
         <v>45924</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21037,7 +21037,7 @@
         <v>45924</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21110,7 +21110,7 @@
         <v>44872</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21183,7 +21183,7 @@
         <v>46148</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21256,7 +21256,7 @@
         <v>46148</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21329,7 +21329,7 @@
         <v>45924</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21402,7 +21402,7 @@
         <v>46148</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21475,7 +21475,7 @@
         <v>45929</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21548,7 +21548,7 @@
         <v>46148</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21621,7 +21621,7 @@
         <v>46148</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21694,7 +21694,7 @@
         <v>46148</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21767,7 +21767,7 @@
         <v>45929</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21840,7 +21840,7 @@
         <v>46149</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21913,7 +21913,7 @@
         <v>45152</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -21986,7 +21986,7 @@
         <v>45929</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22059,7 +22059,7 @@
         <v>45929</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22132,7 +22132,7 @@
         <v>44596</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22205,7 +22205,7 @@
         <v>45015</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22278,7 +22278,7 @@
         <v>46153</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22356,7 +22356,7 @@
         <v>46153</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22434,7 +22434,7 @@
         <v>45936</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22512,7 +22512,7 @@
         <v>45888</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22585,7 +22585,7 @@
         <v>45936</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22663,7 +22663,7 @@
         <v>45089</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22736,7 +22736,7 @@
         <v>44998</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22809,7 +22809,7 @@
         <v>45936</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -22882,7 +22882,7 @@
         <v>44573</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -22955,7 +22955,7 @@
         <v>45252</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23028,7 +23028,7 @@
         <v>44834</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23106,7 +23106,7 @@
         <v>44998</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23179,7 +23179,7 @@
         <v>45191</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23252,7 +23252,7 @@
         <v>46154</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23330,7 +23330,7 @@
         <v>46154</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23403,7 +23403,7 @@
         <v>45532</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23476,7 +23476,7 @@
         <v>44845</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23549,7 +23549,7 @@
         <v>45579</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23622,7 +23622,7 @@
         <v>44917</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23700,7 +23700,7 @@
         <v>44956</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23773,7 +23773,7 @@
         <v>45950</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -23851,7 +23851,7 @@
         <v>45691</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -23924,7 +23924,7 @@
         <v>45440</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -23997,7 +23997,7 @@
         <v>45834</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24070,7 +24070,7 @@
         <v>45408</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24143,7 +24143,7 @@
         <v>45638</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24216,7 +24216,7 @@
         <v>44911</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24289,7 +24289,7 @@
         <v>44523</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24362,7 +24362,7 @@
         <v>45477</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24435,7 +24435,7 @@
         <v>45957</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24508,7 +24508,7 @@
         <v>44518</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24581,7 +24581,7 @@
         <v>45397</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24654,7 +24654,7 @@
         <v>45358</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24727,7 +24727,7 @@
         <v>45623</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -24800,7 +24800,7 @@
         <v>45614</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -24873,7 +24873,7 @@
         <v>44798</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -24946,7 +24946,7 @@
         <v>45904</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25019,7 +25019,7 @@
         <v>45966</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25092,7 +25092,7 @@
         <v>45968</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25165,7 +25165,7 @@
         <v>45203</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25238,7 +25238,7 @@
         <v>45520</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25311,7 +25311,7 @@
         <v>45971</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25384,7 +25384,7 @@
         <v>45737</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25457,7 +25457,7 @@
         <v>45971</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25530,7 +25530,7 @@
         <v>45971</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25608,7 +25608,7 @@
         <v>45161</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25681,7 +25681,7 @@
         <v>45971</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -25759,7 +25759,7 @@
         <v>45971</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -25832,7 +25832,7 @@
         <v>46163</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -25905,7 +25905,7 @@
         <v>44986</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -25978,7 +25978,7 @@
         <v>45184</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26051,7 +26051,7 @@
         <v>45184</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26124,7 +26124,7 @@
         <v>45975</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26197,7 +26197,7 @@
         <v>45191</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26270,7 +26270,7 @@
         <v>44543</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26343,7 +26343,7 @@
         <v>45743</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26416,7 +26416,7 @@
         <v>44865</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26489,7 +26489,7 @@
         <v>46163</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26562,7 +26562,7 @@
         <v>46163</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26635,7 +26635,7 @@
         <v>45981</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -26708,7 +26708,7 @@
         <v>45981</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -26781,7 +26781,7 @@
         <v>46163</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -26854,7 +26854,7 @@
         <v>44915</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -26927,7 +26927,7 @@
         <v>44915</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27000,7 +27000,7 @@
         <v>45692</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27073,7 +27073,7 @@
         <v>45980</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27146,7 +27146,7 @@
         <v>45104</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27219,7 +27219,7 @@
         <v>45981</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27292,7 +27292,7 @@
         <v>45981</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27365,7 +27365,7 @@
         <v>45210</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27438,7 +27438,7 @@
         <v>45733</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27511,7 +27511,7 @@
         <v>44901</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27584,7 +27584,7 @@
         <v>46167</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -27657,7 +27657,7 @@
         <v>44851</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -27730,7 +27730,7 @@
         <v>45106</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -27803,7 +27803,7 @@
         <v>44777</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -27876,7 +27876,7 @@
         <v>45090</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -27949,7 +27949,7 @@
         <v>46167</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28022,7 +28022,7 @@
         <v>45980</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28095,7 +28095,7 @@
         <v>45680</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28168,7 +28168,7 @@
         <v>45021</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28246,7 +28246,7 @@
         <v>45992</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28319,7 +28319,7 @@
         <v>45176</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28392,7 +28392,7 @@
         <v>45992</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28465,7 +28465,7 @@
         <v>45992</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28538,7 +28538,7 @@
         <v>45994</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -28611,7 +28611,7 @@
         <v>45995</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -28684,7 +28684,7 @@
         <v>45994</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -28757,7 +28757,7 @@
         <v>45995</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -28830,7 +28830,7 @@
         <v>45999</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -28903,7 +28903,7 @@
         <v>45435</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -28976,7 +28976,7 @@
         <v>45996</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29049,7 +29049,7 @@
         <v>44881</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29122,7 +29122,7 @@
         <v>46000</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29195,7 +29195,7 @@
         <v>45629</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29268,7 +29268,7 @@
         <v>45603</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29341,7 +29341,7 @@
         <v>45559</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29414,7 +29414,7 @@
         <v>45498</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29487,7 +29487,7 @@
         <v>46002</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -29560,7 +29560,7 @@
         <v>44916</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -29633,7 +29633,7 @@
         <v>46002</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -29706,7 +29706,7 @@
         <v>45756</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -29779,7 +29779,7 @@
         <v>45756</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -29852,7 +29852,7 @@
         <v>45614</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -29925,7 +29925,7 @@
         <v>45281</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -29998,7 +29998,7 @@
         <v>45579</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30071,7 +30071,7 @@
         <v>45636</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30149,7 +30149,7 @@
         <v>46006</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30222,7 +30222,7 @@
         <v>46007</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30295,7 +30295,7 @@
         <v>45061</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30368,7 +30368,7 @@
         <v>45111</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30441,7 +30441,7 @@
         <v>46009</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30514,7 +30514,7 @@
         <v>45204</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -30587,7 +30587,7 @@
         <v>44979</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -30660,7 +30660,7 @@
         <v>46010</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -30733,7 +30733,7 @@
         <v>46013</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -30806,7 +30806,7 @@
         <v>46013</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -30879,7 +30879,7 @@
         <v>46013</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -30952,7 +30952,7 @@
         <v>46010</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31025,7 +31025,7 @@
         <v>46016</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31098,7 +31098,7 @@
         <v>46016</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31171,7 +31171,7 @@
         <v>46016</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31244,7 +31244,7 @@
         <v>44977</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31317,7 +31317,7 @@
         <v>46016</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31390,7 +31390,7 @@
         <v>46016</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31463,7 +31463,7 @@
         <v>45250</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -31536,7 +31536,7 @@
         <v>46016</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -31609,7 +31609,7 @@
         <v>46021</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -31682,7 +31682,7 @@
         <v>46021</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -31760,7 +31760,7 @@
         <v>44970</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -31833,7 +31833,7 @@
         <v>44740</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -31906,7 +31906,7 @@
         <v>46029</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -31979,7 +31979,7 @@
         <v>46029</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -32052,7 +32052,7 @@
         <v>46029</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32125,7 +32125,7 @@
         <v>46029</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32198,7 +32198,7 @@
         <v>46031</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32271,7 +32271,7 @@
         <v>45188</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -32344,7 +32344,7 @@
         <v>46031</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -32417,7 +32417,7 @@
         <v>45704</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -32490,7 +32490,7 @@
         <v>45723</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -32563,7 +32563,7 @@
         <v>46035</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -32636,7 +32636,7 @@
         <v>45520</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -32709,7 +32709,7 @@
         <v>46176</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -32782,7 +32782,7 @@
         <v>46177</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -32855,7 +32855,7 @@
         <v>46178</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -32928,7 +32928,7 @@
         <v>46041</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -33001,7 +33001,7 @@
         <v>46041</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -33074,7 +33074,7 @@
         <v>45510</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -33147,7 +33147,7 @@
         <v>46042</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -33220,7 +33220,7 @@
         <v>45036</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -33293,7 +33293,7 @@
         <v>46043</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -33366,7 +33366,7 @@
         <v>45071</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -33439,7 +33439,7 @@
         <v>44839</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -33512,7 +33512,7 @@
         <v>45301</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -33590,7 +33590,7 @@
         <v>45412</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -33663,7 +33663,7 @@
         <v>46048</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -33736,7 +33736,7 @@
         <v>45646</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -33809,7 +33809,7 @@
         <v>44799</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -33882,7 +33882,7 @@
         <v>46050</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -33955,7 +33955,7 @@
         <v>46050</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -34028,7 +34028,7 @@
         <v>46050</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -34101,7 +34101,7 @@
         <v>46050</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -34174,7 +34174,7 @@
         <v>46055</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -34247,7 +34247,7 @@
         <v>44625</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -34320,7 +34320,7 @@
         <v>45443</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -34393,7 +34393,7 @@
         <v>46059</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -34466,7 +34466,7 @@
         <v>45475</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -34539,7 +34539,7 @@
         <v>45307</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -34612,7 +34612,7 @@
         <v>46059</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -34685,7 +34685,7 @@
         <v>46062</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -34758,7 +34758,7 @@
         <v>46062</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -34831,7 +34831,7 @@
         <v>46064</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -34904,7 +34904,7 @@
         <v>46064</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -34977,7 +34977,7 @@
         <v>46069</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -35050,7 +35050,7 @@
         <v>46069</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -35123,7 +35123,7 @@
         <v>46066</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -35196,7 +35196,7 @@
         <v>44858</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -35269,7 +35269,7 @@
         <v>44970</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -35342,7 +35342,7 @@
         <v>45310</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -35415,7 +35415,7 @@
         <v>45090</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -35488,7 +35488,7 @@
         <v>45090</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -35561,7 +35561,7 @@
         <v>45533</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -35634,7 +35634,7 @@
         <v>45392</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -35707,7 +35707,7 @@
         <v>44746</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -35780,7 +35780,7 @@
         <v>46084</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -35853,7 +35853,7 @@
         <v>46083</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -35926,7 +35926,7 @@
         <v>46083</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -35999,7 +35999,7 @@
         <v>44951</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -36072,7 +36072,7 @@
         <v>46085</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -36145,7 +36145,7 @@
         <v>46085</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -36218,7 +36218,7 @@
         <v>46085</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -36291,7 +36291,7 @@
         <v>46090</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -36369,7 +36369,7 @@
         <v>44798</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -36442,7 +36442,7 @@
         <v>46092</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -36515,7 +36515,7 @@
         <v>46092</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -36588,7 +36588,7 @@
         <v>46092</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -36661,7 +36661,7 @@
         <v>46092</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -36734,7 +36734,7 @@
         <v>46092</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -36807,7 +36807,7 @@
         <v>46092</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -36880,7 +36880,7 @@
         <v>45210</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -36953,7 +36953,7 @@
         <v>44896</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -37026,7 +37026,7 @@
         <v>45603</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -37099,7 +37099,7 @@
         <v>46099</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -37172,7 +37172,7 @@
         <v>46196</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -37245,7 +37245,7 @@
         <v>45308</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -37318,7 +37318,7 @@
         <v>46099</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -37391,7 +37391,7 @@
         <v>46100</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -37469,7 +37469,7 @@
         <v>46195</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -37547,7 +37547,7 @@
         <v>45139</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -37620,7 +37620,7 @@
         <v>46195</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -37698,7 +37698,7 @@
         <v>46101</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -37771,7 +37771,7 @@
         <v>45467</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -37844,7 +37844,7 @@
         <v>46104</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -37917,7 +37917,7 @@
         <v>45105</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -37990,7 +37990,7 @@
         <v>45091</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -38063,7 +38063,7 @@
         <v>45091</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -38136,7 +38136,7 @@
         <v>45751</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -38209,7 +38209,7 @@
         <v>45278</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -38282,7 +38282,7 @@
         <v>44894</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -38355,7 +38355,7 @@
         <v>46196</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -38428,7 +38428,7 @@
         <v>45245</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -38506,7 +38506,7 @@
         <v>46197</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -38584,7 +38584,7 @@
         <v>45552</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -38662,7 +38662,7 @@
         <v>46108</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -38735,7 +38735,7 @@
         <v>46107</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -38808,7 +38808,7 @@
         <v>46108</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -38881,7 +38881,7 @@
         <v>45166</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -38954,7 +38954,7 @@
         <v>46199</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -39027,7 +39027,7 @@
         <v>46119</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -39100,7 +39100,7 @@
         <v>46199</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -39173,7 +39173,7 @@
         <v>46120</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -39246,7 +39246,7 @@
         <v>45173</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -39319,7 +39319,7 @@
         <v>46199</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -39392,7 +39392,7 @@
         <v>46199</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -39465,7 +39465,7 @@
         <v>46119</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -39538,7 +39538,7 @@
         <v>46199</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -39611,7 +39611,7 @@
         <v>44557</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -39684,7 +39684,7 @@
         <v>46070</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -39757,7 +39757,7 @@
         <v>46119</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -39830,7 +39830,7 @@
         <v>46070</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -39903,7 +39903,7 @@
         <v>46124</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -39976,7 +39976,7 @@
         <v>46124</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -40049,7 +40049,7 @@
         <v>45085</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -40122,7 +40122,7 @@
         <v>44575</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -40195,7 +40195,7 @@
         <v>45758</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -40268,7 +40268,7 @@
         <v>44908</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -40341,7 +40341,7 @@
         <v>45600</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -40414,7 +40414,7 @@
         <v>46199</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -40487,7 +40487,7 @@
         <v>46127</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -40560,7 +40560,7 @@
         <v>45092</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -40633,7 +40633,7 @@
         <v>45541</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -40706,7 +40706,7 @@
         <v>45296</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -40779,7 +40779,7 @@
         <v>45714</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -40852,7 +40852,7 @@
         <v>46203</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -40925,7 +40925,7 @@
         <v>46135</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -40998,7 +40998,7 @@
         <v>45246</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -41071,7 +41071,7 @@
         <v>46135</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -41144,7 +41144,7 @@
         <v>45197</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -41217,7 +41217,7 @@
         <v>45224</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -41290,7 +41290,7 @@
         <v>46135</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -41363,7 +41363,7 @@
         <v>45532</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -41436,7 +41436,7 @@
         <v>46203</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -41509,7 +41509,7 @@
         <v>44899</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -41582,7 +41582,7 @@
         <v>46203</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -41655,7 +41655,7 @@
         <v>44537</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -41728,7 +41728,7 @@
         <v>45832</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -41801,7 +41801,7 @@
         <v>45037</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -41874,7 +41874,7 @@
         <v>45719</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -41947,7 +41947,7 @@
         <v>44901</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -42020,7 +42020,7 @@
         <v>45611</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -42093,7 +42093,7 @@
         <v>46104</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -42166,7 +42166,7 @@
         <v>45114</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -42239,7 +42239,7 @@
         <v>45804</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -42312,7 +42312,7 @@
         <v>45301</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -42385,7 +42385,7 @@
         <v>45617</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -42458,7 +42458,7 @@
         <v>44537</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -42531,7 +42531,7 @@
         <v>45054</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -42604,7 +42604,7 @@
         <v>45549</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -42677,7 +42677,7 @@
         <v>45084</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -42750,7 +42750,7 @@
         <v>44546</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -42823,7 +42823,7 @@
         <v>44840</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -42896,7 +42896,7 @@
         <v>45685</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -42969,7 +42969,7 @@
         <v>44966</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -43042,7 +43042,7 @@
         <v>45090</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -43115,7 +43115,7 @@
         <v>45090</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -43188,7 +43188,7 @@
         <v>45090</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -43261,7 +43261,7 @@
         <v>45553</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -43334,7 +43334,7 @@
         <v>45736</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -43407,7 +43407,7 @@
         <v>45106</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -43480,7 +43480,7 @@
         <v>46217</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -43553,7 +43553,7 @@
         <v>44804</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -43626,7 +43626,7 @@
         <v>46217</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -43699,7 +43699,7 @@
         <v>46217</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -43772,7 +43772,7 @@
         <v>45450</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -43845,7 +43845,7 @@
         <v>45290</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -43918,7 +43918,7 @@
         <v>45290</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -43991,7 +43991,7 @@
         <v>45146</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -44064,7 +44064,7 @@
         <v>45176</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -44137,7 +44137,7 @@
         <v>45539</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -44210,7 +44210,7 @@
         <v>45754</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -44283,7 +44283,7 @@
         <v>45654</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -44356,7 +44356,7 @@
         <v>45152</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -44429,7 +44429,7 @@
         <v>45152</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -44502,7 +44502,7 @@
         <v>46275</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -44575,7 +44575,7 @@
         <v>46274</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -44648,7 +44648,7 @@
         <v>46274</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -44721,7 +44721,7 @@
         <v>46233</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -44794,7 +44794,7 @@
         <v>45261</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -44867,7 +44867,7 @@
         <v>45775</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -44940,7 +44940,7 @@
         <v>45098</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -45013,7 +45013,7 @@
         <v>46279</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -45086,7 +45086,7 @@
         <v>46279</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -45159,7 +45159,7 @@
         <v>46273</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -45232,7 +45232,7 @@
         <v>45272</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -45305,7 +45305,7 @@
         <v>44683</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -45378,7 +45378,7 @@
         <v>45084</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -45451,7 +45451,7 @@
         <v>46238</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -45524,7 +45524,7 @@
         <v>45204</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -45597,7 +45597,7 @@
         <v>45279</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -45670,7 +45670,7 @@
         <v>46280</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -45743,7 +45743,7 @@
         <v>45525</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -45816,7 +45816,7 @@
         <v>46237</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -45889,7 +45889,7 @@
         <v>45224</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -45967,7 +45967,7 @@
         <v>46240</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -46040,7 +46040,7 @@
         <v>45267</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -46113,7 +46113,7 @@
         <v>45015</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -46186,7 +46186,7 @@
         <v>45370</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -46259,7 +46259,7 @@
         <v>44966</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -46332,7 +46332,7 @@
         <v>45092</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -46405,7 +46405,7 @@
         <v>44883</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -46478,7 +46478,7 @@
         <v>45684</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -46551,7 +46551,7 @@
         <v>46052</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -46629,7 +46629,7 @@
         <v>45281</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -46702,7 +46702,7 @@
         <v>45975</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -46775,7 +46775,7 @@
         <v>44911</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -46848,7 +46848,7 @@
         <v>45603</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -46921,7 +46921,7 @@
         <v>46199</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -46994,7 +46994,7 @@
         <v>45275</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -47067,7 +47067,7 @@
         <v>44911</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -47140,7 +47140,7 @@
         <v>46147</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -47213,7 +47213,7 @@
         <v>45128</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -47286,7 +47286,7 @@
         <v>45756</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -47359,7 +47359,7 @@
         <v>45281</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -47432,7 +47432,7 @@
         <v>44602</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -47505,7 +47505,7 @@
         <v>45161</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -47578,7 +47578,7 @@
         <v>46289</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -47651,7 +47651,7 @@
         <v>46281</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -47724,7 +47724,7 @@
         <v>45245</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -47802,7 +47802,7 @@
         <v>46245</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -47875,7 +47875,7 @@
         <v>45149</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -47953,7 +47953,7 @@
         <v>45159</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -48026,7 +48026,7 @@
         <v>46245</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -48099,7 +48099,7 @@
         <v>46289</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -48172,7 +48172,7 @@
         <v>45089</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -48245,7 +48245,7 @@
         <v>45426</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -48318,7 +48318,7 @@
         <v>45310</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -48391,7 +48391,7 @@
         <v>45310</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -48464,7 +48464,7 @@
         <v>45090</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -48537,7 +48537,7 @@
         <v>44700</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -48615,7 +48615,7 @@
         <v>45432</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -48688,7 +48688,7 @@
         <v>45054</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -48761,7 +48761,7 @@
         <v>45336</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -48834,7 +48834,7 @@
         <v>45546</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -48907,7 +48907,7 @@
         <v>45455</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -48980,7 +48980,7 @@
         <v>45040</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -49053,7 +49053,7 @@
         <v>46290</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -49126,7 +49126,7 @@
         <v>46290</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -49199,7 +49199,7 @@
         <v>46247</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -49272,7 +49272,7 @@
         <v>46247</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -49345,7 +49345,7 @@
         <v>45294</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -49418,7 +49418,7 @@
         <v>45253</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -49491,7 +49491,7 @@
         <v>45541</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -49564,7 +49564,7 @@
         <v>46290</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -49642,7 +49642,7 @@
         <v>46290</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -49720,7 +49720,7 @@
         <v>46294</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -49793,7 +49793,7 @@
         <v>45692</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -49866,7 +49866,7 @@
         <v>46252</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -49939,7 +49939,7 @@
         <v>45674</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -50012,7 +50012,7 @@
         <v>44966</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -50085,7 +50085,7 @@
         <v>44998</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -50158,7 +50158,7 @@
         <v>44896</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -50231,7 +50231,7 @@
         <v>45306</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -50304,7 +50304,7 @@
         <v>45676</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -50377,7 +50377,7 @@
         <v>45221</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -50455,7 +50455,7 @@
         <v>45221</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -50533,7 +50533,7 @@
         <v>45229</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -50606,7 +50606,7 @@
         <v>44659</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -50679,7 +50679,7 @@
         <v>45175</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -50752,7 +50752,7 @@
         <v>45616</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -50825,7 +50825,7 @@
         <v>44776</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -50903,7 +50903,7 @@
         <v>44714</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -50976,7 +50976,7 @@
         <v>46297</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -51049,7 +51049,7 @@
         <v>44636</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -51122,7 +51122,7 @@
         <v>44636</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -51195,7 +51195,7 @@
         <v>46297</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -51273,7 +51273,7 @@
         <v>46297</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -51346,7 +51346,7 @@
         <v>46247</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -51419,7 +51419,7 @@
         <v>46253</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -51492,7 +51492,7 @@
         <v>44911</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -51565,7 +51565,7 @@
         <v>45015</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -51638,7 +51638,7 @@
         <v>45616</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -51711,7 +51711,7 @@
         <v>44665</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -51784,7 +51784,7 @@
         <v>45775</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -51857,7 +51857,7 @@
         <v>45777</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -51930,7 +51930,7 @@
         <v>45775</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -52003,7 +52003,7 @@
         <v>45783</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -52076,7 +52076,7 @@
         <v>45567</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -52149,7 +52149,7 @@
         <v>45730</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -52222,7 +52222,7 @@
         <v>45629</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -52295,7 +52295,7 @@
         <v>45792</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -52368,7 +52368,7 @@
         <v>46261</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -52446,7 +52446,7 @@
         <v>45576</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -52519,7 +52519,7 @@
         <v>46300</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -52592,7 +52592,7 @@
         <v>45796</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -52665,7 +52665,7 @@
         <v>46261</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -52743,7 +52743,7 @@
         <v>46262</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -52821,7 +52821,7 @@
         <v>45803</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -52894,7 +52894,7 @@
         <v>46266</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -52967,7 +52967,7 @@
         <v>46266</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -53040,7 +53040,7 @@
         <v>45805</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -53118,7 +53118,7 @@
         <v>46308</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -53191,7 +53191,7 @@
         <v>45310</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -53264,7 +53264,7 @@
         <v>45600</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -53337,7 +53337,7 @@
         <v>45726</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -53410,7 +53410,7 @@
         <v>45624</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -53483,7 +53483,7 @@
         <v>46309</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -53556,7 +53556,7 @@
         <v>46147</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -53629,7 +53629,7 @@
         <v>45378</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -53702,7 +53702,7 @@
         <v>44966</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -53780,7 +53780,7 @@
         <v>45502</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -53853,7 +53853,7 @@
         <v>45580</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -53926,7 +53926,7 @@
         <v>45628</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -53999,7 +53999,7 @@
         <v>46269</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -54072,7 +54072,7 @@
         <v>45583</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -54145,7 +54145,7 @@
         <v>45742</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -54218,7 +54218,7 @@
         <v>45590</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -54291,7 +54291,7 @@
         <v>46267</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -54364,7 +54364,7 @@
         <v>45818</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -54437,7 +54437,7 @@
         <v>45818</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -54510,7 +54510,7 @@
         <v>45817</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -54583,7 +54583,7 @@
         <v>45818</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -54656,7 +54656,7 @@
         <v>46310</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -54734,7 +54734,7 @@
         <v>45758</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -54807,7 +54807,7 @@
         <v>46311</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -54880,7 +54880,7 @@
         <v>46269</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -54953,7 +54953,7 @@
         <v>45835</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -55026,7 +55026,7 @@
         <v>45839</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -55099,7 +55099,7 @@
         <v>45838</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -55172,7 +55172,7 @@
         <v>45838</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -55245,7 +55245,7 @@
         <v>45839</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -55318,7 +55318,7 @@
         <v>45841</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -55391,7 +55391,7 @@
         <v>45817</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -55464,7 +55464,7 @@
         <v>45715</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -55537,7 +55537,7 @@
         <v>45253</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -55610,7 +55610,7 @@
         <v>45061</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -55683,7 +55683,7 @@
         <v>45588</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -55756,7 +55756,7 @@
         <v>45736</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -55829,7 +55829,7 @@
         <v>45848</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -55902,7 +55902,7 @@
         <v>45778</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -55975,7 +55975,7 @@
         <v>45856</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -56048,7 +56048,7 @@
         <v>45874</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -56121,7 +56121,7 @@
         <v>45883</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -56194,7 +56194,7 @@
         <v>45882</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -56267,7 +56267,7 @@
         <v>45882</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -56340,7 +56340,7 @@
         <v>44579</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -56418,7 +56418,7 @@
         <v>44893</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -56496,7 +56496,7 @@
         <v>44893</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -56574,7 +56574,7 @@
         <v>44893</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -56652,7 +56652,7 @@
         <v>45731</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -56725,7 +56725,7 @@
         <v>45736</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -56798,7 +56798,7 @@
         <v>46035</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -56876,7 +56876,7 @@
         <v>46163</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>

--- a/Översikt EDA.xlsx
+++ b/Översikt EDA.xlsx
@@ -601,7 +601,7 @@
         <v>45178</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -725,7 +725,7 @@
         <v>45726</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -843,7 +843,7 @@
         <v>44494</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -955,7 +955,7 @@
         <v>45090</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1070,7 +1070,7 @@
         <v>45154</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1180,7 +1180,7 @@
         <v>45306</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1298,7 +1298,7 @@
         <v>44791</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1406,7 +1406,7 @@
         <v>45407</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1514,7 +1514,7 @@
         <v>44740</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1626,7 +1626,7 @@
         <v>45358</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1737,7 +1737,7 @@
         <v>45754</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1848,7 +1848,7 @@
         <v>45293</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1963,7 +1963,7 @@
         <v>44916</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2074,7 +2074,7 @@
         <v>44868</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2180,7 +2180,7 @@
         <v>44865</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2286,7 +2286,7 @@
         <v>44888</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2396,7 +2396,7 @@
         <v>45243</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2502,7 +2502,7 @@
         <v>45310</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2608,7 +2608,7 @@
         <v>45575</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2714,7 +2714,7 @@
         <v>46290</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2820,7 +2820,7 @@
         <v>45856</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2926,7 +2926,7 @@
         <v>44970</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3032,7 +3032,7 @@
         <v>45091</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3142,7 +3142,7 @@
         <v>45426</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3248,7 +3248,7 @@
         <v>45315</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3358,7 +3358,7 @@
         <v>45545</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3464,7 +3464,7 @@
         <v>45243</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3569,7 +3569,7 @@
         <v>45376</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3678,7 +3678,7 @@
         <v>45532</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3783,7 +3783,7 @@
         <v>45432</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3888,7 +3888,7 @@
         <v>45257</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3993,7 +3993,7 @@
         <v>45777</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4107,7 +4107,7 @@
         <v>46092</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4212,7 +4212,7 @@
         <v>46269</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4321,7 +4321,7 @@
         <v>46269</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4431,7 +4431,7 @@
         <v>46316</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4540,7 +4540,7 @@
         <v>45721</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4645,7 +4645,7 @@
         <v>45244</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4750,7 +4750,7 @@
         <v>44579</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4860,7 +4860,7 @@
         <v>44889</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4933,7 +4933,7 @@
         <v>44683</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5006,7 +5006,7 @@
         <v>44810</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5079,7 +5079,7 @@
         <v>44529</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5152,7 +5152,7 @@
         <v>44712</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5225,7 +5225,7 @@
         <v>44852</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5298,7 +5298,7 @@
         <v>44889</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5371,7 +5371,7 @@
         <v>44608</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5449,7 +5449,7 @@
         <v>44582</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5522,7 +5522,7 @@
         <v>44582</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5595,7 +5595,7 @@
         <v>44851</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5668,7 +5668,7 @@
         <v>44538</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5741,7 +5741,7 @@
         <v>44740</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5814,7 +5814,7 @@
         <v>44837</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5887,7 +5887,7 @@
         <v>44816</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5960,7 +5960,7 @@
         <v>44712</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6033,7 +6033,7 @@
         <v>44532</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6106,7 +6106,7 @@
         <v>44874</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6179,7 +6179,7 @@
         <v>44529</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6252,7 +6252,7 @@
         <v>44586</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6325,7 +6325,7 @@
         <v>44722</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6398,7 +6398,7 @@
         <v>44685</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6471,7 +6471,7 @@
         <v>44809</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6544,7 +6544,7 @@
         <v>44858</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6617,7 +6617,7 @@
         <v>44670</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6690,7 +6690,7 @@
         <v>44659</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6763,7 +6763,7 @@
         <v>44740</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6836,7 +6836,7 @@
         <v>44510</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6909,7 +6909,7 @@
         <v>44733</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6982,7 +6982,7 @@
         <v>44853</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7055,7 +7055,7 @@
         <v>44557</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7133,7 +7133,7 @@
         <v>44546</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7206,7 +7206,7 @@
         <v>44817</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7279,7 +7279,7 @@
         <v>44614</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7352,7 +7352,7 @@
         <v>44874</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7425,7 +7425,7 @@
         <v>44874</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7498,7 +7498,7 @@
         <v>44883</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7571,7 +7571,7 @@
         <v>44515</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7649,7 +7649,7 @@
         <v>44799</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7722,7 +7722,7 @@
         <v>44881</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7795,7 +7795,7 @@
         <v>44881</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7868,7 +7868,7 @@
         <v>44588</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7941,7 +7941,7 @@
         <v>44581</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8014,7 +8014,7 @@
         <v>44868</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8087,7 +8087,7 @@
         <v>44705</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8160,7 +8160,7 @@
         <v>44573</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8233,7 +8233,7 @@
         <v>44560</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8311,7 +8311,7 @@
         <v>44614</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8384,7 +8384,7 @@
         <v>44714</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8457,7 +8457,7 @@
         <v>44877</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8530,7 +8530,7 @@
         <v>44852</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8603,7 +8603,7 @@
         <v>44662</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8676,7 +8676,7 @@
         <v>44584</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8749,7 +8749,7 @@
         <v>44643</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8822,7 +8822,7 @@
         <v>44614</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8895,7 +8895,7 @@
         <v>44726</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8968,7 +8968,7 @@
         <v>44818</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9041,7 +9041,7 @@
         <v>45583</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9114,7 +9114,7 @@
         <v>45553</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9187,7 +9187,7 @@
         <v>45161</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9260,7 +9260,7 @@
         <v>44896</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9333,7 +9333,7 @@
         <v>44683</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9406,7 +9406,7 @@
         <v>44851</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9479,7 +9479,7 @@
         <v>45412</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9552,7 +9552,7 @@
         <v>45775</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9625,7 +9625,7 @@
         <v>45041</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9698,7 +9698,7 @@
         <v>45090</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9771,7 +9771,7 @@
         <v>45891</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9849,7 +9849,7 @@
         <v>45883</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9922,7 +9922,7 @@
         <v>44865</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9995,7 +9995,7 @@
         <v>45897</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10068,7 +10068,7 @@
         <v>45582</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10141,7 +10141,7 @@
         <v>44834</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10219,7 +10219,7 @@
         <v>45897</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10297,7 +10297,7 @@
         <v>45897</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10375,7 +10375,7 @@
         <v>45733</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10448,7 +10448,7 @@
         <v>45016</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10526,7 +10526,7 @@
         <v>44777</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10599,7 +10599,7 @@
         <v>45195</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10672,7 +10672,7 @@
         <v>45719</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10745,7 +10745,7 @@
         <v>44908</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10818,7 +10818,7 @@
         <v>45903</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10891,7 +10891,7 @@
         <v>45231</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10964,7 +10964,7 @@
         <v>45903</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11037,7 +11037,7 @@
         <v>45903</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11110,7 +11110,7 @@
         <v>45903</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11183,7 +11183,7 @@
         <v>45281</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11256,7 +11256,7 @@
         <v>45498</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11329,7 +11329,7 @@
         <v>44798</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11402,7 +11402,7 @@
         <v>45910</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11475,7 +11475,7 @@
         <v>45510</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11548,7 +11548,7 @@
         <v>45510</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11621,7 +11621,7 @@
         <v>44917</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11699,7 +11699,7 @@
         <v>44918</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11772,7 +11772,7 @@
         <v>46163</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11845,7 +11845,7 @@
         <v>46163</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11918,7 +11918,7 @@
         <v>46163</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11991,7 +11991,7 @@
         <v>45191</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12064,7 +12064,7 @@
         <v>45128</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12137,7 +12137,7 @@
         <v>44596</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12210,7 +12210,7 @@
         <v>45674</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12283,7 +12283,7 @@
         <v>44602</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12356,7 +12356,7 @@
         <v>46163</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12429,7 +12429,7 @@
         <v>44979</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12502,7 +12502,7 @@
         <v>45918</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12580,7 +12580,7 @@
         <v>45910</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12653,7 +12653,7 @@
         <v>45920</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12726,7 +12726,7 @@
         <v>45694</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12799,7 +12799,7 @@
         <v>44518</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12872,7 +12872,7 @@
         <v>45924</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12945,7 +12945,7 @@
         <v>45176</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13018,7 +13018,7 @@
         <v>45924</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13091,7 +13091,7 @@
         <v>46167</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13164,7 +13164,7 @@
         <v>46167</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13237,7 +13237,7 @@
         <v>45924</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13310,7 +13310,7 @@
         <v>45021</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13383,7 +13383,7 @@
         <v>45071</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13456,7 +13456,7 @@
         <v>45310</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13529,7 +13529,7 @@
         <v>45704</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13602,7 +13602,7 @@
         <v>45929</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13675,7 +13675,7 @@
         <v>45929</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13748,7 +13748,7 @@
         <v>45092</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13821,7 +13821,7 @@
         <v>45092</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13894,7 +13894,7 @@
         <v>45929</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13967,7 +13967,7 @@
         <v>45929</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14040,7 +14040,7 @@
         <v>45763</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14113,7 +14113,7 @@
         <v>45370</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14186,7 +14186,7 @@
         <v>45090</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14259,7 +14259,7 @@
         <v>45090</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14332,7 +14332,7 @@
         <v>45090</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14405,7 +14405,7 @@
         <v>45281</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14478,7 +14478,7 @@
         <v>45281</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14551,7 +14551,7 @@
         <v>45936</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14629,7 +14629,7 @@
         <v>45418</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14702,7 +14702,7 @@
         <v>45888</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14775,7 +14775,7 @@
         <v>45936</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14853,7 +14853,7 @@
         <v>44916</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14926,7 +14926,7 @@
         <v>44977</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14999,7 +14999,7 @@
         <v>45936</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15072,7 +15072,7 @@
         <v>45621</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15145,7 +15145,7 @@
         <v>44937</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15218,7 +15218,7 @@
         <v>45432</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15291,7 +15291,7 @@
         <v>45061</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15364,7 +15364,7 @@
         <v>45162</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15437,7 +15437,7 @@
         <v>45229</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15510,7 +15510,7 @@
         <v>45456</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15583,7 +15583,7 @@
         <v>46176</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15656,7 +15656,7 @@
         <v>45139</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15729,7 +15729,7 @@
         <v>46177</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15802,7 +15802,7 @@
         <v>45554</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15875,7 +15875,7 @@
         <v>44901</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15948,7 +15948,7 @@
         <v>45549</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16021,7 +16021,7 @@
         <v>44799</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16094,7 +16094,7 @@
         <v>44956</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16167,7 +16167,7 @@
         <v>45301</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16245,7 +16245,7 @@
         <v>44894</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16318,7 +16318,7 @@
         <v>44966</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16391,7 +16391,7 @@
         <v>45390</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16464,7 +16464,7 @@
         <v>45756</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16537,7 +16537,7 @@
         <v>45426</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16610,7 +16610,7 @@
         <v>45950</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16688,7 +16688,7 @@
         <v>45090</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16761,7 +16761,7 @@
         <v>46178</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16834,7 +16834,7 @@
         <v>45161</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16907,7 +16907,7 @@
         <v>45520</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16980,7 +16980,7 @@
         <v>44636</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17053,7 +17053,7 @@
         <v>45203</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17126,7 +17126,7 @@
         <v>45629</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17199,7 +17199,7 @@
         <v>45308</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17272,7 +17272,7 @@
         <v>45105</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17345,7 +17345,7 @@
         <v>45727</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17418,7 +17418,7 @@
         <v>45727</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17491,7 +17491,7 @@
         <v>45957</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17564,7 +17564,7 @@
         <v>44776</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17642,7 +17642,7 @@
         <v>45310</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17715,7 +17715,7 @@
         <v>44998</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17788,7 +17788,7 @@
         <v>45692</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17861,7 +17861,7 @@
         <v>45161</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17934,7 +17934,7 @@
         <v>45966</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18007,7 +18007,7 @@
         <v>44865</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18080,7 +18080,7 @@
         <v>45210</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18153,7 +18153,7 @@
         <v>45307</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18226,7 +18226,7 @@
         <v>45968</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18299,7 +18299,7 @@
         <v>45971</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18372,7 +18372,7 @@
         <v>45971</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18450,7 +18450,7 @@
         <v>45971</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18523,7 +18523,7 @@
         <v>46195</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18601,7 +18601,7 @@
         <v>45397</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18674,7 +18674,7 @@
         <v>45971</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18752,7 +18752,7 @@
         <v>45971</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18825,7 +18825,7 @@
         <v>45184</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18898,7 +18898,7 @@
         <v>45184</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18971,7 +18971,7 @@
         <v>45273</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19044,7 +19044,7 @@
         <v>45552</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19122,7 +19122,7 @@
         <v>46197</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19200,7 +19200,7 @@
         <v>45616</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19273,7 +19273,7 @@
         <v>46196</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19346,7 +19346,7 @@
         <v>45392</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19419,7 +19419,7 @@
         <v>45455</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19492,7 +19492,7 @@
         <v>44935</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19565,7 +19565,7 @@
         <v>45636</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19643,7 +19643,7 @@
         <v>46196</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19716,7 +19716,7 @@
         <v>44867</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19789,7 +19789,7 @@
         <v>45975</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19862,7 +19862,7 @@
         <v>46199</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19935,7 +19935,7 @@
         <v>46199</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20008,7 +20008,7 @@
         <v>46199</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20081,7 +20081,7 @@
         <v>46199</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20154,7 +20154,7 @@
         <v>45149</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20232,7 +20232,7 @@
         <v>46199</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20305,7 +20305,7 @@
         <v>46199</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20378,7 +20378,7 @@
         <v>45980</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20451,7 +20451,7 @@
         <v>45680</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20524,7 +20524,7 @@
         <v>45729</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20597,7 +20597,7 @@
         <v>45482</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20670,7 +20670,7 @@
         <v>45981</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20743,7 +20743,7 @@
         <v>45981</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20816,7 +20816,7 @@
         <v>46203</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20889,7 +20889,7 @@
         <v>46203</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20962,7 +20962,7 @@
         <v>45477</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21035,7 +21035,7 @@
         <v>46203</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21108,7 +21108,7 @@
         <v>45756</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21181,7 +21181,7 @@
         <v>45756</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21254,7 +21254,7 @@
         <v>45676</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21327,7 +21327,7 @@
         <v>45981</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21400,7 +21400,7 @@
         <v>45981</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21473,7 +21473,7 @@
         <v>45246</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21546,7 +21546,7 @@
         <v>45152</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21619,7 +21619,7 @@
         <v>44918</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21692,7 +21692,7 @@
         <v>45221</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21770,7 +21770,7 @@
         <v>45221</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21848,7 +21848,7 @@
         <v>45992</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21921,7 +21921,7 @@
         <v>45980</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21994,7 +21994,7 @@
         <v>45226</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22067,7 +22067,7 @@
         <v>45992</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22140,7 +22140,7 @@
         <v>45694</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22213,7 +22213,7 @@
         <v>45245</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22291,7 +22291,7 @@
         <v>45729</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22364,7 +22364,7 @@
         <v>45252</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22437,7 +22437,7 @@
         <v>45684</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22510,7 +22510,7 @@
         <v>45994</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22583,7 +22583,7 @@
         <v>45525</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22656,7 +22656,7 @@
         <v>45992</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22729,7 +22729,7 @@
         <v>45994</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22802,7 +22802,7 @@
         <v>45995</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22875,7 +22875,7 @@
         <v>44956</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -22948,7 +22948,7 @@
         <v>46217</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23021,7 +23021,7 @@
         <v>45995</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23094,7 +23094,7 @@
         <v>45623</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23167,7 +23167,7 @@
         <v>46217</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23240,7 +23240,7 @@
         <v>45692</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23313,7 +23313,7 @@
         <v>46217</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23386,7 +23386,7 @@
         <v>45408</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23459,7 +23459,7 @@
         <v>46000</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23532,7 +23532,7 @@
         <v>45996</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23605,7 +23605,7 @@
         <v>45189</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23678,7 +23678,7 @@
         <v>44537</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23751,7 +23751,7 @@
         <v>45999</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23824,7 +23824,7 @@
         <v>45775</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -23897,7 +23897,7 @@
         <v>45775</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -23970,7 +23970,7 @@
         <v>46002</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24043,7 +24043,7 @@
         <v>45777</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24116,7 +24116,7 @@
         <v>46002</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24189,7 +24189,7 @@
         <v>45783</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24262,7 +24262,7 @@
         <v>45567</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24335,7 +24335,7 @@
         <v>46233</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24408,7 +24408,7 @@
         <v>46006</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24481,7 +24481,7 @@
         <v>46007</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24554,7 +24554,7 @@
         <v>45730</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24627,7 +24627,7 @@
         <v>46009</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24700,7 +24700,7 @@
         <v>46010</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24773,7 +24773,7 @@
         <v>46279</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -24846,7 +24846,7 @@
         <v>46237</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -24919,7 +24919,7 @@
         <v>46010</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -24992,7 +24992,7 @@
         <v>46280</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25065,7 +25065,7 @@
         <v>46013</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25138,7 +25138,7 @@
         <v>46279</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25211,7 +25211,7 @@
         <v>46013</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25284,7 +25284,7 @@
         <v>46013</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25357,7 +25357,7 @@
         <v>46016</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25430,7 +25430,7 @@
         <v>46016</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25503,7 +25503,7 @@
         <v>46238</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25576,7 +25576,7 @@
         <v>46016</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25649,7 +25649,7 @@
         <v>46016</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25722,7 +25722,7 @@
         <v>46016</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -25795,7 +25795,7 @@
         <v>46016</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -25868,7 +25868,7 @@
         <v>45110</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -25941,7 +25941,7 @@
         <v>46021</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26014,7 +26014,7 @@
         <v>46021</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26092,7 +26092,7 @@
         <v>46029</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26165,7 +26165,7 @@
         <v>46029</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26238,7 +26238,7 @@
         <v>46029</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26311,7 +26311,7 @@
         <v>45629</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26384,7 +26384,7 @@
         <v>46029</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26457,7 +26457,7 @@
         <v>46031</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26530,7 +26530,7 @@
         <v>46031</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26603,7 +26603,7 @@
         <v>45792</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26676,7 +26676,7 @@
         <v>46240</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -26749,7 +26749,7 @@
         <v>46035</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -26822,7 +26822,7 @@
         <v>45576</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -26895,7 +26895,7 @@
         <v>46042</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -26968,7 +26968,7 @@
         <v>46041</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27041,7 +27041,7 @@
         <v>46041</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27114,7 +27114,7 @@
         <v>45796</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27187,7 +27187,7 @@
         <v>46052</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27265,7 +27265,7 @@
         <v>44911</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27338,7 +27338,7 @@
         <v>44911</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27411,7 +27411,7 @@
         <v>46199</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27484,7 +27484,7 @@
         <v>46043</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27557,7 +27557,7 @@
         <v>46245</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27630,7 +27630,7 @@
         <v>45975</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -27703,7 +27703,7 @@
         <v>46048</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -27776,7 +27776,7 @@
         <v>46245</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -27849,7 +27849,7 @@
         <v>46147</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -27922,7 +27922,7 @@
         <v>46050</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -27995,7 +27995,7 @@
         <v>46290</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28068,7 +28068,7 @@
         <v>46290</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28141,7 +28141,7 @@
         <v>46050</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28214,7 +28214,7 @@
         <v>46050</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28287,7 +28287,7 @@
         <v>46050</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28360,7 +28360,7 @@
         <v>45803</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28433,7 +28433,7 @@
         <v>45450</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28506,7 +28506,7 @@
         <v>46247</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28579,7 +28579,7 @@
         <v>46055</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -28652,7 +28652,7 @@
         <v>45294</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -28725,7 +28725,7 @@
         <v>46281</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -28798,7 +28798,7 @@
         <v>46289</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -28871,7 +28871,7 @@
         <v>46290</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -28949,7 +28949,7 @@
         <v>45805</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29027,7 +29027,7 @@
         <v>46247</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29100,7 +29100,7 @@
         <v>45502</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29173,7 +29173,7 @@
         <v>46290</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29251,7 +29251,7 @@
         <v>45624</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29324,7 +29324,7 @@
         <v>44966</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29402,7 +29402,7 @@
         <v>45600</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29475,7 +29475,7 @@
         <v>46289</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29548,7 +29548,7 @@
         <v>45378</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -29621,7 +29621,7 @@
         <v>45310</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -29694,7 +29694,7 @@
         <v>46059</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -29767,7 +29767,7 @@
         <v>45726</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -29840,7 +29840,7 @@
         <v>46059</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -29913,7 +29913,7 @@
         <v>45580</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -29986,7 +29986,7 @@
         <v>45628</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30059,7 +30059,7 @@
         <v>46062</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30132,7 +30132,7 @@
         <v>46062</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30205,7 +30205,7 @@
         <v>45742</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30278,7 +30278,7 @@
         <v>45583</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30351,7 +30351,7 @@
         <v>46294</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30424,7 +30424,7 @@
         <v>46064</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30497,7 +30497,7 @@
         <v>45817</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30570,7 +30570,7 @@
         <v>46064</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -30643,7 +30643,7 @@
         <v>46066</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -30716,7 +30716,7 @@
         <v>46069</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -30789,7 +30789,7 @@
         <v>46069</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -30862,7 +30862,7 @@
         <v>45818</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -30935,7 +30935,7 @@
         <v>45590</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31008,7 +31008,7 @@
         <v>45818</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31081,7 +31081,7 @@
         <v>45818</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31154,7 +31154,7 @@
         <v>45278</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31227,7 +31227,7 @@
         <v>45758</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31300,7 +31300,7 @@
         <v>46252</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31373,7 +31373,7 @@
         <v>46083</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31446,7 +31446,7 @@
         <v>46083</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31519,7 +31519,7 @@
         <v>46253</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -31592,7 +31592,7 @@
         <v>46084</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -31665,7 +31665,7 @@
         <v>46085</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -31738,7 +31738,7 @@
         <v>46085</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -31811,7 +31811,7 @@
         <v>46085</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -31884,7 +31884,7 @@
         <v>46297</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -31957,7 +31957,7 @@
         <v>45835</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -32030,7 +32030,7 @@
         <v>45838</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -32103,7 +32103,7 @@
         <v>46090</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32181,7 +32181,7 @@
         <v>45838</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32254,7 +32254,7 @@
         <v>46297</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32327,7 +32327,7 @@
         <v>46092</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -32400,7 +32400,7 @@
         <v>45839</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -32473,7 +32473,7 @@
         <v>46092</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -32546,7 +32546,7 @@
         <v>46092</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -32619,7 +32619,7 @@
         <v>46092</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -32692,7 +32692,7 @@
         <v>46092</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -32765,7 +32765,7 @@
         <v>45839</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -32838,7 +32838,7 @@
         <v>46092</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -32911,7 +32911,7 @@
         <v>45491</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -32984,7 +32984,7 @@
         <v>46099</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -33057,7 +33057,7 @@
         <v>46297</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -33135,7 +33135,7 @@
         <v>46099</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -33208,7 +33208,7 @@
         <v>45841</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -33281,7 +33281,7 @@
         <v>46247</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -33354,7 +33354,7 @@
         <v>45532</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -33427,7 +33427,7 @@
         <v>44943</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -33500,7 +33500,7 @@
         <v>44602</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -33573,7 +33573,7 @@
         <v>46100</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -33651,7 +33651,7 @@
         <v>45544</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -33724,7 +33724,7 @@
         <v>46101</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -33797,7 +33797,7 @@
         <v>45817</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -33870,7 +33870,7 @@
         <v>45253</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -33943,7 +33943,7 @@
         <v>45588</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -34016,7 +34016,7 @@
         <v>45736</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -34089,7 +34089,7 @@
         <v>46104</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -34162,7 +34162,7 @@
         <v>45061</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -34235,7 +34235,7 @@
         <v>45715</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -34308,7 +34308,7 @@
         <v>45176</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -34381,7 +34381,7 @@
         <v>46107</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -34454,7 +34454,7 @@
         <v>45848</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -34527,7 +34527,7 @@
         <v>45778</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -34600,7 +34600,7 @@
         <v>45856</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -34673,7 +34673,7 @@
         <v>46108</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -34746,7 +34746,7 @@
         <v>46108</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -34819,7 +34819,7 @@
         <v>44845</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -34892,7 +34892,7 @@
         <v>46119</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -34965,7 +34965,7 @@
         <v>46119</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -35038,7 +35038,7 @@
         <v>46119</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -35111,7 +35111,7 @@
         <v>44625</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -35184,7 +35184,7 @@
         <v>45874</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -35257,7 +35257,7 @@
         <v>46120</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -35330,7 +35330,7 @@
         <v>46070</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -35403,7 +35403,7 @@
         <v>46070</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -35476,7 +35476,7 @@
         <v>46261</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -35554,7 +35554,7 @@
         <v>46124</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -35627,7 +35627,7 @@
         <v>46124</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -35700,7 +35700,7 @@
         <v>46261</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -35778,7 +35778,7 @@
         <v>46127</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -35851,7 +35851,7 @@
         <v>45758</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -35924,7 +35924,7 @@
         <v>45882</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -35997,7 +35997,7 @@
         <v>45882</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -36070,7 +36070,7 @@
         <v>46262</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -36148,7 +36148,7 @@
         <v>44911</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -36221,7 +36221,7 @@
         <v>46308</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -36294,7 +36294,7 @@
         <v>45714</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -36367,7 +36367,7 @@
         <v>46300</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -36440,7 +36440,7 @@
         <v>46031</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -36513,7 +36513,7 @@
         <v>46135</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -36586,7 +36586,7 @@
         <v>45135</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -36659,7 +36659,7 @@
         <v>45443</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -36732,7 +36732,7 @@
         <v>45355</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -36805,7 +36805,7 @@
         <v>46147</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -36878,7 +36878,7 @@
         <v>46135</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -36951,7 +36951,7 @@
         <v>46266</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -37024,7 +37024,7 @@
         <v>45358</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -37097,7 +37097,7 @@
         <v>45559</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -37170,7 +37170,7 @@
         <v>46135</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -37243,7 +37243,7 @@
         <v>46309</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -37316,7 +37316,7 @@
         <v>46266</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -37389,7 +37389,7 @@
         <v>45749</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -37462,7 +37462,7 @@
         <v>45856</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -37535,7 +37535,7 @@
         <v>45856</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -37608,7 +37608,7 @@
         <v>46267</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -37681,7 +37681,7 @@
         <v>45435</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -37754,7 +37754,7 @@
         <v>46310</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -37832,7 +37832,7 @@
         <v>45691</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -37905,7 +37905,7 @@
         <v>45603</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -37978,7 +37978,7 @@
         <v>44865</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -38051,7 +38051,7 @@
         <v>45915</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -38124,7 +38124,7 @@
         <v>46269</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -38197,7 +38197,7 @@
         <v>46140</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -38275,7 +38275,7 @@
         <v>44881</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -38353,7 +38353,7 @@
         <v>46140</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -38431,7 +38431,7 @@
         <v>45156</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -38504,7 +38504,7 @@
         <v>45671</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -38577,7 +38577,7 @@
         <v>45028</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -38650,7 +38650,7 @@
         <v>45804</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -38723,7 +38723,7 @@
         <v>45691</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -38796,7 +38796,7 @@
         <v>44896</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -38869,7 +38869,7 @@
         <v>46140</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -38942,7 +38942,7 @@
         <v>46140</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -39015,7 +39015,7 @@
         <v>46269</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -39088,7 +39088,7 @@
         <v>45243</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -39161,7 +39161,7 @@
         <v>46273</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -39234,7 +39234,7 @@
         <v>45873</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -39307,7 +39307,7 @@
         <v>44942</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -39380,7 +39380,7 @@
         <v>45733</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -39453,7 +39453,7 @@
         <v>46104</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -39526,7 +39526,7 @@
         <v>45804</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -39599,7 +39599,7 @@
         <v>46316</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -39672,7 +39672,7 @@
         <v>46140</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -39750,7 +39750,7 @@
         <v>45140</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -39823,7 +39823,7 @@
         <v>45832</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -39896,7 +39896,7 @@
         <v>45098</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -39969,7 +39969,7 @@
         <v>45642</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -40042,7 +40042,7 @@
         <v>45932</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -40115,7 +40115,7 @@
         <v>45866</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -40188,7 +40188,7 @@
         <v>46195</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -40266,7 +40266,7 @@
         <v>44899</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -40339,7 +40339,7 @@
         <v>44494</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -40412,7 +40412,7 @@
         <v>45611</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -40485,7 +40485,7 @@
         <v>45751</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -40558,7 +40558,7 @@
         <v>45114</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -40631,7 +40631,7 @@
         <v>45608</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -40704,7 +40704,7 @@
         <v>45754</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -40777,7 +40777,7 @@
         <v>46316</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -40850,7 +40850,7 @@
         <v>45818</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -40923,7 +40923,7 @@
         <v>45541</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -40996,7 +40996,7 @@
         <v>44641</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -41069,7 +41069,7 @@
         <v>46031</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -41142,7 +41142,7 @@
         <v>46311</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -41215,7 +41215,7 @@
         <v>45152</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -41288,7 +41288,7 @@
         <v>45152</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -41361,7 +41361,7 @@
         <v>45058</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -41434,7 +41434,7 @@
         <v>46274</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -41507,7 +41507,7 @@
         <v>44915</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -41580,7 +41580,7 @@
         <v>44915</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -41653,7 +41653,7 @@
         <v>45210</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -41726,7 +41726,7 @@
         <v>46275</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -41799,7 +41799,7 @@
         <v>45722</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -41872,7 +41872,7 @@
         <v>45811</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -41945,7 +41945,7 @@
         <v>44659</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -42018,7 +42018,7 @@
         <v>45623</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -42091,7 +42091,7 @@
         <v>46146</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -42164,7 +42164,7 @@
         <v>46274</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -42237,7 +42237,7 @@
         <v>44986</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -42310,7 +42310,7 @@
         <v>46148</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -42383,7 +42383,7 @@
         <v>46148</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -42456,7 +42456,7 @@
         <v>46148</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -42529,7 +42529,7 @@
         <v>46148</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -42602,7 +42602,7 @@
         <v>46148</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -42675,7 +42675,7 @@
         <v>46148</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -42748,7 +42748,7 @@
         <v>46147</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -42821,7 +42821,7 @@
         <v>44901</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -42894,7 +42894,7 @@
         <v>44614</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -42967,7 +42967,7 @@
         <v>46149</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -43040,7 +43040,7 @@
         <v>45579</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -43113,7 +43113,7 @@
         <v>46153</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -43191,7 +43191,7 @@
         <v>46153</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -43269,7 +43269,7 @@
         <v>46154</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -43342,7 +43342,7 @@
         <v>44746</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -43415,7 +43415,7 @@
         <v>46154</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -43493,7 +43493,7 @@
         <v>45834</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -43566,7 +43566,7 @@
         <v>45021</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -43644,7 +43644,7 @@
         <v>45084</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -43717,7 +43717,7 @@
         <v>44700</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -43795,7 +43795,7 @@
         <v>45904</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -43868,7 +43868,7 @@
         <v>45600</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -43941,7 +43941,7 @@
         <v>45579</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -44014,7 +44014,7 @@
         <v>45434</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -44087,7 +44087,7 @@
         <v>45037</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -44160,7 +44160,7 @@
         <v>45603</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -44233,7 +44233,7 @@
         <v>45609</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -44306,7 +44306,7 @@
         <v>45275</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -44379,7 +44379,7 @@
         <v>45638</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -44452,7 +44452,7 @@
         <v>44970</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -44525,7 +44525,7 @@
         <v>45166</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -44598,7 +44598,7 @@
         <v>44714</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -44671,7 +44671,7 @@
         <v>45617</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -44744,7 +44744,7 @@
         <v>45435</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -44817,7 +44817,7 @@
         <v>44998</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -44890,7 +44890,7 @@
         <v>44523</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -44963,7 +44963,7 @@
         <v>45614</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -45036,7 +45036,7 @@
         <v>45267</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -45109,7 +45109,7 @@
         <v>45646</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -45182,7 +45182,7 @@
         <v>45629</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -45255,7 +45255,7 @@
         <v>45614</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -45328,7 +45328,7 @@
         <v>44665</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -45401,7 +45401,7 @@
         <v>44979</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -45474,7 +45474,7 @@
         <v>45733</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -45547,7 +45547,7 @@
         <v>45184</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -45620,7 +45620,7 @@
         <v>45188</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -45693,7 +45693,7 @@
         <v>45040</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -45766,7 +45766,7 @@
         <v>44839</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -45839,7 +45839,7 @@
         <v>45224</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -45917,7 +45917,7 @@
         <v>45224</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -45990,7 +45990,7 @@
         <v>45737</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -46063,7 +46063,7 @@
         <v>45197</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -46136,7 +46136,7 @@
         <v>45245</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -46214,7 +46214,7 @@
         <v>45173</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -46287,7 +46287,7 @@
         <v>44790</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -46360,7 +46360,7 @@
         <v>44858</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -46433,7 +46433,7 @@
         <v>45533</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -46506,7 +46506,7 @@
         <v>45588</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -46579,7 +46579,7 @@
         <v>45250</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -46652,7 +46652,7 @@
         <v>44966</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -46725,7 +46725,7 @@
         <v>45736</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -46798,7 +46798,7 @@
         <v>45054</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -46871,7 +46871,7 @@
         <v>45036</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -46944,7 +46944,7 @@
         <v>44588</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -47017,7 +47017,7 @@
         <v>44883</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -47090,7 +47090,7 @@
         <v>45090</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -47163,7 +47163,7 @@
         <v>45245</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -47241,7 +47241,7 @@
         <v>45153</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -47314,7 +47314,7 @@
         <v>44881</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -47387,7 +47387,7 @@
         <v>45090</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -47460,7 +47460,7 @@
         <v>45040</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -47533,7 +47533,7 @@
         <v>45089</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -47606,7 +47606,7 @@
         <v>45054</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -47679,7 +47679,7 @@
         <v>45054</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -47752,7 +47752,7 @@
         <v>45751</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -47825,7 +47825,7 @@
         <v>45539</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -47898,7 +47898,7 @@
         <v>45558</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -47971,7 +47971,7 @@
         <v>44966</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -48044,7 +48044,7 @@
         <v>44966</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -48117,7 +48117,7 @@
         <v>44901</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -48190,7 +48190,7 @@
         <v>45336</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -48263,7 +48263,7 @@
         <v>44951</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -48336,7 +48336,7 @@
         <v>45191</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -48409,7 +48409,7 @@
         <v>44537</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -48482,7 +48482,7 @@
         <v>45106</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -48555,7 +48555,7 @@
         <v>45015</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -48628,7 +48628,7 @@
         <v>45015</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -48701,7 +48701,7 @@
         <v>44543</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -48774,7 +48774,7 @@
         <v>45142</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -48847,7 +48847,7 @@
         <v>45119</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -48920,7 +48920,7 @@
         <v>45146</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -48993,7 +48993,7 @@
         <v>45140</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -49066,7 +49066,7 @@
         <v>45467</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -49139,7 +49139,7 @@
         <v>45532</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -49212,7 +49212,7 @@
         <v>45149</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -49290,7 +49290,7 @@
         <v>45477</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -49363,7 +49363,7 @@
         <v>45510</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -49436,7 +49436,7 @@
         <v>44991</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -49509,7 +49509,7 @@
         <v>44546</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -49582,7 +49582,7 @@
         <v>45306</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -49655,7 +49655,7 @@
         <v>45084</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -49728,7 +49728,7 @@
         <v>45525</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -49801,7 +49801,7 @@
         <v>45475</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -49874,7 +49874,7 @@
         <v>45429</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -49947,7 +49947,7 @@
         <v>45654</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -50020,7 +50020,7 @@
         <v>45443</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -50093,7 +50093,7 @@
         <v>44970</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -50166,7 +50166,7 @@
         <v>45616</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -50239,7 +50239,7 @@
         <v>44911</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -50312,7 +50312,7 @@
         <v>45173</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -50385,7 +50385,7 @@
         <v>45541</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -50458,7 +50458,7 @@
         <v>44586</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -50531,7 +50531,7 @@
         <v>45106</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -50604,7 +50604,7 @@
         <v>45142</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -50677,7 +50677,7 @@
         <v>45336</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -50750,7 +50750,7 @@
         <v>45271</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -50823,7 +50823,7 @@
         <v>45204</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -50896,7 +50896,7 @@
         <v>45603</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -50969,7 +50969,7 @@
         <v>45061</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -51042,7 +51042,7 @@
         <v>45614</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -51115,7 +51115,7 @@
         <v>45512</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -51188,7 +51188,7 @@
         <v>45204</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -51261,7 +51261,7 @@
         <v>45054</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -51334,7 +51334,7 @@
         <v>45629</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -51407,7 +51407,7 @@
         <v>44581</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -51480,7 +51480,7 @@
         <v>45623</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -51553,7 +51553,7 @@
         <v>44804</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -51626,7 +51626,7 @@
         <v>44636</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -51699,7 +51699,7 @@
         <v>44629</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -51772,7 +51772,7 @@
         <v>45091</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -51845,7 +51845,7 @@
         <v>45091</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -51918,7 +51918,7 @@
         <v>45091</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -51991,7 +51991,7 @@
         <v>45110</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -52064,7 +52064,7 @@
         <v>45714</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -52137,7 +52137,7 @@
         <v>44998</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -52210,7 +52210,7 @@
         <v>45104</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -52283,7 +52283,7 @@
         <v>44557</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -52356,7 +52356,7 @@
         <v>45176</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -52429,7 +52429,7 @@
         <v>45231</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -52502,7 +52502,7 @@
         <v>45195</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -52575,7 +52575,7 @@
         <v>45111</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -52648,7 +52648,7 @@
         <v>44874</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -52721,7 +52721,7 @@
         <v>45197</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -52794,7 +52794,7 @@
         <v>45616</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -52867,7 +52867,7 @@
         <v>45245</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -52945,7 +52945,7 @@
         <v>45085</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -53018,7 +53018,7 @@
         <v>45253</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -53091,7 +53091,7 @@
         <v>45685</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -53164,7 +53164,7 @@
         <v>45173</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -53237,7 +53237,7 @@
         <v>45173</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -53310,7 +53310,7 @@
         <v>45159</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -53383,7 +53383,7 @@
         <v>44740</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -53456,7 +53456,7 @@
         <v>45175</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -53529,7 +53529,7 @@
         <v>45474</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -53602,7 +53602,7 @@
         <v>45300</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -53675,7 +53675,7 @@
         <v>45267</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -53748,7 +53748,7 @@
         <v>45279</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -53821,7 +53821,7 @@
         <v>45267</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -53894,7 +53894,7 @@
         <v>45440</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -53967,7 +53967,7 @@
         <v>45723</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -54040,7 +54040,7 @@
         <v>45261</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -54113,7 +54113,7 @@
         <v>45265</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -54186,7 +54186,7 @@
         <v>45015</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -54259,7 +54259,7 @@
         <v>44840</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -54332,7 +54332,7 @@
         <v>44872</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -54405,7 +54405,7 @@
         <v>45272</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -54478,7 +54478,7 @@
         <v>45301</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -54551,7 +54551,7 @@
         <v>45089</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -54624,7 +54624,7 @@
         <v>45310</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -54697,7 +54697,7 @@
         <v>45274</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -54770,7 +54770,7 @@
         <v>45293</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -54843,7 +54843,7 @@
         <v>45743</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -54916,7 +54916,7 @@
         <v>45090</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -54989,7 +54989,7 @@
         <v>44798</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -55062,7 +55062,7 @@
         <v>44693</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -55135,7 +55135,7 @@
         <v>45520</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -55208,7 +55208,7 @@
         <v>44896</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -55281,7 +55281,7 @@
         <v>45290</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -55354,7 +55354,7 @@
         <v>45290</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -55427,7 +55427,7 @@
         <v>45733</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -55500,7 +55500,7 @@
         <v>44904</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -55573,7 +55573,7 @@
         <v>45546</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -55646,7 +55646,7 @@
         <v>45296</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -55719,7 +55719,7 @@
         <v>44575</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -55792,7 +55792,7 @@
         <v>44899</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -55865,7 +55865,7 @@
         <v>45680</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -55938,7 +55938,7 @@
         <v>44573</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -56011,7 +56011,7 @@
         <v>45736</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -56084,7 +56084,7 @@
         <v>45338</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -56157,7 +56157,7 @@
         <v>44998</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -56230,7 +56230,7 @@
         <v>44887</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -56303,7 +56303,7 @@
         <v>45525</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -56376,7 +56376,7 @@
         <v>45261</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -56449,7 +56449,7 @@
         <v>44579</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -56527,7 +56527,7 @@
         <v>44893</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -56605,7 +56605,7 @@
         <v>44893</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -56683,7 +56683,7 @@
         <v>44893</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -56761,7 +56761,7 @@
         <v>45731</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -56834,7 +56834,7 @@
         <v>45736</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -56907,7 +56907,7 @@
         <v>46035</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -56985,7 +56985,7 @@
         <v>46163</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>

--- a/Översikt EDA.xlsx
+++ b/Översikt EDA.xlsx
@@ -601,7 +601,7 @@
         <v>45178</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -725,7 +725,7 @@
         <v>45726</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -843,7 +843,7 @@
         <v>44494</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -955,7 +955,7 @@
         <v>45090</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1070,7 +1070,7 @@
         <v>45154</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1180,7 +1180,7 @@
         <v>45306</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1298,7 +1298,7 @@
         <v>44791</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1406,7 +1406,7 @@
         <v>45407</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1514,7 +1514,7 @@
         <v>44740</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1626,7 +1626,7 @@
         <v>45358</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1737,7 +1737,7 @@
         <v>45754</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1848,7 +1848,7 @@
         <v>45293</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1963,7 +1963,7 @@
         <v>44916</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2074,7 +2074,7 @@
         <v>44868</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2180,7 +2180,7 @@
         <v>44865</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2286,7 +2286,7 @@
         <v>44888</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2396,7 +2396,7 @@
         <v>45243</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2502,7 +2502,7 @@
         <v>45310</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2608,7 +2608,7 @@
         <v>45575</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2714,7 +2714,7 @@
         <v>46290</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2820,7 +2820,7 @@
         <v>45856</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2926,7 +2926,7 @@
         <v>44970</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3032,7 +3032,7 @@
         <v>45091</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3142,7 +3142,7 @@
         <v>45426</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3248,7 +3248,7 @@
         <v>45315</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3358,7 +3358,7 @@
         <v>45545</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3464,7 +3464,7 @@
         <v>45243</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3569,7 +3569,7 @@
         <v>45376</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3678,7 +3678,7 @@
         <v>45532</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3783,7 +3783,7 @@
         <v>45432</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3888,7 +3888,7 @@
         <v>45257</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3993,7 +3993,7 @@
         <v>45777</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4107,7 +4107,7 @@
         <v>46092</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4212,7 +4212,7 @@
         <v>46269</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4321,7 +4321,7 @@
         <v>46269</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4431,7 +4431,7 @@
         <v>46316</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4540,7 +4540,7 @@
         <v>45721</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4645,7 +4645,7 @@
         <v>45244</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4750,7 +4750,7 @@
         <v>44579</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4860,7 +4860,7 @@
         <v>44889</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4933,7 +4933,7 @@
         <v>44683</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5006,7 +5006,7 @@
         <v>44810</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5079,7 +5079,7 @@
         <v>44529</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5152,7 +5152,7 @@
         <v>44712</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5225,7 +5225,7 @@
         <v>44852</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5298,7 +5298,7 @@
         <v>44889</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5371,7 +5371,7 @@
         <v>44608</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5449,7 +5449,7 @@
         <v>44582</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5522,7 +5522,7 @@
         <v>44582</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5595,7 +5595,7 @@
         <v>44851</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5668,7 +5668,7 @@
         <v>44538</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5741,7 +5741,7 @@
         <v>44740</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5814,7 +5814,7 @@
         <v>44837</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5887,7 +5887,7 @@
         <v>44816</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5960,7 +5960,7 @@
         <v>44712</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6033,7 +6033,7 @@
         <v>44532</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6106,7 +6106,7 @@
         <v>44874</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6179,7 +6179,7 @@
         <v>44529</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6252,7 +6252,7 @@
         <v>44586</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6325,7 +6325,7 @@
         <v>44722</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6398,7 +6398,7 @@
         <v>44685</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6471,7 +6471,7 @@
         <v>44809</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6544,7 +6544,7 @@
         <v>44858</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6617,7 +6617,7 @@
         <v>44670</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6690,7 +6690,7 @@
         <v>44659</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6763,7 +6763,7 @@
         <v>44740</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6836,7 +6836,7 @@
         <v>44510</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6909,7 +6909,7 @@
         <v>44733</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6982,7 +6982,7 @@
         <v>44853</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7055,7 +7055,7 @@
         <v>44557</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7133,7 +7133,7 @@
         <v>44546</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7206,7 +7206,7 @@
         <v>44817</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7279,7 +7279,7 @@
         <v>44614</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7352,7 +7352,7 @@
         <v>44874</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7425,7 +7425,7 @@
         <v>44874</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7498,7 +7498,7 @@
         <v>44883</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7571,7 +7571,7 @@
         <v>44515</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7649,7 +7649,7 @@
         <v>44799</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7722,7 +7722,7 @@
         <v>44881</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7795,7 +7795,7 @@
         <v>44881</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7868,7 +7868,7 @@
         <v>44588</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7941,7 +7941,7 @@
         <v>44581</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8014,7 +8014,7 @@
         <v>44868</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8087,7 +8087,7 @@
         <v>44705</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8160,7 +8160,7 @@
         <v>44573</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8233,7 +8233,7 @@
         <v>44560</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8311,7 +8311,7 @@
         <v>44614</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8384,7 +8384,7 @@
         <v>44714</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8457,7 +8457,7 @@
         <v>44877</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8530,7 +8530,7 @@
         <v>44852</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8603,7 +8603,7 @@
         <v>44662</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8676,7 +8676,7 @@
         <v>44584</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8749,7 +8749,7 @@
         <v>44643</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8822,7 +8822,7 @@
         <v>44614</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8895,7 +8895,7 @@
         <v>44726</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8968,7 +8968,7 @@
         <v>44818</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9041,7 +9041,7 @@
         <v>45583</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9114,7 +9114,7 @@
         <v>45553</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9187,7 +9187,7 @@
         <v>45161</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9260,7 +9260,7 @@
         <v>44896</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9333,7 +9333,7 @@
         <v>44683</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9406,7 +9406,7 @@
         <v>44851</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9479,7 +9479,7 @@
         <v>45412</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9552,7 +9552,7 @@
         <v>45775</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9625,7 +9625,7 @@
         <v>45041</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9698,7 +9698,7 @@
         <v>45090</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9771,7 +9771,7 @@
         <v>45891</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9849,7 +9849,7 @@
         <v>45883</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9922,7 +9922,7 @@
         <v>44865</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9995,7 +9995,7 @@
         <v>45897</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10068,7 +10068,7 @@
         <v>45582</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10141,7 +10141,7 @@
         <v>44834</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10219,7 +10219,7 @@
         <v>45897</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10297,7 +10297,7 @@
         <v>45897</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10375,7 +10375,7 @@
         <v>45733</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10448,7 +10448,7 @@
         <v>45016</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10526,7 +10526,7 @@
         <v>44777</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10599,7 +10599,7 @@
         <v>45195</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10672,7 +10672,7 @@
         <v>45719</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10745,7 +10745,7 @@
         <v>44908</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10818,7 +10818,7 @@
         <v>45903</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10891,7 +10891,7 @@
         <v>45231</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10964,7 +10964,7 @@
         <v>45903</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11037,7 +11037,7 @@
         <v>45903</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11110,7 +11110,7 @@
         <v>45903</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11183,7 +11183,7 @@
         <v>45281</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11256,7 +11256,7 @@
         <v>45498</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11329,7 +11329,7 @@
         <v>44798</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11402,7 +11402,7 @@
         <v>45910</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11475,7 +11475,7 @@
         <v>45510</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11548,7 +11548,7 @@
         <v>45510</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11621,7 +11621,7 @@
         <v>44917</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11699,7 +11699,7 @@
         <v>44918</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11772,7 +11772,7 @@
         <v>46163</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11845,7 +11845,7 @@
         <v>46163</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11918,7 +11918,7 @@
         <v>46163</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11991,7 +11991,7 @@
         <v>45191</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12064,7 +12064,7 @@
         <v>45128</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12137,7 +12137,7 @@
         <v>44596</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12210,7 +12210,7 @@
         <v>45674</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12283,7 +12283,7 @@
         <v>44602</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12356,7 +12356,7 @@
         <v>46163</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12429,7 +12429,7 @@
         <v>44979</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12502,7 +12502,7 @@
         <v>45918</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12580,7 +12580,7 @@
         <v>45910</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12653,7 +12653,7 @@
         <v>45920</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12726,7 +12726,7 @@
         <v>45694</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12799,7 +12799,7 @@
         <v>44518</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12872,7 +12872,7 @@
         <v>45924</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12945,7 +12945,7 @@
         <v>45176</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13018,7 +13018,7 @@
         <v>45924</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13091,7 +13091,7 @@
         <v>46167</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13164,7 +13164,7 @@
         <v>46167</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13237,7 +13237,7 @@
         <v>45924</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13310,7 +13310,7 @@
         <v>45021</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13383,7 +13383,7 @@
         <v>45071</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13456,7 +13456,7 @@
         <v>45310</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13529,7 +13529,7 @@
         <v>45704</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13602,7 +13602,7 @@
         <v>45929</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13675,7 +13675,7 @@
         <v>45929</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13748,7 +13748,7 @@
         <v>45092</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13821,7 +13821,7 @@
         <v>45092</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13894,7 +13894,7 @@
         <v>45929</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13967,7 +13967,7 @@
         <v>45929</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14040,7 +14040,7 @@
         <v>45763</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14113,7 +14113,7 @@
         <v>45370</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14186,7 +14186,7 @@
         <v>45090</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14259,7 +14259,7 @@
         <v>45090</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14332,7 +14332,7 @@
         <v>45090</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14405,7 +14405,7 @@
         <v>45281</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14478,7 +14478,7 @@
         <v>45281</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14551,7 +14551,7 @@
         <v>45936</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14629,7 +14629,7 @@
         <v>45418</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14702,7 +14702,7 @@
         <v>45888</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14775,7 +14775,7 @@
         <v>45936</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14853,7 +14853,7 @@
         <v>44916</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14926,7 +14926,7 @@
         <v>44977</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14999,7 +14999,7 @@
         <v>45936</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15072,7 +15072,7 @@
         <v>45621</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15145,7 +15145,7 @@
         <v>44937</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15218,7 +15218,7 @@
         <v>45432</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15291,7 +15291,7 @@
         <v>45061</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15364,7 +15364,7 @@
         <v>45162</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15437,7 +15437,7 @@
         <v>45229</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15510,7 +15510,7 @@
         <v>45456</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15583,7 +15583,7 @@
         <v>46176</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15656,7 +15656,7 @@
         <v>45139</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15729,7 +15729,7 @@
         <v>46177</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15802,7 +15802,7 @@
         <v>45554</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15875,7 +15875,7 @@
         <v>44901</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15948,7 +15948,7 @@
         <v>45549</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16021,7 +16021,7 @@
         <v>44799</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16094,7 +16094,7 @@
         <v>44956</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16167,7 +16167,7 @@
         <v>45301</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16245,7 +16245,7 @@
         <v>44894</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16318,7 +16318,7 @@
         <v>44966</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16391,7 +16391,7 @@
         <v>45390</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16464,7 +16464,7 @@
         <v>45756</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16537,7 +16537,7 @@
         <v>45426</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16610,7 +16610,7 @@
         <v>45950</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16688,7 +16688,7 @@
         <v>45090</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16761,7 +16761,7 @@
         <v>46178</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16834,7 +16834,7 @@
         <v>45161</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16907,7 +16907,7 @@
         <v>45520</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16980,7 +16980,7 @@
         <v>44636</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17053,7 +17053,7 @@
         <v>45203</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17126,7 +17126,7 @@
         <v>45629</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17199,7 +17199,7 @@
         <v>45308</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17272,7 +17272,7 @@
         <v>45105</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17345,7 +17345,7 @@
         <v>45727</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17418,7 +17418,7 @@
         <v>45727</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17491,7 +17491,7 @@
         <v>45957</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17564,7 +17564,7 @@
         <v>44776</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17642,7 +17642,7 @@
         <v>45310</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17715,7 +17715,7 @@
         <v>44998</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17788,7 +17788,7 @@
         <v>45692</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17861,7 +17861,7 @@
         <v>45161</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17934,7 +17934,7 @@
         <v>45966</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18007,7 +18007,7 @@
         <v>44865</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18080,7 +18080,7 @@
         <v>45210</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18153,7 +18153,7 @@
         <v>45307</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18226,7 +18226,7 @@
         <v>45968</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18299,7 +18299,7 @@
         <v>45971</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18372,7 +18372,7 @@
         <v>45971</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18450,7 +18450,7 @@
         <v>45971</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18523,7 +18523,7 @@
         <v>46195</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18601,7 +18601,7 @@
         <v>45397</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18674,7 +18674,7 @@
         <v>45971</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18752,7 +18752,7 @@
         <v>45971</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18825,7 +18825,7 @@
         <v>45184</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18898,7 +18898,7 @@
         <v>45184</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18971,7 +18971,7 @@
         <v>45273</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19044,7 +19044,7 @@
         <v>45552</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19122,7 +19122,7 @@
         <v>46197</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19200,7 +19200,7 @@
         <v>45616</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19273,7 +19273,7 @@
         <v>46196</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19346,7 +19346,7 @@
         <v>45392</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19419,7 +19419,7 @@
         <v>45455</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19492,7 +19492,7 @@
         <v>44935</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19565,7 +19565,7 @@
         <v>45636</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19643,7 +19643,7 @@
         <v>46196</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19716,7 +19716,7 @@
         <v>44867</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19789,7 +19789,7 @@
         <v>45975</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19862,7 +19862,7 @@
         <v>46199</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19935,7 +19935,7 @@
         <v>46199</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20008,7 +20008,7 @@
         <v>46199</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20081,7 +20081,7 @@
         <v>46199</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20154,7 +20154,7 @@
         <v>45149</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20232,7 +20232,7 @@
         <v>46199</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20305,7 +20305,7 @@
         <v>46199</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20378,7 +20378,7 @@
         <v>45980</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20451,7 +20451,7 @@
         <v>45680</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20524,7 +20524,7 @@
         <v>45729</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20597,7 +20597,7 @@
         <v>45482</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20670,7 +20670,7 @@
         <v>45981</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20743,7 +20743,7 @@
         <v>45981</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20816,7 +20816,7 @@
         <v>46203</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20889,7 +20889,7 @@
         <v>46203</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20962,7 +20962,7 @@
         <v>45477</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21035,7 +21035,7 @@
         <v>46203</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21108,7 +21108,7 @@
         <v>45756</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21181,7 +21181,7 @@
         <v>45756</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21254,7 +21254,7 @@
         <v>45676</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21327,7 +21327,7 @@
         <v>45981</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21400,7 +21400,7 @@
         <v>45981</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21473,7 +21473,7 @@
         <v>45246</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21546,7 +21546,7 @@
         <v>45152</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21619,7 +21619,7 @@
         <v>44918</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21692,7 +21692,7 @@
         <v>45221</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21770,7 +21770,7 @@
         <v>45221</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21848,7 +21848,7 @@
         <v>45992</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21921,7 +21921,7 @@
         <v>45980</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21994,7 +21994,7 @@
         <v>45226</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22067,7 +22067,7 @@
         <v>45992</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22140,7 +22140,7 @@
         <v>45694</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22213,7 +22213,7 @@
         <v>45245</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22291,7 +22291,7 @@
         <v>45729</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22364,7 +22364,7 @@
         <v>45252</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22437,7 +22437,7 @@
         <v>45684</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22510,7 +22510,7 @@
         <v>45994</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22583,7 +22583,7 @@
         <v>45525</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22656,7 +22656,7 @@
         <v>45992</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22729,7 +22729,7 @@
         <v>45994</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22802,7 +22802,7 @@
         <v>45995</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22875,7 +22875,7 @@
         <v>44956</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -22948,7 +22948,7 @@
         <v>46217</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23021,7 +23021,7 @@
         <v>45995</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23094,7 +23094,7 @@
         <v>45623</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23167,7 +23167,7 @@
         <v>46217</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23240,7 +23240,7 @@
         <v>45692</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23313,7 +23313,7 @@
         <v>46217</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23386,7 +23386,7 @@
         <v>45408</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23459,7 +23459,7 @@
         <v>46000</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23532,7 +23532,7 @@
         <v>45996</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23605,7 +23605,7 @@
         <v>45189</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23678,7 +23678,7 @@
         <v>44537</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23751,7 +23751,7 @@
         <v>45999</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23824,7 +23824,7 @@
         <v>45775</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -23897,7 +23897,7 @@
         <v>45775</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -23970,7 +23970,7 @@
         <v>46002</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24043,7 +24043,7 @@
         <v>45777</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24116,7 +24116,7 @@
         <v>46002</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24189,7 +24189,7 @@
         <v>45783</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24262,7 +24262,7 @@
         <v>45567</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24335,7 +24335,7 @@
         <v>46233</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24408,7 +24408,7 @@
         <v>46006</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24481,7 +24481,7 @@
         <v>46007</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24554,7 +24554,7 @@
         <v>45730</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24627,7 +24627,7 @@
         <v>46009</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24700,7 +24700,7 @@
         <v>46010</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24773,7 +24773,7 @@
         <v>46279</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -24846,7 +24846,7 @@
         <v>46237</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -24919,7 +24919,7 @@
         <v>46010</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -24992,7 +24992,7 @@
         <v>46280</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25065,7 +25065,7 @@
         <v>46013</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25138,7 +25138,7 @@
         <v>46279</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25211,7 +25211,7 @@
         <v>46013</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25284,7 +25284,7 @@
         <v>46013</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25357,7 +25357,7 @@
         <v>46016</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25430,7 +25430,7 @@
         <v>46016</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25503,7 +25503,7 @@
         <v>46238</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25576,7 +25576,7 @@
         <v>46016</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25649,7 +25649,7 @@
         <v>46016</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25722,7 +25722,7 @@
         <v>46016</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -25795,7 +25795,7 @@
         <v>46016</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -25868,7 +25868,7 @@
         <v>45110</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -25941,7 +25941,7 @@
         <v>46021</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26014,7 +26014,7 @@
         <v>46021</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26092,7 +26092,7 @@
         <v>46029</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26165,7 +26165,7 @@
         <v>46029</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26238,7 +26238,7 @@
         <v>46029</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26311,7 +26311,7 @@
         <v>45629</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26384,7 +26384,7 @@
         <v>46029</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26457,7 +26457,7 @@
         <v>46031</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26530,7 +26530,7 @@
         <v>46031</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26603,7 +26603,7 @@
         <v>45792</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26676,7 +26676,7 @@
         <v>46240</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -26749,7 +26749,7 @@
         <v>46035</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -26822,7 +26822,7 @@
         <v>45576</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -26895,7 +26895,7 @@
         <v>46042</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -26968,7 +26968,7 @@
         <v>46041</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27041,7 +27041,7 @@
         <v>46041</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27114,7 +27114,7 @@
         <v>45796</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27187,7 +27187,7 @@
         <v>46052</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27265,7 +27265,7 @@
         <v>44911</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27338,7 +27338,7 @@
         <v>44911</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27411,7 +27411,7 @@
         <v>46199</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27484,7 +27484,7 @@
         <v>46043</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27557,7 +27557,7 @@
         <v>46245</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27630,7 +27630,7 @@
         <v>45975</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -27703,7 +27703,7 @@
         <v>46048</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -27776,7 +27776,7 @@
         <v>46245</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -27849,7 +27849,7 @@
         <v>46147</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -27922,7 +27922,7 @@
         <v>46050</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -27995,7 +27995,7 @@
         <v>46290</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28068,7 +28068,7 @@
         <v>46290</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28141,7 +28141,7 @@
         <v>46050</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28214,7 +28214,7 @@
         <v>46050</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28287,7 +28287,7 @@
         <v>46050</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28360,7 +28360,7 @@
         <v>45803</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28433,7 +28433,7 @@
         <v>45450</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28506,7 +28506,7 @@
         <v>46247</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28579,7 +28579,7 @@
         <v>46055</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -28652,7 +28652,7 @@
         <v>45294</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -28725,7 +28725,7 @@
         <v>46281</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -28798,7 +28798,7 @@
         <v>46289</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -28871,7 +28871,7 @@
         <v>46290</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -28949,7 +28949,7 @@
         <v>45805</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29027,7 +29027,7 @@
         <v>46247</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29100,7 +29100,7 @@
         <v>45502</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29173,7 +29173,7 @@
         <v>46290</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29251,7 +29251,7 @@
         <v>45624</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29324,7 +29324,7 @@
         <v>44966</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29402,7 +29402,7 @@
         <v>45600</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29475,7 +29475,7 @@
         <v>46289</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29548,7 +29548,7 @@
         <v>45378</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -29621,7 +29621,7 @@
         <v>45310</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -29694,7 +29694,7 @@
         <v>46059</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -29767,7 +29767,7 @@
         <v>45726</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -29840,7 +29840,7 @@
         <v>46059</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -29913,7 +29913,7 @@
         <v>45580</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -29986,7 +29986,7 @@
         <v>45628</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30059,7 +30059,7 @@
         <v>46062</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30132,7 +30132,7 @@
         <v>46062</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30205,7 +30205,7 @@
         <v>45742</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30278,7 +30278,7 @@
         <v>45583</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30351,7 +30351,7 @@
         <v>46294</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30424,7 +30424,7 @@
         <v>46064</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30497,7 +30497,7 @@
         <v>45817</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30570,7 +30570,7 @@
         <v>46064</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -30643,7 +30643,7 @@
         <v>46066</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -30716,7 +30716,7 @@
         <v>46069</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -30789,7 +30789,7 @@
         <v>46069</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -30862,7 +30862,7 @@
         <v>45818</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -30935,7 +30935,7 @@
         <v>45590</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31008,7 +31008,7 @@
         <v>45818</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31081,7 +31081,7 @@
         <v>45818</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31154,7 +31154,7 @@
         <v>45278</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31227,7 +31227,7 @@
         <v>45758</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31300,7 +31300,7 @@
         <v>46252</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31373,7 +31373,7 @@
         <v>46083</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31446,7 +31446,7 @@
         <v>46083</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31519,7 +31519,7 @@
         <v>46253</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -31592,7 +31592,7 @@
         <v>46084</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -31665,7 +31665,7 @@
         <v>46085</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -31738,7 +31738,7 @@
         <v>46085</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -31811,7 +31811,7 @@
         <v>46085</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -31884,7 +31884,7 @@
         <v>46297</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -31957,7 +31957,7 @@
         <v>45835</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -32030,7 +32030,7 @@
         <v>45838</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -32103,7 +32103,7 @@
         <v>46090</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32181,7 +32181,7 @@
         <v>45838</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32254,7 +32254,7 @@
         <v>46297</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32327,7 +32327,7 @@
         <v>46092</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -32400,7 +32400,7 @@
         <v>45839</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -32473,7 +32473,7 @@
         <v>46092</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -32546,7 +32546,7 @@
         <v>46092</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -32619,7 +32619,7 @@
         <v>46092</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -32692,7 +32692,7 @@
         <v>46092</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -32765,7 +32765,7 @@
         <v>45839</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -32838,7 +32838,7 @@
         <v>46092</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -32911,7 +32911,7 @@
         <v>45491</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -32984,7 +32984,7 @@
         <v>46099</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -33057,7 +33057,7 @@
         <v>46297</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -33135,7 +33135,7 @@
         <v>46099</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -33208,7 +33208,7 @@
         <v>45841</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -33281,7 +33281,7 @@
         <v>46247</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -33354,7 +33354,7 @@
         <v>45532</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -33427,7 +33427,7 @@
         <v>44943</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -33500,7 +33500,7 @@
         <v>44602</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -33573,7 +33573,7 @@
         <v>46100</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -33651,7 +33651,7 @@
         <v>45544</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -33724,7 +33724,7 @@
         <v>46101</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -33797,7 +33797,7 @@
         <v>45817</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -33870,7 +33870,7 @@
         <v>45253</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -33943,7 +33943,7 @@
         <v>45588</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -34016,7 +34016,7 @@
         <v>45736</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -34089,7 +34089,7 @@
         <v>46104</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -34162,7 +34162,7 @@
         <v>45061</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -34235,7 +34235,7 @@
         <v>45715</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -34308,7 +34308,7 @@
         <v>45176</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -34381,7 +34381,7 @@
         <v>46107</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -34454,7 +34454,7 @@
         <v>45848</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -34527,7 +34527,7 @@
         <v>45778</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -34600,7 +34600,7 @@
         <v>45856</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -34673,7 +34673,7 @@
         <v>46108</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -34746,7 +34746,7 @@
         <v>46108</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -34819,7 +34819,7 @@
         <v>44845</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -34892,7 +34892,7 @@
         <v>46119</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -34965,7 +34965,7 @@
         <v>46119</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -35038,7 +35038,7 @@
         <v>46119</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -35111,7 +35111,7 @@
         <v>44625</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -35184,7 +35184,7 @@
         <v>45874</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -35257,7 +35257,7 @@
         <v>46120</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -35330,7 +35330,7 @@
         <v>46070</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -35403,7 +35403,7 @@
         <v>46070</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -35476,7 +35476,7 @@
         <v>46261</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -35554,7 +35554,7 @@
         <v>46124</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -35627,7 +35627,7 @@
         <v>46124</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -35700,7 +35700,7 @@
         <v>46261</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -35778,7 +35778,7 @@
         <v>46127</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -35851,7 +35851,7 @@
         <v>45758</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -35924,7 +35924,7 @@
         <v>45882</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -35997,7 +35997,7 @@
         <v>45882</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -36070,7 +36070,7 @@
         <v>46262</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -36148,7 +36148,7 @@
         <v>44911</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -36221,7 +36221,7 @@
         <v>46308</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -36294,7 +36294,7 @@
         <v>45714</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -36367,7 +36367,7 @@
         <v>46300</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -36440,7 +36440,7 @@
         <v>46031</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -36513,7 +36513,7 @@
         <v>46135</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -36586,7 +36586,7 @@
         <v>45135</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -36659,7 +36659,7 @@
         <v>45443</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -36732,7 +36732,7 @@
         <v>45355</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -36805,7 +36805,7 @@
         <v>46147</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -36878,7 +36878,7 @@
         <v>46135</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -36951,7 +36951,7 @@
         <v>46266</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -37024,7 +37024,7 @@
         <v>45358</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -37097,7 +37097,7 @@
         <v>45559</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -37170,7 +37170,7 @@
         <v>46135</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -37243,7 +37243,7 @@
         <v>46309</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -37316,7 +37316,7 @@
         <v>46266</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -37389,7 +37389,7 @@
         <v>45749</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -37462,7 +37462,7 @@
         <v>45856</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -37535,7 +37535,7 @@
         <v>45856</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -37608,7 +37608,7 @@
         <v>46267</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -37681,7 +37681,7 @@
         <v>45435</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -37754,7 +37754,7 @@
         <v>46310</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -37832,7 +37832,7 @@
         <v>45691</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -37905,7 +37905,7 @@
         <v>45603</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -37978,7 +37978,7 @@
         <v>44865</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -38051,7 +38051,7 @@
         <v>45915</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -38124,7 +38124,7 @@
         <v>46269</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -38197,7 +38197,7 @@
         <v>46140</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -38275,7 +38275,7 @@
         <v>44881</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -38353,7 +38353,7 @@
         <v>46140</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -38431,7 +38431,7 @@
         <v>45156</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -38504,7 +38504,7 @@
         <v>45671</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -38577,7 +38577,7 @@
         <v>45028</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -38650,7 +38650,7 @@
         <v>45804</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -38723,7 +38723,7 @@
         <v>45691</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -38796,7 +38796,7 @@
         <v>44896</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -38869,7 +38869,7 @@
         <v>46140</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -38942,7 +38942,7 @@
         <v>46140</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -39015,7 +39015,7 @@
         <v>46269</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -39088,7 +39088,7 @@
         <v>45243</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -39161,7 +39161,7 @@
         <v>46273</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -39234,7 +39234,7 @@
         <v>45873</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -39307,7 +39307,7 @@
         <v>44942</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -39380,7 +39380,7 @@
         <v>45733</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -39453,7 +39453,7 @@
         <v>46104</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -39526,7 +39526,7 @@
         <v>45804</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -39599,7 +39599,7 @@
         <v>46316</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -39672,7 +39672,7 @@
         <v>46140</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -39750,7 +39750,7 @@
         <v>45140</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -39823,7 +39823,7 @@
         <v>45832</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -39896,7 +39896,7 @@
         <v>45098</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -39969,7 +39969,7 @@
         <v>45642</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -40042,7 +40042,7 @@
         <v>45932</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -40115,7 +40115,7 @@
         <v>45866</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -40188,7 +40188,7 @@
         <v>46195</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -40266,7 +40266,7 @@
         <v>44899</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -40339,7 +40339,7 @@
         <v>44494</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -40412,7 +40412,7 @@
         <v>45611</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -40485,7 +40485,7 @@
         <v>45751</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -40558,7 +40558,7 @@
         <v>45114</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -40631,7 +40631,7 @@
         <v>45608</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -40704,7 +40704,7 @@
         <v>45754</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -40777,7 +40777,7 @@
         <v>46316</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -40850,7 +40850,7 @@
         <v>45818</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -40923,7 +40923,7 @@
         <v>45541</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -40996,7 +40996,7 @@
         <v>44641</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -41069,7 +41069,7 @@
         <v>46031</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -41142,7 +41142,7 @@
         <v>46311</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -41215,7 +41215,7 @@
         <v>45152</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -41288,7 +41288,7 @@
         <v>45152</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -41361,7 +41361,7 @@
         <v>45058</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -41434,7 +41434,7 @@
         <v>46274</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -41507,7 +41507,7 @@
         <v>44915</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -41580,7 +41580,7 @@
         <v>44915</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -41653,7 +41653,7 @@
         <v>45210</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -41726,7 +41726,7 @@
         <v>46275</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -41799,7 +41799,7 @@
         <v>45722</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -41872,7 +41872,7 @@
         <v>45811</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -41945,7 +41945,7 @@
         <v>44659</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -42018,7 +42018,7 @@
         <v>45623</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -42091,7 +42091,7 @@
         <v>46146</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -42164,7 +42164,7 @@
         <v>46274</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -42237,7 +42237,7 @@
         <v>44986</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -42310,7 +42310,7 @@
         <v>46148</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -42383,7 +42383,7 @@
         <v>46148</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -42456,7 +42456,7 @@
         <v>46148</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -42529,7 +42529,7 @@
         <v>46148</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -42602,7 +42602,7 @@
         <v>46148</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -42675,7 +42675,7 @@
         <v>46148</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -42748,7 +42748,7 @@
         <v>46147</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -42821,7 +42821,7 @@
         <v>44901</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -42894,7 +42894,7 @@
         <v>44614</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -42967,7 +42967,7 @@
         <v>46149</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -43040,7 +43040,7 @@
         <v>45579</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -43113,7 +43113,7 @@
         <v>46153</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -43191,7 +43191,7 @@
         <v>46153</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -43269,7 +43269,7 @@
         <v>46154</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -43342,7 +43342,7 @@
         <v>44746</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -43415,7 +43415,7 @@
         <v>46154</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -43493,7 +43493,7 @@
         <v>45834</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -43566,7 +43566,7 @@
         <v>45021</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -43644,7 +43644,7 @@
         <v>45084</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -43717,7 +43717,7 @@
         <v>44700</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -43795,7 +43795,7 @@
         <v>45904</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -43868,7 +43868,7 @@
         <v>45600</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -43941,7 +43941,7 @@
         <v>45579</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -44014,7 +44014,7 @@
         <v>45434</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -44087,7 +44087,7 @@
         <v>45037</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -44160,7 +44160,7 @@
         <v>45603</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -44233,7 +44233,7 @@
         <v>45609</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -44306,7 +44306,7 @@
         <v>45275</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -44379,7 +44379,7 @@
         <v>45638</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -44452,7 +44452,7 @@
         <v>44970</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -44525,7 +44525,7 @@
         <v>45166</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -44598,7 +44598,7 @@
         <v>44714</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -44671,7 +44671,7 @@
         <v>45617</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -44744,7 +44744,7 @@
         <v>45435</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -44817,7 +44817,7 @@
         <v>44998</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -44890,7 +44890,7 @@
         <v>44523</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -44963,7 +44963,7 @@
         <v>45614</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -45036,7 +45036,7 @@
         <v>45267</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -45109,7 +45109,7 @@
         <v>45646</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -45182,7 +45182,7 @@
         <v>45629</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -45255,7 +45255,7 @@
         <v>45614</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -45328,7 +45328,7 @@
         <v>44665</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -45401,7 +45401,7 @@
         <v>44979</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -45474,7 +45474,7 @@
         <v>45733</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -45547,7 +45547,7 @@
         <v>45184</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -45620,7 +45620,7 @@
         <v>45188</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -45693,7 +45693,7 @@
         <v>45040</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -45766,7 +45766,7 @@
         <v>44839</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -45839,7 +45839,7 @@
         <v>45224</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -45917,7 +45917,7 @@
         <v>45224</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -45990,7 +45990,7 @@
         <v>45737</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -46063,7 +46063,7 @@
         <v>45197</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -46136,7 +46136,7 @@
         <v>45245</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -46214,7 +46214,7 @@
         <v>45173</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -46287,7 +46287,7 @@
         <v>44790</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -46360,7 +46360,7 @@
         <v>44858</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -46433,7 +46433,7 @@
         <v>45533</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -46506,7 +46506,7 @@
         <v>45588</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -46579,7 +46579,7 @@
         <v>45250</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -46652,7 +46652,7 @@
         <v>44966</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -46725,7 +46725,7 @@
         <v>45736</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -46798,7 +46798,7 @@
         <v>45054</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -46871,7 +46871,7 @@
         <v>45036</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -46944,7 +46944,7 @@
         <v>44588</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -47017,7 +47017,7 @@
         <v>44883</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -47090,7 +47090,7 @@
         <v>45090</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -47163,7 +47163,7 @@
         <v>45245</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -47241,7 +47241,7 @@
         <v>45153</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -47314,7 +47314,7 @@
         <v>44881</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -47387,7 +47387,7 @@
         <v>45090</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -47460,7 +47460,7 @@
         <v>45040</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -47533,7 +47533,7 @@
         <v>45089</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -47606,7 +47606,7 @@
         <v>45054</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -47679,7 +47679,7 @@
         <v>45054</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -47752,7 +47752,7 @@
         <v>45751</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -47825,7 +47825,7 @@
         <v>45539</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -47898,7 +47898,7 @@
         <v>45558</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -47971,7 +47971,7 @@
         <v>44966</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -48044,7 +48044,7 @@
         <v>44966</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -48117,7 +48117,7 @@
         <v>44901</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -48190,7 +48190,7 @@
         <v>45336</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -48263,7 +48263,7 @@
         <v>44951</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -48336,7 +48336,7 @@
         <v>45191</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -48409,7 +48409,7 @@
         <v>44537</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -48482,7 +48482,7 @@
         <v>45106</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -48555,7 +48555,7 @@
         <v>45015</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -48628,7 +48628,7 @@
         <v>45015</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -48701,7 +48701,7 @@
         <v>44543</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -48774,7 +48774,7 @@
         <v>45142</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -48847,7 +48847,7 @@
         <v>45119</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -48920,7 +48920,7 @@
         <v>45146</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -48993,7 +48993,7 @@
         <v>45140</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -49066,7 +49066,7 @@
         <v>45467</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -49139,7 +49139,7 @@
         <v>45532</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -49212,7 +49212,7 @@
         <v>45149</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -49290,7 +49290,7 @@
         <v>45477</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -49363,7 +49363,7 @@
         <v>45510</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -49436,7 +49436,7 @@
         <v>44991</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -49509,7 +49509,7 @@
         <v>44546</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -49582,7 +49582,7 @@
         <v>45306</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -49655,7 +49655,7 @@
         <v>45084</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -49728,7 +49728,7 @@
         <v>45525</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -49801,7 +49801,7 @@
         <v>45475</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -49874,7 +49874,7 @@
         <v>45429</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -49947,7 +49947,7 @@
         <v>45654</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -50020,7 +50020,7 @@
         <v>45443</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -50093,7 +50093,7 @@
         <v>44970</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -50166,7 +50166,7 @@
         <v>45616</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -50239,7 +50239,7 @@
         <v>44911</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -50312,7 +50312,7 @@
         <v>45173</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -50385,7 +50385,7 @@
         <v>45541</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -50458,7 +50458,7 @@
         <v>44586</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -50531,7 +50531,7 @@
         <v>45106</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -50604,7 +50604,7 @@
         <v>45142</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -50677,7 +50677,7 @@
         <v>45336</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -50750,7 +50750,7 @@
         <v>45271</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -50823,7 +50823,7 @@
         <v>45204</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -50896,7 +50896,7 @@
         <v>45603</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -50969,7 +50969,7 @@
         <v>45061</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -51042,7 +51042,7 @@
         <v>45614</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -51115,7 +51115,7 @@
         <v>45512</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -51188,7 +51188,7 @@
         <v>45204</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -51261,7 +51261,7 @@
         <v>45054</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -51334,7 +51334,7 @@
         <v>45629</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -51407,7 +51407,7 @@
         <v>44581</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -51480,7 +51480,7 @@
         <v>45623</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -51553,7 +51553,7 @@
         <v>44804</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -51626,7 +51626,7 @@
         <v>44636</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -51699,7 +51699,7 @@
         <v>44629</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -51772,7 +51772,7 @@
         <v>45091</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -51845,7 +51845,7 @@
         <v>45091</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -51918,7 +51918,7 @@
         <v>45091</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -51991,7 +51991,7 @@
         <v>45110</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -52064,7 +52064,7 @@
         <v>45714</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -52137,7 +52137,7 @@
         <v>44998</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -52210,7 +52210,7 @@
         <v>45104</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -52283,7 +52283,7 @@
         <v>44557</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -52356,7 +52356,7 @@
         <v>45176</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -52429,7 +52429,7 @@
         <v>45231</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -52502,7 +52502,7 @@
         <v>45195</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -52575,7 +52575,7 @@
         <v>45111</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -52648,7 +52648,7 @@
         <v>44874</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -52721,7 +52721,7 @@
         <v>45197</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -52794,7 +52794,7 @@
         <v>45616</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -52867,7 +52867,7 @@
         <v>45245</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -52945,7 +52945,7 @@
         <v>45085</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -53018,7 +53018,7 @@
         <v>45253</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -53091,7 +53091,7 @@
         <v>45685</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -53164,7 +53164,7 @@
         <v>45173</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -53237,7 +53237,7 @@
         <v>45173</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -53310,7 +53310,7 @@
         <v>45159</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -53383,7 +53383,7 @@
         <v>44740</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -53456,7 +53456,7 @@
         <v>45175</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -53529,7 +53529,7 @@
         <v>45474</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -53602,7 +53602,7 @@
         <v>45300</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -53675,7 +53675,7 @@
         <v>45267</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -53748,7 +53748,7 @@
         <v>45279</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -53821,7 +53821,7 @@
         <v>45267</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -53894,7 +53894,7 @@
         <v>45440</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -53967,7 +53967,7 @@
         <v>45723</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -54040,7 +54040,7 @@
         <v>45261</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -54113,7 +54113,7 @@
         <v>45265</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -54186,7 +54186,7 @@
         <v>45015</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -54259,7 +54259,7 @@
         <v>44840</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -54332,7 +54332,7 @@
         <v>44872</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -54405,7 +54405,7 @@
         <v>45272</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -54478,7 +54478,7 @@
         <v>45301</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -54551,7 +54551,7 @@
         <v>45089</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -54624,7 +54624,7 @@
         <v>45310</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -54697,7 +54697,7 @@
         <v>45274</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -54770,7 +54770,7 @@
         <v>45293</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -54843,7 +54843,7 @@
         <v>45743</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -54916,7 +54916,7 @@
         <v>45090</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -54989,7 +54989,7 @@
         <v>44798</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -55062,7 +55062,7 @@
         <v>44693</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -55135,7 +55135,7 @@
         <v>45520</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -55208,7 +55208,7 @@
         <v>44896</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -55281,7 +55281,7 @@
         <v>45290</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -55354,7 +55354,7 @@
         <v>45290</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -55427,7 +55427,7 @@
         <v>45733</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -55500,7 +55500,7 @@
         <v>44904</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -55573,7 +55573,7 @@
         <v>45546</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -55646,7 +55646,7 @@
         <v>45296</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -55719,7 +55719,7 @@
         <v>44575</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -55792,7 +55792,7 @@
         <v>44899</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -55865,7 +55865,7 @@
         <v>45680</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -55938,7 +55938,7 @@
         <v>44573</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -56011,7 +56011,7 @@
         <v>45736</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -56084,7 +56084,7 @@
         <v>45338</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -56157,7 +56157,7 @@
         <v>44998</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -56230,7 +56230,7 @@
         <v>44887</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -56303,7 +56303,7 @@
         <v>45525</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -56376,7 +56376,7 @@
         <v>45261</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -56449,7 +56449,7 @@
         <v>44579</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -56527,7 +56527,7 @@
         <v>44893</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -56605,7 +56605,7 @@
         <v>44893</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -56683,7 +56683,7 @@
         <v>44893</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -56761,7 +56761,7 @@
         <v>45731</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -56834,7 +56834,7 @@
         <v>45736</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -56907,7 +56907,7 @@
         <v>46035</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -56985,7 +56985,7 @@
         <v>46163</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
